--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4006" uniqueCount="2172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="2191">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -2809,6 +2809,9 @@
     <t>Thunder Punch He-Man (Deluxe)</t>
   </si>
   <si>
+    <t>Clawful (200x - Cartoon Collection)</t>
+  </si>
+  <si>
     <t>Multi-Bot (Deluxe)</t>
   </si>
   <si>
@@ -2827,6 +2830,9 @@
     <t>$39.97</t>
   </si>
   <si>
+    <t>$26.49</t>
+  </si>
+  <si>
     <t>$32.39</t>
   </si>
   <si>
@@ -2929,6 +2935,9 @@
     <t>194735104178</t>
   </si>
   <si>
+    <t>194735333417</t>
+  </si>
+  <si>
     <t>194735346578</t>
   </si>
   <si>
@@ -2980,6 +2989,9 @@
     <t>/app/data/MOTU/images/thunder-punch-he-man-deluxe-5295.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/clawful-200x-cartoon-collection-13003.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/multi-bot-deluxe-12232.jpg</t>
   </si>
   <si>
@@ -3031,6 +3043,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/thunder-punch-he-man-deluxe-5295.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/clawful-200x-cartoon-collection-13003.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/multi-bot-deluxe-12232.jpg</t>
   </si>
   <si>
@@ -3082,6 +3097,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-deluxe/thunder-punch-he-man-deluxe-5295.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-deluxe/clawful-200x-cartoon-collection-13003.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-deluxe/multi-bot-deluxe-12232.php</t>
   </si>
   <si>
@@ -3133,6 +3151,9 @@
     <t>5295</t>
   </si>
   <si>
+    <t>13003</t>
+  </si>
+  <si>
     <t>12232</t>
   </si>
   <si>
@@ -5626,6 +5647,12 @@
     <t>Tygra</t>
   </si>
   <si>
+    <t>Lion-O (Gold Armor)</t>
+  </si>
+  <si>
+    <t>Panthor (Version 2)</t>
+  </si>
+  <si>
     <t>Panthor Man</t>
   </si>
   <si>
@@ -5665,6 +5692,12 @@
     <t>194735307579</t>
   </si>
   <si>
+    <t>194735377749</t>
+  </si>
+  <si>
+    <t>194735377732</t>
+  </si>
+  <si>
     <t>0194735377725</t>
   </si>
   <si>
@@ -5689,6 +5722,12 @@
     <t>/app/data/MOTU/images/tygra-11288.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/lion-o-gold-armor-13004.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/panthor-version-2-13005.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/panthor-man-12460.jpg</t>
   </si>
   <si>
@@ -5713,6 +5752,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/tygra-11288.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/lion-o-gold-armor-13004.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-version-2-13005.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-man-12460.jpg</t>
   </si>
   <si>
@@ -5737,6 +5782,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/thundercats-crossover/tygra-11288.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/thundercats-crossover/lion-o-gold-armor-13004.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/thundercats-crossover/panthor-version-2-13005.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/thundercats-crossover/panthor-man-12460.php</t>
   </si>
   <si>
@@ -5759,6 +5810,12 @@
   </si>
   <si>
     <t>11288</t>
+  </si>
+  <si>
+    <t>13004</t>
+  </si>
+  <si>
+    <t>13005</t>
   </si>
   <si>
     <t>12460</t>
@@ -13636,7 +13693,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2149</v>
+        <v>2168</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13713,13 +13770,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2150</v>
+        <v>2169</v>
       </c>
       <c r="D3" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E3" t="s">
-        <v>2153</v>
+        <v>2172</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -13728,10 +13785,10 @@
         <v>0.51</v>
       </c>
       <c r="H3" t="s">
-        <v>2155</v>
+        <v>2174</v>
       </c>
       <c r="I3" t="s">
-        <v>2157</v>
+        <v>2176</v>
       </c>
       <c r="J3">
         <v>39.95</v>
@@ -13740,13 +13797,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>2160</v>
+        <v>2179</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2163</v>
+        <v>2182</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2166</v>
+        <v>2185</v>
       </c>
       <c r="O3">
         <v>20.51</v>
@@ -13755,7 +13812,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>2169</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -13763,13 +13820,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2151</v>
+        <v>2170</v>
       </c>
       <c r="D4" t="s">
         <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>2154</v>
+        <v>2173</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -13778,10 +13835,10 @@
         <v>0.6</v>
       </c>
       <c r="H4" t="s">
-        <v>2156</v>
+        <v>2175</v>
       </c>
       <c r="I4" t="s">
-        <v>2158</v>
+        <v>2177</v>
       </c>
       <c r="J4">
         <v>59.95</v>
@@ -13790,13 +13847,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>2161</v>
+        <v>2180</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2164</v>
+        <v>2183</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2167</v>
+        <v>2186</v>
       </c>
       <c r="O4">
         <v>36.25</v>
@@ -13805,7 +13862,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>2170</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -13813,13 +13870,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2152</v>
+        <v>2171</v>
       </c>
       <c r="D5" t="s">
         <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>2154</v>
+        <v>2173</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -13828,7 +13885,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="s">
-        <v>2159</v>
+        <v>2178</v>
       </c>
       <c r="J5">
         <v>59.95</v>
@@ -13837,13 +13894,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>2162</v>
+        <v>2181</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2165</v>
+        <v>2184</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2168</v>
+        <v>2187</v>
       </c>
       <c r="O5">
         <v>138.16</v>
@@ -13852,7 +13909,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>2171</v>
+        <v>2190</v>
       </c>
     </row>
   </sheetData>
@@ -13886,7 +13943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -13983,10 +14040,10 @@
         <v>0.77</v>
       </c>
       <c r="H3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="I3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -13995,13 +14052,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="O3">
         <v>15.46</v>
@@ -14010,7 +14067,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -14021,13 +14078,13 @@
         <v>913</v>
       </c>
       <c r="C4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D4" t="s">
         <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F4">
         <v>1146</v>
@@ -14036,10 +14093,10 @@
         <v>1.29</v>
       </c>
       <c r="H4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="I4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="J4">
         <v>16.99</v>
@@ -14048,13 +14105,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="O4">
         <v>21.9</v>
@@ -14063,7 +14120,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -14086,10 +14143,10 @@
         <v>0.54</v>
       </c>
       <c r="H5" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="I5" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -14098,13 +14155,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="O5">
         <v>10.87</v>
@@ -14113,7 +14170,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -14136,10 +14193,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="I6" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -14148,13 +14205,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="O6">
         <v>16.28</v>
@@ -14163,7 +14220,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -14186,10 +14243,10 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="I7" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -14198,13 +14255,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -14213,7 +14270,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -14236,10 +14293,10 @@
         <v>0.65</v>
       </c>
       <c r="H8" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="I8" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -14248,13 +14305,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="O8">
         <v>13.03</v>
@@ -14263,7 +14320,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -14286,10 +14343,10 @@
         <v>0.76</v>
       </c>
       <c r="H9" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="I9" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -14298,13 +14355,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="O9">
         <v>15.13</v>
@@ -14313,7 +14370,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -14336,10 +14393,10 @@
         <v>0.21</v>
       </c>
       <c r="H10" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="I10" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="J10">
         <v>23.99</v>
@@ -14348,13 +14405,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -14363,7 +14420,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -14386,10 +14443,10 @@
         <v>0.65</v>
       </c>
       <c r="H11" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="I11" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -14398,13 +14455,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="O11">
         <v>13</v>
@@ -14413,7 +14470,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -14436,10 +14493,10 @@
         <v>0.64</v>
       </c>
       <c r="H12" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="I12" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -14448,13 +14505,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="O12">
         <v>12.7</v>
@@ -14463,7 +14520,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -14486,10 +14543,10 @@
         <v>0.4</v>
       </c>
       <c r="H13" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="I13" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="J13">
         <v>23.99</v>
@@ -14498,13 +14555,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="O13">
         <v>9.48</v>
@@ -14513,7 +14570,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -14536,10 +14593,10 @@
         <v>0.53</v>
       </c>
       <c r="H14" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="I14" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="J14">
         <v>23.99</v>
@@ -14548,13 +14605,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="O14">
         <v>12.73</v>
@@ -14563,7 +14620,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -14577,7 +14634,7 @@
         <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F15">
         <v>1001</v>
@@ -14586,10 +14643,10 @@
         <v>2.97</v>
       </c>
       <c r="H15" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="I15" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="J15">
         <v>24.99</v>
@@ -14598,13 +14655,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="O15">
         <v>74.29000000000001</v>
@@ -14613,7 +14670,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -14630,7 +14687,7 @@
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F16">
         <v>1045</v>
@@ -14639,10 +14696,10 @@
         <v>0.68</v>
       </c>
       <c r="H16" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="I16" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="J16">
         <v>39.97</v>
@@ -14651,13 +14708,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="O16">
         <v>27.03</v>
@@ -14666,7 +14723,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -14689,10 +14746,10 @@
         <v>0.53</v>
       </c>
       <c r="H17" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="I17" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="J17">
         <v>23.99</v>
@@ -14701,13 +14758,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="O17">
         <v>12.66</v>
@@ -14716,7 +14773,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -14730,7 +14787,7 @@
         <v>175</v>
       </c>
       <c r="E18" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F18">
         <v>793</v>
@@ -14739,10 +14796,10 @@
         <v>2.6</v>
       </c>
       <c r="H18" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="I18" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="J18">
         <v>24.99</v>
@@ -14751,13 +14808,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="O18">
         <v>64.98999999999999</v>
@@ -14766,67 +14823,114 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>928</v>
       </c>
-      <c r="C19" t="s">
-        <v>930</v>
-      </c>
       <c r="D19" t="s">
         <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>970</v>
+      </c>
+      <c r="J19">
+        <v>26.49</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L19" t="s">
+        <v>988</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>929</v>
+      </c>
+      <c r="C20" t="s">
+        <v>931</v>
+      </c>
+      <c r="D20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E20" t="s">
+        <v>936</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>1.76</v>
       </c>
-      <c r="H19" t="s">
-        <v>951</v>
-      </c>
-      <c r="I19" t="s">
-        <v>968</v>
-      </c>
-      <c r="J19">
+      <c r="H20" t="s">
+        <v>953</v>
+      </c>
+      <c r="I20" t="s">
+        <v>971</v>
+      </c>
+      <c r="J20">
         <v>32.39</v>
       </c>
-      <c r="K19" t="s">
-        <v>425</v>
-      </c>
-      <c r="L19" t="s">
-        <v>985</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="O19">
+      <c r="K20" t="s">
+        <v>425</v>
+      </c>
+      <c r="L20" t="s">
+        <v>989</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O20">
         <v>56.95</v>
       </c>
-      <c r="P19" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>1036</v>
+      <c r="P20" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A19">
+  <conditionalFormatting sqref="A3:A20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -14835,7 +14939,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A20">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14872,8 +14976,11 @@
     <hyperlink ref="N17" r:id="rId30"/>
     <hyperlink ref="M18" r:id="rId31"/>
     <hyperlink ref="N18" r:id="rId32"/>
-    <hyperlink ref="M19" r:id="rId33"/>
-    <hyperlink ref="N19" r:id="rId34"/>
+    <hyperlink ref="K19" r:id="rId33"/>
+    <hyperlink ref="M19" r:id="rId34"/>
+    <hyperlink ref="N19" r:id="rId35"/>
+    <hyperlink ref="M20" r:id="rId36"/>
+    <hyperlink ref="N20" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14886,7 +14993,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14963,16 +15070,16 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="C3" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="D3" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E3" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -14981,10 +15088,10 @@
         <v>9.84</v>
       </c>
       <c r="H3" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="I3" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="J3">
         <v>39.99</v>
@@ -14993,13 +15100,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="O3">
         <v>393.33</v>
@@ -15008,7 +15115,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15016,16 +15123,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="C4" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="D4" t="s">
         <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15034,7 +15141,7 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="J4">
         <v>269.99</v>
@@ -15043,13 +15150,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="O4">
         <v>323.96</v>
@@ -15058,7 +15165,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -15066,16 +15173,16 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="D5" t="s">
         <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -15084,10 +15191,10 @@
         <v>2.75</v>
       </c>
       <c r="H5" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="I5" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="J5">
         <v>39.99</v>
@@ -15096,13 +15203,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="O5">
         <v>110</v>
@@ -15111,7 +15218,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -15119,16 +15226,16 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="C6" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="D6" t="s">
         <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -15137,7 +15244,7 @@
         <v>5.83</v>
       </c>
       <c r="I6" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -15146,13 +15253,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="O6">
         <v>350</v>
@@ -15161,7 +15268,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -15169,16 +15276,16 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="C7" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="D7" t="s">
         <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -15187,7 +15294,7 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -15196,13 +15303,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="O7">
         <v>216.32</v>
@@ -15211,7 +15318,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -15219,16 +15326,16 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="C8" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D8" t="s">
         <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F8">
         <v>1537</v>
@@ -15237,10 +15344,10 @@
         <v>0.48</v>
       </c>
       <c r="H8" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="I8" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="J8">
         <v>29.99</v>
@@ -15249,13 +15356,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="O8">
         <v>14.33</v>
@@ -15264,7 +15371,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -15272,16 +15379,16 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="C9" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="D9" t="s">
         <v>173</v>
       </c>
       <c r="E9" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -15296,13 +15403,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
       <c r="O9">
         <v>109.99</v>
@@ -15311,7 +15418,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -15319,16 +15426,16 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="C10" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D10" t="s">
         <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -15337,7 +15444,7 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -15346,13 +15453,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="O10">
         <v>260</v>
@@ -15361,7 +15468,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -15369,16 +15476,16 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="C11" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D11" t="s">
         <v>173</v>
       </c>
       <c r="E11" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -15393,13 +15500,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="O11">
         <v>299.95</v>
@@ -15408,7 +15515,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -15416,16 +15523,16 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="C12" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -15440,13 +15547,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="O12">
         <v>126.66</v>
@@ -15455,7 +15562,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -15463,16 +15570,16 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="C13" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D13" t="s">
         <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -15481,7 +15588,7 @@
         <v>4.33</v>
       </c>
       <c r="I13" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -15490,13 +15597,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="O13">
         <v>216.67</v>
@@ -15505,7 +15612,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -15513,16 +15620,16 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="C14" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D14" t="s">
         <v>173</v>
       </c>
       <c r="E14" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -15531,7 +15638,7 @@
         <v>1.72</v>
       </c>
       <c r="I14" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -15540,13 +15647,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
       <c r="O14">
         <v>51.65</v>
@@ -15555,7 +15662,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1400</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -15563,16 +15670,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="C15" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D15" t="s">
         <v>173</v>
       </c>
       <c r="E15" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="F15">
         <v>503</v>
@@ -15581,7 +15688,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="J15">
         <v>17</v>
@@ -15590,13 +15697,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="O15">
         <v>95.16</v>
@@ -15605,7 +15712,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -15613,7 +15720,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="C16" t="s">
         <v>164</v>
@@ -15622,7 +15729,7 @@
         <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="F16">
         <v>606</v>
@@ -15631,10 +15738,10 @@
         <v>2.86</v>
       </c>
       <c r="H16" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="I16" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -15643,13 +15750,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="O16">
         <v>85.70999999999999</v>
@@ -15658,7 +15765,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -15666,7 +15773,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="C17" t="s">
         <v>164</v>
@@ -15684,10 +15791,10 @@
         <v>2.33</v>
       </c>
       <c r="H17" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I17" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="J17">
         <v>18</v>
@@ -15696,13 +15803,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="O17">
         <v>42</v>
@@ -15711,7 +15818,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -15719,7 +15826,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="C18" t="s">
         <v>164</v>
@@ -15728,7 +15835,7 @@
         <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -15737,10 +15844,10 @@
         <v>0.53</v>
       </c>
       <c r="H18" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="I18" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J18">
         <v>150</v>
@@ -15749,13 +15856,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="O18">
         <v>79.75</v>
@@ -15764,7 +15871,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -15772,7 +15879,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="C19" t="s">
         <v>164</v>
@@ -15781,7 +15888,7 @@
         <v>174</v>
       </c>
       <c r="E19" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="F19">
         <v>536</v>
@@ -15790,7 +15897,7 @@
         <v>4.54</v>
       </c>
       <c r="I19" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="J19">
         <v>17</v>
@@ -15799,13 +15906,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="O19">
         <v>77.23999999999999</v>
@@ -15814,7 +15921,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -15822,7 +15929,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="C20" t="s">
         <v>164</v>
@@ -15840,10 +15947,10 @@
         <v>1.34</v>
       </c>
       <c r="H20" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="I20" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="J20">
         <v>18</v>
@@ -15852,13 +15959,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="O20">
         <v>24.09</v>
@@ -15867,7 +15974,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -15875,16 +15982,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="C21" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D21" t="s">
         <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="F21">
         <v>671</v>
@@ -15893,7 +16000,7 @@
         <v>0.4</v>
       </c>
       <c r="I21" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="J21">
         <v>49.99</v>
@@ -15902,13 +16009,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="O21">
         <v>19.99</v>
@@ -15917,7 +16024,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -15925,7 +16032,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="C22" t="s">
         <v>164</v>
@@ -15934,7 +16041,7 @@
         <v>174</v>
       </c>
       <c r="E22" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="F22">
         <v>911</v>
@@ -15943,10 +16050,10 @@
         <v>1.93</v>
       </c>
       <c r="H22" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="I22" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="J22">
         <v>17</v>
@@ -15955,13 +16062,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="O22">
         <v>32.76</v>
@@ -15970,7 +16077,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1408</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -15978,13 +16085,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="D23" t="s">
         <v>175</v>
       </c>
       <c r="E23" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="F23">
         <v>524</v>
@@ -15993,10 +16100,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="I23" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="J23">
         <v>64.98999999999999</v>
@@ -16005,13 +16112,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="O23">
         <v>129.79</v>
@@ -16020,7 +16127,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1409</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -16028,7 +16135,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="C24" t="s">
         <v>164</v>
@@ -16046,10 +16153,10 @@
         <v>1.91</v>
       </c>
       <c r="H24" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="I24" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -16058,13 +16165,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="O24">
         <v>38.24</v>
@@ -16073,7 +16180,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -16081,7 +16188,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="C25" t="s">
         <v>164</v>
@@ -16099,10 +16206,10 @@
         <v>1.97</v>
       </c>
       <c r="H25" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="I25" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="J25">
         <v>17.99</v>
@@ -16111,13 +16218,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="O25">
         <v>35.47</v>
@@ -16126,7 +16233,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>1411</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -16134,7 +16241,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="C26" t="s">
         <v>164</v>
@@ -16152,10 +16259,10 @@
         <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="I26" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="J26">
         <v>17.99</v>
@@ -16164,13 +16271,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="O26">
         <v>33.25</v>
@@ -16179,7 +16286,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>1412</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -16187,7 +16294,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="C27" t="s">
         <v>164</v>
@@ -16196,7 +16303,7 @@
         <v>175</v>
       </c>
       <c r="E27" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="F27">
         <v>728</v>
@@ -16205,10 +16312,10 @@
         <v>1.2</v>
       </c>
       <c r="H27" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="I27" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="J27">
         <v>35</v>
@@ -16217,13 +16324,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="O27">
         <v>41.94</v>
@@ -16232,7 +16339,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -16240,10 +16347,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="C28" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D28" t="s">
         <v>175</v>
@@ -16258,10 +16365,10 @@
         <v>2.29</v>
       </c>
       <c r="H28" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="I28" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="J28">
         <v>17.99</v>
@@ -16270,13 +16377,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="O28">
         <v>41.11</v>
@@ -16285,7 +16392,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -16293,16 +16400,16 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="C29" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D29" t="s">
         <v>175</v>
       </c>
       <c r="E29" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="F29">
         <v>508</v>
@@ -16311,10 +16418,10 @@
         <v>0.52</v>
       </c>
       <c r="H29" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="I29" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="J29">
         <v>49.99</v>
@@ -16323,13 +16430,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="O29">
         <v>26.14</v>
@@ -16338,7 +16445,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>1415</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -16346,13 +16453,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="D30" t="s">
         <v>175</v>
       </c>
       <c r="E30" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="F30">
         <v>759</v>
@@ -16361,10 +16468,10 @@
         <v>1.88</v>
       </c>
       <c r="H30" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="I30" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="J30">
         <v>31.99</v>
@@ -16373,13 +16480,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="O30">
         <v>60</v>
@@ -16388,7 +16495,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -16396,7 +16503,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="C31" t="s">
         <v>163</v>
@@ -16405,7 +16512,7 @@
         <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="F31">
         <v>568</v>
@@ -16414,10 +16521,10 @@
         <v>1.09</v>
       </c>
       <c r="H31" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="I31" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="J31">
         <v>22.97</v>
@@ -16426,13 +16533,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="O31">
         <v>24.99</v>
@@ -16441,7 +16548,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -16449,7 +16556,7 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="C32" t="s">
         <v>164</v>
@@ -16458,7 +16565,7 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F32">
         <v>560</v>
@@ -16467,10 +16574,10 @@
         <v>1.56</v>
       </c>
       <c r="H32" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="I32" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="J32">
         <v>20</v>
@@ -16479,13 +16586,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="O32">
         <v>31.2</v>
@@ -16494,7 +16601,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -16502,7 +16609,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="C33" t="s">
         <v>164</v>
@@ -16511,7 +16618,7 @@
         <v>176</v>
       </c>
       <c r="E33" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -16520,10 +16627,10 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="I33" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="J33">
         <v>550</v>
@@ -16532,13 +16639,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="O33">
         <v>700.51</v>
@@ -16547,7 +16654,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -16555,7 +16662,7 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="C34" t="s">
         <v>164</v>
@@ -16564,7 +16671,7 @@
         <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F34">
         <v>664</v>
@@ -16573,10 +16680,10 @@
         <v>1.5</v>
       </c>
       <c r="H34" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="I34" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="J34">
         <v>20</v>
@@ -16585,13 +16692,13 @@
         <v>425</v>
       </c>
       <c r="L34" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="O34">
         <v>29.98</v>
@@ -16600,7 +16707,7 @@
         <v>789</v>
       </c>
       <c r="Q34" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -16608,7 +16715,7 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="C35" t="s">
         <v>164</v>
@@ -16617,7 +16724,7 @@
         <v>176</v>
       </c>
       <c r="E35" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="F35">
         <v>572</v>
@@ -16626,10 +16733,10 @@
         <v>0.88</v>
       </c>
       <c r="H35" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="I35" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="J35">
         <v>22.99</v>
@@ -16638,13 +16745,13 @@
         <v>425</v>
       </c>
       <c r="L35" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="O35">
         <v>20.23</v>
@@ -16653,7 +16760,7 @@
         <v>789</v>
       </c>
       <c r="Q35" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -16661,7 +16768,7 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="C36" t="s">
         <v>164</v>
@@ -16682,13 +16789,13 @@
         <v>425</v>
       </c>
       <c r="L36" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="O36">
         <v>198.33</v>
@@ -16697,7 +16804,7 @@
         <v>789</v>
       </c>
       <c r="Q36" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -16705,7 +16812,7 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="C37" t="s">
         <v>163</v>
@@ -16714,7 +16821,7 @@
         <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="F37">
         <v>615</v>
@@ -16723,10 +16830,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="I37" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="J37">
         <v>22.97</v>
@@ -16735,13 +16842,13 @@
         <v>425</v>
       </c>
       <c r="L37" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="O37">
         <v>16.07</v>
@@ -16750,7 +16857,7 @@
         <v>789</v>
       </c>
       <c r="Q37" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -16758,7 +16865,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="C38" t="s">
         <v>164</v>
@@ -16767,7 +16874,7 @@
         <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F38">
         <v>708</v>
@@ -16776,10 +16883,10 @@
         <v>1.85</v>
       </c>
       <c r="H38" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="I38" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="J38">
         <v>20</v>
@@ -16788,13 +16895,13 @@
         <v>425</v>
       </c>
       <c r="L38" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="O38">
         <v>36.95</v>
@@ -16803,7 +16910,7 @@
         <v>789</v>
       </c>
       <c r="Q38" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -16811,7 +16918,7 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="C39" t="s">
         <v>164</v>
@@ -16820,7 +16927,7 @@
         <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -16829,10 +16936,10 @@
         <v>1.25</v>
       </c>
       <c r="H39" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="I39" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="J39">
         <v>45</v>
@@ -16841,13 +16948,13 @@
         <v>425</v>
       </c>
       <c r="L39" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1309</v>
+        <v>1316</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="O39">
         <v>56.07</v>
@@ -16856,7 +16963,7 @@
         <v>789</v>
       </c>
       <c r="Q39" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -16864,7 +16971,7 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="C40" t="s">
         <v>164</v>
@@ -16873,7 +16980,7 @@
         <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="F40">
         <v>700</v>
@@ -16882,10 +16989,10 @@
         <v>2.24</v>
       </c>
       <c r="H40" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="I40" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -16894,13 +17001,13 @@
         <v>425</v>
       </c>
       <c r="L40" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="O40">
         <v>53.81</v>
@@ -16909,7 +17016,7 @@
         <v>789</v>
       </c>
       <c r="Q40" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -16917,16 +17024,16 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="C41" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -16935,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="J41">
         <v>90</v>
@@ -16944,13 +17051,13 @@
         <v>425</v>
       </c>
       <c r="L41" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -16959,7 +17066,7 @@
         <v>789</v>
       </c>
       <c r="Q41" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -16967,16 +17074,16 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="C42" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="D42" t="s">
         <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -16985,10 +17092,10 @@
         <v>2.66</v>
       </c>
       <c r="H42" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="I42" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -16997,13 +17104,13 @@
         <v>425</v>
       </c>
       <c r="L42" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="O42">
         <v>132.99</v>
@@ -17012,7 +17119,7 @@
         <v>789</v>
       </c>
       <c r="Q42" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -17020,16 +17127,16 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="C43" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D43" t="s">
         <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -17038,10 +17145,10 @@
         <v>1.29</v>
       </c>
       <c r="H43" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="I43" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="J43">
         <v>64.98999999999999</v>
@@ -17050,13 +17157,13 @@
         <v>425</v>
       </c>
       <c r="L43" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="O43">
         <v>83.73</v>
@@ -17065,7 +17172,7 @@
         <v>789</v>
       </c>
       <c r="Q43" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -17073,7 +17180,7 @@
         <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="C44" t="s">
         <v>164</v>
@@ -17082,7 +17189,7 @@
         <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -17097,13 +17204,13 @@
         <v>425</v>
       </c>
       <c r="L44" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1372</v>
+        <v>1379</v>
       </c>
       <c r="O44">
         <v>26.9</v>
@@ -17112,7 +17219,7 @@
         <v>789</v>
       </c>
       <c r="Q44" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -17120,7 +17227,7 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="C45" t="s">
         <v>164</v>
@@ -17129,7 +17236,7 @@
         <v>177</v>
       </c>
       <c r="E45" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -17144,13 +17251,13 @@
         <v>425</v>
       </c>
       <c r="L45" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="O45">
         <v>43.75</v>
@@ -17159,7 +17266,7 @@
         <v>789</v>
       </c>
       <c r="Q45" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -17167,7 +17274,7 @@
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="D46" t="s">
         <v>177</v>
@@ -17182,7 +17289,7 @@
         <v>2.12</v>
       </c>
       <c r="I46" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="J46">
         <v>19.99</v>
@@ -17191,13 +17298,13 @@
         <v>425</v>
       </c>
       <c r="L46" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="O46">
         <v>42.3</v>
@@ -17206,7 +17313,7 @@
         <v>789</v>
       </c>
       <c r="Q46" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -17214,16 +17321,16 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="C47" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="D47" t="s">
         <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -17232,10 +17339,10 @@
         <v>0.87</v>
       </c>
       <c r="H47" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="I47" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="J47">
         <v>20</v>
@@ -17244,13 +17351,13 @@
         <v>425</v>
       </c>
       <c r="L47" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="O47">
         <v>17.33</v>
@@ -17259,7 +17366,7 @@
         <v>789</v>
       </c>
       <c r="Q47" t="s">
-        <v>1433</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -17267,16 +17374,16 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="C48" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="D48" t="s">
         <v>177</v>
       </c>
       <c r="E48" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -17285,7 +17392,7 @@
         <v>0.23</v>
       </c>
       <c r="I48" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="J48">
         <v>100</v>
@@ -17294,13 +17401,13 @@
         <v>425</v>
       </c>
       <c r="L48" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="O48">
         <v>22.95</v>
@@ -17309,7 +17416,7 @@
         <v>789</v>
       </c>
       <c r="Q48" t="s">
-        <v>1434</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -17317,16 +17424,16 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="C49" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D49" t="s">
         <v>177</v>
       </c>
       <c r="E49" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F49">
         <v>509</v>
@@ -17335,10 +17442,10 @@
         <v>0.49</v>
       </c>
       <c r="H49" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="I49" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="J49">
         <v>29.99</v>
@@ -17347,13 +17454,13 @@
         <v>425</v>
       </c>
       <c r="L49" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="O49">
         <v>14.81</v>
@@ -17362,7 +17469,7 @@
         <v>789</v>
       </c>
       <c r="Q49" t="s">
-        <v>1435</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -17370,7 +17477,7 @@
         <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="C50" t="s">
         <v>164</v>
@@ -17379,7 +17486,7 @@
         <v>177</v>
       </c>
       <c r="E50" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -17388,7 +17495,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="J50">
         <v>34.99</v>
@@ -17397,13 +17504,13 @@
         <v>425</v>
       </c>
       <c r="L50" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="O50">
         <v>28.41</v>
@@ -17412,7 +17519,7 @@
         <v>789</v>
       </c>
       <c r="Q50" t="s">
-        <v>1436</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -17420,16 +17527,16 @@
         <v>18</v>
       </c>
       <c r="B51" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="C51" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D51" t="s">
         <v>177</v>
       </c>
       <c r="E51" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F51">
         <v>552</v>
@@ -17438,10 +17545,10 @@
         <v>0.93</v>
       </c>
       <c r="H51" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="I51" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="J51">
         <v>29.99</v>
@@ -17450,13 +17557,13 @@
         <v>425</v>
       </c>
       <c r="L51" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="O51">
         <v>27.99</v>
@@ -17465,7 +17572,7 @@
         <v>789</v>
       </c>
       <c r="Q51" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -17473,7 +17580,7 @@
         <v>18</v>
       </c>
       <c r="B52" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="C52" t="s">
         <v>164</v>
@@ -17482,7 +17589,7 @@
         <v>177</v>
       </c>
       <c r="E52" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -17491,10 +17598,10 @@
         <v>1.06</v>
       </c>
       <c r="H52" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="I52" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="J52">
         <v>31.99</v>
@@ -17503,13 +17610,13 @@
         <v>425</v>
       </c>
       <c r="L52" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="O52">
         <v>34.04</v>
@@ -17518,7 +17625,7 @@
         <v>789</v>
       </c>
       <c r="Q52" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -17526,16 +17633,16 @@
         <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="C53" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D53" t="s">
         <v>177</v>
       </c>
       <c r="E53" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -17544,10 +17651,10 @@
         <v>0.92</v>
       </c>
       <c r="H53" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="I53" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="J53">
         <v>44.99</v>
@@ -17556,13 +17663,13 @@
         <v>425</v>
       </c>
       <c r="L53" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="O53">
         <v>41.52</v>
@@ -17571,7 +17678,7 @@
         <v>789</v>
       </c>
       <c r="Q53" t="s">
-        <v>1439</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -17579,7 +17686,7 @@
         <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="C54" t="s">
         <v>164</v>
@@ -17588,7 +17695,7 @@
         <v>177</v>
       </c>
       <c r="E54" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F54">
         <v>609</v>
@@ -17597,10 +17704,10 @@
         <v>1.17</v>
       </c>
       <c r="H54" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="I54" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J54">
         <v>20</v>
@@ -17609,13 +17716,13 @@
         <v>425</v>
       </c>
       <c r="L54" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="O54">
         <v>23.48</v>
@@ -17624,7 +17731,7 @@
         <v>789</v>
       </c>
       <c r="Q54" t="s">
-        <v>1440</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -17632,7 +17739,7 @@
         <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="C55" t="s">
         <v>164</v>
@@ -17641,7 +17748,7 @@
         <v>177</v>
       </c>
       <c r="E55" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -17650,10 +17757,10 @@
         <v>0.87</v>
       </c>
       <c r="H55" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="I55" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="J55">
         <v>29.99</v>
@@ -17662,13 +17769,13 @@
         <v>425</v>
       </c>
       <c r="L55" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="O55">
         <v>26.18</v>
@@ -17677,7 +17784,7 @@
         <v>789</v>
       </c>
       <c r="Q55" t="s">
-        <v>1441</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -17685,7 +17792,7 @@
         <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="C56" t="s">
         <v>164</v>
@@ -17694,7 +17801,7 @@
         <v>177</v>
       </c>
       <c r="E56" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -17703,10 +17810,10 @@
         <v>0.97</v>
       </c>
       <c r="H56" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="I56" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="J56">
         <v>69.98999999999999</v>
@@ -17715,13 +17822,13 @@
         <v>425</v>
       </c>
       <c r="L56" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="O56">
         <v>67.75</v>
@@ -17730,7 +17837,7 @@
         <v>789</v>
       </c>
       <c r="Q56" t="s">
-        <v>1442</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -17738,10 +17845,10 @@
         <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C57" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D57" t="s">
         <v>177</v>
@@ -17756,10 +17863,10 @@
         <v>0.87</v>
       </c>
       <c r="H57" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="I57" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="J57">
         <v>19.99</v>
@@ -17768,13 +17875,13 @@
         <v>425</v>
       </c>
       <c r="L57" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="O57">
         <v>17.42</v>
@@ -17783,7 +17890,7 @@
         <v>789</v>
       </c>
       <c r="Q57" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -17791,7 +17898,7 @@
         <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="C58" t="s">
         <v>164</v>
@@ -17800,7 +17907,7 @@
         <v>177</v>
       </c>
       <c r="E58" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -17809,10 +17916,10 @@
         <v>1.1</v>
       </c>
       <c r="H58" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="I58" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="J58">
         <v>20</v>
@@ -17821,13 +17928,13 @@
         <v>425</v>
       </c>
       <c r="L58" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="O58">
         <v>22</v>
@@ -17836,7 +17943,7 @@
         <v>789</v>
       </c>
       <c r="Q58" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -17844,7 +17951,7 @@
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="C59" t="s">
         <v>164</v>
@@ -17868,13 +17975,13 @@
         <v>425</v>
       </c>
       <c r="L59" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="O59">
         <v>46.28</v>
@@ -17883,7 +17990,7 @@
         <v>789</v>
       </c>
       <c r="Q59" t="s">
-        <v>1445</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -17891,7 +17998,7 @@
         <v>18</v>
       </c>
       <c r="B60" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="C60" t="s">
         <v>164</v>
@@ -17900,7 +18007,7 @@
         <v>178</v>
       </c>
       <c r="E60" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -17915,13 +18022,13 @@
         <v>425</v>
       </c>
       <c r="L60" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="O60">
         <v>40.52</v>
@@ -17930,7 +18037,7 @@
         <v>789</v>
       </c>
       <c r="Q60" t="s">
-        <v>1446</v>
+        <v>1453</v>
       </c>
     </row>
   </sheetData>
@@ -18079,7 +18186,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18156,16 +18263,16 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="C3" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D3" t="s">
         <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="F3">
         <v>1047</v>
@@ -18174,7 +18281,7 @@
         <v>0.67</v>
       </c>
       <c r="I3" t="s">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="J3">
         <v>49.99</v>
@@ -18183,13 +18290,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="O3">
         <v>33.33</v>
@@ -18198,7 +18305,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1576</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -18206,13 +18313,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
       <c r="D4" t="s">
         <v>173</v>
       </c>
       <c r="E4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -18221,10 +18328,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="I4" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
       <c r="J4">
         <v>24.99</v>
@@ -18233,13 +18340,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
       <c r="O4">
         <v>13.69</v>
@@ -18248,7 +18355,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1577</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -18256,13 +18363,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="D5" t="s">
         <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>1470</v>
+        <v>1477</v>
       </c>
       <c r="F5">
         <v>1752</v>
@@ -18271,10 +18378,10 @@
         <v>1.21</v>
       </c>
       <c r="H5" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="I5" t="s">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="J5">
         <v>74.98999999999999</v>
@@ -18283,13 +18390,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="O5">
         <v>90.84999999999999</v>
@@ -18298,7 +18405,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1578</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -18306,13 +18413,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="D6" t="s">
         <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F6">
         <v>1538</v>
@@ -18321,10 +18428,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="I6" t="s">
-        <v>1494</v>
+        <v>1501</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -18333,13 +18440,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="O6">
         <v>15.03</v>
@@ -18348,7 +18455,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -18356,13 +18463,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="D7" t="s">
         <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F7">
         <v>1759</v>
@@ -18371,10 +18478,10 @@
         <v>0.59</v>
       </c>
       <c r="H7" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="I7" t="s">
-        <v>1495</v>
+        <v>1502</v>
       </c>
       <c r="J7">
         <v>24.99</v>
@@ -18383,13 +18490,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="O7">
         <v>14.62</v>
@@ -18398,7 +18505,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1580</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -18406,7 +18513,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1453</v>
+        <v>1460</v>
       </c>
       <c r="C8" t="s">
         <v>163</v>
@@ -18415,7 +18522,7 @@
         <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F8">
         <v>1179</v>
@@ -18424,10 +18531,10 @@
         <v>0.54</v>
       </c>
       <c r="H8" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="I8" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="J8">
         <v>39.99</v>
@@ -18436,13 +18543,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="O8">
         <v>21.68</v>
@@ -18451,7 +18558,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1581</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -18459,13 +18566,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1454</v>
+        <v>1461</v>
       </c>
       <c r="D9" t="s">
         <v>173</v>
       </c>
       <c r="E9" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F9">
         <v>1805</v>
@@ -18474,10 +18581,10 @@
         <v>0.53</v>
       </c>
       <c r="H9" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="I9" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="J9">
         <v>29.99</v>
@@ -18486,13 +18593,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="O9">
         <v>16</v>
@@ -18501,7 +18608,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -18509,13 +18616,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1455</v>
+        <v>1462</v>
       </c>
       <c r="D10" t="s">
         <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="F10">
         <v>1571</v>
@@ -18524,10 +18631,10 @@
         <v>0.74</v>
       </c>
       <c r="H10" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="I10" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -18536,13 +18643,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="O10">
         <v>22.11</v>
@@ -18551,7 +18658,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -18559,13 +18666,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="D11" t="s">
         <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F11">
         <v>1159</v>
@@ -18574,10 +18681,10 @@
         <v>0.59</v>
       </c>
       <c r="H11" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
       <c r="I11" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
       <c r="J11">
         <v>29.99</v>
@@ -18586,13 +18693,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="O11">
         <v>17.83</v>
@@ -18601,7 +18708,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -18609,13 +18716,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1457</v>
+        <v>1464</v>
       </c>
       <c r="D12" t="s">
         <v>174</v>
       </c>
       <c r="E12" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F12">
         <v>1541</v>
@@ -18624,10 +18731,10 @@
         <v>0.71</v>
       </c>
       <c r="H12" t="s">
-        <v>1481</v>
+        <v>1488</v>
       </c>
       <c r="I12" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -18636,13 +18743,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1563</v>
+        <v>1570</v>
       </c>
       <c r="O12">
         <v>17.77</v>
@@ -18651,7 +18758,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1585</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -18659,13 +18766,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="D13" t="s">
         <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F13">
         <v>857</v>
@@ -18674,10 +18781,10 @@
         <v>1.31</v>
       </c>
       <c r="H13" t="s">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="I13" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="J13">
         <v>29.99</v>
@@ -18686,13 +18793,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="O13">
         <v>39.37</v>
@@ -18701,7 +18808,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -18709,13 +18816,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="D14" t="s">
         <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F14">
         <v>1215</v>
@@ -18724,10 +18831,10 @@
         <v>0.75</v>
       </c>
       <c r="H14" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="I14" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="J14">
         <v>29.99</v>
@@ -18736,13 +18843,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
       <c r="O14">
         <v>22.5</v>
@@ -18751,7 +18858,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -18759,13 +18866,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="D15" t="s">
         <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F15">
         <v>755</v>
@@ -18774,10 +18881,10 @@
         <v>1.22</v>
       </c>
       <c r="H15" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="I15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="J15">
         <v>29.99</v>
@@ -18786,13 +18893,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="O15">
         <v>36.5</v>
@@ -18801,7 +18908,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1588</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -18809,13 +18916,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="D16" t="s">
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="F16">
         <v>888</v>
@@ -18824,10 +18931,10 @@
         <v>3.33</v>
       </c>
       <c r="H16" t="s">
-        <v>1484</v>
+        <v>1491</v>
       </c>
       <c r="I16" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="J16">
         <v>79.98999999999999</v>
@@ -18836,13 +18943,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="O16">
         <v>266.38</v>
@@ -18851,7 +18958,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1589</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -18859,13 +18966,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1462</v>
+        <v>1469</v>
       </c>
       <c r="D17" t="s">
         <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="F17">
         <v>1103</v>
@@ -18874,10 +18981,10 @@
         <v>0.42</v>
       </c>
       <c r="H17" t="s">
-        <v>1485</v>
+        <v>1492</v>
       </c>
       <c r="I17" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="J17">
         <v>44.99</v>
@@ -18886,13 +18993,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1546</v>
+        <v>1553</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="O17">
         <v>18.76</v>
@@ -18901,7 +19008,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1590</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -18909,13 +19016,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1463</v>
+        <v>1470</v>
       </c>
       <c r="D18" t="s">
         <v>176</v>
       </c>
       <c r="E18" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F18">
         <v>520</v>
@@ -18924,10 +19031,10 @@
         <v>0.85</v>
       </c>
       <c r="H18" t="s">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="I18" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="J18">
         <v>39.99</v>
@@ -18936,13 +19043,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="O18">
         <v>33.99</v>
@@ -18951,7 +19058,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1591</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -18959,7 +19066,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
       <c r="C19" t="s">
         <v>164</v>
@@ -18980,13 +19087,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="O19">
         <v>180</v>
@@ -18995,7 +19102,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -19003,7 +19110,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="C20" t="s">
         <v>164</v>
@@ -19012,7 +19119,7 @@
         <v>176</v>
       </c>
       <c r="E20" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -19021,10 +19128,10 @@
         <v>1.12</v>
       </c>
       <c r="H20" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="I20" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="J20">
         <v>33</v>
@@ -19033,13 +19140,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1571</v>
+        <v>1578</v>
       </c>
       <c r="O20">
         <v>37.07</v>
@@ -19048,7 +19155,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1593</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -19056,13 +19163,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="D21" t="s">
         <v>176</v>
       </c>
       <c r="E21" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="F21">
         <v>799</v>
@@ -19071,10 +19178,10 @@
         <v>0.89</v>
       </c>
       <c r="H21" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
       <c r="I21" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -19083,13 +19190,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1572</v>
+        <v>1579</v>
       </c>
       <c r="O21">
         <v>26.75</v>
@@ -19098,7 +19205,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1594</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -19106,13 +19213,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
       <c r="D22" t="s">
         <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -19121,10 +19228,10 @@
         <v>1.38</v>
       </c>
       <c r="H22" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
       <c r="I22" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="J22">
         <v>91.98999999999999</v>
@@ -19133,13 +19240,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
       <c r="O22">
         <v>126.79</v>
@@ -19148,7 +19255,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1595</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -19156,13 +19263,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1468</v>
+        <v>1475</v>
       </c>
       <c r="D23" t="s">
         <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -19171,10 +19278,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>1490</v>
+        <v>1497</v>
       </c>
       <c r="I23" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="J23">
         <v>124.99</v>
@@ -19183,13 +19290,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -19198,7 +19305,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -19206,7 +19313,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="C24" t="s">
         <v>164</v>
@@ -19215,7 +19322,7 @@
         <v>178</v>
       </c>
       <c r="E24" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -19230,13 +19337,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1575</v>
+        <v>1582</v>
       </c>
       <c r="O24">
         <v>499.99</v>
@@ -19245,7 +19352,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1597</v>
+        <v>1604</v>
       </c>
     </row>
   </sheetData>
@@ -19322,7 +19429,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19399,16 +19506,16 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="C3" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D3" t="s">
         <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -19417,7 +19524,7 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="s">
-        <v>1602</v>
+        <v>1609</v>
       </c>
       <c r="J3">
         <v>34.99</v>
@@ -19426,13 +19533,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1608</v>
+        <v>1615</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1611</v>
+        <v>1618</v>
       </c>
       <c r="O3">
         <v>36.09</v>
@@ -19441,7 +19548,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1614</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19449,16 +19556,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1600</v>
+        <v>1607</v>
       </c>
       <c r="C4" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D4" t="s">
         <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -19467,7 +19574,7 @@
         <v>0.64</v>
       </c>
       <c r="I4" t="s">
-        <v>1603</v>
+        <v>1610</v>
       </c>
       <c r="J4">
         <v>34.99</v>
@@ -19476,13 +19583,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1606</v>
+        <v>1613</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1609</v>
+        <v>1616</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1612</v>
+        <v>1619</v>
       </c>
       <c r="O4">
         <v>22.55</v>
@@ -19491,7 +19598,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1615</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19499,16 +19606,16 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="C5" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -19517,7 +19624,7 @@
         <v>1.36</v>
       </c>
       <c r="I5" t="s">
-        <v>1604</v>
+        <v>1611</v>
       </c>
       <c r="J5">
         <v>34.99</v>
@@ -19526,13 +19633,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1607</v>
+        <v>1614</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1613</v>
+        <v>1620</v>
       </c>
       <c r="O5">
         <v>47.57</v>
@@ -19541,7 +19648,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1616</v>
+        <v>1623</v>
       </c>
     </row>
   </sheetData>
@@ -19580,7 +19687,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1617</v>
+        <v>1624</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19657,7 +19764,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1618</v>
+        <v>1625</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
@@ -19666,7 +19773,7 @@
         <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -19675,10 +19782,10 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="I3" t="s">
-        <v>1682</v>
+        <v>1689</v>
       </c>
       <c r="J3">
         <v>24.99</v>
@@ -19687,13 +19794,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1752</v>
+        <v>1759</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1788</v>
+        <v>1795</v>
       </c>
       <c r="O3">
         <v>30.44</v>
@@ -19702,7 +19809,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1824</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19710,7 +19817,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1619</v>
+        <v>1626</v>
       </c>
       <c r="C4" t="s">
         <v>163</v>
@@ -19719,7 +19826,7 @@
         <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -19728,10 +19835,10 @@
         <v>0.52</v>
       </c>
       <c r="H4" t="s">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="I4" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="J4">
         <v>24.97</v>
@@ -19740,13 +19847,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1717</v>
+        <v>1724</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1753</v>
+        <v>1760</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1789</v>
+        <v>1796</v>
       </c>
       <c r="O4">
         <v>12.96</v>
@@ -19755,7 +19862,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1825</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19763,10 +19870,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1620</v>
+        <v>1627</v>
       </c>
       <c r="C5" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D5" t="s">
         <v>176</v>
@@ -19784,13 +19891,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1718</v>
+        <v>1725</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1754</v>
+        <v>1761</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1790</v>
+        <v>1797</v>
       </c>
       <c r="O5">
         <v>48.73</v>
@@ -19799,7 +19906,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1826</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19807,16 +19914,16 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1621</v>
+        <v>1628</v>
       </c>
       <c r="C6" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D6" t="s">
         <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F6">
         <v>516</v>
@@ -19825,10 +19932,10 @@
         <v>0.92</v>
       </c>
       <c r="H6" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="I6" t="s">
-        <v>1684</v>
+        <v>1691</v>
       </c>
       <c r="J6">
         <v>24.99</v>
@@ -19837,13 +19944,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1719</v>
+        <v>1726</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1755</v>
+        <v>1762</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1791</v>
+        <v>1798</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -19852,7 +19959,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1827</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -19860,7 +19967,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="C7" t="s">
         <v>163</v>
@@ -19869,7 +19976,7 @@
         <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -19878,10 +19985,10 @@
         <v>0.82</v>
       </c>
       <c r="H7" t="s">
-        <v>1652</v>
+        <v>1659</v>
       </c>
       <c r="I7" t="s">
-        <v>1685</v>
+        <v>1692</v>
       </c>
       <c r="J7">
         <v>24.97</v>
@@ -19890,13 +19997,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1720</v>
+        <v>1727</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1756</v>
+        <v>1763</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1792</v>
+        <v>1799</v>
       </c>
       <c r="O7">
         <v>20.41</v>
@@ -19905,7 +20012,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1828</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -19913,7 +20020,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1623</v>
+        <v>1630</v>
       </c>
       <c r="C8" t="s">
         <v>163</v>
@@ -19922,7 +20029,7 @@
         <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -19937,13 +20044,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1757</v>
+        <v>1764</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1793</v>
+        <v>1800</v>
       </c>
       <c r="O8">
         <v>37.99</v>
@@ -19952,7 +20059,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1829</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -19960,16 +20067,16 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1624</v>
+        <v>1631</v>
       </c>
       <c r="C9" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D9" t="s">
         <v>176</v>
       </c>
       <c r="E9" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -19978,10 +20085,10 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="s">
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="I9" t="s">
-        <v>1686</v>
+        <v>1693</v>
       </c>
       <c r="J9">
         <v>24.99</v>
@@ -19990,13 +20097,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1758</v>
+        <v>1765</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1794</v>
+        <v>1801</v>
       </c>
       <c r="O9">
         <v>37.71</v>
@@ -20005,7 +20112,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1830</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -20013,16 +20120,16 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>1625</v>
+        <v>1632</v>
       </c>
       <c r="C10" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D10" t="s">
         <v>176</v>
       </c>
       <c r="E10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -20031,10 +20138,10 @@
         <v>0.78</v>
       </c>
       <c r="H10" t="s">
-        <v>1654</v>
+        <v>1661</v>
       </c>
       <c r="I10" t="s">
-        <v>1687</v>
+        <v>1694</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -20043,13 +20150,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1759</v>
+        <v>1766</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1795</v>
+        <v>1802</v>
       </c>
       <c r="O10">
         <v>19.54</v>
@@ -20058,7 +20165,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1831</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -20066,7 +20173,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>1626</v>
+        <v>1633</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -20084,10 +20191,10 @@
         <v>0.82</v>
       </c>
       <c r="H11" t="s">
-        <v>1655</v>
+        <v>1662</v>
       </c>
       <c r="I11" t="s">
-        <v>1688</v>
+        <v>1695</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -20096,13 +20203,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1724</v>
+        <v>1731</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1760</v>
+        <v>1767</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1796</v>
+        <v>1803</v>
       </c>
       <c r="O11">
         <v>16.43</v>
@@ -20111,7 +20218,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1832</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -20119,7 +20226,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1627</v>
+        <v>1634</v>
       </c>
       <c r="C12" t="s">
         <v>141</v>
@@ -20137,10 +20244,10 @@
         <v>1.61</v>
       </c>
       <c r="H12" t="s">
-        <v>1656</v>
+        <v>1663</v>
       </c>
       <c r="I12" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -20149,13 +20256,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1725</v>
+        <v>1732</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1761</v>
+        <v>1768</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1797</v>
+        <v>1804</v>
       </c>
       <c r="O12">
         <v>32.14</v>
@@ -20164,7 +20271,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1833</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -20172,7 +20279,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>1628</v>
+        <v>1635</v>
       </c>
       <c r="C13" t="s">
         <v>141</v>
@@ -20190,10 +20297,10 @@
         <v>0.71</v>
       </c>
       <c r="H13" t="s">
-        <v>1657</v>
+        <v>1664</v>
       </c>
       <c r="I13" t="s">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -20202,13 +20309,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1726</v>
+        <v>1733</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1762</v>
+        <v>1769</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1798</v>
+        <v>1805</v>
       </c>
       <c r="O13">
         <v>14.27</v>
@@ -20217,7 +20324,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1834</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -20225,7 +20332,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1629</v>
+        <v>1636</v>
       </c>
       <c r="C14" t="s">
         <v>141</v>
@@ -20243,10 +20350,10 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="s">
-        <v>1658</v>
+        <v>1665</v>
       </c>
       <c r="I14" t="s">
-        <v>1691</v>
+        <v>1698</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -20255,13 +20362,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1727</v>
+        <v>1734</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1763</v>
+        <v>1770</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1799</v>
+        <v>1806</v>
       </c>
       <c r="O14">
         <v>23.5</v>
@@ -20270,7 +20377,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1835</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -20296,10 +20403,10 @@
         <v>0.65</v>
       </c>
       <c r="H15" t="s">
-        <v>1659</v>
+        <v>1666</v>
       </c>
       <c r="I15" t="s">
-        <v>1692</v>
+        <v>1699</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -20308,13 +20415,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1728</v>
+        <v>1735</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1764</v>
+        <v>1771</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1800</v>
+        <v>1807</v>
       </c>
       <c r="O15">
         <v>12.92</v>
@@ -20323,7 +20430,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1836</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -20331,7 +20438,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -20349,10 +20456,10 @@
         <v>0.78</v>
       </c>
       <c r="H16" t="s">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="I16" t="s">
-        <v>1693</v>
+        <v>1700</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -20361,13 +20468,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1729</v>
+        <v>1736</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1765</v>
+        <v>1772</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1801</v>
+        <v>1808</v>
       </c>
       <c r="O16">
         <v>15.59</v>
@@ -20376,7 +20483,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1837</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -20384,7 +20491,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -20402,10 +20509,10 @@
         <v>2.22</v>
       </c>
       <c r="H17" t="s">
-        <v>1661</v>
+        <v>1668</v>
       </c>
       <c r="I17" t="s">
-        <v>1694</v>
+        <v>1701</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -20414,13 +20521,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1730</v>
+        <v>1737</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1766</v>
+        <v>1773</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1802</v>
+        <v>1809</v>
       </c>
       <c r="O17">
         <v>44.34</v>
@@ -20429,7 +20536,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1838</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -20437,7 +20544,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1632</v>
+        <v>1639</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -20455,10 +20562,10 @@
         <v>2.09</v>
       </c>
       <c r="H18" t="s">
-        <v>1662</v>
+        <v>1669</v>
       </c>
       <c r="I18" t="s">
-        <v>1695</v>
+        <v>1702</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -20467,13 +20574,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1767</v>
+        <v>1774</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1803</v>
+        <v>1810</v>
       </c>
       <c r="O18">
         <v>41.71</v>
@@ -20482,7 +20589,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1839</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -20490,7 +20597,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="C19" t="s">
         <v>143</v>
@@ -20508,10 +20615,10 @@
         <v>0.72</v>
       </c>
       <c r="H19" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="I19" t="s">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -20520,13 +20627,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1804</v>
+        <v>1811</v>
       </c>
       <c r="O19">
         <v>14.3</v>
@@ -20535,7 +20642,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1840</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -20543,7 +20650,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1634</v>
+        <v>1641</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -20561,10 +20668,10 @@
         <v>0.8</v>
       </c>
       <c r="H20" t="s">
-        <v>1664</v>
+        <v>1671</v>
       </c>
       <c r="I20" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -20573,13 +20680,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1733</v>
+        <v>1740</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1769</v>
+        <v>1776</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1805</v>
+        <v>1812</v>
       </c>
       <c r="O20">
         <v>15.98</v>
@@ -20588,7 +20695,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1841</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -20614,10 +20721,10 @@
         <v>0.9</v>
       </c>
       <c r="H21" t="s">
-        <v>1665</v>
+        <v>1672</v>
       </c>
       <c r="I21" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -20626,13 +20733,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1770</v>
+        <v>1777</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1806</v>
+        <v>1813</v>
       </c>
       <c r="O21">
         <v>17.92</v>
@@ -20641,7 +20748,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1842</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -20667,10 +20774,10 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>1666</v>
+        <v>1673</v>
       </c>
       <c r="I22" t="s">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -20679,13 +20786,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1735</v>
+        <v>1742</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1771</v>
+        <v>1778</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1807</v>
+        <v>1814</v>
       </c>
       <c r="O22">
         <v>10.03</v>
@@ -20694,7 +20801,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1843</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -20702,7 +20809,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>1635</v>
+        <v>1642</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -20720,10 +20827,10 @@
         <v>0.89</v>
       </c>
       <c r="H23" t="s">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="I23" t="s">
-        <v>1700</v>
+        <v>1707</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -20732,13 +20839,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1736</v>
+        <v>1743</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1772</v>
+        <v>1779</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="O23">
         <v>17.83</v>
@@ -20747,7 +20854,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1844</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -20755,7 +20862,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1636</v>
+        <v>1643</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -20773,10 +20880,10 @@
         <v>0.72</v>
       </c>
       <c r="H24" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="I24" t="s">
-        <v>1701</v>
+        <v>1708</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -20785,13 +20892,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1737</v>
+        <v>1744</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1773</v>
+        <v>1780</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1809</v>
+        <v>1816</v>
       </c>
       <c r="O24">
         <v>14.35</v>
@@ -20800,7 +20907,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1845</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -20826,10 +20933,10 @@
         <v>0.73</v>
       </c>
       <c r="H25" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="I25" t="s">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -20838,13 +20945,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>1738</v>
+        <v>1745</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1774</v>
+        <v>1781</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1810</v>
+        <v>1817</v>
       </c>
       <c r="O25">
         <v>14.69</v>
@@ -20853,7 +20960,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>1846</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -20879,7 +20986,7 @@
         <v>7.29</v>
       </c>
       <c r="I26" t="s">
-        <v>1703</v>
+        <v>1710</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -20888,13 +20995,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>1739</v>
+        <v>1746</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1775</v>
+        <v>1782</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1811</v>
+        <v>1818</v>
       </c>
       <c r="O26">
         <v>145.79</v>
@@ -20903,7 +21010,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>1847</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -20911,7 +21018,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1637</v>
+        <v>1644</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -20929,10 +21036,10 @@
         <v>0.88</v>
       </c>
       <c r="H27" t="s">
-        <v>1670</v>
+        <v>1677</v>
       </c>
       <c r="I27" t="s">
-        <v>1704</v>
+        <v>1711</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -20941,13 +21048,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1776</v>
+        <v>1783</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1812</v>
+        <v>1819</v>
       </c>
       <c r="O27">
         <v>17.58</v>
@@ -20956,7 +21063,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>1848</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -20964,7 +21071,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -20982,10 +21089,10 @@
         <v>0.82</v>
       </c>
       <c r="H28" t="s">
-        <v>1671</v>
+        <v>1678</v>
       </c>
       <c r="I28" t="s">
-        <v>1705</v>
+        <v>1712</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -20994,13 +21101,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>1741</v>
+        <v>1748</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1813</v>
+        <v>1820</v>
       </c>
       <c r="O28">
         <v>16.46</v>
@@ -21009,7 +21116,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>1849</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -21017,7 +21124,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="C29" t="s">
         <v>145</v>
@@ -21026,7 +21133,7 @@
         <v>176</v>
       </c>
       <c r="E29" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -21035,10 +21142,10 @@
         <v>0.96</v>
       </c>
       <c r="H29" t="s">
-        <v>1672</v>
+        <v>1679</v>
       </c>
       <c r="I29" t="s">
-        <v>1706</v>
+        <v>1713</v>
       </c>
       <c r="J29">
         <v>20.99</v>
@@ -21047,13 +21154,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1778</v>
+        <v>1785</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1814</v>
+        <v>1821</v>
       </c>
       <c r="O29">
         <v>20.09</v>
@@ -21062,7 +21169,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>1850</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -21070,7 +21177,7 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="C30" t="s">
         <v>145</v>
@@ -21079,7 +21186,7 @@
         <v>176</v>
       </c>
       <c r="E30" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -21088,10 +21195,10 @@
         <v>0.83</v>
       </c>
       <c r="H30" t="s">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="I30" t="s">
-        <v>1707</v>
+        <v>1714</v>
       </c>
       <c r="J30">
         <v>20.99</v>
@@ -21100,13 +21207,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>1743</v>
+        <v>1750</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1779</v>
+        <v>1786</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1815</v>
+        <v>1822</v>
       </c>
       <c r="O30">
         <v>17.33</v>
@@ -21115,7 +21222,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>1851</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -21123,7 +21230,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>1641</v>
+        <v>1648</v>
       </c>
       <c r="C31" t="s">
         <v>145</v>
@@ -21132,7 +21239,7 @@
         <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -21141,10 +21248,10 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="s">
-        <v>1674</v>
+        <v>1681</v>
       </c>
       <c r="I31" t="s">
-        <v>1708</v>
+        <v>1715</v>
       </c>
       <c r="J31">
         <v>20.99</v>
@@ -21153,13 +21260,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1780</v>
+        <v>1787</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1816</v>
+        <v>1823</v>
       </c>
       <c r="O31">
         <v>15.75</v>
@@ -21168,7 +21275,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>1852</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -21185,7 +21292,7 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -21194,10 +21301,10 @@
         <v>0.84</v>
       </c>
       <c r="H32" t="s">
-        <v>1675</v>
+        <v>1682</v>
       </c>
       <c r="I32" t="s">
-        <v>1709</v>
+        <v>1716</v>
       </c>
       <c r="J32">
         <v>20.99</v>
@@ -21206,13 +21313,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>1745</v>
+        <v>1752</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1781</v>
+        <v>1788</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1817</v>
+        <v>1824</v>
       </c>
       <c r="O32">
         <v>17.65</v>
@@ -21221,7 +21328,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>1853</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -21229,7 +21336,7 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1642</v>
+        <v>1649</v>
       </c>
       <c r="C33" t="s">
         <v>146</v>
@@ -21247,10 +21354,10 @@
         <v>0.76</v>
       </c>
       <c r="H33" t="s">
-        <v>1676</v>
+        <v>1683</v>
       </c>
       <c r="I33" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
       <c r="J33">
         <v>23.99</v>
@@ -21259,13 +21366,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>1746</v>
+        <v>1753</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1782</v>
+        <v>1789</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1818</v>
+        <v>1825</v>
       </c>
       <c r="O33">
         <v>18.33</v>
@@ -21274,7 +21381,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>1854</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -21282,7 +21389,7 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="C34" t="s">
         <v>146</v>
@@ -21300,10 +21407,10 @@
         <v>0.86</v>
       </c>
       <c r="H34" t="s">
-        <v>1677</v>
+        <v>1684</v>
       </c>
       <c r="I34" t="s">
-        <v>1711</v>
+        <v>1718</v>
       </c>
       <c r="J34">
         <v>23.99</v>
@@ -21312,13 +21419,13 @@
         <v>425</v>
       </c>
       <c r="L34" t="s">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1783</v>
+        <v>1790</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1819</v>
+        <v>1826</v>
       </c>
       <c r="O34">
         <v>20.58</v>
@@ -21327,7 +21434,7 @@
         <v>789</v>
       </c>
       <c r="Q34" t="s">
-        <v>1855</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -21335,7 +21442,7 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>1644</v>
+        <v>1651</v>
       </c>
       <c r="C35" t="s">
         <v>146</v>
@@ -21353,10 +21460,10 @@
         <v>0.64</v>
       </c>
       <c r="H35" t="s">
-        <v>1678</v>
+        <v>1685</v>
       </c>
       <c r="I35" t="s">
-        <v>1712</v>
+        <v>1719</v>
       </c>
       <c r="J35">
         <v>23.99</v>
@@ -21365,13 +21472,13 @@
         <v>425</v>
       </c>
       <c r="L35" t="s">
-        <v>1748</v>
+        <v>1755</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1784</v>
+        <v>1791</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1820</v>
+        <v>1827</v>
       </c>
       <c r="O35">
         <v>15.31</v>
@@ -21380,7 +21487,7 @@
         <v>789</v>
       </c>
       <c r="Q35" t="s">
-        <v>1856</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -21406,10 +21513,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H36" t="s">
-        <v>1679</v>
+        <v>1686</v>
       </c>
       <c r="I36" t="s">
-        <v>1713</v>
+        <v>1720</v>
       </c>
       <c r="J36">
         <v>23.99</v>
@@ -21418,13 +21525,13 @@
         <v>425</v>
       </c>
       <c r="L36" t="s">
-        <v>1749</v>
+        <v>1756</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1785</v>
+        <v>1792</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1821</v>
+        <v>1828</v>
       </c>
       <c r="O36">
         <v>19.5</v>
@@ -21433,7 +21540,7 @@
         <v>789</v>
       </c>
       <c r="Q36" t="s">
-        <v>1857</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -21441,16 +21548,16 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1645</v>
+        <v>1652</v>
       </c>
       <c r="C37" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
       </c>
       <c r="E37" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -21459,10 +21566,10 @@
         <v>0.99</v>
       </c>
       <c r="H37" t="s">
-        <v>1680</v>
+        <v>1687</v>
       </c>
       <c r="I37" t="s">
-        <v>1714</v>
+        <v>1721</v>
       </c>
       <c r="J37">
         <v>45</v>
@@ -21471,13 +21578,13 @@
         <v>425</v>
       </c>
       <c r="L37" t="s">
-        <v>1750</v>
+        <v>1757</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1786</v>
+        <v>1793</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1822</v>
+        <v>1829</v>
       </c>
       <c r="O37">
         <v>44.69</v>
@@ -21486,7 +21593,7 @@
         <v>789</v>
       </c>
       <c r="Q37" t="s">
-        <v>1858</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -21494,7 +21601,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="C38" t="s">
         <v>163</v>
@@ -21503,7 +21610,7 @@
         <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -21512,10 +21619,10 @@
         <v>0.78</v>
       </c>
       <c r="H38" t="s">
-        <v>1681</v>
+        <v>1688</v>
       </c>
       <c r="I38" t="s">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="J38">
         <v>24.97</v>
@@ -21524,13 +21631,13 @@
         <v>425</v>
       </c>
       <c r="L38" t="s">
-        <v>1751</v>
+        <v>1758</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1787</v>
+        <v>1794</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1823</v>
+        <v>1830</v>
       </c>
       <c r="O38">
         <v>19.45</v>
@@ -21539,7 +21646,7 @@
         <v>789</v>
       </c>
       <c r="Q38" t="s">
-        <v>1859</v>
+        <v>1866</v>
       </c>
     </row>
   </sheetData>
@@ -21639,12 +21746,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1860</v>
+        <v>1867</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21721,7 +21828,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1861</v>
+        <v>1868</v>
       </c>
       <c r="C3" t="s">
         <v>141</v>
@@ -21739,10 +21846,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="s">
-        <v>1868</v>
+        <v>1877</v>
       </c>
       <c r="I3" t="s">
-        <v>1876</v>
+        <v>1885</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -21751,13 +21858,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1881</v>
+        <v>1892</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1889</v>
+        <v>1902</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1897</v>
+        <v>1912</v>
       </c>
       <c r="O3">
         <v>23.26</v>
@@ -21766,7 +21873,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1905</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21774,7 +21881,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1862</v>
+        <v>1869</v>
       </c>
       <c r="C4" t="s">
         <v>141</v>
@@ -21792,10 +21899,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="I4" t="s">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -21804,13 +21911,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1882</v>
+        <v>1893</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1890</v>
+        <v>1903</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1898</v>
+        <v>1913</v>
       </c>
       <c r="O4">
         <v>16.41</v>
@@ -21819,7 +21926,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1906</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -21827,7 +21934,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1863</v>
+        <v>1870</v>
       </c>
       <c r="C5" t="s">
         <v>141</v>
@@ -21845,10 +21952,10 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="s">
-        <v>1870</v>
+        <v>1879</v>
       </c>
       <c r="I5" t="s">
-        <v>1878</v>
+        <v>1887</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -21857,13 +21964,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1883</v>
+        <v>1894</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1891</v>
+        <v>1904</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1899</v>
+        <v>1914</v>
       </c>
       <c r="O5">
         <v>23.79</v>
@@ -21872,7 +21979,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1907</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -21880,7 +21987,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
@@ -21889,7 +21996,7 @@
         <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -21898,10 +22005,10 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="s">
-        <v>1871</v>
+        <v>1880</v>
       </c>
       <c r="I6" t="s">
-        <v>1879</v>
+        <v>1888</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -21910,13 +22017,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1884</v>
+        <v>1895</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1892</v>
+        <v>1905</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1900</v>
+        <v>1915</v>
       </c>
       <c r="O6">
         <v>23.94</v>
@@ -21925,7 +22032,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1908</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -21951,7 +22058,7 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>1872</v>
+        <v>1881</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -21960,13 +22067,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1885</v>
+        <v>1896</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1893</v>
+        <v>1906</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1901</v>
+        <v>1916</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -21975,7 +22082,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1909</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -21983,7 +22090,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -22001,7 +22108,7 @@
         <v>1.52</v>
       </c>
       <c r="H8" t="s">
-        <v>1873</v>
+        <v>1882</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -22010,13 +22117,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1886</v>
+        <v>1897</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1894</v>
+        <v>1907</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1902</v>
+        <v>1917</v>
       </c>
       <c r="O8">
         <v>30.47</v>
@@ -22025,7 +22132,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1910</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -22033,7 +22140,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
@@ -22051,7 +22158,7 @@
         <v>1.02</v>
       </c>
       <c r="H9" t="s">
-        <v>1874</v>
+        <v>1883</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -22060,13 +22167,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1887</v>
+        <v>1898</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1895</v>
+        <v>1908</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1903</v>
+        <v>1918</v>
       </c>
       <c r="O9">
         <v>20.39</v>
@@ -22075,7 +22182,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1911</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -22083,7 +22190,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="C10" t="s">
         <v>143</v>
@@ -22092,50 +22199,150 @@
         <v>178</v>
       </c>
       <c r="E10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.29</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1875</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="s">
-        <v>1880</v>
+        <v>1889</v>
       </c>
       <c r="J10">
         <v>24.99</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="2" t="s">
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1888</v>
+        <v>1899</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1896</v>
+        <v>1909</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1904</v>
+        <v>1919</v>
       </c>
       <c r="O10">
+        <v>29.95</v>
+      </c>
+      <c r="P10" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
+        <v>933</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1890</v>
+      </c>
+      <c r="J11">
+        <v>24.99</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1900</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="O11">
+        <v>29.95</v>
+      </c>
+      <c r="P11" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
+        <v>933</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1.29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1884</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1891</v>
+      </c>
+      <c r="J12">
+        <v>24.99</v>
+      </c>
+      <c r="K12" t="s">
+        <v>425</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1901</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="O12">
         <v>32.18</v>
       </c>
-      <c r="P10" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>1912</v>
+      <c r="P12" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1931</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A10">
+  <conditionalFormatting sqref="A3:A12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -22144,7 +22351,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A12">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22163,8 +22370,14 @@
     <hyperlink ref="N8" r:id="rId12"/>
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14"/>
-    <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16"/>
+    <hyperlink ref="K10" r:id="rId15"/>
+    <hyperlink ref="M10" r:id="rId16"/>
+    <hyperlink ref="N10" r:id="rId17"/>
+    <hyperlink ref="K11" r:id="rId18"/>
+    <hyperlink ref="M11" r:id="rId19"/>
+    <hyperlink ref="N11" r:id="rId20"/>
+    <hyperlink ref="M12" r:id="rId21"/>
+    <hyperlink ref="N12" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22177,7 +22390,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1913</v>
+        <v>1932</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22254,16 +22467,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1914</v>
+        <v>1933</v>
       </c>
       <c r="C3" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D3" t="s">
         <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>1918</v>
+        <v>1937</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -22272,10 +22485,10 @@
         <v>0.65</v>
       </c>
       <c r="H3" t="s">
-        <v>1919</v>
+        <v>1938</v>
       </c>
       <c r="I3" t="s">
-        <v>1923</v>
+        <v>1942</v>
       </c>
       <c r="J3">
         <v>32.99</v>
@@ -22284,13 +22497,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1927</v>
+        <v>1946</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1931</v>
+        <v>1950</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1935</v>
+        <v>1954</v>
       </c>
       <c r="O3">
         <v>21.34</v>
@@ -22299,7 +22512,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1939</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22307,16 +22520,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1915</v>
+        <v>1934</v>
       </c>
       <c r="C4" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D4" t="s">
         <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>1918</v>
+        <v>1937</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -22325,10 +22538,10 @@
         <v>0.68</v>
       </c>
       <c r="H4" t="s">
-        <v>1920</v>
+        <v>1939</v>
       </c>
       <c r="I4" t="s">
-        <v>1924</v>
+        <v>1943</v>
       </c>
       <c r="J4">
         <v>32.99</v>
@@ -22337,13 +22550,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1928</v>
+        <v>1947</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1932</v>
+        <v>1951</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1936</v>
+        <v>1955</v>
       </c>
       <c r="O4">
         <v>22.3</v>
@@ -22352,7 +22565,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1940</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22360,16 +22573,16 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1916</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -22378,10 +22591,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="s">
-        <v>1921</v>
+        <v>1940</v>
       </c>
       <c r="I5" t="s">
-        <v>1925</v>
+        <v>1944</v>
       </c>
       <c r="J5">
         <v>29.99</v>
@@ -22390,13 +22603,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1929</v>
+        <v>1948</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1933</v>
+        <v>1952</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1937</v>
+        <v>1956</v>
       </c>
       <c r="O5">
         <v>46.29</v>
@@ -22405,7 +22618,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1941</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22413,16 +22626,16 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1917</v>
+        <v>1936</v>
       </c>
       <c r="C6" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="D6" t="s">
         <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -22431,10 +22644,10 @@
         <v>1.37</v>
       </c>
       <c r="H6" t="s">
-        <v>1922</v>
+        <v>1941</v>
       </c>
       <c r="I6" t="s">
-        <v>1926</v>
+        <v>1945</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -22443,13 +22656,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1930</v>
+        <v>1949</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1934</v>
+        <v>1953</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1938</v>
+        <v>1957</v>
       </c>
       <c r="O6">
         <v>41.15</v>
@@ -22458,7 +22671,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1942</v>
+        <v>1961</v>
       </c>
     </row>
   </sheetData>
@@ -22499,7 +22712,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1943</v>
+        <v>1962</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22576,13 +22789,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1944</v>
+        <v>1963</v>
       </c>
       <c r="C3" t="s">
         <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E3" t="s">
         <v>181</v>
@@ -22594,10 +22807,10 @@
         <v>0.99</v>
       </c>
       <c r="H3" t="s">
-        <v>1975</v>
+        <v>1994</v>
       </c>
       <c r="I3" t="s">
-        <v>1994</v>
+        <v>2013</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -22606,13 +22819,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>2025</v>
+        <v>2044</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2056</v>
+        <v>2075</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2087</v>
+        <v>2106</v>
       </c>
       <c r="O3">
         <v>19.84</v>
@@ -22621,7 +22834,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>2118</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22629,13 +22842,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1945</v>
+        <v>1964</v>
       </c>
       <c r="C4" t="s">
         <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E4" t="s">
         <v>181</v>
@@ -22647,7 +22860,7 @@
         <v>1.42</v>
       </c>
       <c r="I4" t="s">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -22656,13 +22869,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>2026</v>
+        <v>2045</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2057</v>
+        <v>2076</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2088</v>
+        <v>2107</v>
       </c>
       <c r="O4">
         <v>28.43</v>
@@ -22671,7 +22884,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>2119</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22679,13 +22892,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1946</v>
+        <v>1965</v>
       </c>
       <c r="C5" t="s">
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E5" t="s">
         <v>181</v>
@@ -22697,10 +22910,10 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="s">
-        <v>1976</v>
+        <v>1995</v>
       </c>
       <c r="I5" t="s">
-        <v>1996</v>
+        <v>2015</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -22709,13 +22922,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>2027</v>
+        <v>2046</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2058</v>
+        <v>2077</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2089</v>
+        <v>2108</v>
       </c>
       <c r="O5">
         <v>24.47</v>
@@ -22724,7 +22937,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>2120</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22732,13 +22945,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1947</v>
+        <v>1966</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E6" t="s">
         <v>181</v>
@@ -22750,10 +22963,10 @@
         <v>0.86</v>
       </c>
       <c r="H6" t="s">
-        <v>1977</v>
+        <v>1996</v>
       </c>
       <c r="I6" t="s">
-        <v>1997</v>
+        <v>2016</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -22762,13 +22975,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>2028</v>
+        <v>2047</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2059</v>
+        <v>2078</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2090</v>
+        <v>2109</v>
       </c>
       <c r="O6">
         <v>17.15</v>
@@ -22777,7 +22990,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>2121</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -22785,7 +22998,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1948</v>
+        <v>1967</v>
       </c>
       <c r="C7" t="s">
         <v>142</v>
@@ -22803,7 +23016,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="s">
-        <v>1998</v>
+        <v>2017</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -22812,13 +23025,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>2029</v>
+        <v>2048</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>2060</v>
+        <v>2079</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2091</v>
+        <v>2110</v>
       </c>
       <c r="O7">
         <v>14.49</v>
@@ -22827,7 +23040,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>2122</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -22835,7 +23048,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1949</v>
+        <v>1968</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -22853,10 +23066,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>1978</v>
+        <v>1997</v>
       </c>
       <c r="I8" t="s">
-        <v>1999</v>
+        <v>2018</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -22865,13 +23078,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>2030</v>
+        <v>2049</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2061</v>
+        <v>2080</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>2092</v>
+        <v>2111</v>
       </c>
       <c r="O8">
         <v>16.25</v>
@@ -22880,7 +23093,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>2123</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -22888,7 +23101,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1950</v>
+        <v>1969</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
@@ -22906,10 +23119,10 @@
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>1979</v>
+        <v>1998</v>
       </c>
       <c r="I9" t="s">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -22918,13 +23131,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>2031</v>
+        <v>2050</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>2062</v>
+        <v>2081</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>2093</v>
+        <v>2112</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -22933,7 +23146,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>2124</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -22941,7 +23154,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1951</v>
+        <v>1970</v>
       </c>
       <c r="C10" t="s">
         <v>142</v>
@@ -22959,10 +23172,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>1980</v>
+        <v>1999</v>
       </c>
       <c r="I10" t="s">
-        <v>2001</v>
+        <v>2020</v>
       </c>
       <c r="J10">
         <v>19.99</v>
@@ -22971,13 +23184,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>2032</v>
+        <v>2051</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>2063</v>
+        <v>2082</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>2094</v>
+        <v>2113</v>
       </c>
       <c r="O10">
         <v>13.8</v>
@@ -22986,7 +23199,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>2125</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -22994,7 +23207,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1952</v>
+        <v>1971</v>
       </c>
       <c r="C11" t="s">
         <v>143</v>
@@ -23012,7 +23225,7 @@
         <v>0.82</v>
       </c>
       <c r="I11" t="s">
-        <v>2002</v>
+        <v>2021</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -23021,13 +23234,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>2033</v>
+        <v>2052</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>2064</v>
+        <v>2083</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>2095</v>
+        <v>2114</v>
       </c>
       <c r="O11">
         <v>16.49</v>
@@ -23036,7 +23249,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>2126</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -23044,7 +23257,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1953</v>
+        <v>1972</v>
       </c>
       <c r="C12" t="s">
         <v>143</v>
@@ -23062,7 +23275,7 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="s">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -23071,13 +23284,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>2065</v>
+        <v>2084</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>2096</v>
+        <v>2115</v>
       </c>
       <c r="O12">
         <v>21.34</v>
@@ -23086,7 +23299,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>2127</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -23094,7 +23307,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1954</v>
+        <v>1973</v>
       </c>
       <c r="C13" t="s">
         <v>143</v>
@@ -23112,10 +23325,10 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="s">
-        <v>1981</v>
+        <v>2000</v>
       </c>
       <c r="I13" t="s">
-        <v>2004</v>
+        <v>2023</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -23124,13 +23337,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>2035</v>
+        <v>2054</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>2066</v>
+        <v>2085</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>2097</v>
+        <v>2116</v>
       </c>
       <c r="O13">
         <v>35</v>
@@ -23139,7 +23352,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>2128</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -23147,7 +23360,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1955</v>
+        <v>1974</v>
       </c>
       <c r="C14" t="s">
         <v>143</v>
@@ -23165,7 +23378,7 @@
         <v>2.38</v>
       </c>
       <c r="I14" t="s">
-        <v>2005</v>
+        <v>2024</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -23174,13 +23387,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>2036</v>
+        <v>2055</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2067</v>
+        <v>2086</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2098</v>
+        <v>2117</v>
       </c>
       <c r="O14">
         <v>47.66</v>
@@ -23189,7 +23402,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>2129</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -23197,7 +23410,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>1956</v>
+        <v>1975</v>
       </c>
       <c r="C15" t="s">
         <v>144</v>
@@ -23215,10 +23428,10 @@
         <v>2.09</v>
       </c>
       <c r="H15" t="s">
-        <v>1982</v>
+        <v>2001</v>
       </c>
       <c r="I15" t="s">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -23227,13 +23440,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>2037</v>
+        <v>2056</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>2068</v>
+        <v>2087</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>2099</v>
+        <v>2118</v>
       </c>
       <c r="O15">
         <v>41.68</v>
@@ -23242,7 +23455,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>2130</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -23250,7 +23463,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1957</v>
+        <v>1976</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
@@ -23268,10 +23481,10 @@
         <v>1.82</v>
       </c>
       <c r="H16" t="s">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="I16" t="s">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -23280,13 +23493,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>2038</v>
+        <v>2057</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>2069</v>
+        <v>2088</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>2100</v>
+        <v>2119</v>
       </c>
       <c r="O16">
         <v>36.31</v>
@@ -23295,7 +23508,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>2131</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -23303,7 +23516,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1958</v>
+        <v>1977</v>
       </c>
       <c r="C17" t="s">
         <v>144</v>
@@ -23321,7 +23534,7 @@
         <v>0.77</v>
       </c>
       <c r="I17" t="s">
-        <v>2008</v>
+        <v>2027</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -23330,13 +23543,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>2039</v>
+        <v>2058</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>2070</v>
+        <v>2089</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>2101</v>
+        <v>2120</v>
       </c>
       <c r="O17">
         <v>15.49</v>
@@ -23345,7 +23558,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>2132</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -23353,7 +23566,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1959</v>
+        <v>1978</v>
       </c>
       <c r="C18" t="s">
         <v>144</v>
@@ -23371,7 +23584,7 @@
         <v>1.84</v>
       </c>
       <c r="I18" t="s">
-        <v>2009</v>
+        <v>2028</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -23380,13 +23593,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>2040</v>
+        <v>2059</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2071</v>
+        <v>2090</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>2102</v>
+        <v>2121</v>
       </c>
       <c r="O18">
         <v>36.87</v>
@@ -23395,7 +23608,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>2133</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -23403,7 +23616,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1960</v>
+        <v>1979</v>
       </c>
       <c r="C19" t="s">
         <v>145</v>
@@ -23421,10 +23634,10 @@
         <v>0.59</v>
       </c>
       <c r="H19" t="s">
-        <v>1984</v>
+        <v>2003</v>
       </c>
       <c r="I19" t="s">
-        <v>2010</v>
+        <v>2029</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -23433,13 +23646,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>2041</v>
+        <v>2060</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>2072</v>
+        <v>2091</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>2103</v>
+        <v>2122</v>
       </c>
       <c r="O19">
         <v>11.86</v>
@@ -23448,7 +23661,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>2134</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -23456,7 +23669,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1961</v>
+        <v>1980</v>
       </c>
       <c r="C20" t="s">
         <v>145</v>
@@ -23474,7 +23687,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" t="s">
-        <v>2011</v>
+        <v>2030</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -23483,13 +23696,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>2042</v>
+        <v>2061</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>2073</v>
+        <v>2092</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>2104</v>
+        <v>2123</v>
       </c>
       <c r="O20">
         <v>12.35</v>
@@ -23498,7 +23711,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>2135</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -23506,7 +23719,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>1962</v>
+        <v>1981</v>
       </c>
       <c r="C21" t="s">
         <v>145</v>
@@ -23524,10 +23737,10 @@
         <v>0.44</v>
       </c>
       <c r="H21" t="s">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="I21" t="s">
-        <v>2012</v>
+        <v>2031</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -23536,13 +23749,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>2043</v>
+        <v>2062</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2074</v>
+        <v>2093</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2105</v>
+        <v>2124</v>
       </c>
       <c r="O21">
         <v>8.81</v>
@@ -23551,7 +23764,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>2136</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -23559,7 +23772,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1963</v>
+        <v>1982</v>
       </c>
       <c r="C22" t="s">
         <v>145</v>
@@ -23577,7 +23790,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>2013</v>
+        <v>2032</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -23586,13 +23799,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>2044</v>
+        <v>2063</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>2075</v>
+        <v>2094</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>2106</v>
+        <v>2125</v>
       </c>
       <c r="O22">
         <v>11.2</v>
@@ -23601,7 +23814,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>2137</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -23609,7 +23822,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1964</v>
+        <v>1983</v>
       </c>
       <c r="C23" t="s">
         <v>146</v>
@@ -23627,10 +23840,10 @@
         <v>0.61</v>
       </c>
       <c r="H23" t="s">
-        <v>1986</v>
+        <v>2005</v>
       </c>
       <c r="I23" t="s">
-        <v>2014</v>
+        <v>2033</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -23639,13 +23852,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>2045</v>
+        <v>2064</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>2076</v>
+        <v>2095</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>2107</v>
+        <v>2126</v>
       </c>
       <c r="O23">
         <v>12.25</v>
@@ -23654,7 +23867,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>2138</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -23662,7 +23875,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1965</v>
+        <v>1984</v>
       </c>
       <c r="C24" t="s">
         <v>146</v>
@@ -23680,10 +23893,10 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>1987</v>
+        <v>2006</v>
       </c>
       <c r="I24" t="s">
-        <v>2015</v>
+        <v>2034</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -23692,13 +23905,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>2046</v>
+        <v>2065</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2077</v>
+        <v>2096</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2108</v>
+        <v>2127</v>
       </c>
       <c r="O24">
         <v>10.89</v>
@@ -23707,7 +23920,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>2139</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -23715,7 +23928,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>1966</v>
+        <v>1985</v>
       </c>
       <c r="C25" t="s">
         <v>146</v>
@@ -23733,10 +23946,10 @@
         <v>0.38</v>
       </c>
       <c r="H25" t="s">
-        <v>1988</v>
+        <v>2007</v>
       </c>
       <c r="I25" t="s">
-        <v>2016</v>
+        <v>2035</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -23745,13 +23958,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>2047</v>
+        <v>2066</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>2078</v>
+        <v>2097</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>2109</v>
+        <v>2128</v>
       </c>
       <c r="O25">
         <v>7.5</v>
@@ -23760,7 +23973,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>2140</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -23768,7 +23981,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>1967</v>
+        <v>1986</v>
       </c>
       <c r="C26" t="s">
         <v>146</v>
@@ -23786,10 +23999,10 @@
         <v>0.62</v>
       </c>
       <c r="H26" t="s">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="I26" t="s">
-        <v>2017</v>
+        <v>2036</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -23798,13 +24011,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>2048</v>
+        <v>2067</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>2079</v>
+        <v>2098</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2110</v>
+        <v>2129</v>
       </c>
       <c r="O26">
         <v>12.32</v>
@@ -23813,7 +24026,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>2141</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -23821,7 +24034,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>1968</v>
+        <v>1987</v>
       </c>
       <c r="C27" t="s">
         <v>147</v>
@@ -23839,10 +24052,10 @@
         <v>2.43</v>
       </c>
       <c r="H27" t="s">
-        <v>1990</v>
+        <v>2009</v>
       </c>
       <c r="I27" t="s">
-        <v>2018</v>
+        <v>2037</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -23851,13 +24064,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>2049</v>
+        <v>2068</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2080</v>
+        <v>2099</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2111</v>
+        <v>2130</v>
       </c>
       <c r="O27">
         <v>48.66</v>
@@ -23866,7 +24079,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>2142</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -23874,7 +24087,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>1969</v>
+        <v>1988</v>
       </c>
       <c r="C28" t="s">
         <v>147</v>
@@ -23892,7 +24105,7 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="s">
-        <v>2019</v>
+        <v>2038</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -23901,13 +24114,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>2050</v>
+        <v>2069</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2081</v>
+        <v>2100</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2112</v>
+        <v>2131</v>
       </c>
       <c r="O28">
         <v>36.49</v>
@@ -23916,7 +24129,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>2143</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -23924,7 +24137,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>1970</v>
+        <v>1989</v>
       </c>
       <c r="C29" t="s">
         <v>147</v>
@@ -23942,10 +24155,10 @@
         <v>1.33</v>
       </c>
       <c r="H29" t="s">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="I29" t="s">
-        <v>2020</v>
+        <v>2039</v>
       </c>
       <c r="J29">
         <v>19.99</v>
@@ -23954,13 +24167,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>2051</v>
+        <v>2070</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2082</v>
+        <v>2101</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2113</v>
+        <v>2132</v>
       </c>
       <c r="O29">
         <v>26.63</v>
@@ -23969,7 +24182,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>2144</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -23977,7 +24190,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>1971</v>
+        <v>1990</v>
       </c>
       <c r="C30" t="s">
         <v>147</v>
@@ -23995,7 +24208,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="s">
-        <v>2021</v>
+        <v>2040</v>
       </c>
       <c r="J30">
         <v>19.99</v>
@@ -24004,13 +24217,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>2052</v>
+        <v>2071</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2083</v>
+        <v>2102</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2114</v>
+        <v>2133</v>
       </c>
       <c r="O30">
         <v>50.71</v>
@@ -24019,7 +24232,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>2145</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -24027,7 +24240,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>1972</v>
+        <v>1991</v>
       </c>
       <c r="C31" t="s">
         <v>148</v>
@@ -24045,10 +24258,10 @@
         <v>0.85</v>
       </c>
       <c r="H31" t="s">
-        <v>1992</v>
+        <v>2011</v>
       </c>
       <c r="I31" t="s">
-        <v>2022</v>
+        <v>2041</v>
       </c>
       <c r="J31">
         <v>19.99</v>
@@ -24057,13 +24270,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>2053</v>
+        <v>2072</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2084</v>
+        <v>2103</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2115</v>
+        <v>2134</v>
       </c>
       <c r="O31">
         <v>16.93</v>
@@ -24072,7 +24285,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>2146</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -24080,7 +24293,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>1973</v>
+        <v>1992</v>
       </c>
       <c r="C32" t="s">
         <v>148</v>
@@ -24098,7 +24311,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" t="s">
-        <v>2023</v>
+        <v>2042</v>
       </c>
       <c r="J32">
         <v>19.99</v>
@@ -24107,13 +24320,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>2054</v>
+        <v>2073</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2085</v>
+        <v>2104</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2116</v>
+        <v>2135</v>
       </c>
       <c r="O32">
         <v>17.97</v>
@@ -24122,7 +24335,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>2147</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -24130,7 +24343,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>1974</v>
+        <v>1993</v>
       </c>
       <c r="C33" t="s">
         <v>148</v>
@@ -24148,10 +24361,10 @@
         <v>0.89</v>
       </c>
       <c r="H33" t="s">
-        <v>1993</v>
+        <v>2012</v>
       </c>
       <c r="I33" t="s">
-        <v>2024</v>
+        <v>2043</v>
       </c>
       <c r="J33">
         <v>19.99</v>
@@ -24160,13 +24373,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>2055</v>
+        <v>2074</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2086</v>
+        <v>2105</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2117</v>
+        <v>2136</v>
       </c>
       <c r="O33">
         <v>17.84</v>
@@ -24175,7 +24388,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>2148</v>
+        <v>2167</v>
       </c>
     </row>
   </sheetData>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="2191">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="2196">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -3334,6 +3334,9 @@
     <t>Great Black Wizard</t>
   </si>
   <si>
+    <t>Stonedar</t>
+  </si>
+  <si>
     <t>SDCC</t>
   </si>
   <si>
@@ -3865,6 +3868,9 @@
     <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-and-he-man-2-pack-2424.jpg</t>
   </si>
   <si>
@@ -4039,6 +4045,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/prince-adam-and-he-man-2-pack-2424.php</t>
   </si>
   <si>
@@ -4213,6 +4222,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
+  </si>
+  <si>
     <t>2424</t>
   </si>
   <si>
@@ -4385,6 +4397,9 @@
   </si>
   <si>
     <t>12852</t>
+  </si>
+  <si>
+    <t>13031</t>
   </si>
   <si>
     <t>Origins Beasts, Vehicles and Playsets Checklist</t>
@@ -13693,7 +13708,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13770,13 +13785,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="D3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E3" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -13785,10 +13800,10 @@
         <v>0.51</v>
       </c>
       <c r="H3" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
       <c r="I3" t="s">
-        <v>2176</v>
+        <v>2181</v>
       </c>
       <c r="J3">
         <v>39.95</v>
@@ -13797,13 +13812,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>2179</v>
+        <v>2184</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2182</v>
+        <v>2187</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="O3">
         <v>20.51</v>
@@ -13812,7 +13827,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>2188</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -13820,13 +13835,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="D4" t="s">
         <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -13835,10 +13850,10 @@
         <v>0.6</v>
       </c>
       <c r="H4" t="s">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="I4" t="s">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="J4">
         <v>59.95</v>
@@ -13847,13 +13862,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2183</v>
+        <v>2188</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="O4">
         <v>36.25</v>
@@ -13862,7 +13877,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>2189</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -13870,13 +13885,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2171</v>
+        <v>2176</v>
       </c>
       <c r="D5" t="s">
         <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -13885,7 +13900,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="s">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="J5">
         <v>59.95</v>
@@ -13894,13 +13909,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>2181</v>
+        <v>2186</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2187</v>
+        <v>2192</v>
       </c>
       <c r="O5">
         <v>138.16</v>
@@ -13909,7 +13924,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>2190</v>
+        <v>2195</v>
       </c>
     </row>
   </sheetData>
@@ -14988,7 +15003,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -15073,13 +15088,13 @@
         <v>1045</v>
       </c>
       <c r="C3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15088,10 +15103,10 @@
         <v>9.84</v>
       </c>
       <c r="H3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="I3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="J3">
         <v>39.99</v>
@@ -15100,13 +15115,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="O3">
         <v>393.33</v>
@@ -15115,7 +15130,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15126,13 +15141,13 @@
         <v>1046</v>
       </c>
       <c r="C4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D4" t="s">
         <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15141,7 +15156,7 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="J4">
         <v>269.99</v>
@@ -15150,13 +15165,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="O4">
         <v>323.96</v>
@@ -15165,7 +15180,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -15176,13 +15191,13 @@
         <v>1047</v>
       </c>
       <c r="C5" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D5" t="s">
         <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -15191,10 +15206,10 @@
         <v>2.75</v>
       </c>
       <c r="H5" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="I5" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="J5">
         <v>39.99</v>
@@ -15203,13 +15218,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="O5">
         <v>110</v>
@@ -15218,7 +15233,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -15229,13 +15244,13 @@
         <v>1048</v>
       </c>
       <c r="C6" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D6" t="s">
         <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -15244,7 +15259,7 @@
         <v>5.83</v>
       </c>
       <c r="I6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -15253,13 +15268,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="O6">
         <v>350</v>
@@ -15268,7 +15283,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -15279,13 +15294,13 @@
         <v>1049</v>
       </c>
       <c r="C7" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D7" t="s">
         <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -15294,7 +15309,7 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -15303,13 +15318,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="O7">
         <v>216.32</v>
@@ -15318,7 +15333,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -15329,13 +15344,13 @@
         <v>1050</v>
       </c>
       <c r="C8" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D8" t="s">
         <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F8">
         <v>1537</v>
@@ -15344,10 +15359,10 @@
         <v>0.48</v>
       </c>
       <c r="H8" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="I8" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="J8">
         <v>29.99</v>
@@ -15356,13 +15371,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="O8">
         <v>14.33</v>
@@ -15371,7 +15386,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -15382,13 +15397,13 @@
         <v>1051</v>
       </c>
       <c r="C9" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D9" t="s">
         <v>173</v>
       </c>
       <c r="E9" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -15403,13 +15418,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="O9">
         <v>109.99</v>
@@ -15418,7 +15433,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -15429,13 +15444,13 @@
         <v>1052</v>
       </c>
       <c r="C10" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D10" t="s">
         <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -15444,7 +15459,7 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -15453,13 +15468,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="O10">
         <v>260</v>
@@ -15468,7 +15483,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -15479,13 +15494,13 @@
         <v>1053</v>
       </c>
       <c r="C11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D11" t="s">
         <v>173</v>
       </c>
       <c r="E11" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -15500,13 +15515,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="O11">
         <v>299.95</v>
@@ -15515,7 +15530,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -15526,13 +15541,13 @@
         <v>1054</v>
       </c>
       <c r="C12" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -15547,13 +15562,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="O12">
         <v>126.66</v>
@@ -15562,7 +15577,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -15573,13 +15588,13 @@
         <v>1055</v>
       </c>
       <c r="C13" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D13" t="s">
         <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -15588,7 +15603,7 @@
         <v>4.33</v>
       </c>
       <c r="I13" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -15597,13 +15612,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="O13">
         <v>216.67</v>
@@ -15612,7 +15627,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -15623,13 +15638,13 @@
         <v>1056</v>
       </c>
       <c r="C14" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D14" t="s">
         <v>173</v>
       </c>
       <c r="E14" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -15638,7 +15653,7 @@
         <v>1.72</v>
       </c>
       <c r="I14" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -15647,13 +15662,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="O14">
         <v>51.65</v>
@@ -15662,7 +15677,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -15673,13 +15688,13 @@
         <v>1057</v>
       </c>
       <c r="C15" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D15" t="s">
         <v>173</v>
       </c>
       <c r="E15" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F15">
         <v>503</v>
@@ -15688,7 +15703,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J15">
         <v>17</v>
@@ -15697,13 +15712,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="O15">
         <v>95.16</v>
@@ -15712,7 +15727,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -15729,7 +15744,7 @@
         <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F16">
         <v>606</v>
@@ -15738,10 +15753,10 @@
         <v>2.86</v>
       </c>
       <c r="H16" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I16" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -15750,13 +15765,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="O16">
         <v>85.70999999999999</v>
@@ -15765,7 +15780,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -15791,10 +15806,10 @@
         <v>2.33</v>
       </c>
       <c r="H17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="I17" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J17">
         <v>18</v>
@@ -15803,13 +15818,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="O17">
         <v>42</v>
@@ -15818,7 +15833,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -15835,7 +15850,7 @@
         <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -15844,10 +15859,10 @@
         <v>0.53</v>
       </c>
       <c r="H18" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="I18" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="J18">
         <v>150</v>
@@ -15856,13 +15871,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="O18">
         <v>79.75</v>
@@ -15871,7 +15886,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -15888,7 +15903,7 @@
         <v>174</v>
       </c>
       <c r="E19" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F19">
         <v>536</v>
@@ -15897,7 +15912,7 @@
         <v>4.54</v>
       </c>
       <c r="I19" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="J19">
         <v>17</v>
@@ -15906,13 +15921,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="O19">
         <v>77.23999999999999</v>
@@ -15921,7 +15936,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -15947,10 +15962,10 @@
         <v>1.34</v>
       </c>
       <c r="H20" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="I20" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="J20">
         <v>18</v>
@@ -15959,13 +15974,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="O20">
         <v>24.09</v>
@@ -15974,7 +15989,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -15985,13 +16000,13 @@
         <v>1063</v>
       </c>
       <c r="C21" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D21" t="s">
         <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F21">
         <v>671</v>
@@ -16000,7 +16015,7 @@
         <v>0.4</v>
       </c>
       <c r="I21" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J21">
         <v>49.99</v>
@@ -16009,13 +16024,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="O21">
         <v>19.99</v>
@@ -16024,7 +16039,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -16041,7 +16056,7 @@
         <v>174</v>
       </c>
       <c r="E22" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F22">
         <v>911</v>
@@ -16050,10 +16065,10 @@
         <v>1.93</v>
       </c>
       <c r="H22" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="I22" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="J22">
         <v>17</v>
@@ -16062,13 +16077,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="O22">
         <v>32.76</v>
@@ -16077,7 +16092,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -16091,7 +16106,7 @@
         <v>175</v>
       </c>
       <c r="E23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F23">
         <v>524</v>
@@ -16100,10 +16115,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="I23" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="J23">
         <v>64.98999999999999</v>
@@ -16112,13 +16127,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="O23">
         <v>129.79</v>
@@ -16127,7 +16142,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -16153,10 +16168,10 @@
         <v>1.91</v>
       </c>
       <c r="H24" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="I24" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -16165,13 +16180,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="O24">
         <v>38.24</v>
@@ -16180,7 +16195,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -16206,10 +16221,10 @@
         <v>1.97</v>
       </c>
       <c r="H25" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="I25" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="J25">
         <v>17.99</v>
@@ -16218,13 +16233,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="O25">
         <v>35.47</v>
@@ -16233,7 +16248,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -16259,10 +16274,10 @@
         <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I26" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="J26">
         <v>17.99</v>
@@ -16271,13 +16286,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="O26">
         <v>33.25</v>
@@ -16286,7 +16301,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -16303,7 +16318,7 @@
         <v>175</v>
       </c>
       <c r="E27" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F27">
         <v>728</v>
@@ -16312,10 +16327,10 @@
         <v>1.2</v>
       </c>
       <c r="H27" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I27" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="J27">
         <v>35</v>
@@ -16324,13 +16339,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="O27">
         <v>41.94</v>
@@ -16339,7 +16354,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -16365,10 +16380,10 @@
         <v>2.29</v>
       </c>
       <c r="H28" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I28" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="J28">
         <v>17.99</v>
@@ -16377,13 +16392,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="O28">
         <v>41.11</v>
@@ -16392,7 +16407,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -16403,13 +16418,13 @@
         <v>1071</v>
       </c>
       <c r="C29" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D29" t="s">
         <v>175</v>
       </c>
       <c r="E29" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F29">
         <v>508</v>
@@ -16418,10 +16433,10 @@
         <v>0.52</v>
       </c>
       <c r="H29" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="I29" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="J29">
         <v>49.99</v>
@@ -16430,13 +16445,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="O29">
         <v>26.14</v>
@@ -16445,7 +16460,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -16459,7 +16474,7 @@
         <v>175</v>
       </c>
       <c r="E30" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F30">
         <v>759</v>
@@ -16468,10 +16483,10 @@
         <v>1.88</v>
       </c>
       <c r="H30" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I30" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="J30">
         <v>31.99</v>
@@ -16480,13 +16495,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="O30">
         <v>60</v>
@@ -16495,7 +16510,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -16512,7 +16527,7 @@
         <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F31">
         <v>568</v>
@@ -16521,10 +16536,10 @@
         <v>1.09</v>
       </c>
       <c r="H31" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I31" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="J31">
         <v>22.97</v>
@@ -16533,13 +16548,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="O31">
         <v>24.99</v>
@@ -16548,7 +16563,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -16565,7 +16580,7 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F32">
         <v>560</v>
@@ -16574,10 +16589,10 @@
         <v>1.56</v>
       </c>
       <c r="H32" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I32" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="J32">
         <v>20</v>
@@ -16586,13 +16601,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="O32">
         <v>31.2</v>
@@ -16601,7 +16616,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -16618,7 +16633,7 @@
         <v>176</v>
       </c>
       <c r="E33" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -16627,10 +16642,10 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I33" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J33">
         <v>550</v>
@@ -16639,13 +16654,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="O33">
         <v>700.51</v>
@@ -16654,7 +16669,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -16671,7 +16686,7 @@
         <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F34">
         <v>664</v>
@@ -16680,10 +16695,10 @@
         <v>1.5</v>
       </c>
       <c r="H34" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="I34" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="J34">
         <v>20</v>
@@ -16692,13 +16707,13 @@
         <v>425</v>
       </c>
       <c r="L34" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="O34">
         <v>29.98</v>
@@ -16707,7 +16722,7 @@
         <v>789</v>
       </c>
       <c r="Q34" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -16724,7 +16739,7 @@
         <v>176</v>
       </c>
       <c r="E35" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F35">
         <v>572</v>
@@ -16733,10 +16748,10 @@
         <v>0.88</v>
       </c>
       <c r="H35" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="I35" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="J35">
         <v>22.99</v>
@@ -16745,13 +16760,13 @@
         <v>425</v>
       </c>
       <c r="L35" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="O35">
         <v>20.23</v>
@@ -16760,7 +16775,7 @@
         <v>789</v>
       </c>
       <c r="Q35" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -16789,13 +16804,13 @@
         <v>425</v>
       </c>
       <c r="L36" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="O36">
         <v>198.33</v>
@@ -16804,7 +16819,7 @@
         <v>789</v>
       </c>
       <c r="Q36" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -16821,7 +16836,7 @@
         <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F37">
         <v>615</v>
@@ -16830,10 +16845,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="I37" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="J37">
         <v>22.97</v>
@@ -16842,13 +16857,13 @@
         <v>425</v>
       </c>
       <c r="L37" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="O37">
         <v>16.07</v>
@@ -16857,7 +16872,7 @@
         <v>789</v>
       </c>
       <c r="Q37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -16874,7 +16889,7 @@
         <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F38">
         <v>708</v>
@@ -16883,10 +16898,10 @@
         <v>1.85</v>
       </c>
       <c r="H38" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="I38" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J38">
         <v>20</v>
@@ -16895,13 +16910,13 @@
         <v>425</v>
       </c>
       <c r="L38" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="O38">
         <v>36.95</v>
@@ -16910,7 +16925,7 @@
         <v>789</v>
       </c>
       <c r="Q38" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -16927,7 +16942,7 @@
         <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -16936,10 +16951,10 @@
         <v>1.25</v>
       </c>
       <c r="H39" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I39" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="J39">
         <v>45</v>
@@ -16948,13 +16963,13 @@
         <v>425</v>
       </c>
       <c r="L39" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="O39">
         <v>56.07</v>
@@ -16963,7 +16978,7 @@
         <v>789</v>
       </c>
       <c r="Q39" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -16980,7 +16995,7 @@
         <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F40">
         <v>700</v>
@@ -16989,10 +17004,10 @@
         <v>2.24</v>
       </c>
       <c r="H40" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I40" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -17001,13 +17016,13 @@
         <v>425</v>
       </c>
       <c r="L40" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="O40">
         <v>53.81</v>
@@ -17016,7 +17031,7 @@
         <v>789</v>
       </c>
       <c r="Q40" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -17027,13 +17042,13 @@
         <v>1083</v>
       </c>
       <c r="C41" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -17042,7 +17057,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J41">
         <v>90</v>
@@ -17051,13 +17066,13 @@
         <v>425</v>
       </c>
       <c r="L41" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -17066,7 +17081,7 @@
         <v>789</v>
       </c>
       <c r="Q41" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -17077,13 +17092,13 @@
         <v>1084</v>
       </c>
       <c r="C42" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D42" t="s">
         <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -17092,10 +17107,10 @@
         <v>2.66</v>
       </c>
       <c r="H42" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I42" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -17104,13 +17119,13 @@
         <v>425</v>
       </c>
       <c r="L42" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="O42">
         <v>132.99</v>
@@ -17119,7 +17134,7 @@
         <v>789</v>
       </c>
       <c r="Q42" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -17136,7 +17151,7 @@
         <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -17145,10 +17160,10 @@
         <v>1.29</v>
       </c>
       <c r="H43" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="I43" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="J43">
         <v>64.98999999999999</v>
@@ -17157,13 +17172,13 @@
         <v>425</v>
       </c>
       <c r="L43" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="O43">
         <v>83.73</v>
@@ -17172,7 +17187,7 @@
         <v>789</v>
       </c>
       <c r="Q43" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -17189,7 +17204,7 @@
         <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -17204,13 +17219,13 @@
         <v>425</v>
       </c>
       <c r="L44" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="O44">
         <v>26.9</v>
@@ -17219,7 +17234,7 @@
         <v>789</v>
       </c>
       <c r="Q44" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -17236,7 +17251,7 @@
         <v>177</v>
       </c>
       <c r="E45" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -17251,13 +17266,13 @@
         <v>425</v>
       </c>
       <c r="L45" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="O45">
         <v>43.75</v>
@@ -17266,7 +17281,7 @@
         <v>789</v>
       </c>
       <c r="Q45" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -17289,7 +17304,7 @@
         <v>2.12</v>
       </c>
       <c r="I46" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="J46">
         <v>19.99</v>
@@ -17298,13 +17313,13 @@
         <v>425</v>
       </c>
       <c r="L46" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="O46">
         <v>42.3</v>
@@ -17313,7 +17328,7 @@
         <v>789</v>
       </c>
       <c r="Q46" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -17324,13 +17339,13 @@
         <v>1089</v>
       </c>
       <c r="C47" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D47" t="s">
         <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -17339,10 +17354,10 @@
         <v>0.87</v>
       </c>
       <c r="H47" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I47" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="J47">
         <v>20</v>
@@ -17351,13 +17366,13 @@
         <v>425</v>
       </c>
       <c r="L47" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="O47">
         <v>17.33</v>
@@ -17366,7 +17381,7 @@
         <v>789</v>
       </c>
       <c r="Q47" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -17377,13 +17392,13 @@
         <v>1090</v>
       </c>
       <c r="C48" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D48" t="s">
         <v>177</v>
       </c>
       <c r="E48" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -17392,7 +17407,7 @@
         <v>0.23</v>
       </c>
       <c r="I48" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="J48">
         <v>100</v>
@@ -17401,13 +17416,13 @@
         <v>425</v>
       </c>
       <c r="L48" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="O48">
         <v>22.95</v>
@@ -17416,7 +17431,7 @@
         <v>789</v>
       </c>
       <c r="Q48" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -17427,13 +17442,13 @@
         <v>1091</v>
       </c>
       <c r="C49" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D49" t="s">
         <v>177</v>
       </c>
       <c r="E49" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F49">
         <v>509</v>
@@ -17442,10 +17457,10 @@
         <v>0.49</v>
       </c>
       <c r="H49" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="I49" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="J49">
         <v>29.99</v>
@@ -17454,13 +17469,13 @@
         <v>425</v>
       </c>
       <c r="L49" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="O49">
         <v>14.81</v>
@@ -17469,7 +17484,7 @@
         <v>789</v>
       </c>
       <c r="Q49" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -17486,7 +17501,7 @@
         <v>177</v>
       </c>
       <c r="E50" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -17495,7 +17510,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="J50">
         <v>34.99</v>
@@ -17504,13 +17519,13 @@
         <v>425</v>
       </c>
       <c r="L50" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="O50">
         <v>28.41</v>
@@ -17519,7 +17534,7 @@
         <v>789</v>
       </c>
       <c r="Q50" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -17536,7 +17551,7 @@
         <v>177</v>
       </c>
       <c r="E51" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F51">
         <v>552</v>
@@ -17545,10 +17560,10 @@
         <v>0.93</v>
       </c>
       <c r="H51" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I51" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J51">
         <v>29.99</v>
@@ -17557,13 +17572,13 @@
         <v>425</v>
       </c>
       <c r="L51" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="O51">
         <v>27.99</v>
@@ -17572,7 +17587,7 @@
         <v>789</v>
       </c>
       <c r="Q51" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -17589,7 +17604,7 @@
         <v>177</v>
       </c>
       <c r="E52" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -17598,10 +17613,10 @@
         <v>1.06</v>
       </c>
       <c r="H52" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="I52" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="J52">
         <v>31.99</v>
@@ -17610,13 +17625,13 @@
         <v>425</v>
       </c>
       <c r="L52" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="O52">
         <v>34.04</v>
@@ -17625,7 +17640,7 @@
         <v>789</v>
       </c>
       <c r="Q52" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -17636,13 +17651,13 @@
         <v>1095</v>
       </c>
       <c r="C53" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D53" t="s">
         <v>177</v>
       </c>
       <c r="E53" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -17651,10 +17666,10 @@
         <v>0.92</v>
       </c>
       <c r="H53" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="I53" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="J53">
         <v>44.99</v>
@@ -17663,13 +17678,13 @@
         <v>425</v>
       </c>
       <c r="L53" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="O53">
         <v>41.52</v>
@@ -17678,7 +17693,7 @@
         <v>789</v>
       </c>
       <c r="Q53" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -17695,7 +17710,7 @@
         <v>177</v>
       </c>
       <c r="E54" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F54">
         <v>609</v>
@@ -17704,10 +17719,10 @@
         <v>1.17</v>
       </c>
       <c r="H54" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I54" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="J54">
         <v>20</v>
@@ -17716,13 +17731,13 @@
         <v>425</v>
       </c>
       <c r="L54" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="O54">
         <v>23.48</v>
@@ -17731,7 +17746,7 @@
         <v>789</v>
       </c>
       <c r="Q54" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -17748,7 +17763,7 @@
         <v>177</v>
       </c>
       <c r="E55" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -17757,10 +17772,10 @@
         <v>0.87</v>
       </c>
       <c r="H55" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="I55" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="J55">
         <v>29.99</v>
@@ -17769,13 +17784,13 @@
         <v>425</v>
       </c>
       <c r="L55" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="O55">
         <v>26.18</v>
@@ -17784,7 +17799,7 @@
         <v>789</v>
       </c>
       <c r="Q55" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -17801,7 +17816,7 @@
         <v>177</v>
       </c>
       <c r="E56" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -17810,10 +17825,10 @@
         <v>0.97</v>
       </c>
       <c r="H56" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="I56" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="J56">
         <v>69.98999999999999</v>
@@ -17822,13 +17837,13 @@
         <v>425</v>
       </c>
       <c r="L56" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="O56">
         <v>67.75</v>
@@ -17837,7 +17852,7 @@
         <v>789</v>
       </c>
       <c r="Q56" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -17848,7 +17863,7 @@
         <v>1099</v>
       </c>
       <c r="C57" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D57" t="s">
         <v>177</v>
@@ -17863,10 +17878,10 @@
         <v>0.87</v>
       </c>
       <c r="H57" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="I57" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="J57">
         <v>19.99</v>
@@ -17875,13 +17890,13 @@
         <v>425</v>
       </c>
       <c r="L57" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="O57">
         <v>17.42</v>
@@ -17890,7 +17905,7 @@
         <v>789</v>
       </c>
       <c r="Q57" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -17907,7 +17922,7 @@
         <v>177</v>
       </c>
       <c r="E58" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -17916,10 +17931,10 @@
         <v>1.1</v>
       </c>
       <c r="H58" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I58" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="J58">
         <v>20</v>
@@ -17928,13 +17943,13 @@
         <v>425</v>
       </c>
       <c r="L58" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="O58">
         <v>22</v>
@@ -17943,7 +17958,7 @@
         <v>789</v>
       </c>
       <c r="Q58" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -17975,13 +17990,13 @@
         <v>425</v>
       </c>
       <c r="L59" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="O59">
         <v>46.28</v>
@@ -17990,7 +18005,7 @@
         <v>789</v>
       </c>
       <c r="Q59" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -18007,7 +18022,7 @@
         <v>178</v>
       </c>
       <c r="E60" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -18022,13 +18037,13 @@
         <v>425</v>
       </c>
       <c r="L60" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="O60">
         <v>40.52</v>
@@ -18037,14 +18052,61 @@
         <v>789</v>
       </c>
       <c r="Q60" t="s">
-        <v>1453</v>
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" t="s">
+        <v>186</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>22</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L61" t="s">
+        <v>1281</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>1458</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A60">
+  <conditionalFormatting sqref="A3:A61">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -18053,7 +18115,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A61">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18174,6 +18236,9 @@
     <hyperlink ref="N59" r:id="rId114"/>
     <hyperlink ref="M60" r:id="rId115"/>
     <hyperlink ref="N60" r:id="rId116"/>
+    <hyperlink ref="K61" r:id="rId117"/>
+    <hyperlink ref="M61" r:id="rId118"/>
+    <hyperlink ref="N61" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18186,7 +18251,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18263,16 +18328,16 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1455</v>
+        <v>1460</v>
       </c>
       <c r="C3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D3" t="s">
         <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F3">
         <v>1047</v>
@@ -18281,7 +18346,7 @@
         <v>0.67</v>
       </c>
       <c r="I3" t="s">
-        <v>1498</v>
+        <v>1503</v>
       </c>
       <c r="J3">
         <v>49.99</v>
@@ -18290,13 +18355,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="O3">
         <v>33.33</v>
@@ -18305,7 +18370,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -18313,7 +18378,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1456</v>
+        <v>1461</v>
       </c>
       <c r="D4" t="s">
         <v>173</v>
@@ -18328,10 +18393,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" t="s">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="I4" t="s">
-        <v>1499</v>
+        <v>1504</v>
       </c>
       <c r="J4">
         <v>24.99</v>
@@ -18340,13 +18405,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="O4">
         <v>13.69</v>
@@ -18355,7 +18420,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -18363,13 +18428,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="D5" t="s">
         <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="F5">
         <v>1752</v>
@@ -18378,10 +18443,10 @@
         <v>1.21</v>
       </c>
       <c r="H5" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I5" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="J5">
         <v>74.98999999999999</v>
@@ -18390,13 +18455,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="O5">
         <v>90.84999999999999</v>
@@ -18405,7 +18470,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -18413,13 +18478,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="D6" t="s">
         <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F6">
         <v>1538</v>
@@ -18428,10 +18493,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="I6" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -18440,13 +18505,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1542</v>
+        <v>1547</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
       <c r="O6">
         <v>15.03</v>
@@ -18455,7 +18520,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -18463,7 +18528,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="D7" t="s">
         <v>173</v>
@@ -18478,10 +18543,10 @@
         <v>0.59</v>
       </c>
       <c r="H7" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="I7" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
       <c r="J7">
         <v>24.99</v>
@@ -18490,13 +18555,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="O7">
         <v>14.62</v>
@@ -18505,7 +18570,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -18513,7 +18578,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="C8" t="s">
         <v>163</v>
@@ -18522,7 +18587,7 @@
         <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F8">
         <v>1179</v>
@@ -18531,10 +18596,10 @@
         <v>0.54</v>
       </c>
       <c r="H8" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="I8" t="s">
-        <v>1503</v>
+        <v>1508</v>
       </c>
       <c r="J8">
         <v>39.99</v>
@@ -18543,13 +18608,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1544</v>
+        <v>1549</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="O8">
         <v>21.68</v>
@@ -18558,7 +18623,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -18566,13 +18631,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1461</v>
+        <v>1466</v>
       </c>
       <c r="D9" t="s">
         <v>173</v>
       </c>
       <c r="E9" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F9">
         <v>1805</v>
@@ -18581,10 +18646,10 @@
         <v>0.53</v>
       </c>
       <c r="H9" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="I9" t="s">
-        <v>1504</v>
+        <v>1509</v>
       </c>
       <c r="J9">
         <v>29.99</v>
@@ -18593,13 +18658,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="O9">
         <v>16</v>
@@ -18608,7 +18673,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -18616,13 +18681,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="D10" t="s">
         <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F10">
         <v>1571</v>
@@ -18631,10 +18696,10 @@
         <v>0.74</v>
       </c>
       <c r="H10" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="I10" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -18643,13 +18708,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="O10">
         <v>22.11</v>
@@ -18658,7 +18723,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -18666,13 +18731,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1463</v>
+        <v>1468</v>
       </c>
       <c r="D11" t="s">
         <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F11">
         <v>1159</v>
@@ -18681,10 +18746,10 @@
         <v>0.59</v>
       </c>
       <c r="H11" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="I11" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="J11">
         <v>29.99</v>
@@ -18693,13 +18758,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1547</v>
+        <v>1552</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
       <c r="O11">
         <v>17.83</v>
@@ -18708,7 +18773,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -18716,7 +18781,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D12" t="s">
         <v>174</v>
@@ -18731,10 +18796,10 @@
         <v>0.71</v>
       </c>
       <c r="H12" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="I12" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -18743,13 +18808,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1526</v>
+        <v>1531</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="O12">
         <v>17.77</v>
@@ -18758,7 +18823,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -18766,13 +18831,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D13" t="s">
         <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F13">
         <v>857</v>
@@ -18781,10 +18846,10 @@
         <v>1.31</v>
       </c>
       <c r="H13" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="I13" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="J13">
         <v>29.99</v>
@@ -18793,13 +18858,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1527</v>
+        <v>1532</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="O13">
         <v>39.37</v>
@@ -18808,7 +18873,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -18816,13 +18881,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="D14" t="s">
         <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F14">
         <v>1215</v>
@@ -18831,10 +18896,10 @@
         <v>0.75</v>
       </c>
       <c r="H14" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="I14" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
       <c r="J14">
         <v>29.99</v>
@@ -18843,13 +18908,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1528</v>
+        <v>1533</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="O14">
         <v>22.5</v>
@@ -18858,7 +18923,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -18866,13 +18931,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="D15" t="s">
         <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F15">
         <v>755</v>
@@ -18893,13 +18958,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="O15">
         <v>36.5</v>
@@ -18908,7 +18973,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -18916,13 +18981,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="D16" t="s">
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="F16">
         <v>888</v>
@@ -18931,10 +18996,10 @@
         <v>3.33</v>
       </c>
       <c r="H16" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="I16" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="J16">
         <v>79.98999999999999</v>
@@ -18943,13 +19008,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1530</v>
+        <v>1535</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="O16">
         <v>266.38</v>
@@ -18958,7 +19023,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -18966,13 +19031,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D17" t="s">
         <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F17">
         <v>1103</v>
@@ -18981,10 +19046,10 @@
         <v>0.42</v>
       </c>
       <c r="H17" t="s">
-        <v>1492</v>
+        <v>1497</v>
       </c>
       <c r="I17" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="J17">
         <v>44.99</v>
@@ -18993,13 +19058,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="O17">
         <v>18.76</v>
@@ -19008,7 +19073,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -19016,13 +19081,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1470</v>
+        <v>1475</v>
       </c>
       <c r="D18" t="s">
         <v>176</v>
       </c>
       <c r="E18" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F18">
         <v>520</v>
@@ -19031,10 +19096,10 @@
         <v>0.85</v>
       </c>
       <c r="H18" t="s">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="I18" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
       <c r="J18">
         <v>39.99</v>
@@ -19043,13 +19108,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="O18">
         <v>33.99</v>
@@ -19058,7 +19123,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -19066,7 +19131,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="C19" t="s">
         <v>164</v>
@@ -19087,13 +19152,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="O19">
         <v>180</v>
@@ -19102,7 +19167,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -19110,7 +19175,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="C20" t="s">
         <v>164</v>
@@ -19119,7 +19184,7 @@
         <v>176</v>
       </c>
       <c r="E20" t="s">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -19128,10 +19193,10 @@
         <v>1.12</v>
       </c>
       <c r="H20" t="s">
-        <v>1494</v>
+        <v>1499</v>
       </c>
       <c r="I20" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
       <c r="J20">
         <v>33</v>
@@ -19140,13 +19205,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="O20">
         <v>37.07</v>
@@ -19155,7 +19220,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -19163,13 +19228,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1473</v>
+        <v>1478</v>
       </c>
       <c r="D21" t="s">
         <v>176</v>
       </c>
       <c r="E21" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F21">
         <v>799</v>
@@ -19178,10 +19243,10 @@
         <v>0.89</v>
       </c>
       <c r="H21" t="s">
-        <v>1495</v>
+        <v>1500</v>
       </c>
       <c r="I21" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -19190,13 +19255,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="O21">
         <v>26.75</v>
@@ -19205,7 +19270,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -19213,13 +19278,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D22" t="s">
         <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -19228,10 +19293,10 @@
         <v>1.38</v>
       </c>
       <c r="H22" t="s">
-        <v>1496</v>
+        <v>1501</v>
       </c>
       <c r="I22" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="J22">
         <v>91.98999999999999</v>
@@ -19240,13 +19305,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
       <c r="O22">
         <v>126.79</v>
@@ -19255,7 +19320,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -19263,13 +19328,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D23" t="s">
         <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -19278,10 +19343,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>1497</v>
+        <v>1502</v>
       </c>
       <c r="I23" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
       <c r="J23">
         <v>124.99</v>
@@ -19290,13 +19355,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -19305,7 +19370,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -19313,7 +19378,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="C24" t="s">
         <v>164</v>
@@ -19322,7 +19387,7 @@
         <v>178</v>
       </c>
       <c r="E24" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -19337,13 +19402,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
       <c r="O24">
         <v>499.99</v>
@@ -19352,7 +19417,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
     </row>
   </sheetData>
@@ -19429,7 +19494,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19506,16 +19571,16 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
       <c r="C3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D3" t="s">
         <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -19524,7 +19589,7 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="J3">
         <v>34.99</v>
@@ -19533,13 +19598,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="O3">
         <v>36.09</v>
@@ -19548,7 +19613,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19556,16 +19621,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="C4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D4" t="s">
         <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -19574,7 +19639,7 @@
         <v>0.64</v>
       </c>
       <c r="I4" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="J4">
         <v>34.99</v>
@@ -19583,13 +19648,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="O4">
         <v>22.55</v>
@@ -19598,7 +19663,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19606,16 +19671,16 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="C5" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -19624,7 +19689,7 @@
         <v>1.36</v>
       </c>
       <c r="I5" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="J5">
         <v>34.99</v>
@@ -19633,13 +19698,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="O5">
         <v>47.57</v>
@@ -19648,7 +19713,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
     </row>
   </sheetData>
@@ -19687,7 +19752,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19764,7 +19829,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="C3" t="s">
         <v>163</v>
@@ -19782,10 +19847,10 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="I3" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="J3">
         <v>24.99</v>
@@ -19794,13 +19859,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="O3">
         <v>30.44</v>
@@ -19809,7 +19874,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1831</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19817,7 +19882,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="C4" t="s">
         <v>163</v>
@@ -19826,7 +19891,7 @@
         <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -19835,10 +19900,10 @@
         <v>0.52</v>
       </c>
       <c r="H4" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="I4" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
       <c r="J4">
         <v>24.97</v>
@@ -19847,13 +19912,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="O4">
         <v>12.96</v>
@@ -19862,7 +19927,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19870,10 +19935,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D5" t="s">
         <v>176</v>
@@ -19891,13 +19956,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="O5">
         <v>48.73</v>
@@ -19906,7 +19971,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19914,10 +19979,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
       <c r="C6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D6" t="s">
         <v>176</v>
@@ -19932,10 +19997,10 @@
         <v>0.92</v>
       </c>
       <c r="H6" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="I6" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="J6">
         <v>24.99</v>
@@ -19944,13 +20009,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -19959,7 +20024,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1834</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -19967,7 +20032,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="C7" t="s">
         <v>163</v>
@@ -19976,7 +20041,7 @@
         <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -19985,10 +20050,10 @@
         <v>0.82</v>
       </c>
       <c r="H7" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="I7" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="J7">
         <v>24.97</v>
@@ -19997,13 +20062,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="O7">
         <v>20.41</v>
@@ -20012,7 +20077,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1835</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -20020,7 +20085,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="C8" t="s">
         <v>163</v>
@@ -20044,13 +20109,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1728</v>
+        <v>1733</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="O8">
         <v>37.99</v>
@@ -20059,7 +20124,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1836</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -20067,10 +20132,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="C9" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D9" t="s">
         <v>176</v>
@@ -20085,10 +20150,10 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="I9" t="s">
-        <v>1693</v>
+        <v>1698</v>
       </c>
       <c r="J9">
         <v>24.99</v>
@@ -20097,13 +20162,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1729</v>
+        <v>1734</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="O9">
         <v>37.71</v>
@@ -20112,7 +20177,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1837</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -20120,10 +20185,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="C10" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D10" t="s">
         <v>176</v>
@@ -20138,10 +20203,10 @@
         <v>0.78</v>
       </c>
       <c r="H10" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="I10" t="s">
-        <v>1694</v>
+        <v>1699</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -20150,13 +20215,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1730</v>
+        <v>1735</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="O10">
         <v>19.54</v>
@@ -20165,7 +20230,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1838</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -20173,7 +20238,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -20191,10 +20256,10 @@
         <v>0.82</v>
       </c>
       <c r="H11" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="I11" t="s">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -20203,13 +20268,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="O11">
         <v>16.43</v>
@@ -20218,7 +20283,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1839</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -20226,7 +20291,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="C12" t="s">
         <v>141</v>
@@ -20244,10 +20309,10 @@
         <v>1.61</v>
       </c>
       <c r="H12" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="I12" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -20256,13 +20321,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1732</v>
+        <v>1737</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="O12">
         <v>32.14</v>
@@ -20271,7 +20336,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1840</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -20279,7 +20344,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="C13" t="s">
         <v>141</v>
@@ -20297,10 +20362,10 @@
         <v>0.71</v>
       </c>
       <c r="H13" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="I13" t="s">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -20309,13 +20374,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>1733</v>
+        <v>1738</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="O13">
         <v>14.27</v>
@@ -20324,7 +20389,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>1841</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -20332,7 +20397,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="C14" t="s">
         <v>141</v>
@@ -20350,10 +20415,10 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="I14" t="s">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -20362,13 +20427,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>1734</v>
+        <v>1739</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="O14">
         <v>23.5</v>
@@ -20377,7 +20442,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>1842</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -20403,10 +20468,10 @@
         <v>0.65</v>
       </c>
       <c r="H15" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
       <c r="I15" t="s">
-        <v>1699</v>
+        <v>1704</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -20415,13 +20480,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>1735</v>
+        <v>1740</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="O15">
         <v>12.92</v>
@@ -20430,7 +20495,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -20438,7 +20503,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -20456,10 +20521,10 @@
         <v>0.78</v>
       </c>
       <c r="H16" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="I16" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -20468,13 +20533,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>1736</v>
+        <v>1741</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="O16">
         <v>15.59</v>
@@ -20483,7 +20548,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -20491,7 +20556,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -20509,10 +20574,10 @@
         <v>2.22</v>
       </c>
       <c r="H17" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="I17" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -20521,13 +20586,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>1737</v>
+        <v>1742</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="O17">
         <v>44.34</v>
@@ -20536,7 +20601,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>1845</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -20544,7 +20609,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -20562,10 +20627,10 @@
         <v>2.09</v>
       </c>
       <c r="H18" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="I18" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -20574,13 +20639,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>1738</v>
+        <v>1743</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="O18">
         <v>41.71</v>
@@ -20589,7 +20654,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>1846</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -20597,7 +20662,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="C19" t="s">
         <v>143</v>
@@ -20615,10 +20680,10 @@
         <v>0.72</v>
       </c>
       <c r="H19" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="I19" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -20627,13 +20692,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>1739</v>
+        <v>1744</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="O19">
         <v>14.3</v>
@@ -20642,7 +20707,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>1847</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -20650,7 +20715,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -20668,10 +20733,10 @@
         <v>0.8</v>
       </c>
       <c r="H20" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="I20" t="s">
-        <v>1704</v>
+        <v>1709</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -20680,13 +20745,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>1740</v>
+        <v>1745</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="O20">
         <v>15.98</v>
@@ -20695,7 +20760,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>1848</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -20721,10 +20786,10 @@
         <v>0.9</v>
       </c>
       <c r="H21" t="s">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="I21" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -20733,13 +20798,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>1741</v>
+        <v>1746</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="O21">
         <v>17.92</v>
@@ -20748,7 +20813,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -20774,10 +20839,10 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="I22" t="s">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -20786,13 +20851,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>1742</v>
+        <v>1747</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="O22">
         <v>10.03</v>
@@ -20801,7 +20866,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>1850</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -20809,7 +20874,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -20827,10 +20892,10 @@
         <v>0.89</v>
       </c>
       <c r="H23" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="I23" t="s">
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -20839,13 +20904,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>1743</v>
+        <v>1748</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="O23">
         <v>17.83</v>
@@ -20854,7 +20919,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>1851</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -20862,7 +20927,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -20880,10 +20945,10 @@
         <v>0.72</v>
       </c>
       <c r="H24" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
       <c r="I24" t="s">
-        <v>1708</v>
+        <v>1713</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -20892,13 +20957,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>1744</v>
+        <v>1749</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="O24">
         <v>14.35</v>
@@ -20907,7 +20972,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>1852</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -20933,10 +20998,10 @@
         <v>0.73</v>
       </c>
       <c r="H25" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="I25" t="s">
-        <v>1709</v>
+        <v>1714</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -20945,13 +21010,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="O25">
         <v>14.69</v>
@@ -20960,7 +21025,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>1853</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -20986,7 +21051,7 @@
         <v>7.29</v>
       </c>
       <c r="I26" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -20995,13 +21060,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="O26">
         <v>145.79</v>
@@ -21010,7 +21075,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>1854</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -21018,7 +21083,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -21036,10 +21101,10 @@
         <v>0.88</v>
       </c>
       <c r="H27" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="I27" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -21048,13 +21113,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="O27">
         <v>17.58</v>
@@ -21063,7 +21128,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>1855</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -21071,7 +21136,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -21089,10 +21154,10 @@
         <v>0.82</v>
       </c>
       <c r="H28" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="I28" t="s">
-        <v>1712</v>
+        <v>1717</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -21101,13 +21166,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="O28">
         <v>16.46</v>
@@ -21116,7 +21181,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>1856</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -21124,7 +21189,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="C29" t="s">
         <v>145</v>
@@ -21133,7 +21198,7 @@
         <v>176</v>
       </c>
       <c r="E29" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -21142,10 +21207,10 @@
         <v>0.96</v>
       </c>
       <c r="H29" t="s">
-        <v>1679</v>
+        <v>1684</v>
       </c>
       <c r="I29" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="J29">
         <v>20.99</v>
@@ -21154,13 +21219,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>1749</v>
+        <v>1754</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="O29">
         <v>20.09</v>
@@ -21169,7 +21234,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>1857</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -21177,7 +21242,7 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="C30" t="s">
         <v>145</v>
@@ -21186,7 +21251,7 @@
         <v>176</v>
       </c>
       <c r="E30" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -21195,10 +21260,10 @@
         <v>0.83</v>
       </c>
       <c r="H30" t="s">
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="I30" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="J30">
         <v>20.99</v>
@@ -21207,13 +21272,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>1750</v>
+        <v>1755</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="O30">
         <v>17.33</v>
@@ -21222,7 +21287,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>1858</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -21230,7 +21295,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="C31" t="s">
         <v>145</v>
@@ -21239,7 +21304,7 @@
         <v>176</v>
       </c>
       <c r="E31" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -21248,10 +21313,10 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="I31" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="J31">
         <v>20.99</v>
@@ -21260,13 +21325,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>1751</v>
+        <v>1756</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="O31">
         <v>15.75</v>
@@ -21275,7 +21340,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>1859</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -21292,7 +21357,7 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -21301,10 +21366,10 @@
         <v>0.84</v>
       </c>
       <c r="H32" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="I32" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="J32">
         <v>20.99</v>
@@ -21313,13 +21378,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>1752</v>
+        <v>1757</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1824</v>
+        <v>1829</v>
       </c>
       <c r="O32">
         <v>17.65</v>
@@ -21328,7 +21393,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -21336,7 +21401,7 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="C33" t="s">
         <v>146</v>
@@ -21354,10 +21419,10 @@
         <v>0.76</v>
       </c>
       <c r="H33" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="I33" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="J33">
         <v>23.99</v>
@@ -21366,13 +21431,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1825</v>
+        <v>1830</v>
       </c>
       <c r="O33">
         <v>18.33</v>
@@ -21381,7 +21446,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>1861</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -21389,7 +21454,7 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="C34" t="s">
         <v>146</v>
@@ -21407,10 +21472,10 @@
         <v>0.86</v>
       </c>
       <c r="H34" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="I34" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="J34">
         <v>23.99</v>
@@ -21419,13 +21484,13 @@
         <v>425</v>
       </c>
       <c r="L34" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1826</v>
+        <v>1831</v>
       </c>
       <c r="O34">
         <v>20.58</v>
@@ -21434,7 +21499,7 @@
         <v>789</v>
       </c>
       <c r="Q34" t="s">
-        <v>1862</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -21442,7 +21507,7 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="C35" t="s">
         <v>146</v>
@@ -21460,10 +21525,10 @@
         <v>0.64</v>
       </c>
       <c r="H35" t="s">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="I35" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="J35">
         <v>23.99</v>
@@ -21472,13 +21537,13 @@
         <v>425</v>
       </c>
       <c r="L35" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1827</v>
+        <v>1832</v>
       </c>
       <c r="O35">
         <v>15.31</v>
@@ -21487,7 +21552,7 @@
         <v>789</v>
       </c>
       <c r="Q35" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -21513,10 +21578,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H36" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="I36" t="s">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="J36">
         <v>23.99</v>
@@ -21525,13 +21590,13 @@
         <v>425</v>
       </c>
       <c r="L36" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1792</v>
+        <v>1797</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="O36">
         <v>19.5</v>
@@ -21540,7 +21605,7 @@
         <v>789</v>
       </c>
       <c r="Q36" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -21548,16 +21613,16 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="C37" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
       </c>
       <c r="E37" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -21566,10 +21631,10 @@
         <v>0.99</v>
       </c>
       <c r="H37" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="I37" t="s">
-        <v>1721</v>
+        <v>1726</v>
       </c>
       <c r="J37">
         <v>45</v>
@@ -21578,13 +21643,13 @@
         <v>425</v>
       </c>
       <c r="L37" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1829</v>
+        <v>1834</v>
       </c>
       <c r="O37">
         <v>44.69</v>
@@ -21593,7 +21658,7 @@
         <v>789</v>
       </c>
       <c r="Q37" t="s">
-        <v>1865</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -21601,7 +21666,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="C38" t="s">
         <v>163</v>
@@ -21610,7 +21675,7 @@
         <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -21619,10 +21684,10 @@
         <v>0.78</v>
       </c>
       <c r="H38" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="I38" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="J38">
         <v>24.97</v>
@@ -21631,13 +21696,13 @@
         <v>425</v>
       </c>
       <c r="L38" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1830</v>
+        <v>1835</v>
       </c>
       <c r="O38">
         <v>19.45</v>
@@ -21646,7 +21711,7 @@
         <v>789</v>
       </c>
       <c r="Q38" t="s">
-        <v>1866</v>
+        <v>1871</v>
       </c>
     </row>
   </sheetData>
@@ -21751,7 +21816,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21828,7 +21893,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="C3" t="s">
         <v>141</v>
@@ -21846,10 +21911,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="s">
-        <v>1877</v>
+        <v>1882</v>
       </c>
       <c r="I3" t="s">
-        <v>1885</v>
+        <v>1890</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -21858,13 +21923,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1902</v>
+        <v>1907</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1912</v>
+        <v>1917</v>
       </c>
       <c r="O3">
         <v>23.26</v>
@@ -21873,7 +21938,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1922</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21881,7 +21946,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1869</v>
+        <v>1874</v>
       </c>
       <c r="C4" t="s">
         <v>141</v>
@@ -21899,10 +21964,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="I4" t="s">
-        <v>1886</v>
+        <v>1891</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -21911,13 +21976,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1903</v>
+        <v>1908</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1913</v>
+        <v>1918</v>
       </c>
       <c r="O4">
         <v>16.41</v>
@@ -21926,7 +21991,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1923</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -21934,7 +21999,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="C5" t="s">
         <v>141</v>
@@ -21952,10 +22017,10 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="s">
-        <v>1879</v>
+        <v>1884</v>
       </c>
       <c r="I5" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -21964,13 +22029,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1894</v>
+        <v>1899</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1904</v>
+        <v>1909</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1914</v>
+        <v>1919</v>
       </c>
       <c r="O5">
         <v>23.79</v>
@@ -21979,7 +22044,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1924</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -21987,7 +22052,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1871</v>
+        <v>1876</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
@@ -21996,7 +22061,7 @@
         <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -22005,10 +22070,10 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="s">
-        <v>1880</v>
+        <v>1885</v>
       </c>
       <c r="I6" t="s">
-        <v>1888</v>
+        <v>1893</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -22017,13 +22082,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1895</v>
+        <v>1900</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1905</v>
+        <v>1910</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1915</v>
+        <v>1920</v>
       </c>
       <c r="O6">
         <v>23.94</v>
@@ -22032,7 +22097,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1925</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -22058,7 +22123,7 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>1881</v>
+        <v>1886</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -22067,13 +22132,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>1896</v>
+        <v>1901</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1906</v>
+        <v>1911</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1916</v>
+        <v>1921</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -22082,7 +22147,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>1926</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -22090,7 +22155,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -22108,7 +22173,7 @@
         <v>1.52</v>
       </c>
       <c r="H8" t="s">
-        <v>1882</v>
+        <v>1887</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -22117,13 +22182,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>1897</v>
+        <v>1902</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1907</v>
+        <v>1912</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1917</v>
+        <v>1922</v>
       </c>
       <c r="O8">
         <v>30.47</v>
@@ -22132,7 +22197,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>1927</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -22140,7 +22205,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1873</v>
+        <v>1878</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
@@ -22158,7 +22223,7 @@
         <v>1.02</v>
       </c>
       <c r="H9" t="s">
-        <v>1883</v>
+        <v>1888</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -22167,13 +22232,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>1898</v>
+        <v>1903</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1908</v>
+        <v>1913</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1918</v>
+        <v>1923</v>
       </c>
       <c r="O9">
         <v>20.39</v>
@@ -22182,7 +22247,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>1928</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -22190,7 +22255,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1874</v>
+        <v>1879</v>
       </c>
       <c r="C10" t="s">
         <v>143</v>
@@ -22208,7 +22273,7 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="s">
-        <v>1889</v>
+        <v>1894</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -22217,13 +22282,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>1899</v>
+        <v>1904</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1909</v>
+        <v>1914</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1919</v>
+        <v>1924</v>
       </c>
       <c r="O10">
         <v>29.95</v>
@@ -22232,7 +22297,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>1929</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -22240,7 +22305,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="C11" t="s">
         <v>143</v>
@@ -22258,7 +22323,7 @@
         <v>1.2</v>
       </c>
       <c r="I11" t="s">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="J11">
         <v>24.99</v>
@@ -22267,13 +22332,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1910</v>
+        <v>1915</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1920</v>
+        <v>1925</v>
       </c>
       <c r="O11">
         <v>29.95</v>
@@ -22282,7 +22347,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>1930</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -22290,7 +22355,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1876</v>
+        <v>1881</v>
       </c>
       <c r="C12" t="s">
         <v>143</v>
@@ -22308,10 +22373,10 @@
         <v>1.29</v>
       </c>
       <c r="H12" t="s">
-        <v>1884</v>
+        <v>1889</v>
       </c>
       <c r="I12" t="s">
-        <v>1891</v>
+        <v>1896</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -22320,13 +22385,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1911</v>
+        <v>1916</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1921</v>
+        <v>1926</v>
       </c>
       <c r="O12">
         <v>32.18</v>
@@ -22335,7 +22400,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>1931</v>
+        <v>1936</v>
       </c>
     </row>
   </sheetData>
@@ -22390,7 +22455,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1932</v>
+        <v>1937</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22467,16 +22532,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1933</v>
+        <v>1938</v>
       </c>
       <c r="C3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D3" t="s">
         <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>1937</v>
+        <v>1942</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -22485,10 +22550,10 @@
         <v>0.65</v>
       </c>
       <c r="H3" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="I3" t="s">
-        <v>1942</v>
+        <v>1947</v>
       </c>
       <c r="J3">
         <v>32.99</v>
@@ -22497,13 +22562,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="O3">
         <v>21.34</v>
@@ -22512,7 +22577,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>1958</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22520,16 +22585,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1934</v>
+        <v>1939</v>
       </c>
       <c r="C4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D4" t="s">
         <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>1937</v>
+        <v>1942</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -22538,10 +22603,10 @@
         <v>0.68</v>
       </c>
       <c r="H4" t="s">
-        <v>1939</v>
+        <v>1944</v>
       </c>
       <c r="I4" t="s">
-        <v>1943</v>
+        <v>1948</v>
       </c>
       <c r="J4">
         <v>32.99</v>
@@ -22550,13 +22615,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="O4">
         <v>22.3</v>
@@ -22565,7 +22630,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>1959</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22573,16 +22638,16 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="C5" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -22591,10 +22656,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="s">
-        <v>1940</v>
+        <v>1945</v>
       </c>
       <c r="I5" t="s">
-        <v>1944</v>
+        <v>1949</v>
       </c>
       <c r="J5">
         <v>29.99</v>
@@ -22603,13 +22668,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="O5">
         <v>46.29</v>
@@ -22618,7 +22683,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>1960</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22626,16 +22691,16 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1936</v>
+        <v>1941</v>
       </c>
       <c r="C6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D6" t="s">
         <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -22644,10 +22709,10 @@
         <v>1.37</v>
       </c>
       <c r="H6" t="s">
-        <v>1941</v>
+        <v>1946</v>
       </c>
       <c r="I6" t="s">
-        <v>1945</v>
+        <v>1950</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -22656,13 +22721,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="O6">
         <v>41.15</v>
@@ -22671,7 +22736,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>1961</v>
+        <v>1966</v>
       </c>
     </row>
   </sheetData>
@@ -22712,7 +22777,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22789,13 +22854,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="C3" t="s">
         <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E3" t="s">
         <v>181</v>
@@ -22807,10 +22872,10 @@
         <v>0.99</v>
       </c>
       <c r="H3" t="s">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="I3" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -22819,13 +22884,13 @@
         <v>425</v>
       </c>
       <c r="L3" t="s">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2106</v>
+        <v>2111</v>
       </c>
       <c r="O3">
         <v>19.84</v>
@@ -22834,7 +22899,7 @@
         <v>789</v>
       </c>
       <c r="Q3" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22842,13 +22907,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="C4" t="s">
         <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E4" t="s">
         <v>181</v>
@@ -22860,7 +22925,7 @@
         <v>1.42</v>
       </c>
       <c r="I4" t="s">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -22869,13 +22934,13 @@
         <v>425</v>
       </c>
       <c r="L4" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2107</v>
+        <v>2112</v>
       </c>
       <c r="O4">
         <v>28.43</v>
@@ -22884,7 +22949,7 @@
         <v>789</v>
       </c>
       <c r="Q4" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22892,13 +22957,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="C5" t="s">
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E5" t="s">
         <v>181</v>
@@ -22910,10 +22975,10 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="s">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="I5" t="s">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -22922,13 +22987,13 @@
         <v>425</v>
       </c>
       <c r="L5" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2077</v>
+        <v>2082</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2108</v>
+        <v>2113</v>
       </c>
       <c r="O5">
         <v>24.47</v>
@@ -22937,7 +23002,7 @@
         <v>789</v>
       </c>
       <c r="Q5" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22945,13 +23010,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E6" t="s">
         <v>181</v>
@@ -22963,10 +23028,10 @@
         <v>0.86</v>
       </c>
       <c r="H6" t="s">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="I6" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -22975,13 +23040,13 @@
         <v>425</v>
       </c>
       <c r="L6" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2109</v>
+        <v>2114</v>
       </c>
       <c r="O6">
         <v>17.15</v>
@@ -22990,7 +23055,7 @@
         <v>789</v>
       </c>
       <c r="Q6" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -22998,7 +23063,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="C7" t="s">
         <v>142</v>
@@ -23016,7 +23081,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="s">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -23025,13 +23090,13 @@
         <v>425</v>
       </c>
       <c r="L7" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2110</v>
+        <v>2115</v>
       </c>
       <c r="O7">
         <v>14.49</v>
@@ -23040,7 +23105,7 @@
         <v>789</v>
       </c>
       <c r="Q7" t="s">
-        <v>2141</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -23048,7 +23113,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1968</v>
+        <v>1973</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -23066,10 +23131,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="I8" t="s">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -23078,13 +23143,13 @@
         <v>425</v>
       </c>
       <c r="L8" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>2111</v>
+        <v>2116</v>
       </c>
       <c r="O8">
         <v>16.25</v>
@@ -23093,7 +23158,7 @@
         <v>789</v>
       </c>
       <c r="Q8" t="s">
-        <v>2142</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -23101,7 +23166,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
@@ -23119,10 +23184,10 @@
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="I9" t="s">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -23131,13 +23196,13 @@
         <v>425</v>
       </c>
       <c r="L9" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -23146,7 +23211,7 @@
         <v>789</v>
       </c>
       <c r="Q9" t="s">
-        <v>2143</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -23154,7 +23219,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="C10" t="s">
         <v>142</v>
@@ -23172,10 +23237,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="I10" t="s">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="J10">
         <v>19.99</v>
@@ -23184,13 +23249,13 @@
         <v>425</v>
       </c>
       <c r="L10" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>2082</v>
+        <v>2087</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
       <c r="O10">
         <v>13.8</v>
@@ -23199,7 +23264,7 @@
         <v>789</v>
       </c>
       <c r="Q10" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -23207,7 +23272,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="C11" t="s">
         <v>143</v>
@@ -23225,7 +23290,7 @@
         <v>0.82</v>
       </c>
       <c r="I11" t="s">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -23234,13 +23299,13 @@
         <v>425</v>
       </c>
       <c r="L11" t="s">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>2083</v>
+        <v>2088</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="O11">
         <v>16.49</v>
@@ -23249,7 +23314,7 @@
         <v>789</v>
       </c>
       <c r="Q11" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -23257,7 +23322,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="C12" t="s">
         <v>143</v>
@@ -23275,7 +23340,7 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -23284,13 +23349,13 @@
         <v>425</v>
       </c>
       <c r="L12" t="s">
-        <v>2053</v>
+        <v>2058</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>2084</v>
+        <v>2089</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="O12">
         <v>21.34</v>
@@ -23299,7 +23364,7 @@
         <v>789</v>
       </c>
       <c r="Q12" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -23307,7 +23372,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="C13" t="s">
         <v>143</v>
@@ -23325,10 +23390,10 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="I13" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -23337,13 +23402,13 @@
         <v>425</v>
       </c>
       <c r="L13" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>2085</v>
+        <v>2090</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="O13">
         <v>35</v>
@@ -23352,7 +23417,7 @@
         <v>789</v>
       </c>
       <c r="Q13" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -23360,7 +23425,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="C14" t="s">
         <v>143</v>
@@ -23378,7 +23443,7 @@
         <v>2.38</v>
       </c>
       <c r="I14" t="s">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -23387,13 +23452,13 @@
         <v>425</v>
       </c>
       <c r="L14" t="s">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="O14">
         <v>47.66</v>
@@ -23402,7 +23467,7 @@
         <v>789</v>
       </c>
       <c r="Q14" t="s">
-        <v>2148</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -23410,7 +23475,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="C15" t="s">
         <v>144</v>
@@ -23428,10 +23493,10 @@
         <v>2.09</v>
       </c>
       <c r="H15" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="I15" t="s">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -23440,13 +23505,13 @@
         <v>425</v>
       </c>
       <c r="L15" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>2087</v>
+        <v>2092</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="O15">
         <v>41.68</v>
@@ -23455,7 +23520,7 @@
         <v>789</v>
       </c>
       <c r="Q15" t="s">
-        <v>2149</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -23463,7 +23528,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="C16" t="s">
         <v>144</v>
@@ -23481,10 +23546,10 @@
         <v>1.82</v>
       </c>
       <c r="H16" t="s">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="I16" t="s">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -23493,13 +23558,13 @@
         <v>425</v>
       </c>
       <c r="L16" t="s">
-        <v>2057</v>
+        <v>2062</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>2088</v>
+        <v>2093</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="O16">
         <v>36.31</v>
@@ -23508,7 +23573,7 @@
         <v>789</v>
       </c>
       <c r="Q16" t="s">
-        <v>2150</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -23516,7 +23581,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="C17" t="s">
         <v>144</v>
@@ -23534,7 +23599,7 @@
         <v>0.77</v>
       </c>
       <c r="I17" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -23543,13 +23608,13 @@
         <v>425</v>
       </c>
       <c r="L17" t="s">
-        <v>2058</v>
+        <v>2063</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="O17">
         <v>15.49</v>
@@ -23558,7 +23623,7 @@
         <v>789</v>
       </c>
       <c r="Q17" t="s">
-        <v>2151</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -23566,7 +23631,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="C18" t="s">
         <v>144</v>
@@ -23584,7 +23649,7 @@
         <v>1.84</v>
       </c>
       <c r="I18" t="s">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -23593,13 +23658,13 @@
         <v>425</v>
       </c>
       <c r="L18" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>2121</v>
+        <v>2126</v>
       </c>
       <c r="O18">
         <v>36.87</v>
@@ -23608,7 +23673,7 @@
         <v>789</v>
       </c>
       <c r="Q18" t="s">
-        <v>2152</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -23616,7 +23681,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="C19" t="s">
         <v>145</v>
@@ -23634,10 +23699,10 @@
         <v>0.59</v>
       </c>
       <c r="H19" t="s">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="I19" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -23646,13 +23711,13 @@
         <v>425</v>
       </c>
       <c r="L19" t="s">
-        <v>2060</v>
+        <v>2065</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>2091</v>
+        <v>2096</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>2122</v>
+        <v>2127</v>
       </c>
       <c r="O19">
         <v>11.86</v>
@@ -23661,7 +23726,7 @@
         <v>789</v>
       </c>
       <c r="Q19" t="s">
-        <v>2153</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -23669,7 +23734,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="C20" t="s">
         <v>145</v>
@@ -23687,7 +23752,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" t="s">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -23696,13 +23761,13 @@
         <v>425</v>
       </c>
       <c r="L20" t="s">
-        <v>2061</v>
+        <v>2066</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>2092</v>
+        <v>2097</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="O20">
         <v>12.35</v>
@@ -23711,7 +23776,7 @@
         <v>789</v>
       </c>
       <c r="Q20" t="s">
-        <v>2154</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -23719,7 +23784,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="C21" t="s">
         <v>145</v>
@@ -23737,10 +23802,10 @@
         <v>0.44</v>
       </c>
       <c r="H21" t="s">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="I21" t="s">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -23749,13 +23814,13 @@
         <v>425</v>
       </c>
       <c r="L21" t="s">
-        <v>2062</v>
+        <v>2067</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="O21">
         <v>8.81</v>
@@ -23764,7 +23829,7 @@
         <v>789</v>
       </c>
       <c r="Q21" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -23772,7 +23837,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="C22" t="s">
         <v>145</v>
@@ -23790,7 +23855,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -23799,13 +23864,13 @@
         <v>425</v>
       </c>
       <c r="L22" t="s">
-        <v>2063</v>
+        <v>2068</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>2094</v>
+        <v>2099</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="O22">
         <v>11.2</v>
@@ -23814,7 +23879,7 @@
         <v>789</v>
       </c>
       <c r="Q22" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -23822,7 +23887,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1983</v>
+        <v>1988</v>
       </c>
       <c r="C23" t="s">
         <v>146</v>
@@ -23840,10 +23905,10 @@
         <v>0.61</v>
       </c>
       <c r="H23" t="s">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="I23" t="s">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -23852,13 +23917,13 @@
         <v>425</v>
       </c>
       <c r="L23" t="s">
-        <v>2064</v>
+        <v>2069</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="O23">
         <v>12.25</v>
@@ -23867,7 +23932,7 @@
         <v>789</v>
       </c>
       <c r="Q23" t="s">
-        <v>2157</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -23875,7 +23940,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="C24" t="s">
         <v>146</v>
@@ -23893,10 +23958,10 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="I24" t="s">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -23905,13 +23970,13 @@
         <v>425</v>
       </c>
       <c r="L24" t="s">
-        <v>2065</v>
+        <v>2070</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2096</v>
+        <v>2101</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2127</v>
+        <v>2132</v>
       </c>
       <c r="O24">
         <v>10.89</v>
@@ -23920,7 +23985,7 @@
         <v>789</v>
       </c>
       <c r="Q24" t="s">
-        <v>2158</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -23928,7 +23993,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>1985</v>
+        <v>1990</v>
       </c>
       <c r="C25" t="s">
         <v>146</v>
@@ -23946,10 +24011,10 @@
         <v>0.38</v>
       </c>
       <c r="H25" t="s">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="I25" t="s">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -23958,13 +24023,13 @@
         <v>425</v>
       </c>
       <c r="L25" t="s">
-        <v>2066</v>
+        <v>2071</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>2097</v>
+        <v>2102</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>2128</v>
+        <v>2133</v>
       </c>
       <c r="O25">
         <v>7.5</v>
@@ -23973,7 +24038,7 @@
         <v>789</v>
       </c>
       <c r="Q25" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -23981,7 +24046,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>1986</v>
+        <v>1991</v>
       </c>
       <c r="C26" t="s">
         <v>146</v>
@@ -23999,10 +24064,10 @@
         <v>0.62</v>
       </c>
       <c r="H26" t="s">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="I26" t="s">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -24011,13 +24076,13 @@
         <v>425</v>
       </c>
       <c r="L26" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="O26">
         <v>12.32</v>
@@ -24026,7 +24091,7 @@
         <v>789</v>
       </c>
       <c r="Q26" t="s">
-        <v>2160</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -24034,7 +24099,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>1987</v>
+        <v>1992</v>
       </c>
       <c r="C27" t="s">
         <v>147</v>
@@ -24052,10 +24117,10 @@
         <v>2.43</v>
       </c>
       <c r="H27" t="s">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="I27" t="s">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -24064,13 +24129,13 @@
         <v>425</v>
       </c>
       <c r="L27" t="s">
-        <v>2068</v>
+        <v>2073</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2099</v>
+        <v>2104</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="O27">
         <v>48.66</v>
@@ -24079,7 +24144,7 @@
         <v>789</v>
       </c>
       <c r="Q27" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -24087,7 +24152,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>1988</v>
+        <v>1993</v>
       </c>
       <c r="C28" t="s">
         <v>147</v>
@@ -24105,7 +24170,7 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="s">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -24114,13 +24179,13 @@
         <v>425</v>
       </c>
       <c r="L28" t="s">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2100</v>
+        <v>2105</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="O28">
         <v>36.49</v>
@@ -24129,7 +24194,7 @@
         <v>789</v>
       </c>
       <c r="Q28" t="s">
-        <v>2162</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -24137,7 +24202,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>1989</v>
+        <v>1994</v>
       </c>
       <c r="C29" t="s">
         <v>147</v>
@@ -24155,10 +24220,10 @@
         <v>1.33</v>
       </c>
       <c r="H29" t="s">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="I29" t="s">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="J29">
         <v>19.99</v>
@@ -24167,13 +24232,13 @@
         <v>425</v>
       </c>
       <c r="L29" t="s">
-        <v>2070</v>
+        <v>2075</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2132</v>
+        <v>2137</v>
       </c>
       <c r="O29">
         <v>26.63</v>
@@ -24182,7 +24247,7 @@
         <v>789</v>
       </c>
       <c r="Q29" t="s">
-        <v>2163</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -24190,7 +24255,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="C30" t="s">
         <v>147</v>
@@ -24208,7 +24273,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="s">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="J30">
         <v>19.99</v>
@@ -24217,13 +24282,13 @@
         <v>425</v>
       </c>
       <c r="L30" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="O30">
         <v>50.71</v>
@@ -24232,7 +24297,7 @@
         <v>789</v>
       </c>
       <c r="Q30" t="s">
-        <v>2164</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -24240,7 +24305,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="C31" t="s">
         <v>148</v>
@@ -24258,10 +24323,10 @@
         <v>0.85</v>
       </c>
       <c r="H31" t="s">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="I31" t="s">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="J31">
         <v>19.99</v>
@@ -24270,13 +24335,13 @@
         <v>425</v>
       </c>
       <c r="L31" t="s">
-        <v>2072</v>
+        <v>2077</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2134</v>
+        <v>2139</v>
       </c>
       <c r="O31">
         <v>16.93</v>
@@ -24285,7 +24350,7 @@
         <v>789</v>
       </c>
       <c r="Q31" t="s">
-        <v>2165</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -24293,7 +24358,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="C32" t="s">
         <v>148</v>
@@ -24311,7 +24376,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="J32">
         <v>19.99</v>
@@ -24320,13 +24385,13 @@
         <v>425</v>
       </c>
       <c r="L32" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="O32">
         <v>17.97</v>
@@ -24335,7 +24400,7 @@
         <v>789</v>
       </c>
       <c r="Q32" t="s">
-        <v>2166</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -24343,7 +24408,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>1993</v>
+        <v>1998</v>
       </c>
       <c r="C33" t="s">
         <v>148</v>
@@ -24361,10 +24426,10 @@
         <v>0.89</v>
       </c>
       <c r="H33" t="s">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="I33" t="s">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="J33">
         <v>19.99</v>
@@ -24373,13 +24438,13 @@
         <v>425</v>
       </c>
       <c r="L33" t="s">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
       <c r="O33">
         <v>17.84</v>
@@ -24388,7 +24453,7 @@
         <v>789</v>
       </c>
       <c r="Q33" t="s">
-        <v>2167</v>
+        <v>2172</v>
       </c>
     </row>
   </sheetData>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="2196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="2196">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="2201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4069" uniqueCount="2201">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -3010,7 +3010,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17309,7 +17309,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Panthor (Standard)</t>
+          <t>Panthor (Flocked)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17319,14 +17324,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$24.99</t>
+          <t>$39.99</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1759</v>
+        <v>1179</v>
       </c>
       <c r="G7" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -17335,11 +17340,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>887961930849</t>
+          <t>887961979831</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>24.99</v>
+        <v>39.99</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -17348,21 +17353,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
+          <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>14.62</v>
+        <v>21.68</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -17371,7 +17376,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2425</t>
         </is>
       </c>
     </row>
@@ -17383,12 +17388,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Panthor (Flocked)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Walmart</t>
+          <t>Panthor (Standard)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17398,14 +17398,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$39.99</t>
+          <t>$24.99</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1179</v>
+        <v>1759</v>
       </c>
       <c r="G8" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -17414,11 +17414,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>887961979831</t>
+          <t>887961930849</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>39.99</v>
+        <v>24.99</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -17427,21 +17427,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
+          <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>21.68</v>
+        <v>14.62</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2414</t>
         </is>
       </c>
     </row>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -4417,12 +4417,12 @@
     <t>Land Shark</t>
   </si>
   <si>
+    <t>Panthor (Standard)</t>
+  </si>
+  <si>
     <t>Panthor (Flocked)</t>
   </si>
   <si>
-    <t>Panthor (Standard)</t>
-  </si>
-  <si>
     <t>Prince Adam Sky Sled</t>
   </si>
   <si>
@@ -4546,12 +4546,12 @@
     <t>887961960211</t>
   </si>
   <si>
+    <t>887961930849</t>
+  </si>
+  <si>
     <t>887961979831</t>
   </si>
   <si>
-    <t>887961930849</t>
-  </si>
-  <si>
     <t>887961893243</t>
   </si>
   <si>
@@ -4603,12 +4603,12 @@
     <t>/app/data/MOTU/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
   </si>
   <si>
-    <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
-  </si>
-  <si>
     <t>/app/data/MOTU/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4669,12 +4669,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4735,12 +4735,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/land-shark-2412.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/prince-adam-sky-sled-2413.php</t>
   </si>
   <si>
@@ -4801,10 +4801,10 @@
     <t>2412</t>
   </si>
   <si>
+    <t>2414</t>
+  </si>
+  <si>
     <t>2425</t>
-  </si>
-  <si>
-    <t>2414</t>
   </si>
   <si>
     <t>2413</t>
@@ -18545,20 +18545,17 @@
       <c r="B7" t="s">
         <v>1464</v>
       </c>
-      <c r="C7" t="s">
-        <v>163</v>
-      </c>
       <c r="D7" t="s">
         <v>173</v>
       </c>
       <c r="E7" t="s">
-        <v>1111</v>
+        <v>933</v>
       </c>
       <c r="F7">
-        <v>1179</v>
+        <v>1759</v>
       </c>
       <c r="G7">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="H7" t="s">
         <v>1489</v>
@@ -18567,7 +18564,7 @@
         <v>1507</v>
       </c>
       <c r="J7">
-        <v>39.99</v>
+        <v>24.99</v>
       </c>
       <c r="K7" t="s">
         <v>425</v>
@@ -18582,7 +18579,7 @@
         <v>1570</v>
       </c>
       <c r="O7">
-        <v>21.68</v>
+        <v>14.62</v>
       </c>
       <c r="P7" t="s">
         <v>789</v>
@@ -18598,17 +18595,20 @@
       <c r="B8" t="s">
         <v>1465</v>
       </c>
+      <c r="C8" t="s">
+        <v>163</v>
+      </c>
       <c r="D8" t="s">
         <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>933</v>
+        <v>1111</v>
       </c>
       <c r="F8">
-        <v>1759</v>
+        <v>1179</v>
       </c>
       <c r="G8">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H8" t="s">
         <v>1489</v>
@@ -18617,7 +18617,7 @@
         <v>1508</v>
       </c>
       <c r="J8">
-        <v>24.99</v>
+        <v>39.99</v>
       </c>
       <c r="K8" t="s">
         <v>425</v>
@@ -18632,7 +18632,7 @@
         <v>1571</v>
       </c>
       <c r="O8">
-        <v>14.62</v>
+        <v>21.68</v>
       </c>
       <c r="P8" t="s">
         <v>789</v>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="2231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4125" uniqueCount="2231">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4163" uniqueCount="2252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="2252">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4166" uniqueCount="2252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="2257">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -3490,6 +3490,9 @@
     <t>Great Black Wizard</t>
   </si>
   <si>
+    <t>Laser Power He-Man</t>
+  </si>
+  <si>
     <t>Stonedar</t>
   </si>
   <si>
@@ -3586,6 +3589,9 @@
     <t>$69.99</t>
   </si>
   <si>
+    <t>$33.00</t>
+  </si>
+  <si>
     <t>B0GFQ55H21</t>
   </si>
   <si>
@@ -4021,6 +4027,9 @@
     <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
+  </si>
+  <si>
     <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
   </si>
   <si>
@@ -4198,6 +4207,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
   </si>
   <si>
@@ -4375,6 +4387,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
   </si>
   <si>
@@ -4552,6 +4567,9 @@
     <t>12852</t>
   </si>
   <si>
+    <t>13263</t>
+  </si>
+  <si>
     <t>13031</t>
   </si>
   <si>
@@ -4628,9 +4646,6 @@
   </si>
   <si>
     <t>$79.99</t>
-  </si>
-  <si>
-    <t>$33.00</t>
   </si>
   <si>
     <t>$91.99</t>
@@ -14265,7 +14280,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14342,13 +14357,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2230</v>
+        <v>2235</v>
       </c>
       <c r="D3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E3" t="s">
-        <v>2233</v>
+        <v>2238</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -14357,10 +14372,10 @@
         <v>0.51</v>
       </c>
       <c r="H3" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="I3" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
       <c r="J3">
         <v>39.95</v>
@@ -14369,13 +14384,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2240</v>
+        <v>2245</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2243</v>
+        <v>2248</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2246</v>
+        <v>2251</v>
       </c>
       <c r="O3">
         <v>20.51</v>
@@ -14384,7 +14399,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2249</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -14392,13 +14407,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="D4" t="s">
         <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -14407,10 +14422,10 @@
         <v>0.6</v>
       </c>
       <c r="H4" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="I4" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="J4">
         <v>59.95</v>
@@ -14419,13 +14434,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2241</v>
+        <v>2246</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2244</v>
+        <v>2249</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2247</v>
+        <v>2252</v>
       </c>
       <c r="O4">
         <v>36.25</v>
@@ -14434,7 +14449,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2250</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -14442,13 +14457,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2232</v>
+        <v>2237</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -14457,7 +14472,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="s">
-        <v>2239</v>
+        <v>2244</v>
       </c>
       <c r="J5">
         <v>59.95</v>
@@ -14466,13 +14481,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2242</v>
+        <v>2247</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2248</v>
+        <v>2253</v>
       </c>
       <c r="O5">
         <v>138.16</v>
@@ -14481,7 +14496,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2251</v>
+        <v>2256</v>
       </c>
     </row>
   </sheetData>
@@ -15560,7 +15575,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -15645,13 +15660,13 @@
         <v>1097</v>
       </c>
       <c r="C3" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15660,10 +15675,10 @@
         <v>9.84</v>
       </c>
       <c r="H3" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="I3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="J3">
         <v>39.99</v>
@@ -15672,13 +15687,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="O3">
         <v>393.33</v>
@@ -15687,7 +15702,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15698,13 +15713,13 @@
         <v>1098</v>
       </c>
       <c r="C4" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D4" t="s">
         <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15713,7 +15728,7 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="J4">
         <v>269.99</v>
@@ -15722,13 +15737,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="O4">
         <v>323.96</v>
@@ -15737,7 +15752,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -15748,13 +15763,13 @@
         <v>1099</v>
       </c>
       <c r="C5" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -15763,10 +15778,10 @@
         <v>2.75</v>
       </c>
       <c r="H5" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="I5" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="J5">
         <v>39.99</v>
@@ -15775,13 +15790,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="O5">
         <v>110</v>
@@ -15790,7 +15805,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -15801,13 +15816,13 @@
         <v>1100</v>
       </c>
       <c r="C6" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -15816,7 +15831,7 @@
         <v>5.83</v>
       </c>
       <c r="I6" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -15825,13 +15840,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O6">
         <v>350</v>
@@ -15840,7 +15855,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1454</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -15851,13 +15866,13 @@
         <v>1101</v>
       </c>
       <c r="C7" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -15866,7 +15881,7 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -15875,13 +15890,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="O7">
         <v>216.32</v>
@@ -15890,7 +15905,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1455</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -15907,7 +15922,7 @@
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F8">
         <v>1537</v>
@@ -15916,10 +15931,10 @@
         <v>0.48</v>
       </c>
       <c r="H8" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="I8" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="J8">
         <v>29.99</v>
@@ -15928,13 +15943,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="O8">
         <v>14.33</v>
@@ -15943,7 +15958,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1456</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -15954,13 +15969,13 @@
         <v>1103</v>
       </c>
       <c r="C9" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -15975,13 +15990,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="O9">
         <v>109.99</v>
@@ -15990,7 +16005,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1457</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -16001,13 +16016,13 @@
         <v>1104</v>
       </c>
       <c r="C10" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16016,7 +16031,7 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -16025,13 +16040,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="O10">
         <v>260</v>
@@ -16040,7 +16055,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1458</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -16051,13 +16066,13 @@
         <v>1105</v>
       </c>
       <c r="C11" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D11" t="s">
         <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -16072,13 +16087,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="O11">
         <v>299.95</v>
@@ -16087,7 +16102,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1459</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -16098,13 +16113,13 @@
         <v>1106</v>
       </c>
       <c r="C12" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
       </c>
       <c r="E12" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16119,13 +16134,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="O12">
         <v>126.66</v>
@@ -16134,7 +16149,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1460</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -16145,13 +16160,13 @@
         <v>1107</v>
       </c>
       <c r="C13" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
       </c>
       <c r="E13" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16160,7 +16175,7 @@
         <v>4.33</v>
       </c>
       <c r="I13" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -16169,13 +16184,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="O13">
         <v>216.67</v>
@@ -16184,7 +16199,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1461</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -16195,13 +16210,13 @@
         <v>1108</v>
       </c>
       <c r="C14" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D14" t="s">
         <v>182</v>
       </c>
       <c r="E14" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -16210,7 +16225,7 @@
         <v>1.72</v>
       </c>
       <c r="I14" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -16219,13 +16234,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="O14">
         <v>51.65</v>
@@ -16234,7 +16249,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -16245,13 +16260,13 @@
         <v>1109</v>
       </c>
       <c r="C15" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D15" t="s">
         <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F15">
         <v>503</v>
@@ -16260,7 +16275,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="J15">
         <v>17</v>
@@ -16269,13 +16284,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="O15">
         <v>95.16</v>
@@ -16284,7 +16299,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1463</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -16301,7 +16316,7 @@
         <v>183</v>
       </c>
       <c r="E16" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F16">
         <v>606</v>
@@ -16310,10 +16325,10 @@
         <v>2.86</v>
       </c>
       <c r="H16" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="I16" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -16322,13 +16337,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="O16">
         <v>85.70999999999999</v>
@@ -16337,7 +16352,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -16363,10 +16378,10 @@
         <v>2.33</v>
       </c>
       <c r="H17" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="I17" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="J17">
         <v>18</v>
@@ -16375,13 +16390,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="O17">
         <v>42</v>
@@ -16390,7 +16405,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -16407,7 +16422,7 @@
         <v>183</v>
       </c>
       <c r="E18" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -16416,10 +16431,10 @@
         <v>0.53</v>
       </c>
       <c r="H18" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="I18" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="J18">
         <v>150</v>
@@ -16428,13 +16443,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="O18">
         <v>79.75</v>
@@ -16443,7 +16458,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -16460,7 +16475,7 @@
         <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F19">
         <v>536</v>
@@ -16469,7 +16484,7 @@
         <v>4.54</v>
       </c>
       <c r="I19" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="J19">
         <v>17</v>
@@ -16478,13 +16493,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="O19">
         <v>77.23999999999999</v>
@@ -16493,7 +16508,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1467</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -16519,10 +16534,10 @@
         <v>1.34</v>
       </c>
       <c r="H20" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="I20" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="J20">
         <v>18</v>
@@ -16531,13 +16546,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="O20">
         <v>24.09</v>
@@ -16546,7 +16561,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1468</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -16563,7 +16578,7 @@
         <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F21">
         <v>671</v>
@@ -16572,7 +16587,7 @@
         <v>0.4</v>
       </c>
       <c r="I21" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="J21">
         <v>49.99</v>
@@ -16581,13 +16596,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="O21">
         <v>19.99</v>
@@ -16596,7 +16611,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1469</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -16613,7 +16628,7 @@
         <v>183</v>
       </c>
       <c r="E22" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F22">
         <v>911</v>
@@ -16622,10 +16637,10 @@
         <v>1.93</v>
       </c>
       <c r="H22" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="I22" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="J22">
         <v>17</v>
@@ -16634,13 +16649,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="O22">
         <v>32.76</v>
@@ -16649,7 +16664,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1470</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -16663,7 +16678,7 @@
         <v>184</v>
       </c>
       <c r="E23" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F23">
         <v>524</v>
@@ -16672,10 +16687,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="I23" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="J23">
         <v>64.98999999999999</v>
@@ -16684,13 +16699,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="O23">
         <v>129.79</v>
@@ -16699,7 +16714,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -16725,10 +16740,10 @@
         <v>1.91</v>
       </c>
       <c r="H24" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="I24" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -16737,13 +16752,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="O24">
         <v>38.24</v>
@@ -16752,7 +16767,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -16778,10 +16793,10 @@
         <v>1.97</v>
       </c>
       <c r="H25" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="I25" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="J25">
         <v>17.99</v>
@@ -16790,13 +16805,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="O25">
         <v>35.47</v>
@@ -16805,7 +16820,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>1473</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -16831,10 +16846,10 @@
         <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="I26" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J26">
         <v>17.99</v>
@@ -16843,13 +16858,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="O26">
         <v>33.25</v>
@@ -16858,7 +16873,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>1474</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -16875,7 +16890,7 @@
         <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F27">
         <v>728</v>
@@ -16884,10 +16899,10 @@
         <v>1.2</v>
       </c>
       <c r="H27" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="I27" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="J27">
         <v>35</v>
@@ -16896,13 +16911,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="O27">
         <v>41.94</v>
@@ -16911,7 +16926,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>1475</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -16937,10 +16952,10 @@
         <v>2.29</v>
       </c>
       <c r="H28" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="I28" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="J28">
         <v>17.99</v>
@@ -16949,13 +16964,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="O28">
         <v>41.11</v>
@@ -16964,7 +16979,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>1476</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -16981,7 +16996,7 @@
         <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F29">
         <v>508</v>
@@ -16990,10 +17005,10 @@
         <v>0.52</v>
       </c>
       <c r="H29" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="I29" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="J29">
         <v>49.99</v>
@@ -17002,13 +17017,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="O29">
         <v>26.14</v>
@@ -17017,7 +17032,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>1477</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -17031,7 +17046,7 @@
         <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F30">
         <v>759</v>
@@ -17040,10 +17055,10 @@
         <v>1.88</v>
       </c>
       <c r="H30" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="I30" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="J30">
         <v>31.99</v>
@@ -17052,13 +17067,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="O30">
         <v>60</v>
@@ -17067,7 +17082,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>1478</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -17084,7 +17099,7 @@
         <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F31">
         <v>568</v>
@@ -17093,10 +17108,10 @@
         <v>1.09</v>
       </c>
       <c r="H31" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="I31" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="J31">
         <v>22.97</v>
@@ -17105,13 +17120,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="O31">
         <v>24.99</v>
@@ -17120,7 +17135,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>1479</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -17137,7 +17152,7 @@
         <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F32">
         <v>560</v>
@@ -17146,10 +17161,10 @@
         <v>1.56</v>
       </c>
       <c r="H32" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="I32" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="J32">
         <v>20</v>
@@ -17158,13 +17173,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="O32">
         <v>31.2</v>
@@ -17173,7 +17188,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -17190,7 +17205,7 @@
         <v>185</v>
       </c>
       <c r="E33" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -17199,10 +17214,10 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="I33" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="J33">
         <v>550</v>
@@ -17211,13 +17226,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="O33">
         <v>700.51</v>
@@ -17226,7 +17241,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>1481</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -17243,7 +17258,7 @@
         <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F34">
         <v>664</v>
@@ -17252,10 +17267,10 @@
         <v>1.5</v>
       </c>
       <c r="H34" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="I34" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="J34">
         <v>20</v>
@@ -17264,13 +17279,13 @@
         <v>449</v>
       </c>
       <c r="L34" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="O34">
         <v>29.98</v>
@@ -17279,7 +17294,7 @@
         <v>834</v>
       </c>
       <c r="Q34" t="s">
-        <v>1482</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -17296,7 +17311,7 @@
         <v>185</v>
       </c>
       <c r="E35" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="F35">
         <v>572</v>
@@ -17305,10 +17320,10 @@
         <v>0.88</v>
       </c>
       <c r="H35" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="I35" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="J35">
         <v>22.99</v>
@@ -17317,13 +17332,13 @@
         <v>449</v>
       </c>
       <c r="L35" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="O35">
         <v>20.23</v>
@@ -17332,7 +17347,7 @@
         <v>834</v>
       </c>
       <c r="Q35" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -17361,13 +17376,13 @@
         <v>449</v>
       </c>
       <c r="L36" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="O36">
         <v>198.33</v>
@@ -17376,7 +17391,7 @@
         <v>834</v>
       </c>
       <c r="Q36" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -17393,7 +17408,7 @@
         <v>185</v>
       </c>
       <c r="E37" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F37">
         <v>615</v>
@@ -17402,10 +17417,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="I37" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="J37">
         <v>22.97</v>
@@ -17414,13 +17429,13 @@
         <v>449</v>
       </c>
       <c r="L37" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="O37">
         <v>16.07</v>
@@ -17429,7 +17444,7 @@
         <v>834</v>
       </c>
       <c r="Q37" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -17446,7 +17461,7 @@
         <v>185</v>
       </c>
       <c r="E38" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F38">
         <v>708</v>
@@ -17455,10 +17470,10 @@
         <v>1.85</v>
       </c>
       <c r="H38" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="I38" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="J38">
         <v>20</v>
@@ -17467,13 +17482,13 @@
         <v>449</v>
       </c>
       <c r="L38" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="O38">
         <v>36.95</v>
@@ -17482,7 +17497,7 @@
         <v>834</v>
       </c>
       <c r="Q38" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -17499,7 +17514,7 @@
         <v>185</v>
       </c>
       <c r="E39" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -17508,10 +17523,10 @@
         <v>1.25</v>
       </c>
       <c r="H39" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="I39" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="J39">
         <v>45</v>
@@ -17520,13 +17535,13 @@
         <v>449</v>
       </c>
       <c r="L39" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="O39">
         <v>56.07</v>
@@ -17535,7 +17550,7 @@
         <v>834</v>
       </c>
       <c r="Q39" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -17552,7 +17567,7 @@
         <v>185</v>
       </c>
       <c r="E40" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="F40">
         <v>700</v>
@@ -17561,10 +17576,10 @@
         <v>2.24</v>
       </c>
       <c r="H40" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="I40" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -17573,13 +17588,13 @@
         <v>449</v>
       </c>
       <c r="L40" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="O40">
         <v>53.81</v>
@@ -17588,7 +17603,7 @@
         <v>834</v>
       </c>
       <c r="Q40" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -17599,13 +17614,13 @@
         <v>1135</v>
       </c>
       <c r="C41" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D41" t="s">
         <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -17614,7 +17629,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="J41">
         <v>90</v>
@@ -17623,13 +17638,13 @@
         <v>449</v>
       </c>
       <c r="L41" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -17638,7 +17653,7 @@
         <v>834</v>
       </c>
       <c r="Q41" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -17649,13 +17664,13 @@
         <v>1136</v>
       </c>
       <c r="C42" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D42" t="s">
         <v>185</v>
       </c>
       <c r="E42" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -17664,10 +17679,10 @@
         <v>2.66</v>
       </c>
       <c r="H42" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="I42" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -17676,13 +17691,13 @@
         <v>449</v>
       </c>
       <c r="L42" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="O42">
         <v>132.99</v>
@@ -17691,7 +17706,7 @@
         <v>834</v>
       </c>
       <c r="Q42" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -17708,7 +17723,7 @@
         <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -17717,10 +17732,10 @@
         <v>1.29</v>
       </c>
       <c r="H43" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="I43" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="J43">
         <v>64.98999999999999</v>
@@ -17729,13 +17744,13 @@
         <v>449</v>
       </c>
       <c r="L43" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="O43">
         <v>83.73</v>
@@ -17744,7 +17759,7 @@
         <v>834</v>
       </c>
       <c r="Q43" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -17761,7 +17776,7 @@
         <v>186</v>
       </c>
       <c r="E44" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -17776,13 +17791,13 @@
         <v>449</v>
       </c>
       <c r="L44" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="O44">
         <v>26.9</v>
@@ -17791,7 +17806,7 @@
         <v>834</v>
       </c>
       <c r="Q44" t="s">
-        <v>1492</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -17808,7 +17823,7 @@
         <v>186</v>
       </c>
       <c r="E45" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -17823,13 +17838,13 @@
         <v>449</v>
       </c>
       <c r="L45" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="O45">
         <v>43.75</v>
@@ -17838,7 +17853,7 @@
         <v>834</v>
       </c>
       <c r="Q45" t="s">
-        <v>1493</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -17861,7 +17876,7 @@
         <v>2.12</v>
       </c>
       <c r="I46" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="J46">
         <v>19.99</v>
@@ -17870,13 +17885,13 @@
         <v>449</v>
       </c>
       <c r="L46" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="O46">
         <v>42.3</v>
@@ -17885,7 +17900,7 @@
         <v>834</v>
       </c>
       <c r="Q46" t="s">
-        <v>1494</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -17896,13 +17911,13 @@
         <v>1141</v>
       </c>
       <c r="C47" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -17911,10 +17926,10 @@
         <v>0.87</v>
       </c>
       <c r="H47" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="I47" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="J47">
         <v>20</v>
@@ -17923,13 +17938,13 @@
         <v>449</v>
       </c>
       <c r="L47" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="O47">
         <v>17.33</v>
@@ -17938,7 +17953,7 @@
         <v>834</v>
       </c>
       <c r="Q47" t="s">
-        <v>1495</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -17949,13 +17964,13 @@
         <v>1142</v>
       </c>
       <c r="C48" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -17964,7 +17979,7 @@
         <v>0.23</v>
       </c>
       <c r="I48" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="J48">
         <v>100</v>
@@ -17973,13 +17988,13 @@
         <v>449</v>
       </c>
       <c r="L48" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="O48">
         <v>22.95</v>
@@ -17988,7 +18003,7 @@
         <v>834</v>
       </c>
       <c r="Q48" t="s">
-        <v>1496</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -18005,7 +18020,7 @@
         <v>186</v>
       </c>
       <c r="E49" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F49">
         <v>509</v>
@@ -18014,10 +18029,10 @@
         <v>0.49</v>
       </c>
       <c r="H49" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="I49" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="J49">
         <v>29.99</v>
@@ -18026,13 +18041,13 @@
         <v>449</v>
       </c>
       <c r="L49" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="O49">
         <v>14.81</v>
@@ -18041,7 +18056,7 @@
         <v>834</v>
       </c>
       <c r="Q49" t="s">
-        <v>1497</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -18058,7 +18073,7 @@
         <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -18067,7 +18082,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="J50">
         <v>34.99</v>
@@ -18076,13 +18091,13 @@
         <v>449</v>
       </c>
       <c r="L50" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="O50">
         <v>28.41</v>
@@ -18091,7 +18106,7 @@
         <v>834</v>
       </c>
       <c r="Q50" t="s">
-        <v>1498</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -18108,7 +18123,7 @@
         <v>186</v>
       </c>
       <c r="E51" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F51">
         <v>552</v>
@@ -18117,10 +18132,10 @@
         <v>0.93</v>
       </c>
       <c r="H51" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="I51" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="J51">
         <v>29.99</v>
@@ -18129,13 +18144,13 @@
         <v>449</v>
       </c>
       <c r="L51" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="O51">
         <v>27.99</v>
@@ -18144,7 +18159,7 @@
         <v>834</v>
       </c>
       <c r="Q51" t="s">
-        <v>1499</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -18161,7 +18176,7 @@
         <v>186</v>
       </c>
       <c r="E52" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -18170,10 +18185,10 @@
         <v>1.06</v>
       </c>
       <c r="H52" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="I52" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="J52">
         <v>31.99</v>
@@ -18182,13 +18197,13 @@
         <v>449</v>
       </c>
       <c r="L52" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="O52">
         <v>34.04</v>
@@ -18197,7 +18212,7 @@
         <v>834</v>
       </c>
       <c r="Q52" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -18214,7 +18229,7 @@
         <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -18223,10 +18238,10 @@
         <v>0.92</v>
       </c>
       <c r="H53" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="I53" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="J53">
         <v>44.99</v>
@@ -18235,13 +18250,13 @@
         <v>449</v>
       </c>
       <c r="L53" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="O53">
         <v>41.52</v>
@@ -18250,7 +18265,7 @@
         <v>834</v>
       </c>
       <c r="Q53" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -18267,7 +18282,7 @@
         <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F54">
         <v>609</v>
@@ -18276,10 +18291,10 @@
         <v>1.17</v>
       </c>
       <c r="H54" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="I54" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="J54">
         <v>20</v>
@@ -18288,13 +18303,13 @@
         <v>449</v>
       </c>
       <c r="L54" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="O54">
         <v>23.48</v>
@@ -18303,7 +18318,7 @@
         <v>834</v>
       </c>
       <c r="Q54" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -18320,7 +18335,7 @@
         <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -18329,10 +18344,10 @@
         <v>0.87</v>
       </c>
       <c r="H55" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="I55" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="J55">
         <v>29.99</v>
@@ -18341,13 +18356,13 @@
         <v>449</v>
       </c>
       <c r="L55" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="O55">
         <v>26.18</v>
@@ -18356,7 +18371,7 @@
         <v>834</v>
       </c>
       <c r="Q55" t="s">
-        <v>1503</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -18373,7 +18388,7 @@
         <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -18382,10 +18397,10 @@
         <v>0.97</v>
       </c>
       <c r="H56" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="I56" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="J56">
         <v>69.98999999999999</v>
@@ -18394,13 +18409,13 @@
         <v>449</v>
       </c>
       <c r="L56" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="O56">
         <v>67.75</v>
@@ -18409,7 +18424,7 @@
         <v>834</v>
       </c>
       <c r="Q56" t="s">
-        <v>1504</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -18435,10 +18450,10 @@
         <v>0.87</v>
       </c>
       <c r="H57" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="I57" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="J57">
         <v>19.99</v>
@@ -18447,13 +18462,13 @@
         <v>449</v>
       </c>
       <c r="L57" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="O57">
         <v>17.42</v>
@@ -18462,7 +18477,7 @@
         <v>834</v>
       </c>
       <c r="Q57" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -18479,7 +18494,7 @@
         <v>186</v>
       </c>
       <c r="E58" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -18488,10 +18503,10 @@
         <v>1.1</v>
       </c>
       <c r="H58" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="I58" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="J58">
         <v>20</v>
@@ -18500,13 +18515,13 @@
         <v>449</v>
       </c>
       <c r="L58" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="O58">
         <v>22</v>
@@ -18515,7 +18530,7 @@
         <v>834</v>
       </c>
       <c r="Q58" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -18547,13 +18562,13 @@
         <v>449</v>
       </c>
       <c r="L59" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="O59">
         <v>46.28</v>
@@ -18562,7 +18577,7 @@
         <v>834</v>
       </c>
       <c r="Q59" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -18579,7 +18594,7 @@
         <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -18594,13 +18609,13 @@
         <v>449</v>
       </c>
       <c r="L60" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="O60">
         <v>40.52</v>
@@ -18609,12 +18624,12 @@
         <v>834</v>
       </c>
       <c r="Q60" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="61" spans="1:17">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
         <v>1155</v>
@@ -18626,7 +18641,7 @@
         <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>195</v>
+        <v>1188</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -18635,19 +18650,19 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>449</v>
       </c>
       <c r="L61" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -18656,14 +18671,61 @@
         <v>834</v>
       </c>
       <c r="Q61" t="s">
-        <v>1509</v>
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C62" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" t="s">
+        <v>187</v>
+      </c>
+      <c r="E62" t="s">
+        <v>195</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>22</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L62" t="s">
+        <v>1335</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>1515</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A61">
+  <conditionalFormatting sqref="A3:A62">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -18672,7 +18734,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A62">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18796,6 +18858,9 @@
     <hyperlink ref="K61" r:id="rId117"/>
     <hyperlink ref="M61" r:id="rId118"/>
     <hyperlink ref="N61" r:id="rId119"/>
+    <hyperlink ref="K62" r:id="rId120"/>
+    <hyperlink ref="M62" r:id="rId121"/>
+    <hyperlink ref="N62" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18808,7 +18873,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18885,7 +18950,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -18894,7 +18959,7 @@
         <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F3">
         <v>1047</v>
@@ -18903,7 +18968,7 @@
         <v>0.67</v>
       </c>
       <c r="I3" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="J3">
         <v>49.99</v>
@@ -18912,13 +18977,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="O3">
         <v>33.33</v>
@@ -18927,7 +18992,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -18935,7 +19000,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -18950,10 +19015,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="I4" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="J4">
         <v>24.99</v>
@@ -18962,13 +19027,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="O4">
         <v>13.69</v>
@@ -18977,7 +19042,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -18985,13 +19050,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
       </c>
       <c r="E5" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="F5">
         <v>1752</v>
@@ -19000,10 +19065,10 @@
         <v>1.21</v>
       </c>
       <c r="H5" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="I5" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="J5">
         <v>74.98999999999999</v>
@@ -19012,13 +19077,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="O5">
         <v>90.84999999999999</v>
@@ -19027,7 +19092,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19035,13 +19100,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F6">
         <v>1538</v>
@@ -19050,10 +19115,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
       <c r="I6" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -19062,13 +19127,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="O6">
         <v>15.03</v>
@@ -19077,7 +19142,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -19085,7 +19150,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -19100,10 +19165,10 @@
         <v>0.59</v>
       </c>
       <c r="H7" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="I7" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="J7">
         <v>24.99</v>
@@ -19112,13 +19177,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="O7">
         <v>14.62</v>
@@ -19127,7 +19192,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -19135,7 +19200,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="C8" t="s">
         <v>170</v>
@@ -19144,7 +19209,7 @@
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F8">
         <v>1179</v>
@@ -19153,10 +19218,10 @@
         <v>0.54</v>
       </c>
       <c r="H8" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="I8" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
       <c r="J8">
         <v>39.99</v>
@@ -19165,13 +19230,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="O8">
         <v>21.68</v>
@@ -19180,7 +19245,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -19188,13 +19253,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F9">
         <v>1805</v>
@@ -19203,10 +19268,10 @@
         <v>0.53</v>
       </c>
       <c r="H9" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I9" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="J9">
         <v>29.99</v>
@@ -19215,13 +19280,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="O9">
         <v>16</v>
@@ -19230,7 +19295,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -19238,13 +19303,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F10">
         <v>1571</v>
@@ -19253,10 +19318,10 @@
         <v>0.74</v>
       </c>
       <c r="H10" t="s">
-        <v>1542</v>
+        <v>1547</v>
       </c>
       <c r="I10" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -19265,13 +19330,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="O10">
         <v>22.11</v>
@@ -19280,7 +19345,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -19288,13 +19353,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="D11" t="s">
         <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F11">
         <v>1159</v>
@@ -19303,10 +19368,10 @@
         <v>0.59</v>
       </c>
       <c r="H11" t="s">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="I11" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J11">
         <v>29.99</v>
@@ -19315,13 +19380,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="O11">
         <v>17.83</v>
@@ -19330,7 +19395,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -19338,7 +19403,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="D12" t="s">
         <v>183</v>
@@ -19353,10 +19418,10 @@
         <v>0.71</v>
       </c>
       <c r="H12" t="s">
-        <v>1544</v>
+        <v>1549</v>
       </c>
       <c r="I12" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -19365,13 +19430,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="O12">
         <v>17.77</v>
@@ -19380,7 +19445,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -19388,13 +19453,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D13" t="s">
         <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F13">
         <v>857</v>
@@ -19403,10 +19468,10 @@
         <v>1.31</v>
       </c>
       <c r="H13" t="s">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="I13" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
       <c r="J13">
         <v>29.99</v>
@@ -19415,13 +19480,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="O13">
         <v>39.37</v>
@@ -19430,7 +19495,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -19438,13 +19503,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
       </c>
       <c r="E14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F14">
         <v>1215</v>
@@ -19453,10 +19518,10 @@
         <v>0.75</v>
       </c>
       <c r="H14" t="s">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="I14" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="J14">
         <v>29.99</v>
@@ -19465,13 +19530,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
       <c r="O14">
         <v>22.5</v>
@@ -19480,7 +19545,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -19488,13 +19553,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
       </c>
       <c r="E15" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F15">
         <v>755</v>
@@ -19515,13 +19580,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="O15">
         <v>36.5</v>
@@ -19530,7 +19595,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -19538,13 +19603,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
       </c>
       <c r="E16" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="F16">
         <v>888</v>
@@ -19553,10 +19618,10 @@
         <v>3.33</v>
       </c>
       <c r="H16" t="s">
-        <v>1547</v>
+        <v>1552</v>
       </c>
       <c r="I16" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="J16">
         <v>79.98999999999999</v>
@@ -19565,13 +19630,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="O16">
         <v>266.38</v>
@@ -19580,7 +19645,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -19588,13 +19653,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F17">
         <v>1103</v>
@@ -19603,10 +19668,10 @@
         <v>0.42</v>
       </c>
       <c r="H17" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="I17" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="J17">
         <v>44.99</v>
@@ -19615,13 +19680,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="O17">
         <v>18.76</v>
@@ -19630,7 +19695,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -19638,13 +19703,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="D18" t="s">
         <v>185</v>
       </c>
       <c r="E18" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F18">
         <v>520</v>
@@ -19653,10 +19718,10 @@
         <v>0.85</v>
       </c>
       <c r="H18" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="I18" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="J18">
         <v>39.99</v>
@@ -19665,13 +19730,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="O18">
         <v>33.99</v>
@@ -19680,7 +19745,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -19688,7 +19753,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="C19" t="s">
         <v>171</v>
@@ -19709,13 +19774,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="O19">
         <v>180</v>
@@ -19724,7 +19789,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -19732,7 +19797,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="C20" t="s">
         <v>171</v>
@@ -19741,7 +19806,7 @@
         <v>185</v>
       </c>
       <c r="E20" t="s">
-        <v>1535</v>
+        <v>1188</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -19750,10 +19815,10 @@
         <v>1.12</v>
       </c>
       <c r="H20" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="I20" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
       <c r="J20">
         <v>33</v>
@@ -19762,13 +19827,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="O20">
         <v>37.07</v>
@@ -19777,7 +19842,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -19785,13 +19850,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="D21" t="s">
         <v>185</v>
       </c>
       <c r="E21" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="F21">
         <v>799</v>
@@ -19800,10 +19865,10 @@
         <v>0.89</v>
       </c>
       <c r="H21" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="I21" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -19812,13 +19877,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="O21">
         <v>26.75</v>
@@ -19827,7 +19892,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -19835,13 +19900,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -19850,10 +19915,10 @@
         <v>1.38</v>
       </c>
       <c r="H22" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="I22" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="J22">
         <v>91.98999999999999</v>
@@ -19862,13 +19927,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="O22">
         <v>126.79</v>
@@ -19877,7 +19942,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -19885,13 +19950,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="D23" t="s">
         <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -19900,10 +19965,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="I23" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="J23">
         <v>124.99</v>
@@ -19912,13 +19977,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -19927,7 +19992,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -19935,7 +20000,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="C24" t="s">
         <v>171</v>
@@ -19944,7 +20009,7 @@
         <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -19959,13 +20024,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="O24">
         <v>499.99</v>
@@ -19974,7 +20039,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
     </row>
   </sheetData>
@@ -20051,7 +20116,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20128,7 +20193,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -20137,7 +20202,7 @@
         <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -20146,7 +20211,7 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="J3">
         <v>34.99</v>
@@ -20155,13 +20220,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="O3">
         <v>36.09</v>
@@ -20170,7 +20235,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -20178,7 +20243,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
@@ -20187,7 +20252,7 @@
         <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -20196,7 +20261,7 @@
         <v>0.64</v>
       </c>
       <c r="I4" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
       <c r="J4">
         <v>34.99</v>
@@ -20205,13 +20270,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
       <c r="O4">
         <v>22.55</v>
@@ -20220,7 +20285,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -20228,7 +20293,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -20237,7 +20302,7 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -20246,7 +20311,7 @@
         <v>1.36</v>
       </c>
       <c r="I5" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="J5">
         <v>34.99</v>
@@ -20255,13 +20320,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="O5">
         <v>47.57</v>
@@ -20270,7 +20335,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1679</v>
+        <v>1684</v>
       </c>
     </row>
   </sheetData>
@@ -20309,7 +20374,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20386,7 +20451,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="C3" t="s">
         <v>170</v>
@@ -20404,10 +20469,10 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="s">
-        <v>1712</v>
+        <v>1717</v>
       </c>
       <c r="I3" t="s">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="J3">
         <v>24.99</v>
@@ -20416,13 +20481,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1851</v>
+        <v>1856</v>
       </c>
       <c r="O3">
         <v>30.44</v>
@@ -20431,7 +20496,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -20439,7 +20504,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="C4" t="s">
         <v>170</v>
@@ -20448,7 +20513,7 @@
         <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -20457,10 +20522,10 @@
         <v>0.52</v>
       </c>
       <c r="H4" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="I4" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="J4">
         <v>24.97</v>
@@ -20469,13 +20534,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="O4">
         <v>12.96</v>
@@ -20484,7 +20549,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1888</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -20492,7 +20557,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -20513,13 +20578,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="O5">
         <v>48.73</v>
@@ -20528,7 +20593,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1889</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -20536,7 +20601,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="C6" t="s">
         <v>176</v>
@@ -20554,10 +20619,10 @@
         <v>0.92</v>
       </c>
       <c r="H6" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="I6" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="J6">
         <v>24.99</v>
@@ -20566,13 +20631,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1854</v>
+        <v>1859</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -20581,7 +20646,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1890</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -20589,7 +20654,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="C7" t="s">
         <v>170</v>
@@ -20598,7 +20663,7 @@
         <v>185</v>
       </c>
       <c r="E7" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -20607,10 +20672,10 @@
         <v>0.82</v>
       </c>
       <c r="H7" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="I7" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
       <c r="J7">
         <v>24.97</v>
@@ -20619,13 +20684,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1855</v>
+        <v>1860</v>
       </c>
       <c r="O7">
         <v>20.41</v>
@@ -20634,7 +20699,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1891</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -20642,7 +20707,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="C8" t="s">
         <v>170</v>
@@ -20666,13 +20731,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1856</v>
+        <v>1861</v>
       </c>
       <c r="O8">
         <v>37.99</v>
@@ -20681,7 +20746,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1892</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -20689,7 +20754,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="C9" t="s">
         <v>176</v>
@@ -20707,10 +20772,10 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="I9" t="s">
-        <v>1749</v>
+        <v>1754</v>
       </c>
       <c r="J9">
         <v>24.99</v>
@@ -20719,13 +20784,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1857</v>
+        <v>1862</v>
       </c>
       <c r="O9">
         <v>37.71</v>
@@ -20734,7 +20799,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -20742,7 +20807,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="C10" t="s">
         <v>176</v>
@@ -20760,10 +20825,10 @@
         <v>0.78</v>
       </c>
       <c r="H10" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="I10" t="s">
-        <v>1750</v>
+        <v>1755</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -20772,13 +20837,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1858</v>
+        <v>1863</v>
       </c>
       <c r="O10">
         <v>19.54</v>
@@ -20787,7 +20852,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1894</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -20795,7 +20860,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="C11" t="s">
         <v>148</v>
@@ -20813,10 +20878,10 @@
         <v>0.82</v>
       </c>
       <c r="H11" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="I11" t="s">
-        <v>1751</v>
+        <v>1756</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -20825,13 +20890,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1859</v>
+        <v>1864</v>
       </c>
       <c r="O11">
         <v>16.43</v>
@@ -20840,7 +20905,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1895</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -20848,7 +20913,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
       <c r="C12" t="s">
         <v>148</v>
@@ -20866,10 +20931,10 @@
         <v>1.61</v>
       </c>
       <c r="H12" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="I12" t="s">
-        <v>1752</v>
+        <v>1757</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -20878,13 +20943,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1824</v>
+        <v>1829</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="O12">
         <v>32.14</v>
@@ -20893,7 +20958,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1896</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -20901,7 +20966,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="C13" t="s">
         <v>148</v>
@@ -20919,10 +20984,10 @@
         <v>0.71</v>
       </c>
       <c r="H13" t="s">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="I13" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -20931,13 +20996,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1825</v>
+        <v>1830</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="O13">
         <v>14.27</v>
@@ -20946,7 +21011,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1897</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -20954,7 +21019,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="C14" t="s">
         <v>148</v>
@@ -20972,10 +21037,10 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="s">
-        <v>1721</v>
+        <v>1726</v>
       </c>
       <c r="I14" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -20984,13 +21049,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1826</v>
+        <v>1831</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1862</v>
+        <v>1867</v>
       </c>
       <c r="O14">
         <v>23.5</v>
@@ -20999,7 +21064,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1898</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -21025,10 +21090,10 @@
         <v>0.65</v>
       </c>
       <c r="H15" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="I15" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -21037,13 +21102,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1827</v>
+        <v>1832</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="O15">
         <v>12.92</v>
@@ -21052,7 +21117,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1899</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -21060,7 +21125,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1693</v>
+        <v>1698</v>
       </c>
       <c r="C16" t="s">
         <v>149</v>
@@ -21078,10 +21143,10 @@
         <v>0.78</v>
       </c>
       <c r="H16" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="I16" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -21090,13 +21155,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1792</v>
+        <v>1797</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
       <c r="O16">
         <v>15.59</v>
@@ -21105,7 +21170,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -21113,7 +21178,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1694</v>
+        <v>1699</v>
       </c>
       <c r="C17" t="s">
         <v>149</v>
@@ -21131,10 +21196,10 @@
         <v>2.22</v>
       </c>
       <c r="H17" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="I17" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -21143,13 +21208,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1829</v>
+        <v>1834</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1865</v>
+        <v>1870</v>
       </c>
       <c r="O17">
         <v>44.34</v>
@@ -21158,7 +21223,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -21166,7 +21231,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="C18" t="s">
         <v>149</v>
@@ -21184,10 +21249,10 @@
         <v>2.09</v>
       </c>
       <c r="H18" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="I18" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -21196,13 +21261,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1830</v>
+        <v>1835</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1866</v>
+        <v>1871</v>
       </c>
       <c r="O18">
         <v>41.71</v>
@@ -21211,7 +21276,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1902</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -21219,7 +21284,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="C19" t="s">
         <v>150</v>
@@ -21237,10 +21302,10 @@
         <v>0.72</v>
       </c>
       <c r="H19" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="I19" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -21249,13 +21314,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="O19">
         <v>14.3</v>
@@ -21264,7 +21329,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1903</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -21272,7 +21337,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="C20" t="s">
         <v>150</v>
@@ -21290,10 +21355,10 @@
         <v>0.8</v>
       </c>
       <c r="H20" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
       <c r="I20" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -21302,13 +21367,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="O20">
         <v>15.98</v>
@@ -21317,7 +21382,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1904</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -21343,10 +21408,10 @@
         <v>0.9</v>
       </c>
       <c r="H21" t="s">
-        <v>1728</v>
+        <v>1733</v>
       </c>
       <c r="I21" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -21355,13 +21420,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1869</v>
+        <v>1874</v>
       </c>
       <c r="O21">
         <v>17.92</v>
@@ -21370,7 +21435,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1905</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -21396,10 +21461,10 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>1729</v>
+        <v>1734</v>
       </c>
       <c r="I22" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -21408,13 +21473,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="O22">
         <v>10.03</v>
@@ -21423,7 +21488,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1906</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -21431,7 +21496,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="C23" t="s">
         <v>151</v>
@@ -21449,10 +21514,10 @@
         <v>0.89</v>
       </c>
       <c r="H23" t="s">
-        <v>1730</v>
+        <v>1735</v>
       </c>
       <c r="I23" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -21461,13 +21526,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1835</v>
+        <v>1840</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1871</v>
+        <v>1876</v>
       </c>
       <c r="O23">
         <v>17.83</v>
@@ -21476,7 +21541,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1907</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -21484,7 +21549,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>1699</v>
+        <v>1704</v>
       </c>
       <c r="C24" t="s">
         <v>151</v>
@@ -21502,10 +21567,10 @@
         <v>0.72</v>
       </c>
       <c r="H24" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="I24" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -21514,13 +21579,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1836</v>
+        <v>1841</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="O24">
         <v>14.35</v>
@@ -21529,7 +21594,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1908</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -21555,10 +21620,10 @@
         <v>0.73</v>
       </c>
       <c r="H25" t="s">
-        <v>1732</v>
+        <v>1737</v>
       </c>
       <c r="I25" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -21567,13 +21632,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1837</v>
+        <v>1842</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1873</v>
+        <v>1878</v>
       </c>
       <c r="O25">
         <v>14.69</v>
@@ -21582,7 +21647,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>1909</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -21608,7 +21673,7 @@
         <v>7.29</v>
       </c>
       <c r="I26" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -21617,13 +21682,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1838</v>
+        <v>1843</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1874</v>
+        <v>1879</v>
       </c>
       <c r="O26">
         <v>145.79</v>
@@ -21632,7 +21697,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>1910</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -21640,7 +21705,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="C27" t="s">
         <v>151</v>
@@ -21658,10 +21723,10 @@
         <v>0.88</v>
       </c>
       <c r="H27" t="s">
-        <v>1733</v>
+        <v>1738</v>
       </c>
       <c r="I27" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -21670,13 +21735,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1839</v>
+        <v>1844</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="O27">
         <v>17.58</v>
@@ -21685,7 +21750,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>1911</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -21693,7 +21758,7 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="C28" t="s">
         <v>151</v>
@@ -21711,10 +21776,10 @@
         <v>0.82</v>
       </c>
       <c r="H28" t="s">
-        <v>1734</v>
+        <v>1739</v>
       </c>
       <c r="I28" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -21723,13 +21788,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1840</v>
+        <v>1845</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1876</v>
+        <v>1881</v>
       </c>
       <c r="O28">
         <v>16.46</v>
@@ -21738,7 +21803,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>1912</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -21746,7 +21811,7 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="C29" t="s">
         <v>152</v>
@@ -21755,7 +21820,7 @@
         <v>185</v>
       </c>
       <c r="E29" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -21764,10 +21829,10 @@
         <v>0.96</v>
       </c>
       <c r="H29" t="s">
-        <v>1735</v>
+        <v>1740</v>
       </c>
       <c r="I29" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="J29">
         <v>20.99</v>
@@ -21776,13 +21841,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1877</v>
+        <v>1882</v>
       </c>
       <c r="O29">
         <v>20.09</v>
@@ -21791,7 +21856,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>1913</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -21799,7 +21864,7 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="C30" t="s">
         <v>152</v>
@@ -21808,7 +21873,7 @@
         <v>185</v>
       </c>
       <c r="E30" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -21817,10 +21882,10 @@
         <v>0.83</v>
       </c>
       <c r="H30" t="s">
-        <v>1736</v>
+        <v>1741</v>
       </c>
       <c r="I30" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="J30">
         <v>20.99</v>
@@ -21829,13 +21894,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1842</v>
+        <v>1847</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="O30">
         <v>17.33</v>
@@ -21844,7 +21909,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>1914</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -21852,7 +21917,7 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>1704</v>
+        <v>1709</v>
       </c>
       <c r="C31" t="s">
         <v>152</v>
@@ -21861,7 +21926,7 @@
         <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -21870,10 +21935,10 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="s">
-        <v>1737</v>
+        <v>1742</v>
       </c>
       <c r="I31" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="J31">
         <v>20.99</v>
@@ -21882,13 +21947,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1879</v>
+        <v>1884</v>
       </c>
       <c r="O31">
         <v>15.75</v>
@@ -21897,7 +21962,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>1915</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -21914,7 +21979,7 @@
         <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -21923,10 +21988,10 @@
         <v>0.84</v>
       </c>
       <c r="H32" t="s">
-        <v>1738</v>
+        <v>1743</v>
       </c>
       <c r="I32" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
       <c r="J32">
         <v>20.99</v>
@@ -21935,13 +22000,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1880</v>
+        <v>1885</v>
       </c>
       <c r="O32">
         <v>17.65</v>
@@ -21950,7 +22015,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>1916</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -21958,7 +22023,7 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="C33" t="s">
         <v>153</v>
@@ -21976,10 +22041,10 @@
         <v>0.76</v>
       </c>
       <c r="H33" t="s">
-        <v>1739</v>
+        <v>1744</v>
       </c>
       <c r="I33" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="J33">
         <v>23.99</v>
@@ -21988,13 +22053,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1881</v>
+        <v>1886</v>
       </c>
       <c r="O33">
         <v>18.33</v>
@@ -22003,7 +22068,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>1917</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -22011,7 +22076,7 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="C34" t="s">
         <v>153</v>
@@ -22029,10 +22094,10 @@
         <v>0.86</v>
       </c>
       <c r="H34" t="s">
-        <v>1740</v>
+        <v>1745</v>
       </c>
       <c r="I34" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="J34">
         <v>23.99</v>
@@ -22041,13 +22106,13 @@
         <v>449</v>
       </c>
       <c r="L34" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1846</v>
+        <v>1851</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1882</v>
+        <v>1887</v>
       </c>
       <c r="O34">
         <v>20.58</v>
@@ -22056,7 +22121,7 @@
         <v>834</v>
       </c>
       <c r="Q34" t="s">
-        <v>1918</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -22064,7 +22129,7 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="C35" t="s">
         <v>153</v>
@@ -22082,10 +22147,10 @@
         <v>0.64</v>
       </c>
       <c r="H35" t="s">
-        <v>1741</v>
+        <v>1746</v>
       </c>
       <c r="I35" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="J35">
         <v>23.99</v>
@@ -22094,13 +22159,13 @@
         <v>449</v>
       </c>
       <c r="L35" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1847</v>
+        <v>1852</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1883</v>
+        <v>1888</v>
       </c>
       <c r="O35">
         <v>15.31</v>
@@ -22109,7 +22174,7 @@
         <v>834</v>
       </c>
       <c r="Q35" t="s">
-        <v>1919</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -22135,10 +22200,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H36" t="s">
-        <v>1742</v>
+        <v>1747</v>
       </c>
       <c r="I36" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="J36">
         <v>23.99</v>
@@ -22147,13 +22212,13 @@
         <v>449</v>
       </c>
       <c r="L36" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1884</v>
+        <v>1889</v>
       </c>
       <c r="O36">
         <v>19.5</v>
@@ -22162,7 +22227,7 @@
         <v>834</v>
       </c>
       <c r="Q36" t="s">
-        <v>1920</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -22170,16 +22235,16 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1708</v>
+        <v>1713</v>
       </c>
       <c r="C37" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D37" t="s">
         <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -22188,10 +22253,10 @@
         <v>0.99</v>
       </c>
       <c r="H37" t="s">
-        <v>1743</v>
+        <v>1748</v>
       </c>
       <c r="I37" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="J37">
         <v>45</v>
@@ -22200,13 +22265,13 @@
         <v>449</v>
       </c>
       <c r="L37" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1885</v>
+        <v>1890</v>
       </c>
       <c r="O37">
         <v>44.69</v>
@@ -22215,7 +22280,7 @@
         <v>834</v>
       </c>
       <c r="Q37" t="s">
-        <v>1921</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -22223,7 +22288,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1709</v>
+        <v>1714</v>
       </c>
       <c r="C38" t="s">
         <v>170</v>
@@ -22232,7 +22297,7 @@
         <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -22241,10 +22306,10 @@
         <v>0.78</v>
       </c>
       <c r="H38" t="s">
-        <v>1744</v>
+        <v>1749</v>
       </c>
       <c r="I38" t="s">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="J38">
         <v>24.97</v>
@@ -22253,13 +22318,13 @@
         <v>449</v>
       </c>
       <c r="L38" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1850</v>
+        <v>1855</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1886</v>
+        <v>1891</v>
       </c>
       <c r="O38">
         <v>19.45</v>
@@ -22268,7 +22333,7 @@
         <v>834</v>
       </c>
       <c r="Q38" t="s">
-        <v>1922</v>
+        <v>1927</v>
       </c>
     </row>
   </sheetData>
@@ -22373,7 +22438,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1923</v>
+        <v>1928</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22450,7 +22515,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1924</v>
+        <v>1929</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
@@ -22468,10 +22533,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="s">
-        <v>1934</v>
+        <v>1939</v>
       </c>
       <c r="I3" t="s">
-        <v>1943</v>
+        <v>1948</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -22480,13 +22545,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="O3">
         <v>23.26</v>
@@ -22495,7 +22560,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1983</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22503,7 +22568,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1925</v>
+        <v>1930</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
@@ -22521,10 +22586,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" t="s">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="I4" t="s">
-        <v>1944</v>
+        <v>1949</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -22533,13 +22598,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="O4">
         <v>16.41</v>
@@ -22548,7 +22613,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1984</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22556,7 +22621,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1926</v>
+        <v>1931</v>
       </c>
       <c r="C5" t="s">
         <v>148</v>
@@ -22574,10 +22639,10 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="s">
-        <v>1936</v>
+        <v>1941</v>
       </c>
       <c r="I5" t="s">
-        <v>1945</v>
+        <v>1950</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -22586,13 +22651,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="O5">
         <v>23.79</v>
@@ -22601,7 +22666,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1985</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22609,7 +22674,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
@@ -22618,7 +22683,7 @@
         <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -22627,10 +22692,10 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="s">
-        <v>1937</v>
+        <v>1942</v>
       </c>
       <c r="I6" t="s">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -22639,13 +22704,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="O6">
         <v>23.94</v>
@@ -22654,7 +22719,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1986</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -22680,7 +22745,7 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -22689,13 +22754,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -22704,7 +22769,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1987</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -22712,7 +22777,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>1928</v>
+        <v>1933</v>
       </c>
       <c r="C8" t="s">
         <v>149</v>
@@ -22730,7 +22795,7 @@
         <v>1.52</v>
       </c>
       <c r="H8" t="s">
-        <v>1939</v>
+        <v>1944</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -22739,13 +22804,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="O8">
         <v>30.47</v>
@@ -22754,7 +22819,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1988</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -22762,7 +22827,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1929</v>
+        <v>1934</v>
       </c>
       <c r="C9" t="s">
         <v>149</v>
@@ -22780,7 +22845,7 @@
         <v>1.02</v>
       </c>
       <c r="H9" t="s">
-        <v>1940</v>
+        <v>1945</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -22789,13 +22854,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="O9">
         <v>20.39</v>
@@ -22804,7 +22869,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1989</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -22812,7 +22877,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1930</v>
+        <v>1935</v>
       </c>
       <c r="C10" t="s">
         <v>150</v>
@@ -22830,7 +22895,7 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="s">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -22839,13 +22904,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1968</v>
+        <v>1973</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="O10">
         <v>29.95</v>
@@ -22854,7 +22919,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1990</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -22862,7 +22927,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1931</v>
+        <v>1936</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -22880,10 +22945,10 @@
         <v>1.29</v>
       </c>
       <c r="H11" t="s">
-        <v>1941</v>
+        <v>1946</v>
       </c>
       <c r="I11" t="s">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="J11">
         <v>24.99</v>
@@ -22892,13 +22957,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="O11">
         <v>32.18</v>
@@ -22907,7 +22972,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1991</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -22915,7 +22980,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1932</v>
+        <v>1937</v>
       </c>
       <c r="C12" t="s">
         <v>150</v>
@@ -22933,10 +22998,10 @@
         <v>1.2</v>
       </c>
       <c r="H12" t="s">
-        <v>1942</v>
+        <v>1947</v>
       </c>
       <c r="I12" t="s">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -22945,13 +23010,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1959</v>
+        <v>1964</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="O12">
         <v>29.95</v>
@@ -22960,7 +23025,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1992</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -22968,7 +23033,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1933</v>
+        <v>1938</v>
       </c>
       <c r="C13" t="s">
         <v>150</v>
@@ -22986,7 +23051,7 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="s">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="J13">
         <v>24.99</v>
@@ -22995,13 +23060,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="O13">
         <v>29.95</v>
@@ -23010,7 +23075,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1992</v>
+        <v>1997</v>
       </c>
     </row>
   </sheetData>
@@ -23067,7 +23132,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1993</v>
+        <v>1998</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23144,7 +23209,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -23153,7 +23218,7 @@
         <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -23162,10 +23227,10 @@
         <v>0.65</v>
       </c>
       <c r="H3" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="I3" t="s">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="J3">
         <v>32.99</v>
@@ -23174,13 +23239,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="O3">
         <v>21.34</v>
@@ -23189,7 +23254,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23197,7 +23262,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
@@ -23206,7 +23271,7 @@
         <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -23215,10 +23280,10 @@
         <v>0.68</v>
       </c>
       <c r="H4" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="I4" t="s">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="J4">
         <v>32.99</v>
@@ -23227,13 +23292,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="O4">
         <v>22.3</v>
@@ -23242,7 +23307,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -23250,7 +23315,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -23259,7 +23324,7 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -23268,10 +23333,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="I5" t="s">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="J5">
         <v>29.99</v>
@@ -23280,13 +23345,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="O5">
         <v>46.29</v>
@@ -23295,7 +23360,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -23303,7 +23368,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="C6" t="s">
         <v>176</v>
@@ -23312,7 +23377,7 @@
         <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -23321,10 +23386,10 @@
         <v>1.37</v>
       </c>
       <c r="H6" t="s">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="I6" t="s">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -23333,13 +23398,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="O6">
         <v>41.15</v>
@@ -23348,7 +23413,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
     </row>
   </sheetData>
@@ -23389,7 +23454,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23466,13 +23531,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E3" t="s">
         <v>190</v>
@@ -23484,10 +23549,10 @@
         <v>0.99</v>
       </c>
       <c r="H3" t="s">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="I3" t="s">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -23496,13 +23561,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2167</v>
+        <v>2172</v>
       </c>
       <c r="O3">
         <v>19.84</v>
@@ -23511,7 +23576,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2198</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23519,13 +23584,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E4" t="s">
         <v>190</v>
@@ -23537,7 +23602,7 @@
         <v>1.42</v>
       </c>
       <c r="I4" t="s">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -23546,13 +23611,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2106</v>
+        <v>2111</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="O4">
         <v>28.43</v>
@@ -23561,7 +23626,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -23569,13 +23634,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="C5" t="s">
         <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E5" t="s">
         <v>190</v>
@@ -23587,10 +23652,10 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="I5" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -23599,13 +23664,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2107</v>
+        <v>2112</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="O5">
         <v>24.47</v>
@@ -23614,7 +23679,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2200</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -23622,13 +23687,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E6" t="s">
         <v>190</v>
@@ -23640,10 +23705,10 @@
         <v>0.86</v>
       </c>
       <c r="H6" t="s">
-        <v>2057</v>
+        <v>2062</v>
       </c>
       <c r="I6" t="s">
-        <v>2077</v>
+        <v>2082</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -23652,13 +23717,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>2108</v>
+        <v>2113</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="O6">
         <v>17.15</v>
@@ -23667,7 +23732,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>2201</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -23675,7 +23740,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="C7" t="s">
         <v>149</v>
@@ -23693,7 +23758,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -23702,13 +23767,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>2109</v>
+        <v>2114</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2171</v>
+        <v>2176</v>
       </c>
       <c r="O7">
         <v>14.49</v>
@@ -23717,7 +23782,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>2202</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -23725,7 +23790,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="C8" t="s">
         <v>149</v>
@@ -23743,10 +23808,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>2058</v>
+        <v>2063</v>
       </c>
       <c r="I8" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -23755,13 +23820,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>2110</v>
+        <v>2115</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2141</v>
+        <v>2146</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="O8">
         <v>16.25</v>
@@ -23770,7 +23835,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>2203</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -23778,7 +23843,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="C9" t="s">
         <v>149</v>
@@ -23796,10 +23861,10 @@
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="I9" t="s">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -23808,13 +23873,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>2111</v>
+        <v>2116</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>2142</v>
+        <v>2147</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -23823,7 +23888,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>2204</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -23831,7 +23896,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="C10" t="s">
         <v>149</v>
@@ -23849,10 +23914,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>2060</v>
+        <v>2065</v>
       </c>
       <c r="I10" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
       <c r="J10">
         <v>19.99</v>
@@ -23861,13 +23926,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>2143</v>
+        <v>2148</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
       <c r="O10">
         <v>13.8</v>
@@ -23876,7 +23941,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>2205</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -23884,7 +23949,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -23902,7 +23967,7 @@
         <v>0.82</v>
       </c>
       <c r="I11" t="s">
-        <v>2082</v>
+        <v>2087</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -23911,13 +23976,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="O11">
         <v>16.49</v>
@@ -23926,7 +23991,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>2206</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -23934,7 +23999,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="C12" t="s">
         <v>150</v>
@@ -23952,7 +24017,7 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="s">
-        <v>2083</v>
+        <v>2088</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -23961,13 +24026,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>2176</v>
+        <v>2181</v>
       </c>
       <c r="O12">
         <v>21.34</v>
@@ -23976,7 +24041,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -23984,7 +24049,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="C13" t="s">
         <v>150</v>
@@ -24002,10 +24067,10 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="s">
-        <v>2061</v>
+        <v>2066</v>
       </c>
       <c r="I13" t="s">
-        <v>2084</v>
+        <v>2089</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -24014,13 +24079,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="O13">
         <v>35</v>
@@ -24029,7 +24094,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>2208</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -24037,7 +24102,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="C14" t="s">
         <v>150</v>
@@ -24055,7 +24120,7 @@
         <v>2.38</v>
       </c>
       <c r="I14" t="s">
-        <v>2085</v>
+        <v>2090</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -24064,13 +24129,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="O14">
         <v>47.66</v>
@@ -24079,7 +24144,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>2209</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -24087,7 +24152,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="C15" t="s">
         <v>151</v>
@@ -24105,10 +24170,10 @@
         <v>2.09</v>
       </c>
       <c r="H15" t="s">
-        <v>2062</v>
+        <v>2067</v>
       </c>
       <c r="I15" t="s">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -24117,13 +24182,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>2148</v>
+        <v>2153</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>2179</v>
+        <v>2184</v>
       </c>
       <c r="O15">
         <v>41.68</v>
@@ -24132,7 +24197,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>2210</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -24140,7 +24205,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="C16" t="s">
         <v>151</v>
@@ -24158,10 +24223,10 @@
         <v>1.82</v>
       </c>
       <c r="H16" t="s">
-        <v>2063</v>
+        <v>2068</v>
       </c>
       <c r="I16" t="s">
-        <v>2087</v>
+        <v>2092</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -24170,13 +24235,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>2149</v>
+        <v>2154</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="O16">
         <v>36.31</v>
@@ -24185,7 +24250,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>2211</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -24193,7 +24258,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="C17" t="s">
         <v>151</v>
@@ -24211,7 +24276,7 @@
         <v>0.77</v>
       </c>
       <c r="I17" t="s">
-        <v>2088</v>
+        <v>2093</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -24220,13 +24285,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>2150</v>
+        <v>2155</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>2181</v>
+        <v>2186</v>
       </c>
       <c r="O17">
         <v>15.49</v>
@@ -24235,7 +24300,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>2212</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -24243,7 +24308,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="C18" t="s">
         <v>151</v>
@@ -24261,7 +24326,7 @@
         <v>1.84</v>
       </c>
       <c r="I18" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -24270,13 +24335,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2151</v>
+        <v>2156</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>2182</v>
+        <v>2187</v>
       </c>
       <c r="O18">
         <v>36.87</v>
@@ -24285,7 +24350,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -24293,7 +24358,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="C19" t="s">
         <v>152</v>
@@ -24311,10 +24376,10 @@
         <v>0.59</v>
       </c>
       <c r="H19" t="s">
-        <v>2064</v>
+        <v>2069</v>
       </c>
       <c r="I19" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -24323,13 +24388,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>2121</v>
+        <v>2126</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>2152</v>
+        <v>2157</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>2183</v>
+        <v>2188</v>
       </c>
       <c r="O19">
         <v>11.86</v>
@@ -24338,7 +24403,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>2214</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -24346,7 +24411,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="C20" t="s">
         <v>152</v>
@@ -24364,7 +24429,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" t="s">
-        <v>2091</v>
+        <v>2096</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -24373,13 +24438,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>2122</v>
+        <v>2127</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>2153</v>
+        <v>2158</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="O20">
         <v>12.35</v>
@@ -24388,7 +24453,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>2215</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -24396,7 +24461,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="C21" t="s">
         <v>152</v>
@@ -24414,10 +24479,10 @@
         <v>0.44</v>
       </c>
       <c r="H21" t="s">
-        <v>2065</v>
+        <v>2070</v>
       </c>
       <c r="I21" t="s">
-        <v>2092</v>
+        <v>2097</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -24426,13 +24491,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2154</v>
+        <v>2159</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="O21">
         <v>8.81</v>
@@ -24441,7 +24506,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>2216</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -24449,7 +24514,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="C22" t="s">
         <v>152</v>
@@ -24467,7 +24532,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -24476,13 +24541,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="O22">
         <v>11.2</v>
@@ -24491,7 +24556,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>2217</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -24499,7 +24564,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="C23" t="s">
         <v>153</v>
@@ -24517,10 +24582,10 @@
         <v>0.61</v>
       </c>
       <c r="H23" t="s">
-        <v>2066</v>
+        <v>2071</v>
       </c>
       <c r="I23" t="s">
-        <v>2094</v>
+        <v>2099</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -24529,13 +24594,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>2187</v>
+        <v>2192</v>
       </c>
       <c r="O23">
         <v>12.25</v>
@@ -24544,7 +24609,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>2218</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -24552,7 +24617,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="C24" t="s">
         <v>153</v>
@@ -24570,10 +24635,10 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="I24" t="s">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -24582,13 +24647,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2157</v>
+        <v>2162</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2188</v>
+        <v>2193</v>
       </c>
       <c r="O24">
         <v>10.89</v>
@@ -24597,7 +24662,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>2219</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -24605,7 +24670,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="C25" t="s">
         <v>153</v>
@@ -24623,10 +24688,10 @@
         <v>0.38</v>
       </c>
       <c r="H25" t="s">
-        <v>2068</v>
+        <v>2073</v>
       </c>
       <c r="I25" t="s">
-        <v>2096</v>
+        <v>2101</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -24635,13 +24700,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>2127</v>
+        <v>2132</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>2158</v>
+        <v>2163</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>2189</v>
+        <v>2194</v>
       </c>
       <c r="O25">
         <v>7.5</v>
@@ -24650,7 +24715,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>2220</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -24658,7 +24723,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="C26" t="s">
         <v>153</v>
@@ -24676,10 +24741,10 @@
         <v>0.62</v>
       </c>
       <c r="H26" t="s">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="I26" t="s">
-        <v>2097</v>
+        <v>2102</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -24688,13 +24753,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>2128</v>
+        <v>2133</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2190</v>
+        <v>2195</v>
       </c>
       <c r="O26">
         <v>12.32</v>
@@ -24703,7 +24768,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>2221</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -24711,7 +24776,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="C27" t="s">
         <v>154</v>
@@ -24729,10 +24794,10 @@
         <v>2.43</v>
       </c>
       <c r="H27" t="s">
-        <v>2070</v>
+        <v>2075</v>
       </c>
       <c r="I27" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -24741,13 +24806,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2160</v>
+        <v>2165</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2191</v>
+        <v>2196</v>
       </c>
       <c r="O27">
         <v>48.66</v>
@@ -24756,7 +24821,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>2222</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -24764,7 +24829,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="C28" t="s">
         <v>154</v>
@@ -24782,7 +24847,7 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="s">
-        <v>2099</v>
+        <v>2104</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -24791,13 +24856,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2192</v>
+        <v>2197</v>
       </c>
       <c r="O28">
         <v>36.49</v>
@@ -24806,7 +24871,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>2223</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -24814,7 +24879,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="C29" t="s">
         <v>154</v>
@@ -24832,10 +24897,10 @@
         <v>1.33</v>
       </c>
       <c r="H29" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
       <c r="I29" t="s">
-        <v>2100</v>
+        <v>2105</v>
       </c>
       <c r="J29">
         <v>19.99</v>
@@ -24844,13 +24909,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2162</v>
+        <v>2167</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2193</v>
+        <v>2198</v>
       </c>
       <c r="O29">
         <v>26.63</v>
@@ -24859,7 +24924,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>2224</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -24867,7 +24932,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="C30" t="s">
         <v>154</v>
@@ -24885,7 +24950,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="J30">
         <v>19.99</v>
@@ -24894,13 +24959,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>2132</v>
+        <v>2137</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2163</v>
+        <v>2168</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2194</v>
+        <v>2199</v>
       </c>
       <c r="O30">
         <v>50.71</v>
@@ -24909,7 +24974,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -24917,7 +24982,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="C31" t="s">
         <v>155</v>
@@ -24935,10 +25000,10 @@
         <v>0.85</v>
       </c>
       <c r="H31" t="s">
-        <v>2072</v>
+        <v>2077</v>
       </c>
       <c r="I31" t="s">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="J31">
         <v>19.99</v>
@@ -24947,13 +25012,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2164</v>
+        <v>2169</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2195</v>
+        <v>2200</v>
       </c>
       <c r="O31">
         <v>16.93</v>
@@ -24962,7 +25027,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -24970,7 +25035,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>2053</v>
+        <v>2058</v>
       </c>
       <c r="C32" t="s">
         <v>155</v>
@@ -24988,7 +25053,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
       <c r="J32">
         <v>19.99</v>
@@ -24997,13 +25062,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>2134</v>
+        <v>2139</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2165</v>
+        <v>2170</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2196</v>
+        <v>2201</v>
       </c>
       <c r="O32">
         <v>17.97</v>
@@ -25012,7 +25077,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>2227</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -25020,7 +25085,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="C33" t="s">
         <v>155</v>
@@ -25038,10 +25103,10 @@
         <v>0.89</v>
       </c>
       <c r="H33" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="I33" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="J33">
         <v>19.99</v>
@@ -25050,13 +25115,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2166</v>
+        <v>2171</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="O33">
         <v>17.84</v>
@@ -25065,7 +25130,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
     </row>
   </sheetData>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="2257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="2257">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="2257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="2267">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -3490,6 +3490,12 @@
     <t>Great Black Wizard</t>
   </si>
   <si>
+    <t>James Jean Coral Skeletor and Panthor</t>
+  </si>
+  <si>
+    <t>James Jean Floral He-Man and Battle Cat</t>
+  </si>
+  <si>
     <t>Laser Power He-Man</t>
   </si>
   <si>
@@ -4027,6 +4033,12 @@
     <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+  </si>
+  <si>
     <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
   </si>
   <si>
@@ -4207,6 +4219,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
   </si>
   <si>
@@ -4387,6 +4405,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-coral-skeletor-and-panthor-13312.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-floral-he-man-and-battle-cat-13313.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
   </si>
   <si>
@@ -4565,6 +4589,12 @@
   </si>
   <si>
     <t>12852</t>
+  </si>
+  <si>
+    <t>13312</t>
+  </si>
+  <si>
+    <t>13313</t>
   </si>
   <si>
     <t>13263</t>
@@ -14280,7 +14310,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14357,13 +14387,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
       <c r="D3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E3" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -14372,10 +14402,10 @@
         <v>0.51</v>
       </c>
       <c r="H3" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="I3" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
       <c r="J3">
         <v>39.95</v>
@@ -14384,13 +14414,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="O3">
         <v>20.51</v>
@@ -14399,7 +14429,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -14407,13 +14437,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="D4" t="s">
         <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -14422,10 +14452,10 @@
         <v>0.6</v>
       </c>
       <c r="H4" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="I4" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="J4">
         <v>59.95</v>
@@ -14434,13 +14464,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
       <c r="O4">
         <v>36.25</v>
@@ -14449,7 +14479,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -14457,13 +14487,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -14472,7 +14502,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="J5">
         <v>59.95</v>
@@ -14481,13 +14511,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="O5">
         <v>138.16</v>
@@ -14496,7 +14526,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
     </row>
   </sheetData>
@@ -15575,7 +15605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -15660,13 +15690,13 @@
         <v>1097</v>
       </c>
       <c r="C3" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E3" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15675,10 +15705,10 @@
         <v>9.84</v>
       </c>
       <c r="H3" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="I3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="J3">
         <v>39.99</v>
@@ -15687,13 +15717,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="O3">
         <v>393.33</v>
@@ -15702,7 +15732,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15713,13 +15743,13 @@
         <v>1098</v>
       </c>
       <c r="C4" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D4" t="s">
         <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15728,7 +15758,7 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="J4">
         <v>269.99</v>
@@ -15737,13 +15767,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="O4">
         <v>323.96</v>
@@ -15752,7 +15782,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -15763,13 +15793,13 @@
         <v>1099</v>
       </c>
       <c r="C5" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -15778,10 +15808,10 @@
         <v>2.75</v>
       </c>
       <c r="H5" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="I5" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="J5">
         <v>39.99</v>
@@ -15790,13 +15820,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="O5">
         <v>110</v>
@@ -15805,7 +15835,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -15816,13 +15846,13 @@
         <v>1100</v>
       </c>
       <c r="C6" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -15831,7 +15861,7 @@
         <v>5.83</v>
       </c>
       <c r="I6" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -15840,13 +15870,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="O6">
         <v>350</v>
@@ -15855,7 +15885,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -15866,13 +15896,13 @@
         <v>1101</v>
       </c>
       <c r="C7" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -15881,7 +15911,7 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -15890,13 +15920,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="O7">
         <v>216.32</v>
@@ -15905,7 +15935,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -15922,7 +15952,7 @@
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F8">
         <v>1537</v>
@@ -15931,10 +15961,10 @@
         <v>0.48</v>
       </c>
       <c r="H8" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="I8" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="J8">
         <v>29.99</v>
@@ -15943,13 +15973,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="O8">
         <v>14.33</v>
@@ -15958,7 +15988,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -15969,13 +15999,13 @@
         <v>1103</v>
       </c>
       <c r="C9" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -15990,13 +16020,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="O9">
         <v>109.99</v>
@@ -16005,7 +16035,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -16016,13 +16046,13 @@
         <v>1104</v>
       </c>
       <c r="C10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16031,7 +16061,7 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -16040,13 +16070,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="O10">
         <v>260</v>
@@ -16055,7 +16085,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -16066,13 +16096,13 @@
         <v>1105</v>
       </c>
       <c r="C11" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D11" t="s">
         <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -16087,13 +16117,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="O11">
         <v>299.95</v>
@@ -16102,7 +16132,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -16113,13 +16143,13 @@
         <v>1106</v>
       </c>
       <c r="C12" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
       </c>
       <c r="E12" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16134,13 +16164,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="O12">
         <v>126.66</v>
@@ -16149,7 +16179,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -16160,13 +16190,13 @@
         <v>1107</v>
       </c>
       <c r="C13" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
       </c>
       <c r="E13" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16175,7 +16205,7 @@
         <v>4.33</v>
       </c>
       <c r="I13" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -16184,13 +16214,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="O13">
         <v>216.67</v>
@@ -16199,7 +16229,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -16210,13 +16240,13 @@
         <v>1108</v>
       </c>
       <c r="C14" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D14" t="s">
         <v>182</v>
       </c>
       <c r="E14" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -16225,7 +16255,7 @@
         <v>1.72</v>
       </c>
       <c r="I14" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -16234,13 +16264,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="O14">
         <v>51.65</v>
@@ -16249,7 +16279,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -16260,13 +16290,13 @@
         <v>1109</v>
       </c>
       <c r="C15" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D15" t="s">
         <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F15">
         <v>503</v>
@@ -16275,7 +16305,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="J15">
         <v>17</v>
@@ -16284,13 +16314,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="O15">
         <v>95.16</v>
@@ -16299,7 +16329,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -16316,7 +16346,7 @@
         <v>183</v>
       </c>
       <c r="E16" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F16">
         <v>606</v>
@@ -16325,10 +16355,10 @@
         <v>2.86</v>
       </c>
       <c r="H16" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="I16" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -16337,13 +16367,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="O16">
         <v>85.70999999999999</v>
@@ -16352,7 +16382,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -16378,10 +16408,10 @@
         <v>2.33</v>
       </c>
       <c r="H17" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="I17" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="J17">
         <v>18</v>
@@ -16390,13 +16420,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="O17">
         <v>42</v>
@@ -16405,7 +16435,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -16422,7 +16452,7 @@
         <v>183</v>
       </c>
       <c r="E18" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -16431,10 +16461,10 @@
         <v>0.53</v>
       </c>
       <c r="H18" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="I18" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="J18">
         <v>150</v>
@@ -16443,13 +16473,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="O18">
         <v>79.75</v>
@@ -16458,7 +16488,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -16475,7 +16505,7 @@
         <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F19">
         <v>536</v>
@@ -16484,7 +16514,7 @@
         <v>4.54</v>
       </c>
       <c r="I19" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="J19">
         <v>17</v>
@@ -16493,13 +16523,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="O19">
         <v>77.23999999999999</v>
@@ -16508,7 +16538,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -16534,10 +16564,10 @@
         <v>1.34</v>
       </c>
       <c r="H20" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="I20" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="J20">
         <v>18</v>
@@ -16546,13 +16576,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="O20">
         <v>24.09</v>
@@ -16561,7 +16591,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -16578,7 +16608,7 @@
         <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F21">
         <v>671</v>
@@ -16587,7 +16617,7 @@
         <v>0.4</v>
       </c>
       <c r="I21" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="J21">
         <v>49.99</v>
@@ -16596,13 +16626,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="O21">
         <v>19.99</v>
@@ -16611,7 +16641,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -16628,7 +16658,7 @@
         <v>183</v>
       </c>
       <c r="E22" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F22">
         <v>911</v>
@@ -16637,10 +16667,10 @@
         <v>1.93</v>
       </c>
       <c r="H22" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="I22" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="J22">
         <v>17</v>
@@ -16649,13 +16679,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="O22">
         <v>32.76</v>
@@ -16664,7 +16694,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -16678,7 +16708,7 @@
         <v>184</v>
       </c>
       <c r="E23" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="F23">
         <v>524</v>
@@ -16687,10 +16717,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="I23" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="J23">
         <v>64.98999999999999</v>
@@ -16699,13 +16729,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="O23">
         <v>129.79</v>
@@ -16714,7 +16744,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -16740,10 +16770,10 @@
         <v>1.91</v>
       </c>
       <c r="H24" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="I24" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -16752,13 +16782,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="O24">
         <v>38.24</v>
@@ -16767,7 +16797,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -16793,10 +16823,10 @@
         <v>1.97</v>
       </c>
       <c r="H25" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="I25" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="J25">
         <v>17.99</v>
@@ -16805,13 +16835,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="O25">
         <v>35.47</v>
@@ -16820,7 +16850,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -16846,10 +16876,10 @@
         <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="I26" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="J26">
         <v>17.99</v>
@@ -16858,13 +16888,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="O26">
         <v>33.25</v>
@@ -16873,7 +16903,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -16890,7 +16920,7 @@
         <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="F27">
         <v>728</v>
@@ -16899,10 +16929,10 @@
         <v>1.2</v>
       </c>
       <c r="H27" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="I27" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="J27">
         <v>35</v>
@@ -16911,13 +16941,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="O27">
         <v>41.94</v>
@@ -16926,7 +16956,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -16952,10 +16982,10 @@
         <v>2.29</v>
       </c>
       <c r="H28" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="I28" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="J28">
         <v>17.99</v>
@@ -16964,13 +16994,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="O28">
         <v>41.11</v>
@@ -16979,7 +17009,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -16996,7 +17026,7 @@
         <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F29">
         <v>508</v>
@@ -17005,10 +17035,10 @@
         <v>0.52</v>
       </c>
       <c r="H29" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="I29" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="J29">
         <v>49.99</v>
@@ -17017,13 +17047,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="O29">
         <v>26.14</v>
@@ -17032,7 +17062,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -17046,7 +17076,7 @@
         <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F30">
         <v>759</v>
@@ -17055,10 +17085,10 @@
         <v>1.88</v>
       </c>
       <c r="H30" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="I30" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="J30">
         <v>31.99</v>
@@ -17067,13 +17097,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="O30">
         <v>60</v>
@@ -17082,7 +17112,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -17099,7 +17129,7 @@
         <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F31">
         <v>568</v>
@@ -17108,10 +17138,10 @@
         <v>1.09</v>
       </c>
       <c r="H31" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="I31" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="J31">
         <v>22.97</v>
@@ -17120,13 +17150,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="O31">
         <v>24.99</v>
@@ -17135,7 +17165,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -17152,7 +17182,7 @@
         <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F32">
         <v>560</v>
@@ -17161,10 +17191,10 @@
         <v>1.56</v>
       </c>
       <c r="H32" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="I32" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="J32">
         <v>20</v>
@@ -17173,13 +17203,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="O32">
         <v>31.2</v>
@@ -17188,7 +17218,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -17205,7 +17235,7 @@
         <v>185</v>
       </c>
       <c r="E33" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -17214,10 +17244,10 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="I33" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="J33">
         <v>550</v>
@@ -17226,13 +17256,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="O33">
         <v>700.51</v>
@@ -17241,7 +17271,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -17258,7 +17288,7 @@
         <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F34">
         <v>664</v>
@@ -17267,10 +17297,10 @@
         <v>1.5</v>
       </c>
       <c r="H34" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="I34" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="J34">
         <v>20</v>
@@ -17279,13 +17309,13 @@
         <v>449</v>
       </c>
       <c r="L34" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="O34">
         <v>29.98</v>
@@ -17294,7 +17324,7 @@
         <v>834</v>
       </c>
       <c r="Q34" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -17311,7 +17341,7 @@
         <v>185</v>
       </c>
       <c r="E35" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="F35">
         <v>572</v>
@@ -17320,10 +17350,10 @@
         <v>0.88</v>
       </c>
       <c r="H35" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="I35" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="J35">
         <v>22.99</v>
@@ -17332,13 +17362,13 @@
         <v>449</v>
       </c>
       <c r="L35" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="O35">
         <v>20.23</v>
@@ -17347,7 +17377,7 @@
         <v>834</v>
       </c>
       <c r="Q35" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -17376,13 +17406,13 @@
         <v>449</v>
       </c>
       <c r="L36" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="O36">
         <v>198.33</v>
@@ -17391,7 +17421,7 @@
         <v>834</v>
       </c>
       <c r="Q36" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -17408,7 +17438,7 @@
         <v>185</v>
       </c>
       <c r="E37" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F37">
         <v>615</v>
@@ -17417,10 +17447,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="I37" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="J37">
         <v>22.97</v>
@@ -17429,13 +17459,13 @@
         <v>449</v>
       </c>
       <c r="L37" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="O37">
         <v>16.07</v>
@@ -17444,7 +17474,7 @@
         <v>834</v>
       </c>
       <c r="Q37" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -17461,7 +17491,7 @@
         <v>185</v>
       </c>
       <c r="E38" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F38">
         <v>708</v>
@@ -17470,10 +17500,10 @@
         <v>1.85</v>
       </c>
       <c r="H38" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="I38" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="J38">
         <v>20</v>
@@ -17482,13 +17512,13 @@
         <v>449</v>
       </c>
       <c r="L38" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="O38">
         <v>36.95</v>
@@ -17497,7 +17527,7 @@
         <v>834</v>
       </c>
       <c r="Q38" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -17514,7 +17544,7 @@
         <v>185</v>
       </c>
       <c r="E39" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -17523,10 +17553,10 @@
         <v>1.25</v>
       </c>
       <c r="H39" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="I39" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="J39">
         <v>45</v>
@@ -17535,13 +17565,13 @@
         <v>449</v>
       </c>
       <c r="L39" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="O39">
         <v>56.07</v>
@@ -17550,7 +17580,7 @@
         <v>834</v>
       </c>
       <c r="Q39" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -17567,7 +17597,7 @@
         <v>185</v>
       </c>
       <c r="E40" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="F40">
         <v>700</v>
@@ -17576,10 +17606,10 @@
         <v>2.24</v>
       </c>
       <c r="H40" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="I40" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -17588,13 +17618,13 @@
         <v>449</v>
       </c>
       <c r="L40" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="O40">
         <v>53.81</v>
@@ -17603,7 +17633,7 @@
         <v>834</v>
       </c>
       <c r="Q40" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -17614,13 +17644,13 @@
         <v>1135</v>
       </c>
       <c r="C41" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D41" t="s">
         <v>185</v>
       </c>
       <c r="E41" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -17629,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="J41">
         <v>90</v>
@@ -17638,13 +17668,13 @@
         <v>449</v>
       </c>
       <c r="L41" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -17653,7 +17683,7 @@
         <v>834</v>
       </c>
       <c r="Q41" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -17664,13 +17694,13 @@
         <v>1136</v>
       </c>
       <c r="C42" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D42" t="s">
         <v>185</v>
       </c>
       <c r="E42" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -17679,10 +17709,10 @@
         <v>2.66</v>
       </c>
       <c r="H42" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="I42" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -17691,13 +17721,13 @@
         <v>449</v>
       </c>
       <c r="L42" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="O42">
         <v>132.99</v>
@@ -17706,7 +17736,7 @@
         <v>834</v>
       </c>
       <c r="Q42" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -17723,7 +17753,7 @@
         <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -17732,10 +17762,10 @@
         <v>1.29</v>
       </c>
       <c r="H43" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="I43" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="J43">
         <v>64.98999999999999</v>
@@ -17744,13 +17774,13 @@
         <v>449</v>
       </c>
       <c r="L43" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="O43">
         <v>83.73</v>
@@ -17759,7 +17789,7 @@
         <v>834</v>
       </c>
       <c r="Q43" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -17776,7 +17806,7 @@
         <v>186</v>
       </c>
       <c r="E44" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -17791,13 +17821,13 @@
         <v>449</v>
       </c>
       <c r="L44" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="O44">
         <v>26.9</v>
@@ -17806,7 +17836,7 @@
         <v>834</v>
       </c>
       <c r="Q44" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -17823,7 +17853,7 @@
         <v>186</v>
       </c>
       <c r="E45" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -17838,13 +17868,13 @@
         <v>449</v>
       </c>
       <c r="L45" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="O45">
         <v>43.75</v>
@@ -17853,7 +17883,7 @@
         <v>834</v>
       </c>
       <c r="Q45" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -17876,7 +17906,7 @@
         <v>2.12</v>
       </c>
       <c r="I46" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="J46">
         <v>19.99</v>
@@ -17885,13 +17915,13 @@
         <v>449</v>
       </c>
       <c r="L46" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="O46">
         <v>42.3</v>
@@ -17900,7 +17930,7 @@
         <v>834</v>
       </c>
       <c r="Q46" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -17911,13 +17941,13 @@
         <v>1141</v>
       </c>
       <c r="C47" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -17926,10 +17956,10 @@
         <v>0.87</v>
       </c>
       <c r="H47" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="I47" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="J47">
         <v>20</v>
@@ -17938,13 +17968,13 @@
         <v>449</v>
       </c>
       <c r="L47" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="O47">
         <v>17.33</v>
@@ -17953,7 +17983,7 @@
         <v>834</v>
       </c>
       <c r="Q47" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -17964,13 +17994,13 @@
         <v>1142</v>
       </c>
       <c r="C48" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -17979,7 +18009,7 @@
         <v>0.23</v>
       </c>
       <c r="I48" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="J48">
         <v>100</v>
@@ -17988,13 +18018,13 @@
         <v>449</v>
       </c>
       <c r="L48" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="O48">
         <v>22.95</v>
@@ -18003,7 +18033,7 @@
         <v>834</v>
       </c>
       <c r="Q48" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -18020,7 +18050,7 @@
         <v>186</v>
       </c>
       <c r="E49" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F49">
         <v>509</v>
@@ -18029,10 +18059,10 @@
         <v>0.49</v>
       </c>
       <c r="H49" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="I49" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="J49">
         <v>29.99</v>
@@ -18041,13 +18071,13 @@
         <v>449</v>
       </c>
       <c r="L49" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="O49">
         <v>14.81</v>
@@ -18056,7 +18086,7 @@
         <v>834</v>
       </c>
       <c r="Q49" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -18073,7 +18103,7 @@
         <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -18082,7 +18112,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="J50">
         <v>34.99</v>
@@ -18091,13 +18121,13 @@
         <v>449</v>
       </c>
       <c r="L50" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="O50">
         <v>28.41</v>
@@ -18106,7 +18136,7 @@
         <v>834</v>
       </c>
       <c r="Q50" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -18123,7 +18153,7 @@
         <v>186</v>
       </c>
       <c r="E51" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F51">
         <v>552</v>
@@ -18132,10 +18162,10 @@
         <v>0.93</v>
       </c>
       <c r="H51" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="I51" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="J51">
         <v>29.99</v>
@@ -18144,13 +18174,13 @@
         <v>449</v>
       </c>
       <c r="L51" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="O51">
         <v>27.99</v>
@@ -18159,7 +18189,7 @@
         <v>834</v>
       </c>
       <c r="Q51" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -18176,7 +18206,7 @@
         <v>186</v>
       </c>
       <c r="E52" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -18185,10 +18215,10 @@
         <v>1.06</v>
       </c>
       <c r="H52" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="I52" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="J52">
         <v>31.99</v>
@@ -18197,13 +18227,13 @@
         <v>449</v>
       </c>
       <c r="L52" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="O52">
         <v>34.04</v>
@@ -18212,7 +18242,7 @@
         <v>834</v>
       </c>
       <c r="Q52" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -18229,7 +18259,7 @@
         <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -18238,10 +18268,10 @@
         <v>0.92</v>
       </c>
       <c r="H53" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="I53" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="J53">
         <v>44.99</v>
@@ -18250,13 +18280,13 @@
         <v>449</v>
       </c>
       <c r="L53" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="O53">
         <v>41.52</v>
@@ -18265,7 +18295,7 @@
         <v>834</v>
       </c>
       <c r="Q53" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -18282,7 +18312,7 @@
         <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F54">
         <v>609</v>
@@ -18291,10 +18321,10 @@
         <v>1.17</v>
       </c>
       <c r="H54" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="I54" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="J54">
         <v>20</v>
@@ -18303,13 +18333,13 @@
         <v>449</v>
       </c>
       <c r="L54" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="O54">
         <v>23.48</v>
@@ -18318,7 +18348,7 @@
         <v>834</v>
       </c>
       <c r="Q54" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -18335,7 +18365,7 @@
         <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -18344,10 +18374,10 @@
         <v>0.87</v>
       </c>
       <c r="H55" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="I55" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="J55">
         <v>29.99</v>
@@ -18356,13 +18386,13 @@
         <v>449</v>
       </c>
       <c r="L55" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="O55">
         <v>26.18</v>
@@ -18371,7 +18401,7 @@
         <v>834</v>
       </c>
       <c r="Q55" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -18388,7 +18418,7 @@
         <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -18397,10 +18427,10 @@
         <v>0.97</v>
       </c>
       <c r="H56" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="I56" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="J56">
         <v>69.98999999999999</v>
@@ -18409,13 +18439,13 @@
         <v>449</v>
       </c>
       <c r="L56" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="O56">
         <v>67.75</v>
@@ -18424,7 +18454,7 @@
         <v>834</v>
       </c>
       <c r="Q56" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -18450,10 +18480,10 @@
         <v>0.87</v>
       </c>
       <c r="H57" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="I57" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="J57">
         <v>19.99</v>
@@ -18462,13 +18492,13 @@
         <v>449</v>
       </c>
       <c r="L57" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="O57">
         <v>17.42</v>
@@ -18477,7 +18507,7 @@
         <v>834</v>
       </c>
       <c r="Q57" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -18494,7 +18524,7 @@
         <v>186</v>
       </c>
       <c r="E58" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -18503,10 +18533,10 @@
         <v>1.1</v>
       </c>
       <c r="H58" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="I58" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="J58">
         <v>20</v>
@@ -18515,13 +18545,13 @@
         <v>449</v>
       </c>
       <c r="L58" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="O58">
         <v>22</v>
@@ -18530,7 +18560,7 @@
         <v>834</v>
       </c>
       <c r="Q58" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -18562,13 +18592,13 @@
         <v>449</v>
       </c>
       <c r="L59" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="O59">
         <v>46.28</v>
@@ -18577,7 +18607,7 @@
         <v>834</v>
       </c>
       <c r="Q59" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -18594,7 +18624,7 @@
         <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -18609,13 +18639,13 @@
         <v>449</v>
       </c>
       <c r="L60" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="O60">
         <v>40.52</v>
@@ -18624,7 +18654,7 @@
         <v>834</v>
       </c>
       <c r="Q60" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -18641,7 +18671,7 @@
         <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -18650,19 +18680,19 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>449</v>
       </c>
       <c r="L61" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -18671,12 +18701,12 @@
         <v>834</v>
       </c>
       <c r="Q61" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="62" spans="1:17">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B62" t="s">
         <v>1156</v>
@@ -18688,7 +18718,7 @@
         <v>187</v>
       </c>
       <c r="E62" t="s">
-        <v>195</v>
+        <v>1186</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -18697,19 +18727,19 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>449</v>
       </c>
       <c r="L62" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -18718,14 +18748,108 @@
         <v>834</v>
       </c>
       <c r="Q62" t="s">
-        <v>1515</v>
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C63" t="s">
+        <v>171</v>
+      </c>
+      <c r="D63" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>33</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L63" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D64" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>22</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>1525</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A62">
+  <conditionalFormatting sqref="A3:A64">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -18734,7 +18858,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A64">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18861,6 +18985,12 @@
     <hyperlink ref="K62" r:id="rId120"/>
     <hyperlink ref="M62" r:id="rId121"/>
     <hyperlink ref="N62" r:id="rId122"/>
+    <hyperlink ref="K63" r:id="rId123"/>
+    <hyperlink ref="M63" r:id="rId124"/>
+    <hyperlink ref="N63" r:id="rId125"/>
+    <hyperlink ref="K64" r:id="rId126"/>
+    <hyperlink ref="M64" r:id="rId127"/>
+    <hyperlink ref="N64" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18873,7 +19003,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18950,7 +19080,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -18959,7 +19089,7 @@
         <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F3">
         <v>1047</v>
@@ -18968,7 +19098,7 @@
         <v>0.67</v>
       </c>
       <c r="I3" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="J3">
         <v>49.99</v>
@@ -18977,13 +19107,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="O3">
         <v>33.33</v>
@@ -18992,7 +19122,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19000,7 +19130,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -19015,10 +19145,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
       <c r="I4" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="J4">
         <v>24.99</v>
@@ -19027,13 +19157,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1601</v>
+        <v>1611</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="O4">
         <v>13.69</v>
@@ -19042,7 +19172,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19050,13 +19180,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
       </c>
       <c r="E5" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
       <c r="F5">
         <v>1752</v>
@@ -19065,10 +19195,10 @@
         <v>1.21</v>
       </c>
       <c r="H5" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="I5" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="J5">
         <v>74.98999999999999</v>
@@ -19077,13 +19207,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="O5">
         <v>90.84999999999999</v>
@@ -19092,7 +19222,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19100,13 +19230,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F6">
         <v>1538</v>
@@ -19115,10 +19245,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="I6" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -19127,13 +19257,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
       <c r="O6">
         <v>15.03</v>
@@ -19142,7 +19272,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -19150,7 +19280,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -19165,10 +19295,10 @@
         <v>0.59</v>
       </c>
       <c r="H7" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="I7" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="J7">
         <v>24.99</v>
@@ -19177,13 +19307,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1604</v>
+        <v>1614</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="O7">
         <v>14.62</v>
@@ -19192,7 +19322,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -19200,7 +19330,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="C8" t="s">
         <v>170</v>
@@ -19209,7 +19339,7 @@
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F8">
         <v>1179</v>
@@ -19218,10 +19348,10 @@
         <v>0.54</v>
       </c>
       <c r="H8" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="I8" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="J8">
         <v>39.99</v>
@@ -19230,13 +19360,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1605</v>
+        <v>1615</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="O8">
         <v>21.68</v>
@@ -19245,7 +19375,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -19253,13 +19383,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F9">
         <v>1805</v>
@@ -19268,10 +19398,10 @@
         <v>0.53</v>
       </c>
       <c r="H9" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="I9" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="J9">
         <v>29.99</v>
@@ -19280,13 +19410,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="O9">
         <v>16</v>
@@ -19295,7 +19425,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -19303,13 +19433,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F10">
         <v>1571</v>
@@ -19318,10 +19448,10 @@
         <v>0.74</v>
       </c>
       <c r="H10" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="I10" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -19330,13 +19460,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
       <c r="O10">
         <v>22.11</v>
@@ -19345,7 +19475,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -19353,13 +19483,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="D11" t="s">
         <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F11">
         <v>1159</v>
@@ -19368,10 +19498,10 @@
         <v>0.59</v>
       </c>
       <c r="H11" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="I11" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="J11">
         <v>29.99</v>
@@ -19380,13 +19510,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="O11">
         <v>17.83</v>
@@ -19395,7 +19525,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -19403,7 +19533,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="D12" t="s">
         <v>183</v>
@@ -19418,10 +19548,10 @@
         <v>0.71</v>
       </c>
       <c r="H12" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="I12" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -19430,13 +19560,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
       <c r="O12">
         <v>17.77</v>
@@ -19445,7 +19575,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -19453,13 +19583,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="D13" t="s">
         <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F13">
         <v>857</v>
@@ -19468,10 +19598,10 @@
         <v>1.31</v>
       </c>
       <c r="H13" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="I13" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="J13">
         <v>29.99</v>
@@ -19480,13 +19610,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="O13">
         <v>39.37</v>
@@ -19495,7 +19625,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -19503,13 +19633,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
       </c>
       <c r="E14" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F14">
         <v>1215</v>
@@ -19518,10 +19648,10 @@
         <v>0.75</v>
       </c>
       <c r="H14" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="I14" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="J14">
         <v>29.99</v>
@@ -19530,13 +19660,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
       <c r="O14">
         <v>22.5</v>
@@ -19545,7 +19675,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -19553,13 +19683,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
       </c>
       <c r="E15" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F15">
         <v>755</v>
@@ -19580,13 +19710,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="O15">
         <v>36.5</v>
@@ -19595,7 +19725,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -19603,13 +19733,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="D16" t="s">
         <v>184</v>
       </c>
       <c r="E16" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="F16">
         <v>888</v>
@@ -19618,10 +19748,10 @@
         <v>3.33</v>
       </c>
       <c r="H16" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="I16" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="J16">
         <v>79.98999999999999</v>
@@ -19630,13 +19760,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="O16">
         <v>266.38</v>
@@ -19645,7 +19775,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -19653,13 +19783,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F17">
         <v>1103</v>
@@ -19668,10 +19798,10 @@
         <v>0.42</v>
       </c>
       <c r="H17" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="I17" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
       <c r="J17">
         <v>44.99</v>
@@ -19680,13 +19810,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="O17">
         <v>18.76</v>
@@ -19695,7 +19825,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -19703,13 +19833,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="D18" t="s">
         <v>185</v>
       </c>
       <c r="E18" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F18">
         <v>520</v>
@@ -19718,10 +19848,10 @@
         <v>0.85</v>
       </c>
       <c r="H18" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="I18" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="J18">
         <v>39.99</v>
@@ -19730,13 +19860,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
       <c r="O18">
         <v>33.99</v>
@@ -19745,7 +19875,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -19753,7 +19883,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
       <c r="C19" t="s">
         <v>171</v>
@@ -19774,13 +19904,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1616</v>
+        <v>1626</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="O19">
         <v>180</v>
@@ -19789,7 +19919,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -19797,7 +19927,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="C20" t="s">
         <v>171</v>
@@ -19806,7 +19936,7 @@
         <v>185</v>
       </c>
       <c r="E20" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -19815,10 +19945,10 @@
         <v>1.12</v>
       </c>
       <c r="H20" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="I20" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
       <c r="J20">
         <v>33</v>
@@ -19827,13 +19957,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1617</v>
+        <v>1627</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
       <c r="O20">
         <v>37.07</v>
@@ -19842,7 +19972,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -19850,13 +19980,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="D21" t="s">
         <v>185</v>
       </c>
       <c r="E21" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F21">
         <v>799</v>
@@ -19865,10 +19995,10 @@
         <v>0.89</v>
       </c>
       <c r="H21" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
       <c r="I21" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -19877,13 +20007,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="O21">
         <v>26.75</v>
@@ -19892,7 +20022,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -19900,13 +20030,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="D22" t="s">
         <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -19915,10 +20045,10 @@
         <v>1.38</v>
       </c>
       <c r="H22" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="I22" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="J22">
         <v>91.98999999999999</v>
@@ -19927,13 +20057,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1597</v>
+        <v>1607</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1619</v>
+        <v>1629</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
       <c r="O22">
         <v>126.79</v>
@@ -19942,7 +20072,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -19950,13 +20080,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="D23" t="s">
         <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -19965,10 +20095,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="I23" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
       <c r="J23">
         <v>124.99</v>
@@ -19977,13 +20107,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1598</v>
+        <v>1608</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1642</v>
+        <v>1652</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -19992,7 +20122,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -20000,7 +20130,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="C24" t="s">
         <v>171</v>
@@ -20009,7 +20139,7 @@
         <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -20024,13 +20154,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1599</v>
+        <v>1609</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1621</v>
+        <v>1631</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1643</v>
+        <v>1653</v>
       </c>
       <c r="O24">
         <v>499.99</v>
@@ -20039,7 +20169,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
     </row>
   </sheetData>
@@ -20116,7 +20246,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20193,7 +20323,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -20202,7 +20332,7 @@
         <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -20211,7 +20341,7 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="s">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="J3">
         <v>34.99</v>
@@ -20220,13 +20350,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1673</v>
+        <v>1683</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1679</v>
+        <v>1689</v>
       </c>
       <c r="O3">
         <v>36.09</v>
@@ -20235,7 +20365,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1682</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -20243,7 +20373,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
@@ -20252,7 +20382,7 @@
         <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -20261,7 +20391,7 @@
         <v>0.64</v>
       </c>
       <c r="I4" t="s">
-        <v>1671</v>
+        <v>1681</v>
       </c>
       <c r="J4">
         <v>34.99</v>
@@ -20270,13 +20400,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1677</v>
+        <v>1687</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="O4">
         <v>22.55</v>
@@ -20285,7 +20415,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1683</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -20293,7 +20423,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -20302,7 +20432,7 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -20311,7 +20441,7 @@
         <v>1.36</v>
       </c>
       <c r="I5" t="s">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="J5">
         <v>34.99</v>
@@ -20320,13 +20450,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1675</v>
+        <v>1685</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1678</v>
+        <v>1688</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1681</v>
+        <v>1691</v>
       </c>
       <c r="O5">
         <v>47.57</v>
@@ -20335,7 +20465,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1684</v>
+        <v>1694</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20504,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1685</v>
+        <v>1695</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20451,7 +20581,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1686</v>
+        <v>1696</v>
       </c>
       <c r="C3" t="s">
         <v>170</v>
@@ -20469,10 +20599,10 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="s">
-        <v>1717</v>
+        <v>1727</v>
       </c>
       <c r="I3" t="s">
-        <v>1750</v>
+        <v>1760</v>
       </c>
       <c r="J3">
         <v>24.99</v>
@@ -20481,13 +20611,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1784</v>
+        <v>1794</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1856</v>
+        <v>1866</v>
       </c>
       <c r="O3">
         <v>30.44</v>
@@ -20496,7 +20626,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -20504,7 +20634,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1687</v>
+        <v>1697</v>
       </c>
       <c r="C4" t="s">
         <v>170</v>
@@ -20513,7 +20643,7 @@
         <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -20522,10 +20652,10 @@
         <v>0.52</v>
       </c>
       <c r="H4" t="s">
-        <v>1718</v>
+        <v>1728</v>
       </c>
       <c r="I4" t="s">
-        <v>1751</v>
+        <v>1761</v>
       </c>
       <c r="J4">
         <v>24.97</v>
@@ -20534,13 +20664,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1785</v>
+        <v>1795</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="O4">
         <v>12.96</v>
@@ -20549,7 +20679,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -20557,7 +20687,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>1688</v>
+        <v>1698</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -20578,13 +20708,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1858</v>
+        <v>1868</v>
       </c>
       <c r="O5">
         <v>48.73</v>
@@ -20593,7 +20723,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -20601,7 +20731,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1689</v>
+        <v>1699</v>
       </c>
       <c r="C6" t="s">
         <v>176</v>
@@ -20619,10 +20749,10 @@
         <v>0.92</v>
       </c>
       <c r="H6" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="I6" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="J6">
         <v>24.99</v>
@@ -20631,13 +20761,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1787</v>
+        <v>1797</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -20646,7 +20776,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -20654,7 +20784,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>1690</v>
+        <v>1700</v>
       </c>
       <c r="C7" t="s">
         <v>170</v>
@@ -20663,7 +20793,7 @@
         <v>185</v>
       </c>
       <c r="E7" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -20672,10 +20802,10 @@
         <v>0.82</v>
       </c>
       <c r="H7" t="s">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="I7" t="s">
-        <v>1753</v>
+        <v>1763</v>
       </c>
       <c r="J7">
         <v>24.97</v>
@@ -20684,13 +20814,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="O7">
         <v>20.41</v>
@@ -20699,7 +20829,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -20707,7 +20837,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="C8" t="s">
         <v>170</v>
@@ -20731,13 +20861,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="O8">
         <v>37.99</v>
@@ -20746,7 +20876,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -20754,7 +20884,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1692</v>
+        <v>1702</v>
       </c>
       <c r="C9" t="s">
         <v>176</v>
@@ -20772,10 +20902,10 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="s">
-        <v>1721</v>
+        <v>1731</v>
       </c>
       <c r="I9" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="J9">
         <v>24.99</v>
@@ -20784,13 +20914,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="O9">
         <v>37.71</v>
@@ -20799,7 +20929,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -20807,7 +20937,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>1693</v>
+        <v>1703</v>
       </c>
       <c r="C10" t="s">
         <v>176</v>
@@ -20825,10 +20955,10 @@
         <v>0.78</v>
       </c>
       <c r="H10" t="s">
-        <v>1722</v>
+        <v>1732</v>
       </c>
       <c r="I10" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -20837,13 +20967,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1827</v>
+        <v>1837</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1863</v>
+        <v>1873</v>
       </c>
       <c r="O10">
         <v>19.54</v>
@@ -20852,7 +20982,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -20860,7 +20990,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>1694</v>
+        <v>1704</v>
       </c>
       <c r="C11" t="s">
         <v>148</v>
@@ -20878,10 +21008,10 @@
         <v>0.82</v>
       </c>
       <c r="H11" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="I11" t="s">
-        <v>1756</v>
+        <v>1766</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -20890,13 +21020,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1864</v>
+        <v>1874</v>
       </c>
       <c r="O11">
         <v>16.43</v>
@@ -20905,7 +21035,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -20913,7 +21043,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1695</v>
+        <v>1705</v>
       </c>
       <c r="C12" t="s">
         <v>148</v>
@@ -20931,10 +21061,10 @@
         <v>1.61</v>
       </c>
       <c r="H12" t="s">
-        <v>1724</v>
+        <v>1734</v>
       </c>
       <c r="I12" t="s">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -20943,13 +21073,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1829</v>
+        <v>1839</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="O12">
         <v>32.14</v>
@@ -20958,7 +21088,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1901</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -20966,7 +21096,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
       <c r="C13" t="s">
         <v>148</v>
@@ -20984,10 +21114,10 @@
         <v>0.71</v>
       </c>
       <c r="H13" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="I13" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -20996,13 +21126,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="O13">
         <v>14.27</v>
@@ -21011,7 +21141,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -21019,7 +21149,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="C14" t="s">
         <v>148</v>
@@ -21037,10 +21167,10 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
       <c r="I14" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -21049,13 +21179,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>1831</v>
+        <v>1841</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="O14">
         <v>23.5</v>
@@ -21064,7 +21194,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -21090,10 +21220,10 @@
         <v>0.65</v>
       </c>
       <c r="H15" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="I15" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -21102,13 +21232,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>1868</v>
+        <v>1878</v>
       </c>
       <c r="O15">
         <v>12.92</v>
@@ -21117,7 +21247,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -21125,7 +21255,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1698</v>
+        <v>1708</v>
       </c>
       <c r="C16" t="s">
         <v>149</v>
@@ -21143,10 +21273,10 @@
         <v>0.78</v>
       </c>
       <c r="H16" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
       <c r="I16" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -21155,13 +21285,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1869</v>
+        <v>1879</v>
       </c>
       <c r="O16">
         <v>15.59</v>
@@ -21170,7 +21300,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -21178,7 +21308,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1699</v>
+        <v>1709</v>
       </c>
       <c r="C17" t="s">
         <v>149</v>
@@ -21196,10 +21326,10 @@
         <v>2.22</v>
       </c>
       <c r="H17" t="s">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="I17" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -21208,13 +21338,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="O17">
         <v>44.34</v>
@@ -21223,7 +21353,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -21231,7 +21361,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1700</v>
+        <v>1710</v>
       </c>
       <c r="C18" t="s">
         <v>149</v>
@@ -21249,10 +21379,10 @@
         <v>2.09</v>
       </c>
       <c r="H18" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="I18" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -21261,13 +21391,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1835</v>
+        <v>1845</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>1871</v>
+        <v>1881</v>
       </c>
       <c r="O18">
         <v>41.71</v>
@@ -21276,7 +21406,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -21284,7 +21414,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="C19" t="s">
         <v>150</v>
@@ -21302,10 +21432,10 @@
         <v>0.72</v>
       </c>
       <c r="H19" t="s">
-        <v>1731</v>
+        <v>1741</v>
       </c>
       <c r="I19" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -21314,13 +21444,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>1800</v>
+        <v>1810</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1836</v>
+        <v>1846</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1872</v>
+        <v>1882</v>
       </c>
       <c r="O19">
         <v>14.3</v>
@@ -21329,7 +21459,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>1908</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -21337,7 +21467,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1702</v>
+        <v>1712</v>
       </c>
       <c r="C20" t="s">
         <v>150</v>
@@ -21355,10 +21485,10 @@
         <v>0.8</v>
       </c>
       <c r="H20" t="s">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="I20" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -21367,13 +21497,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1873</v>
+        <v>1883</v>
       </c>
       <c r="O20">
         <v>15.98</v>
@@ -21382,7 +21512,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -21408,10 +21538,10 @@
         <v>0.9</v>
       </c>
       <c r="H21" t="s">
-        <v>1733</v>
+        <v>1743</v>
       </c>
       <c r="I21" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -21420,13 +21550,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>1802</v>
+        <v>1812</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1838</v>
+        <v>1848</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="O21">
         <v>17.92</v>
@@ -21435,7 +21565,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -21461,10 +21591,10 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>1734</v>
+        <v>1744</v>
       </c>
       <c r="I22" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -21473,13 +21603,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1839</v>
+        <v>1849</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="O22">
         <v>10.03</v>
@@ -21488,7 +21618,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>1911</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -21496,7 +21626,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="C23" t="s">
         <v>151</v>
@@ -21514,10 +21644,10 @@
         <v>0.89</v>
       </c>
       <c r="H23" t="s">
-        <v>1735</v>
+        <v>1745</v>
       </c>
       <c r="I23" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -21526,13 +21656,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="O23">
         <v>17.83</v>
@@ -21541,7 +21671,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -21549,7 +21679,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="C24" t="s">
         <v>151</v>
@@ -21567,10 +21697,10 @@
         <v>0.72</v>
       </c>
       <c r="H24" t="s">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="I24" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -21579,13 +21709,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="O24">
         <v>14.35</v>
@@ -21594,7 +21724,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -21620,10 +21750,10 @@
         <v>0.73</v>
       </c>
       <c r="H25" t="s">
-        <v>1737</v>
+        <v>1747</v>
       </c>
       <c r="I25" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -21632,13 +21762,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>1806</v>
+        <v>1816</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1842</v>
+        <v>1852</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="O25">
         <v>14.69</v>
@@ -21647,7 +21777,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -21673,7 +21803,7 @@
         <v>7.29</v>
       </c>
       <c r="I26" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -21682,13 +21812,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>1807</v>
+        <v>1817</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1843</v>
+        <v>1853</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>1879</v>
+        <v>1889</v>
       </c>
       <c r="O26">
         <v>145.79</v>
@@ -21697,7 +21827,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -21705,7 +21835,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1705</v>
+        <v>1715</v>
       </c>
       <c r="C27" t="s">
         <v>151</v>
@@ -21723,10 +21853,10 @@
         <v>0.88</v>
       </c>
       <c r="H27" t="s">
-        <v>1738</v>
+        <v>1748</v>
       </c>
       <c r="I27" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -21735,13 +21865,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>1808</v>
+        <v>1818</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="O27">
         <v>17.58</v>
@@ -21750,7 +21880,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>1916</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -21758,7 +21888,7 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>1706</v>
+        <v>1716</v>
       </c>
       <c r="C28" t="s">
         <v>151</v>
@@ -21776,10 +21906,10 @@
         <v>0.82</v>
       </c>
       <c r="H28" t="s">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="I28" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -21788,13 +21918,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="O28">
         <v>16.46</v>
@@ -21803,7 +21933,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -21811,7 +21941,7 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="C29" t="s">
         <v>152</v>
@@ -21820,7 +21950,7 @@
         <v>185</v>
       </c>
       <c r="E29" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -21829,10 +21959,10 @@
         <v>0.96</v>
       </c>
       <c r="H29" t="s">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="I29" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="J29">
         <v>20.99</v>
@@ -21841,13 +21971,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="O29">
         <v>20.09</v>
@@ -21856,7 +21986,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -21864,7 +21994,7 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>1708</v>
+        <v>1718</v>
       </c>
       <c r="C30" t="s">
         <v>152</v>
@@ -21873,7 +22003,7 @@
         <v>185</v>
       </c>
       <c r="E30" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -21882,10 +22012,10 @@
         <v>0.83</v>
       </c>
       <c r="H30" t="s">
-        <v>1741</v>
+        <v>1751</v>
       </c>
       <c r="I30" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="J30">
         <v>20.99</v>
@@ -21894,13 +22024,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1847</v>
+        <v>1857</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="O30">
         <v>17.33</v>
@@ -21909,7 +22039,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -21917,7 +22047,7 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>1709</v>
+        <v>1719</v>
       </c>
       <c r="C31" t="s">
         <v>152</v>
@@ -21926,7 +22056,7 @@
         <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -21935,10 +22065,10 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="I31" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="J31">
         <v>20.99</v>
@@ -21947,13 +22077,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>1848</v>
+        <v>1858</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="O31">
         <v>15.75</v>
@@ -21962,7 +22092,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -21979,7 +22109,7 @@
         <v>185</v>
       </c>
       <c r="E32" t="s">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -21988,10 +22118,10 @@
         <v>0.84</v>
       </c>
       <c r="H32" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="I32" t="s">
-        <v>1777</v>
+        <v>1787</v>
       </c>
       <c r="J32">
         <v>20.99</v>
@@ -22000,13 +22130,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1849</v>
+        <v>1859</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="O32">
         <v>17.65</v>
@@ -22015,7 +22145,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -22023,7 +22153,7 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="C33" t="s">
         <v>153</v>
@@ -22041,10 +22171,10 @@
         <v>0.76</v>
       </c>
       <c r="H33" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="I33" t="s">
-        <v>1778</v>
+        <v>1788</v>
       </c>
       <c r="J33">
         <v>23.99</v>
@@ -22053,13 +22183,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="O33">
         <v>18.33</v>
@@ -22068,7 +22198,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -22076,7 +22206,7 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="C34" t="s">
         <v>153</v>
@@ -22094,10 +22224,10 @@
         <v>0.86</v>
       </c>
       <c r="H34" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="I34" t="s">
-        <v>1779</v>
+        <v>1789</v>
       </c>
       <c r="J34">
         <v>23.99</v>
@@ -22106,13 +22236,13 @@
         <v>449</v>
       </c>
       <c r="L34" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>1851</v>
+        <v>1861</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="O34">
         <v>20.58</v>
@@ -22121,7 +22251,7 @@
         <v>834</v>
       </c>
       <c r="Q34" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -22129,7 +22259,7 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="C35" t="s">
         <v>153</v>
@@ -22147,10 +22277,10 @@
         <v>0.64</v>
       </c>
       <c r="H35" t="s">
-        <v>1746</v>
+        <v>1756</v>
       </c>
       <c r="I35" t="s">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="J35">
         <v>23.99</v>
@@ -22159,13 +22289,13 @@
         <v>449</v>
       </c>
       <c r="L35" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="O35">
         <v>15.31</v>
@@ -22174,7 +22304,7 @@
         <v>834</v>
       </c>
       <c r="Q35" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -22200,10 +22330,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H36" t="s">
-        <v>1747</v>
+        <v>1757</v>
       </c>
       <c r="I36" t="s">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="J36">
         <v>23.99</v>
@@ -22212,13 +22342,13 @@
         <v>449</v>
       </c>
       <c r="L36" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="O36">
         <v>19.5</v>
@@ -22227,7 +22357,7 @@
         <v>834</v>
       </c>
       <c r="Q36" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -22235,16 +22365,16 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="C37" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D37" t="s">
         <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -22253,10 +22383,10 @@
         <v>0.99</v>
       </c>
       <c r="H37" t="s">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="I37" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="J37">
         <v>45</v>
@@ -22265,13 +22395,13 @@
         <v>449</v>
       </c>
       <c r="L37" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1854</v>
+        <v>1864</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="O37">
         <v>44.69</v>
@@ -22280,7 +22410,7 @@
         <v>834</v>
       </c>
       <c r="Q37" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -22288,7 +22418,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1714</v>
+        <v>1724</v>
       </c>
       <c r="C38" t="s">
         <v>170</v>
@@ -22297,7 +22427,7 @@
         <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>1715</v>
+        <v>1725</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -22306,10 +22436,10 @@
         <v>0.78</v>
       </c>
       <c r="H38" t="s">
-        <v>1749</v>
+        <v>1759</v>
       </c>
       <c r="I38" t="s">
-        <v>1783</v>
+        <v>1793</v>
       </c>
       <c r="J38">
         <v>24.97</v>
@@ -22318,13 +22448,13 @@
         <v>449</v>
       </c>
       <c r="L38" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="O38">
         <v>19.45</v>
@@ -22333,7 +22463,7 @@
         <v>834</v>
       </c>
       <c r="Q38" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
     </row>
   </sheetData>
@@ -22438,7 +22568,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22515,7 +22645,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
@@ -22533,10 +22663,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="I3" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -22545,13 +22675,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="O3">
         <v>23.26</v>
@@ -22560,7 +22690,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22568,7 +22698,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
@@ -22586,10 +22716,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="I4" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -22598,13 +22728,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1978</v>
+        <v>1988</v>
       </c>
       <c r="O4">
         <v>16.41</v>
@@ -22613,7 +22743,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -22621,7 +22751,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="C5" t="s">
         <v>148</v>
@@ -22639,10 +22769,10 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="I5" t="s">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -22651,13 +22781,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="O5">
         <v>23.79</v>
@@ -22666,7 +22796,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>1990</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -22674,7 +22804,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
@@ -22683,7 +22813,7 @@
         <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -22692,10 +22822,10 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="I6" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -22704,13 +22834,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="O6">
         <v>23.94</v>
@@ -22719,7 +22849,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -22745,7 +22875,7 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -22754,13 +22884,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -22769,7 +22899,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>1992</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -22777,7 +22907,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="C8" t="s">
         <v>149</v>
@@ -22795,7 +22925,7 @@
         <v>1.52</v>
       </c>
       <c r="H8" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -22804,13 +22934,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="O8">
         <v>30.47</v>
@@ -22819,7 +22949,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -22827,7 +22957,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="C9" t="s">
         <v>149</v>
@@ -22845,7 +22975,7 @@
         <v>1.02</v>
       </c>
       <c r="H9" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -22854,13 +22984,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="O9">
         <v>20.39</v>
@@ -22869,7 +22999,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -22877,7 +23007,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="C10" t="s">
         <v>150</v>
@@ -22895,7 +23025,7 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="s">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -22904,13 +23034,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="O10">
         <v>29.95</v>
@@ -22919,7 +23049,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -22927,7 +23057,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1936</v>
+        <v>1946</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -22945,10 +23075,10 @@
         <v>1.29</v>
       </c>
       <c r="H11" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="I11" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="J11">
         <v>24.99</v>
@@ -22957,13 +23087,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>1963</v>
+        <v>1973</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="O11">
         <v>32.18</v>
@@ -22972,7 +23102,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -22980,7 +23110,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="C12" t="s">
         <v>150</v>
@@ -22998,10 +23128,10 @@
         <v>1.2</v>
       </c>
       <c r="H12" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="I12" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -23010,13 +23140,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="O12">
         <v>29.95</v>
@@ -23025,7 +23155,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -23033,7 +23163,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1938</v>
+        <v>1948</v>
       </c>
       <c r="C13" t="s">
         <v>150</v>
@@ -23051,7 +23181,7 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="s">
-        <v>1954</v>
+        <v>1964</v>
       </c>
       <c r="J13">
         <v>24.99</v>
@@ -23060,13 +23190,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1976</v>
+        <v>1986</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="O13">
         <v>29.95</v>
@@ -23075,7 +23205,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
     </row>
   </sheetData>
@@ -23132,7 +23262,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23209,7 +23339,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -23218,7 +23348,7 @@
         <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -23227,10 +23357,10 @@
         <v>0.65</v>
       </c>
       <c r="H3" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="I3" t="s">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="J3">
         <v>32.99</v>
@@ -23239,13 +23369,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="O3">
         <v>21.34</v>
@@ -23254,7 +23384,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23262,7 +23392,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
@@ -23271,7 +23401,7 @@
         <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -23280,10 +23410,10 @@
         <v>0.68</v>
       </c>
       <c r="H4" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="I4" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="J4">
         <v>32.99</v>
@@ -23292,13 +23422,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="O4">
         <v>22.3</v>
@@ -23307,7 +23437,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2025</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -23315,7 +23445,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
@@ -23324,7 +23454,7 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -23333,10 +23463,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="s">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="I5" t="s">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="J5">
         <v>29.99</v>
@@ -23345,13 +23475,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="O5">
         <v>46.29</v>
@@ -23360,7 +23490,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -23368,7 +23498,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="C6" t="s">
         <v>176</v>
@@ -23377,7 +23507,7 @@
         <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -23386,10 +23516,10 @@
         <v>1.37</v>
       </c>
       <c r="H6" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="I6" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -23398,13 +23528,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2023</v>
+        <v>2033</v>
       </c>
       <c r="O6">
         <v>41.15</v>
@@ -23413,7 +23543,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>2027</v>
+        <v>2037</v>
       </c>
     </row>
   </sheetData>
@@ -23454,7 +23584,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23531,13 +23661,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E3" t="s">
         <v>190</v>
@@ -23549,10 +23679,10 @@
         <v>0.99</v>
       </c>
       <c r="H3" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="I3" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -23561,13 +23691,13 @@
         <v>449</v>
       </c>
       <c r="L3" t="s">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>2141</v>
+        <v>2151</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2172</v>
+        <v>2182</v>
       </c>
       <c r="O3">
         <v>19.84</v>
@@ -23576,7 +23706,7 @@
         <v>834</v>
       </c>
       <c r="Q3" t="s">
-        <v>2203</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23584,13 +23714,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E4" t="s">
         <v>190</v>
@@ -23602,7 +23732,7 @@
         <v>1.42</v>
       </c>
       <c r="I4" t="s">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -23611,13 +23741,13 @@
         <v>449</v>
       </c>
       <c r="L4" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="O4">
         <v>28.43</v>
@@ -23626,7 +23756,7 @@
         <v>834</v>
       </c>
       <c r="Q4" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -23634,13 +23764,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="C5" t="s">
         <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E5" t="s">
         <v>190</v>
@@ -23652,10 +23782,10 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="I5" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -23664,13 +23794,13 @@
         <v>449</v>
       </c>
       <c r="L5" t="s">
-        <v>2112</v>
+        <v>2122</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="O5">
         <v>24.47</v>
@@ -23679,7 +23809,7 @@
         <v>834</v>
       </c>
       <c r="Q5" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -23687,13 +23817,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>2032</v>
+        <v>2042</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E6" t="s">
         <v>190</v>
@@ -23705,10 +23835,10 @@
         <v>0.86</v>
       </c>
       <c r="H6" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="I6" t="s">
-        <v>2082</v>
+        <v>2092</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -23717,13 +23847,13 @@
         <v>449</v>
       </c>
       <c r="L6" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
       <c r="O6">
         <v>17.15</v>
@@ -23732,7 +23862,7 @@
         <v>834</v>
       </c>
       <c r="Q6" t="s">
-        <v>2206</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -23740,7 +23870,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="C7" t="s">
         <v>149</v>
@@ -23758,7 +23888,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -23767,13 +23897,13 @@
         <v>449</v>
       </c>
       <c r="L7" t="s">
-        <v>2114</v>
+        <v>2124</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2176</v>
+        <v>2186</v>
       </c>
       <c r="O7">
         <v>14.49</v>
@@ -23782,7 +23912,7 @@
         <v>834</v>
       </c>
       <c r="Q7" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -23790,7 +23920,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="C8" t="s">
         <v>149</v>
@@ -23808,10 +23938,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="I8" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -23820,13 +23950,13 @@
         <v>449</v>
       </c>
       <c r="L8" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>2146</v>
+        <v>2156</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="O8">
         <v>16.25</v>
@@ -23835,7 +23965,7 @@
         <v>834</v>
       </c>
       <c r="Q8" t="s">
-        <v>2208</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -23843,7 +23973,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="C9" t="s">
         <v>149</v>
@@ -23861,10 +23991,10 @@
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="I9" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -23873,13 +24003,13 @@
         <v>449</v>
       </c>
       <c r="L9" t="s">
-        <v>2116</v>
+        <v>2126</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>2178</v>
+        <v>2188</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -23888,7 +24018,7 @@
         <v>834</v>
       </c>
       <c r="Q9" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -23896,7 +24026,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="C10" t="s">
         <v>149</v>
@@ -23914,10 +24044,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="I10" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="J10">
         <v>19.99</v>
@@ -23926,13 +24056,13 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="O10">
         <v>13.8</v>
@@ -23941,7 +24071,7 @@
         <v>834</v>
       </c>
       <c r="Q10" t="s">
-        <v>2210</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -23949,7 +24079,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
@@ -23967,7 +24097,7 @@
         <v>0.82</v>
       </c>
       <c r="I11" t="s">
-        <v>2087</v>
+        <v>2097</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -23976,13 +24106,13 @@
         <v>449</v>
       </c>
       <c r="L11" t="s">
-        <v>2118</v>
+        <v>2128</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>2180</v>
+        <v>2190</v>
       </c>
       <c r="O11">
         <v>16.49</v>
@@ -23991,7 +24121,7 @@
         <v>834</v>
       </c>
       <c r="Q11" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -23999,7 +24129,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="C12" t="s">
         <v>150</v>
@@ -24017,7 +24147,7 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -24026,13 +24156,13 @@
         <v>449</v>
       </c>
       <c r="L12" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
       <c r="O12">
         <v>21.34</v>
@@ -24041,7 +24171,7 @@
         <v>834</v>
       </c>
       <c r="Q12" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -24049,7 +24179,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="C13" t="s">
         <v>150</v>
@@ -24067,10 +24197,10 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="I13" t="s">
-        <v>2089</v>
+        <v>2099</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -24079,13 +24209,13 @@
         <v>449</v>
       </c>
       <c r="L13" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="O13">
         <v>35</v>
@@ -24094,7 +24224,7 @@
         <v>834</v>
       </c>
       <c r="Q13" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -24102,7 +24232,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="C14" t="s">
         <v>150</v>
@@ -24120,7 +24250,7 @@
         <v>2.38</v>
       </c>
       <c r="I14" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -24129,13 +24259,13 @@
         <v>449</v>
       </c>
       <c r="L14" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="O14">
         <v>47.66</v>
@@ -24144,7 +24274,7 @@
         <v>834</v>
       </c>
       <c r="Q14" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -24152,7 +24282,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="C15" t="s">
         <v>151</v>
@@ -24170,10 +24300,10 @@
         <v>2.09</v>
       </c>
       <c r="H15" t="s">
-        <v>2067</v>
+        <v>2077</v>
       </c>
       <c r="I15" t="s">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -24182,13 +24312,13 @@
         <v>449</v>
       </c>
       <c r="L15" t="s">
-        <v>2122</v>
+        <v>2132</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>2153</v>
+        <v>2163</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>2184</v>
+        <v>2194</v>
       </c>
       <c r="O15">
         <v>41.68</v>
@@ -24197,7 +24327,7 @@
         <v>834</v>
       </c>
       <c r="Q15" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -24205,7 +24335,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="C16" t="s">
         <v>151</v>
@@ -24223,10 +24353,10 @@
         <v>1.82</v>
       </c>
       <c r="H16" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="I16" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -24235,13 +24365,13 @@
         <v>449</v>
       </c>
       <c r="L16" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="O16">
         <v>36.31</v>
@@ -24250,7 +24380,7 @@
         <v>834</v>
       </c>
       <c r="Q16" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -24258,7 +24388,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="C17" t="s">
         <v>151</v>
@@ -24276,7 +24406,7 @@
         <v>0.77</v>
       </c>
       <c r="I17" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -24285,13 +24415,13 @@
         <v>449</v>
       </c>
       <c r="L17" t="s">
-        <v>2124</v>
+        <v>2134</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>2155</v>
+        <v>2165</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="O17">
         <v>15.49</v>
@@ -24300,7 +24430,7 @@
         <v>834</v>
       </c>
       <c r="Q17" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -24308,7 +24438,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="C18" t="s">
         <v>151</v>
@@ -24326,7 +24456,7 @@
         <v>1.84</v>
       </c>
       <c r="I18" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -24335,13 +24465,13 @@
         <v>449</v>
       </c>
       <c r="L18" t="s">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="O18">
         <v>36.87</v>
@@ -24350,7 +24480,7 @@
         <v>834</v>
       </c>
       <c r="Q18" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -24358,7 +24488,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="C19" t="s">
         <v>152</v>
@@ -24376,10 +24506,10 @@
         <v>0.59</v>
       </c>
       <c r="H19" t="s">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="I19" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -24388,13 +24518,13 @@
         <v>449</v>
       </c>
       <c r="L19" t="s">
-        <v>2126</v>
+        <v>2136</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>2188</v>
+        <v>2198</v>
       </c>
       <c r="O19">
         <v>11.86</v>
@@ -24403,7 +24533,7 @@
         <v>834</v>
       </c>
       <c r="Q19" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -24411,7 +24541,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="C20" t="s">
         <v>152</v>
@@ -24429,7 +24559,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -24438,13 +24568,13 @@
         <v>449</v>
       </c>
       <c r="L20" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="O20">
         <v>12.35</v>
@@ -24453,7 +24583,7 @@
         <v>834</v>
       </c>
       <c r="Q20" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -24461,7 +24591,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="C21" t="s">
         <v>152</v>
@@ -24479,10 +24609,10 @@
         <v>0.44</v>
       </c>
       <c r="H21" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="I21" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -24491,13 +24621,13 @@
         <v>449</v>
       </c>
       <c r="L21" t="s">
-        <v>2128</v>
+        <v>2138</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="O21">
         <v>8.81</v>
@@ -24506,7 +24636,7 @@
         <v>834</v>
       </c>
       <c r="Q21" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -24514,7 +24644,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="C22" t="s">
         <v>152</v>
@@ -24532,7 +24662,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -24541,13 +24671,13 @@
         <v>449</v>
       </c>
       <c r="L22" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>2160</v>
+        <v>2170</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="O22">
         <v>11.2</v>
@@ -24556,7 +24686,7 @@
         <v>834</v>
       </c>
       <c r="Q22" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -24564,7 +24694,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
       <c r="C23" t="s">
         <v>153</v>
@@ -24582,10 +24712,10 @@
         <v>0.61</v>
       </c>
       <c r="H23" t="s">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="I23" t="s">
-        <v>2099</v>
+        <v>2109</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -24594,13 +24724,13 @@
         <v>449</v>
       </c>
       <c r="L23" t="s">
-        <v>2130</v>
+        <v>2140</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="O23">
         <v>12.25</v>
@@ -24609,7 +24739,7 @@
         <v>834</v>
       </c>
       <c r="Q23" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -24617,7 +24747,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="C24" t="s">
         <v>153</v>
@@ -24635,10 +24765,10 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="I24" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -24647,13 +24777,13 @@
         <v>449</v>
       </c>
       <c r="L24" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2162</v>
+        <v>2172</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2193</v>
+        <v>2203</v>
       </c>
       <c r="O24">
         <v>10.89</v>
@@ -24662,7 +24792,7 @@
         <v>834</v>
       </c>
       <c r="Q24" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -24670,7 +24800,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="C25" t="s">
         <v>153</v>
@@ -24688,10 +24818,10 @@
         <v>0.38</v>
       </c>
       <c r="H25" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="I25" t="s">
-        <v>2101</v>
+        <v>2111</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -24700,13 +24830,13 @@
         <v>449</v>
       </c>
       <c r="L25" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="O25">
         <v>7.5</v>
@@ -24715,7 +24845,7 @@
         <v>834</v>
       </c>
       <c r="Q25" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -24723,7 +24853,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="C26" t="s">
         <v>153</v>
@@ -24741,10 +24871,10 @@
         <v>0.62</v>
       </c>
       <c r="H26" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
       <c r="I26" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -24753,13 +24883,13 @@
         <v>449</v>
       </c>
       <c r="L26" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>2164</v>
+        <v>2174</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="O26">
         <v>12.32</v>
@@ -24768,7 +24898,7 @@
         <v>834</v>
       </c>
       <c r="Q26" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -24776,7 +24906,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="C27" t="s">
         <v>154</v>
@@ -24794,10 +24924,10 @@
         <v>2.43</v>
       </c>
       <c r="H27" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="I27" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -24806,13 +24936,13 @@
         <v>449</v>
       </c>
       <c r="L27" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="O27">
         <v>48.66</v>
@@ -24821,7 +24951,7 @@
         <v>834</v>
       </c>
       <c r="Q27" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -24829,7 +24959,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="C28" t="s">
         <v>154</v>
@@ -24847,7 +24977,7 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="s">
-        <v>2104</v>
+        <v>2114</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -24856,13 +24986,13 @@
         <v>449</v>
       </c>
       <c r="L28" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>2166</v>
+        <v>2176</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="O28">
         <v>36.49</v>
@@ -24871,7 +25001,7 @@
         <v>834</v>
       </c>
       <c r="Q28" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -24879,7 +25009,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="C29" t="s">
         <v>154</v>
@@ -24897,10 +25027,10 @@
         <v>1.33</v>
       </c>
       <c r="H29" t="s">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="I29" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="J29">
         <v>19.99</v>
@@ -24909,13 +25039,13 @@
         <v>449</v>
       </c>
       <c r="L29" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="O29">
         <v>26.63</v>
@@ -24924,7 +25054,7 @@
         <v>834</v>
       </c>
       <c r="Q29" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -24932,7 +25062,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="C30" t="s">
         <v>154</v>
@@ -24950,7 +25080,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="s">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="J30">
         <v>19.99</v>
@@ -24959,13 +25089,13 @@
         <v>449</v>
       </c>
       <c r="L30" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="O30">
         <v>50.71</v>
@@ -24974,7 +25104,7 @@
         <v>834</v>
       </c>
       <c r="Q30" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -24982,7 +25112,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="C31" t="s">
         <v>155</v>
@@ -25000,10 +25130,10 @@
         <v>0.85</v>
       </c>
       <c r="H31" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="I31" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="J31">
         <v>19.99</v>
@@ -25012,13 +25142,13 @@
         <v>449</v>
       </c>
       <c r="L31" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="O31">
         <v>16.93</v>
@@ -25027,7 +25157,7 @@
         <v>834</v>
       </c>
       <c r="Q31" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -25035,7 +25165,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="C32" t="s">
         <v>155</v>
@@ -25053,7 +25183,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
       <c r="J32">
         <v>19.99</v>
@@ -25062,13 +25192,13 @@
         <v>449</v>
       </c>
       <c r="L32" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="O32">
         <v>17.97</v>
@@ -25077,7 +25207,7 @@
         <v>834</v>
       </c>
       <c r="Q32" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -25085,7 +25215,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="C33" t="s">
         <v>155</v>
@@ -25103,10 +25233,10 @@
         <v>0.89</v>
       </c>
       <c r="H33" t="s">
-        <v>2078</v>
+        <v>2088</v>
       </c>
       <c r="I33" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
       <c r="J33">
         <v>19.99</v>
@@ -25115,13 +25245,13 @@
         <v>449</v>
       </c>
       <c r="L33" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="O33">
         <v>17.84</v>
@@ -25130,7 +25260,7 @@
         <v>834</v>
       </c>
       <c r="Q33" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
     </row>
   </sheetData>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4202" uniqueCount="2267">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -4618,12 +4618,12 @@
     <t>Land Shark</t>
   </si>
   <si>
+    <t>Panthor (Flocked)</t>
+  </si>
+  <si>
     <t>Panthor (Standard)</t>
   </si>
   <si>
-    <t>Panthor (Flocked)</t>
-  </si>
-  <si>
     <t>Prince Adam Sky Sled</t>
   </si>
   <si>
@@ -4744,12 +4744,12 @@
     <t>887961960211</t>
   </si>
   <si>
+    <t>887961979831</t>
+  </si>
+  <si>
     <t>887961930849</t>
   </si>
   <si>
-    <t>887961979831</t>
-  </si>
-  <si>
     <t>887961893243</t>
   </si>
   <si>
@@ -4801,12 +4801,12 @@
     <t>/app/data/MOTU/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
   </si>
   <si>
-    <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
-  </si>
-  <si>
     <t>/app/data/MOTU/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4867,12 +4867,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4933,12 +4933,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/land-shark-2412.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/prince-adam-sky-sled-2413.php</t>
   </si>
   <si>
@@ -4999,10 +4999,10 @@
     <t>2412</t>
   </si>
   <si>
+    <t>2425</t>
+  </si>
+  <si>
     <t>2414</t>
-  </si>
-  <si>
-    <t>2425</t>
   </si>
   <si>
     <t>2413</t>
@@ -19282,17 +19282,20 @@
       <c r="B7" t="s">
         <v>1531</v>
       </c>
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
       <c r="D7" t="s">
         <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>985</v>
+        <v>1165</v>
       </c>
       <c r="F7">
-        <v>1759</v>
+        <v>1179</v>
       </c>
       <c r="G7">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H7" t="s">
         <v>1555</v>
@@ -19301,7 +19304,7 @@
         <v>1573</v>
       </c>
       <c r="J7">
-        <v>24.99</v>
+        <v>39.99</v>
       </c>
       <c r="K7" t="s">
         <v>449</v>
@@ -19316,7 +19319,7 @@
         <v>1636</v>
       </c>
       <c r="O7">
-        <v>14.62</v>
+        <v>21.68</v>
       </c>
       <c r="P7" t="s">
         <v>834</v>
@@ -19332,20 +19335,17 @@
       <c r="B8" t="s">
         <v>1532</v>
       </c>
-      <c r="C8" t="s">
-        <v>170</v>
-      </c>
       <c r="D8" t="s">
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>1165</v>
+        <v>985</v>
       </c>
       <c r="F8">
-        <v>1179</v>
+        <v>1759</v>
       </c>
       <c r="G8">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="s">
         <v>1555</v>
@@ -19354,7 +19354,7 @@
         <v>1574</v>
       </c>
       <c r="J8">
-        <v>39.99</v>
+        <v>24.99</v>
       </c>
       <c r="K8" t="s">
         <v>449</v>
@@ -19369,7 +19369,7 @@
         <v>1637</v>
       </c>
       <c r="O8">
-        <v>21.68</v>
+        <v>14.62</v>
       </c>
       <c r="P8" t="s">
         <v>834</v>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -4618,12 +4618,12 @@
     <t>Land Shark</t>
   </si>
   <si>
+    <t>Panthor (Standard)</t>
+  </si>
+  <si>
     <t>Panthor (Flocked)</t>
   </si>
   <si>
-    <t>Panthor (Standard)</t>
-  </si>
-  <si>
     <t>Prince Adam Sky Sled</t>
   </si>
   <si>
@@ -4744,12 +4744,12 @@
     <t>887961960211</t>
   </si>
   <si>
+    <t>887961930849</t>
+  </si>
+  <si>
     <t>887961979831</t>
   </si>
   <si>
-    <t>887961930849</t>
-  </si>
-  <si>
     <t>887961893243</t>
   </si>
   <si>
@@ -4801,12 +4801,12 @@
     <t>/app/data/MOTU/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/panthor-flocked-2425.jpg</t>
   </si>
   <si>
-    <t>/app/data/MOTU/images/panthor-standard-2414.jpg</t>
-  </si>
-  <si>
     <t>/app/data/MOTU/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4867,12 +4867,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/land-shark-2412.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-flocked-2425.jpg</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/panthor-standard-2414.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-sky-sled-2413.jpg</t>
   </si>
   <si>
@@ -4933,12 +4933,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/land-shark-2412.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-flocked-2425.php</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/panthor-standard-2414.php</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/prince-adam-sky-sled-2413.php</t>
   </si>
   <si>
@@ -4999,10 +4999,10 @@
     <t>2412</t>
   </si>
   <si>
+    <t>2414</t>
+  </si>
+  <si>
     <t>2425</t>
-  </si>
-  <si>
-    <t>2414</t>
   </si>
   <si>
     <t>2413</t>
@@ -19282,20 +19282,17 @@
       <c r="B7" t="s">
         <v>1531</v>
       </c>
-      <c r="C7" t="s">
-        <v>170</v>
-      </c>
       <c r="D7" t="s">
         <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>1165</v>
+        <v>985</v>
       </c>
       <c r="F7">
-        <v>1179</v>
+        <v>1759</v>
       </c>
       <c r="G7">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="H7" t="s">
         <v>1555</v>
@@ -19304,7 +19301,7 @@
         <v>1573</v>
       </c>
       <c r="J7">
-        <v>39.99</v>
+        <v>24.99</v>
       </c>
       <c r="K7" t="s">
         <v>449</v>
@@ -19319,7 +19316,7 @@
         <v>1636</v>
       </c>
       <c r="O7">
-        <v>21.68</v>
+        <v>14.62</v>
       </c>
       <c r="P7" t="s">
         <v>834</v>
@@ -19335,17 +19332,20 @@
       <c r="B8" t="s">
         <v>1532</v>
       </c>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
       <c r="D8" t="s">
         <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>985</v>
+        <v>1165</v>
       </c>
       <c r="F8">
-        <v>1759</v>
+        <v>1179</v>
       </c>
       <c r="G8">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H8" t="s">
         <v>1555</v>
@@ -19354,7 +19354,7 @@
         <v>1574</v>
       </c>
       <c r="J8">
-        <v>24.99</v>
+        <v>39.99</v>
       </c>
       <c r="K8" t="s">
         <v>449</v>
@@ -19369,7 +19369,7 @@
         <v>1637</v>
       </c>
       <c r="O8">
-        <v>14.62</v>
+        <v>21.68</v>
       </c>
       <c r="P8" t="s">
         <v>834</v>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4271" uniqueCount="2308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="2308">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -7898,7 +7898,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14873,7 +14873,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="2308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="2308">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -3538,27 +3538,27 @@
     <t>Vultak</t>
   </si>
   <si>
+    <t>Blast-Attak</t>
+  </si>
+  <si>
+    <t>Great Black Wizard</t>
+  </si>
+  <si>
+    <t>James Jean Coral Skeletor and Panthor</t>
+  </si>
+  <si>
+    <t>James Jean Floral He-Man and Battle Cat</t>
+  </si>
+  <si>
+    <t>Laser Power He-Man</t>
+  </si>
+  <si>
+    <t>Stonedar</t>
+  </si>
+  <si>
     <t>2026 Movie 4 Pack</t>
   </si>
   <si>
-    <t>Blast-Attak</t>
-  </si>
-  <si>
-    <t>Great Black Wizard</t>
-  </si>
-  <si>
-    <t>James Jean Coral Skeletor and Panthor</t>
-  </si>
-  <si>
-    <t>James Jean Floral He-Man and Battle Cat</t>
-  </si>
-  <si>
-    <t>Laser Power He-Man</t>
-  </si>
-  <si>
-    <t>Stonedar</t>
-  </si>
-  <si>
     <t>SDCC</t>
   </si>
   <si>
@@ -3652,12 +3652,12 @@
     <t>$69.99</t>
   </si>
   <si>
+    <t>$33.00</t>
+  </si>
+  <si>
     <t>$37.79</t>
   </si>
   <si>
-    <t>$33.00</t>
-  </si>
-  <si>
     <t>B0GFQ55H21</t>
   </si>
   <si>
@@ -4093,27 +4093,27 @@
     <t>/app/data/MOTU/images/vultak-10404.jpg</t>
   </si>
   <si>
+    <t>/app/data/MOTU/images/blast-attak-12884.jpg</t>
+  </si>
+  <si>
+    <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
+  </si>
+  <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
+  </si>
+  <si>
     <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/2026-movie-4-pack-13440.jpg</t>
   </si>
   <si>
-    <t>/app/data/MOTU/images/blast-attak-12884.jpg</t>
-  </si>
-  <si>
-    <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
-  </si>
-  <si>
-    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
-  </si>
-  <si>
-    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
-  </si>
-  <si>
-    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
-  </si>
-  <si>
-    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-and-he-man-2-pack-2424.jpg</t>
   </si>
   <si>
@@ -4282,27 +4282,27 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/vultak-10404.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/blast-attak-12884.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/2026-movie-4-pack-13440.jpg</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/blast-attak-12884.jpg</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/prince-adam-and-he-man-2-pack-2424.php</t>
   </si>
   <si>
@@ -4471,27 +4471,27 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/vultak-10404.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/blast-attak-12884.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-coral-skeletor-and-panthor-13312.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-floral-he-man-and-battle-cat-13313.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
+  </si>
+  <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/2026-movie-4-pack-13440.php</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/blast-attak-12884.php</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-coral-skeletor-and-panthor-13312.php</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-floral-he-man-and-battle-cat-13313.php</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
-  </si>
-  <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
-  </si>
-  <si>
     <t>2424</t>
   </si>
   <si>
@@ -4660,27 +4660,27 @@
     <t>10404</t>
   </si>
   <si>
+    <t>12884</t>
+  </si>
+  <si>
+    <t>12852</t>
+  </si>
+  <si>
+    <t>13312</t>
+  </si>
+  <si>
+    <t>13313</t>
+  </si>
+  <si>
+    <t>13263</t>
+  </si>
+  <si>
+    <t>13031</t>
+  </si>
+  <si>
     <t>13440</t>
   </si>
   <si>
-    <t>12884</t>
-  </si>
-  <si>
-    <t>12852</t>
-  </si>
-  <si>
-    <t>13312</t>
-  </si>
-  <si>
-    <t>13313</t>
-  </si>
-  <si>
-    <t>13263</t>
-  </si>
-  <si>
-    <t>13031</t>
-  </si>
-  <si>
     <t>Origins Beasts, Vehicles and Playsets Checklist</t>
   </si>
   <si>
@@ -4750,12 +4750,12 @@
     <t>Fright Fighter (2026 Movie)</t>
   </si>
   <si>
+    <t>Snake Lair Playset</t>
+  </si>
+  <si>
     <t>He-Man and Sky Sled (2026 Movie)</t>
   </si>
   <si>
-    <t>Snake Lair Playset</t>
-  </si>
-  <si>
     <t>$74.99</t>
   </si>
   <si>
@@ -4954,12 +4954,12 @@
     <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/fright-fighter-2026-movie-13439.jpg</t>
   </si>
   <si>
+    <t>/app/data/MOTU/images/snake-lair-playset-11542.jpg</t>
+  </si>
+  <si>
     <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/he-man-and-sky-sled-2026-movie-13444.jpg</t>
   </si>
   <si>
-    <t>/app/data/MOTU/images/snake-lair-playset-11542.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/battle-armor-he-man-and-battle-cat-battlefield-warriors-2732.jpg</t>
   </si>
   <si>
@@ -5026,12 +5026,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/fright-fighter-2026-movie-13439.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/snake-lair-playset-11542.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-and-sky-sled-2026-movie-13444.jpg</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/images/snake-lair-playset-11542.jpg</t>
-  </si>
-  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/battle-armor-he-man-and-battle-cat-battlefield-warriors-2732.php</t>
   </si>
   <si>
@@ -5098,12 +5098,12 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/fright-fighter-2026-movie-13439.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/snake-lair-playset-11542.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/he-man-and-sky-sled-2026-movie-13444.php</t>
   </si>
   <si>
-    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/snake-lair-playset-11542.php</t>
-  </si>
-  <si>
     <t>2732</t>
   </si>
   <si>
@@ -5170,10 +5170,10 @@
     <t>13439</t>
   </si>
   <si>
+    <t>11542</t>
+  </si>
+  <si>
     <t>13444</t>
-  </si>
-  <si>
-    <t>11542</t>
   </si>
   <si>
     <t>Stranger Things Crossover Checklist</t>
@@ -18835,36 +18835,30 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
         <v>1171</v>
       </c>
       <c r="C59" t="s">
-        <v>996</v>
+        <v>173</v>
       </c>
       <c r="D59" t="s">
         <v>189</v>
       </c>
       <c r="E59" t="s">
-        <v>1209</v>
+        <v>197</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59" t="s">
-        <v>1248</v>
-      </c>
-      <c r="I59" t="s">
-        <v>1299</v>
+        <v>2.1</v>
       </c>
       <c r="J59">
-        <v>37.79</v>
-      </c>
-      <c r="K59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" t="s">
         <v>453</v>
       </c>
       <c r="L59" t="s">
@@ -18877,7 +18871,7 @@
         <v>1482</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>46.28</v>
       </c>
       <c r="P59" t="s">
         <v>844</v>
@@ -18900,16 +18894,16 @@
         <v>189</v>
       </c>
       <c r="E60" t="s">
-        <v>197</v>
+        <v>1196</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="J60">
-        <v>22</v>
+        <v>31.99</v>
       </c>
       <c r="K60" t="s">
         <v>453</v>
@@ -18924,7 +18918,7 @@
         <v>1483</v>
       </c>
       <c r="O60">
-        <v>46.28</v>
+        <v>40.52</v>
       </c>
       <c r="P60" t="s">
         <v>844</v>
@@ -18947,18 +18941,18 @@
         <v>189</v>
       </c>
       <c r="E61" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <v>31.99</v>
-      </c>
-      <c r="K61" t="s">
+        <v>100</v>
+      </c>
+      <c r="K61" s="2" t="s">
         <v>453</v>
       </c>
       <c r="L61" t="s">
@@ -18971,7 +18965,7 @@
         <v>1484</v>
       </c>
       <c r="O61">
-        <v>40.52</v>
+        <v>0</v>
       </c>
       <c r="P61" t="s">
         <v>844</v>
@@ -19041,7 +19035,7 @@
         <v>189</v>
       </c>
       <c r="E63" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -19050,7 +19044,7 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>453</v>
@@ -19088,7 +19082,7 @@
         <v>189</v>
       </c>
       <c r="E64" t="s">
-        <v>1210</v>
+        <v>197</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -19097,7 +19091,7 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>453</v>
@@ -19123,19 +19117,19 @@
     </row>
     <row r="65" spans="1:17">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B65" t="s">
         <v>1177</v>
       </c>
       <c r="C65" t="s">
-        <v>173</v>
+        <v>996</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
       </c>
       <c r="E65" t="s">
-        <v>197</v>
+        <v>1210</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -19143,10 +19137,16 @@
       <c r="G65">
         <v>1</v>
       </c>
+      <c r="H65" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I65" t="s">
+        <v>1299</v>
+      </c>
       <c r="J65">
-        <v>22</v>
-      </c>
-      <c r="K65" s="2" t="s">
+        <v>37.79</v>
+      </c>
+      <c r="K65" t="s">
         <v>453</v>
       </c>
       <c r="L65" t="s">
@@ -19298,11 +19298,11 @@
     <hyperlink ref="N57" r:id="rId110"/>
     <hyperlink ref="M58" r:id="rId111"/>
     <hyperlink ref="N58" r:id="rId112"/>
-    <hyperlink ref="K59" r:id="rId113"/>
-    <hyperlink ref="M59" r:id="rId114"/>
-    <hyperlink ref="N59" r:id="rId115"/>
-    <hyperlink ref="M60" r:id="rId116"/>
-    <hyperlink ref="N60" r:id="rId117"/>
+    <hyperlink ref="M59" r:id="rId113"/>
+    <hyperlink ref="N59" r:id="rId114"/>
+    <hyperlink ref="M60" r:id="rId115"/>
+    <hyperlink ref="N60" r:id="rId116"/>
+    <hyperlink ref="K61" r:id="rId117"/>
     <hyperlink ref="M61" r:id="rId118"/>
     <hyperlink ref="N61" r:id="rId119"/>
     <hyperlink ref="K62" r:id="rId120"/>
@@ -19314,9 +19314,8 @@
     <hyperlink ref="K64" r:id="rId126"/>
     <hyperlink ref="M64" r:id="rId127"/>
     <hyperlink ref="N64" r:id="rId128"/>
-    <hyperlink ref="K65" r:id="rId129"/>
-    <hyperlink ref="M65" r:id="rId130"/>
-    <hyperlink ref="N65" r:id="rId131"/>
+    <hyperlink ref="M65" r:id="rId129"/>
+    <hyperlink ref="N65" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20262,7 +20261,7 @@
         <v>187</v>
       </c>
       <c r="E20" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -20506,30 +20505,24 @@
         <v>1575</v>
       </c>
       <c r="C25" t="s">
-        <v>996</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
         <v>189</v>
       </c>
       <c r="E25" t="s">
-        <v>1582</v>
+        <v>1190</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>1599</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1620</v>
+        <v>1.67</v>
       </c>
       <c r="J25">
-        <v>26.99</v>
-      </c>
-      <c r="K25" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K25" t="s">
         <v>453</v>
       </c>
       <c r="L25" t="s">
@@ -20542,7 +20535,7 @@
         <v>1691</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>499.99</v>
       </c>
       <c r="P25" t="s">
         <v>844</v>
@@ -20559,22 +20552,28 @@
         <v>1576</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>996</v>
       </c>
       <c r="D26" t="s">
         <v>189</v>
       </c>
       <c r="E26" t="s">
-        <v>1190</v>
+        <v>1582</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1.67</v>
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1620</v>
       </c>
       <c r="J26">
-        <v>300</v>
+        <v>26.99</v>
       </c>
       <c r="K26" t="s">
         <v>453</v>
@@ -20589,7 +20588,7 @@
         <v>1692</v>
       </c>
       <c r="O26">
-        <v>499.99</v>
+        <v>0</v>
       </c>
       <c r="P26" t="s">
         <v>844</v>
@@ -20661,11 +20660,10 @@
     <hyperlink ref="K24" r:id="rId43"/>
     <hyperlink ref="M24" r:id="rId44"/>
     <hyperlink ref="N24" r:id="rId45"/>
-    <hyperlink ref="K25" r:id="rId46"/>
-    <hyperlink ref="M25" r:id="rId47"/>
-    <hyperlink ref="N25" r:id="rId48"/>
-    <hyperlink ref="M26" r:id="rId49"/>
-    <hyperlink ref="N26" r:id="rId50"/>
+    <hyperlink ref="M25" r:id="rId46"/>
+    <hyperlink ref="N25" r:id="rId47"/>
+    <hyperlink ref="M26" r:id="rId48"/>
+    <hyperlink ref="N26" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4286" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4287" uniqueCount="2314">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -7009,12 +7009,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -7025,9 +7040,12 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -7370,55 +7388,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7459,10 +7477,10 @@
       <c r="L3" t="s">
         <v>454</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>714</v>
       </c>
       <c r="O3">
@@ -7512,10 +7530,10 @@
       <c r="L4" t="s">
         <v>455</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>715</v>
       </c>
       <c r="O4">
@@ -7565,10 +7583,10 @@
       <c r="L5" t="s">
         <v>456</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>716</v>
       </c>
       <c r="O5">
@@ -7618,10 +7636,10 @@
       <c r="L6" t="s">
         <v>457</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>717</v>
       </c>
       <c r="O6">
@@ -7671,10 +7689,10 @@
       <c r="L7" t="s">
         <v>458</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>718</v>
       </c>
       <c r="O7">
@@ -7724,10 +7742,10 @@
       <c r="L8" t="s">
         <v>459</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>719</v>
       </c>
       <c r="O8">
@@ -7777,10 +7795,10 @@
       <c r="L9" t="s">
         <v>460</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>720</v>
       </c>
       <c r="O9">
@@ -7830,10 +7848,10 @@
       <c r="L10" t="s">
         <v>461</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>721</v>
       </c>
       <c r="O10">
@@ -7883,10 +7901,10 @@
       <c r="L11" t="s">
         <v>462</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>722</v>
       </c>
       <c r="O11">
@@ -7936,10 +7954,10 @@
       <c r="L12" t="s">
         <v>463</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>723</v>
       </c>
       <c r="O12">
@@ -7989,10 +8007,10 @@
       <c r="L13" t="s">
         <v>464</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>724</v>
       </c>
       <c r="O13">
@@ -8042,10 +8060,10 @@
       <c r="L14" t="s">
         <v>465</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>725</v>
       </c>
       <c r="O14">
@@ -8095,10 +8113,10 @@
       <c r="L15" t="s">
         <v>466</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>726</v>
       </c>
       <c r="O15">
@@ -8148,10 +8166,10 @@
       <c r="L16" t="s">
         <v>467</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>727</v>
       </c>
       <c r="O16">
@@ -8201,10 +8219,10 @@
       <c r="L17" t="s">
         <v>468</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>728</v>
       </c>
       <c r="O17">
@@ -8254,10 +8272,10 @@
       <c r="L18" t="s">
         <v>469</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>729</v>
       </c>
       <c r="O18">
@@ -8307,10 +8325,10 @@
       <c r="L19" t="s">
         <v>470</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>730</v>
       </c>
       <c r="O19">
@@ -8360,10 +8378,10 @@
       <c r="L20" t="s">
         <v>471</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>731</v>
       </c>
       <c r="O20">
@@ -8410,10 +8428,10 @@
       <c r="L21" t="s">
         <v>472</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>732</v>
       </c>
       <c r="O21">
@@ -8460,10 +8478,10 @@
       <c r="L22" t="s">
         <v>473</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>733</v>
       </c>
       <c r="O22">
@@ -8513,10 +8531,10 @@
       <c r="L23" t="s">
         <v>474</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>734</v>
       </c>
       <c r="O23">
@@ -8566,10 +8584,10 @@
       <c r="L24" t="s">
         <v>475</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>735</v>
       </c>
       <c r="O24">
@@ -8619,10 +8637,10 @@
       <c r="L25" t="s">
         <v>476</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>736</v>
       </c>
       <c r="O25">
@@ -8672,10 +8690,10 @@
       <c r="L26" t="s">
         <v>477</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="3" t="s">
         <v>737</v>
       </c>
       <c r="O26">
@@ -8725,10 +8743,10 @@
       <c r="L27" t="s">
         <v>478</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="3" t="s">
         <v>738</v>
       </c>
       <c r="O27">
@@ -8778,10 +8796,10 @@
       <c r="L28" t="s">
         <v>479</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="M28" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="3" t="s">
         <v>739</v>
       </c>
       <c r="O28">
@@ -8831,10 +8849,10 @@
       <c r="L29" t="s">
         <v>480</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>740</v>
       </c>
       <c r="O29">
@@ -8884,10 +8902,10 @@
       <c r="L30" t="s">
         <v>481</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="3" t="s">
         <v>741</v>
       </c>
       <c r="O30">
@@ -8937,10 +8955,10 @@
       <c r="L31" t="s">
         <v>482</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="3" t="s">
         <v>742</v>
       </c>
       <c r="O31">
@@ -8990,10 +9008,10 @@
       <c r="L32" t="s">
         <v>483</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="3" t="s">
         <v>743</v>
       </c>
       <c r="O32">
@@ -9043,10 +9061,10 @@
       <c r="L33" t="s">
         <v>484</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="3" t="s">
         <v>744</v>
       </c>
       <c r="O33">
@@ -9096,10 +9114,10 @@
       <c r="L34" t="s">
         <v>485</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="3" t="s">
         <v>745</v>
       </c>
       <c r="O34">
@@ -9149,10 +9167,10 @@
       <c r="L35" t="s">
         <v>486</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" s="3" t="s">
         <v>746</v>
       </c>
       <c r="O35">
@@ -9202,10 +9220,10 @@
       <c r="L36" t="s">
         <v>487</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="N36" s="3" t="s">
         <v>747</v>
       </c>
       <c r="O36">
@@ -9255,10 +9273,10 @@
       <c r="L37" t="s">
         <v>488</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="3" t="s">
         <v>748</v>
       </c>
       <c r="O37">
@@ -9308,10 +9326,10 @@
       <c r="L38" t="s">
         <v>489</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="3" t="s">
         <v>749</v>
       </c>
       <c r="O38">
@@ -9361,10 +9379,10 @@
       <c r="L39" t="s">
         <v>490</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M39" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="N39" s="3" t="s">
         <v>750</v>
       </c>
       <c r="O39">
@@ -9414,10 +9432,10 @@
       <c r="L40" t="s">
         <v>491</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M40" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="N40" s="3" t="s">
         <v>751</v>
       </c>
       <c r="O40">
@@ -9467,10 +9485,10 @@
       <c r="L41" t="s">
         <v>492</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="N41" s="3" t="s">
         <v>752</v>
       </c>
       <c r="O41">
@@ -9520,10 +9538,10 @@
       <c r="L42" t="s">
         <v>493</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="M42" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="N42" s="3" t="s">
         <v>753</v>
       </c>
       <c r="O42">
@@ -9573,10 +9591,10 @@
       <c r="L43" t="s">
         <v>494</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M43" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="N43" s="3" t="s">
         <v>754</v>
       </c>
       <c r="O43">
@@ -9626,10 +9644,10 @@
       <c r="L44" t="s">
         <v>495</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M44" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="N44" s="3" t="s">
         <v>755</v>
       </c>
       <c r="O44">
@@ -9679,10 +9697,10 @@
       <c r="L45" t="s">
         <v>496</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M45" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="N45" s="3" t="s">
         <v>756</v>
       </c>
       <c r="O45">
@@ -9732,10 +9750,10 @@
       <c r="L46" t="s">
         <v>497</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M46" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="N46" s="3" t="s">
         <v>757</v>
       </c>
       <c r="O46">
@@ -9785,10 +9803,10 @@
       <c r="L47" t="s">
         <v>498</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="M47" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="N47" s="3" t="s">
         <v>758</v>
       </c>
       <c r="O47">
@@ -9838,10 +9856,10 @@
       <c r="L48" t="s">
         <v>499</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="M48" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="N48" s="3" t="s">
         <v>759</v>
       </c>
       <c r="O48">
@@ -9891,10 +9909,10 @@
       <c r="L49" t="s">
         <v>500</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="M49" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="N49" s="3" t="s">
         <v>760</v>
       </c>
       <c r="O49">
@@ -9944,10 +9962,10 @@
       <c r="L50" t="s">
         <v>501</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="M50" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="N50" s="3" t="s">
         <v>761</v>
       </c>
       <c r="O50">
@@ -9997,10 +10015,10 @@
       <c r="L51" t="s">
         <v>502</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="N51" s="2" t="s">
+      <c r="N51" s="3" t="s">
         <v>762</v>
       </c>
       <c r="O51">
@@ -10050,10 +10068,10 @@
       <c r="L52" t="s">
         <v>503</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M52" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="N52" s="3" t="s">
         <v>763</v>
       </c>
       <c r="O52">
@@ -10103,10 +10121,10 @@
       <c r="L53" t="s">
         <v>504</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="N53" s="3" t="s">
         <v>764</v>
       </c>
       <c r="O53">
@@ -10156,10 +10174,10 @@
       <c r="L54" t="s">
         <v>505</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="M54" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="N54" s="3" t="s">
         <v>765</v>
       </c>
       <c r="O54">
@@ -10209,10 +10227,10 @@
       <c r="L55" t="s">
         <v>506</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="M55" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="N55" s="3" t="s">
         <v>766</v>
       </c>
       <c r="O55">
@@ -10262,10 +10280,10 @@
       <c r="L56" t="s">
         <v>507</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="M56" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="N56" s="3" t="s">
         <v>767</v>
       </c>
       <c r="O56">
@@ -10315,10 +10333,10 @@
       <c r="L57" t="s">
         <v>508</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="M57" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="N57" s="3" t="s">
         <v>768</v>
       </c>
       <c r="O57">
@@ -10368,10 +10386,10 @@
       <c r="L58" t="s">
         <v>509</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="M58" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="N58" s="3" t="s">
         <v>769</v>
       </c>
       <c r="O58">
@@ -10421,10 +10439,10 @@
       <c r="L59" t="s">
         <v>510</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="M59" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="N59" s="3" t="s">
         <v>770</v>
       </c>
       <c r="O59">
@@ -10474,10 +10492,10 @@
       <c r="L60" t="s">
         <v>511</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M60" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="N60" s="3" t="s">
         <v>771</v>
       </c>
       <c r="O60">
@@ -10527,10 +10545,10 @@
       <c r="L61" t="s">
         <v>512</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M61" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="N61" s="3" t="s">
         <v>772</v>
       </c>
       <c r="O61">
@@ -10580,10 +10598,10 @@
       <c r="L62" t="s">
         <v>513</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M62" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="N62" s="3" t="s">
         <v>773</v>
       </c>
       <c r="O62">
@@ -10633,10 +10651,10 @@
       <c r="L63" t="s">
         <v>514</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="M63" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="N63" s="2" t="s">
+      <c r="N63" s="3" t="s">
         <v>774</v>
       </c>
       <c r="O63">
@@ -10683,10 +10701,10 @@
       <c r="L64" t="s">
         <v>515</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="M64" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="N64" s="2" t="s">
+      <c r="N64" s="3" t="s">
         <v>775</v>
       </c>
       <c r="O64">
@@ -10733,10 +10751,10 @@
       <c r="L65" t="s">
         <v>516</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="M65" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="N65" s="2" t="s">
+      <c r="N65" s="3" t="s">
         <v>776</v>
       </c>
       <c r="O65">
@@ -10786,10 +10804,10 @@
       <c r="L66" t="s">
         <v>517</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="M66" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="N66" s="2" t="s">
+      <c r="N66" s="3" t="s">
         <v>777</v>
       </c>
       <c r="O66">
@@ -10839,10 +10857,10 @@
       <c r="L67" t="s">
         <v>518</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="M67" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="N67" s="2" t="s">
+      <c r="N67" s="3" t="s">
         <v>778</v>
       </c>
       <c r="O67">
@@ -10892,10 +10910,10 @@
       <c r="L68" t="s">
         <v>519</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="M68" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="N68" s="2" t="s">
+      <c r="N68" s="3" t="s">
         <v>779</v>
       </c>
       <c r="O68">
@@ -10945,10 +10963,10 @@
       <c r="L69" t="s">
         <v>520</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="M69" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="N69" s="2" t="s">
+      <c r="N69" s="3" t="s">
         <v>780</v>
       </c>
       <c r="O69">
@@ -10998,10 +11016,10 @@
       <c r="L70" t="s">
         <v>521</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="M70" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="N70" s="2" t="s">
+      <c r="N70" s="3" t="s">
         <v>781</v>
       </c>
       <c r="O70">
@@ -11051,10 +11069,10 @@
       <c r="L71" t="s">
         <v>522</v>
       </c>
-      <c r="M71" s="2" t="s">
+      <c r="M71" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="N71" s="2" t="s">
+      <c r="N71" s="3" t="s">
         <v>782</v>
       </c>
       <c r="O71">
@@ -11104,10 +11122,10 @@
       <c r="L72" t="s">
         <v>523</v>
       </c>
-      <c r="M72" s="2" t="s">
+      <c r="M72" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="N72" s="2" t="s">
+      <c r="N72" s="3" t="s">
         <v>783</v>
       </c>
       <c r="O72">
@@ -11157,10 +11175,10 @@
       <c r="L73" t="s">
         <v>524</v>
       </c>
-      <c r="M73" s="2" t="s">
+      <c r="M73" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="N73" s="2" t="s">
+      <c r="N73" s="3" t="s">
         <v>784</v>
       </c>
       <c r="O73">
@@ -11210,10 +11228,10 @@
       <c r="L74" t="s">
         <v>525</v>
       </c>
-      <c r="M74" s="2" t="s">
+      <c r="M74" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="N74" s="2" t="s">
+      <c r="N74" s="3" t="s">
         <v>785</v>
       </c>
       <c r="O74">
@@ -11263,10 +11281,10 @@
       <c r="L75" t="s">
         <v>526</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="M75" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="N75" s="2" t="s">
+      <c r="N75" s="3" t="s">
         <v>786</v>
       </c>
       <c r="O75">
@@ -11316,10 +11334,10 @@
       <c r="L76" t="s">
         <v>527</v>
       </c>
-      <c r="M76" s="2" t="s">
+      <c r="M76" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="N76" s="2" t="s">
+      <c r="N76" s="3" t="s">
         <v>787</v>
       </c>
       <c r="O76">
@@ -11369,10 +11387,10 @@
       <c r="L77" t="s">
         <v>528</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="M77" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="N77" s="2" t="s">
+      <c r="N77" s="3" t="s">
         <v>788</v>
       </c>
       <c r="O77">
@@ -11422,10 +11440,10 @@
       <c r="L78" t="s">
         <v>529</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="M78" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="N78" s="2" t="s">
+      <c r="N78" s="3" t="s">
         <v>789</v>
       </c>
       <c r="O78">
@@ -11475,10 +11493,10 @@
       <c r="L79" t="s">
         <v>530</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="M79" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="N79" s="2" t="s">
+      <c r="N79" s="3" t="s">
         <v>790</v>
       </c>
       <c r="O79">
@@ -11528,10 +11546,10 @@
       <c r="L80" t="s">
         <v>531</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="M80" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="N80" s="2" t="s">
+      <c r="N80" s="3" t="s">
         <v>791</v>
       </c>
       <c r="O80">
@@ -11581,10 +11599,10 @@
       <c r="L81" t="s">
         <v>532</v>
       </c>
-      <c r="M81" s="2" t="s">
+      <c r="M81" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="N81" s="2" t="s">
+      <c r="N81" s="3" t="s">
         <v>792</v>
       </c>
       <c r="O81">
@@ -11634,10 +11652,10 @@
       <c r="L82" t="s">
         <v>533</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="M82" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="N82" s="2" t="s">
+      <c r="N82" s="3" t="s">
         <v>793</v>
       </c>
       <c r="O82">
@@ -11687,10 +11705,10 @@
       <c r="L83" t="s">
         <v>534</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="M83" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="N83" s="2" t="s">
+      <c r="N83" s="3" t="s">
         <v>794</v>
       </c>
       <c r="O83">
@@ -11740,10 +11758,10 @@
       <c r="L84" t="s">
         <v>535</v>
       </c>
-      <c r="M84" s="2" t="s">
+      <c r="M84" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="N84" s="2" t="s">
+      <c r="N84" s="3" t="s">
         <v>795</v>
       </c>
       <c r="O84">
@@ -11793,10 +11811,10 @@
       <c r="L85" t="s">
         <v>536</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="M85" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="N85" s="2" t="s">
+      <c r="N85" s="3" t="s">
         <v>796</v>
       </c>
       <c r="O85">
@@ -11846,10 +11864,10 @@
       <c r="L86" t="s">
         <v>537</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="M86" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="N86" s="2" t="s">
+      <c r="N86" s="3" t="s">
         <v>797</v>
       </c>
       <c r="O86">
@@ -11899,10 +11917,10 @@
       <c r="L87" t="s">
         <v>538</v>
       </c>
-      <c r="M87" s="2" t="s">
+      <c r="M87" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="N87" s="2" t="s">
+      <c r="N87" s="3" t="s">
         <v>798</v>
       </c>
       <c r="O87">
@@ -11952,10 +11970,10 @@
       <c r="L88" t="s">
         <v>539</v>
       </c>
-      <c r="M88" s="2" t="s">
+      <c r="M88" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="N88" s="2" t="s">
+      <c r="N88" s="3" t="s">
         <v>799</v>
       </c>
       <c r="O88">
@@ -12005,10 +12023,10 @@
       <c r="L89" t="s">
         <v>540</v>
       </c>
-      <c r="M89" s="2" t="s">
+      <c r="M89" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="N89" s="2" t="s">
+      <c r="N89" s="3" t="s">
         <v>800</v>
       </c>
       <c r="O89">
@@ -12058,10 +12076,10 @@
       <c r="L90" t="s">
         <v>541</v>
       </c>
-      <c r="M90" s="2" t="s">
+      <c r="M90" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="N90" s="2" t="s">
+      <c r="N90" s="3" t="s">
         <v>801</v>
       </c>
       <c r="O90">
@@ -12111,10 +12129,10 @@
       <c r="L91" t="s">
         <v>542</v>
       </c>
-      <c r="M91" s="2" t="s">
+      <c r="M91" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="N91" s="2" t="s">
+      <c r="N91" s="3" t="s">
         <v>802</v>
       </c>
       <c r="O91">
@@ -12164,10 +12182,10 @@
       <c r="L92" t="s">
         <v>543</v>
       </c>
-      <c r="M92" s="2" t="s">
+      <c r="M92" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="N92" s="2" t="s">
+      <c r="N92" s="3" t="s">
         <v>803</v>
       </c>
       <c r="O92">
@@ -12217,10 +12235,10 @@
       <c r="L93" t="s">
         <v>544</v>
       </c>
-      <c r="M93" s="2" t="s">
+      <c r="M93" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="N93" s="2" t="s">
+      <c r="N93" s="3" t="s">
         <v>804</v>
       </c>
       <c r="O93">
@@ -12270,10 +12288,10 @@
       <c r="L94" t="s">
         <v>545</v>
       </c>
-      <c r="M94" s="2" t="s">
+      <c r="M94" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="N94" s="2" t="s">
+      <c r="N94" s="3" t="s">
         <v>805</v>
       </c>
       <c r="O94">
@@ -12323,10 +12341,10 @@
       <c r="L95" t="s">
         <v>546</v>
       </c>
-      <c r="M95" s="2" t="s">
+      <c r="M95" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="N95" s="2" t="s">
+      <c r="N95" s="3" t="s">
         <v>806</v>
       </c>
       <c r="O95">
@@ -12370,10 +12388,10 @@
       <c r="L96" t="s">
         <v>547</v>
       </c>
-      <c r="M96" s="2" t="s">
+      <c r="M96" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="N96" s="2" t="s">
+      <c r="N96" s="3" t="s">
         <v>807</v>
       </c>
       <c r="O96">
@@ -12420,10 +12438,10 @@
       <c r="L97" t="s">
         <v>548</v>
       </c>
-      <c r="M97" s="2" t="s">
+      <c r="M97" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="N97" s="2" t="s">
+      <c r="N97" s="3" t="s">
         <v>808</v>
       </c>
       <c r="O97">
@@ -12473,10 +12491,10 @@
       <c r="L98" t="s">
         <v>549</v>
       </c>
-      <c r="M98" s="2" t="s">
+      <c r="M98" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="N98" s="2" t="s">
+      <c r="N98" s="3" t="s">
         <v>809</v>
       </c>
       <c r="O98">
@@ -12526,10 +12544,10 @@
       <c r="L99" t="s">
         <v>550</v>
       </c>
-      <c r="M99" s="2" t="s">
+      <c r="M99" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="N99" s="2" t="s">
+      <c r="N99" s="3" t="s">
         <v>810</v>
       </c>
       <c r="O99">
@@ -12579,10 +12597,10 @@
       <c r="L100" t="s">
         <v>551</v>
       </c>
-      <c r="M100" s="2" t="s">
+      <c r="M100" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="N100" s="2" t="s">
+      <c r="N100" s="3" t="s">
         <v>811</v>
       </c>
       <c r="O100">
@@ -12632,10 +12650,10 @@
       <c r="L101" t="s">
         <v>552</v>
       </c>
-      <c r="M101" s="2" t="s">
+      <c r="M101" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="N101" s="2" t="s">
+      <c r="N101" s="3" t="s">
         <v>812</v>
       </c>
       <c r="O101">
@@ -12685,10 +12703,10 @@
       <c r="L102" t="s">
         <v>553</v>
       </c>
-      <c r="M102" s="2" t="s">
+      <c r="M102" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="N102" s="2" t="s">
+      <c r="N102" s="3" t="s">
         <v>813</v>
       </c>
       <c r="O102">
@@ -12738,10 +12756,10 @@
       <c r="L103" t="s">
         <v>554</v>
       </c>
-      <c r="M103" s="2" t="s">
+      <c r="M103" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="N103" s="2" t="s">
+      <c r="N103" s="3" t="s">
         <v>814</v>
       </c>
       <c r="O103">
@@ -12791,10 +12809,10 @@
       <c r="L104" t="s">
         <v>555</v>
       </c>
-      <c r="M104" s="2" t="s">
+      <c r="M104" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="N104" s="2" t="s">
+      <c r="N104" s="3" t="s">
         <v>815</v>
       </c>
       <c r="O104">
@@ -12844,10 +12862,10 @@
       <c r="L105" t="s">
         <v>556</v>
       </c>
-      <c r="M105" s="2" t="s">
+      <c r="M105" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="N105" s="2" t="s">
+      <c r="N105" s="3" t="s">
         <v>816</v>
       </c>
       <c r="O105">
@@ -12897,10 +12915,10 @@
       <c r="L106" t="s">
         <v>557</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="M106" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="N106" s="2" t="s">
+      <c r="N106" s="3" t="s">
         <v>817</v>
       </c>
       <c r="O106">
@@ -12950,10 +12968,10 @@
       <c r="L107" t="s">
         <v>558</v>
       </c>
-      <c r="M107" s="2" t="s">
+      <c r="M107" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="N107" s="2" t="s">
+      <c r="N107" s="3" t="s">
         <v>818</v>
       </c>
       <c r="O107">
@@ -13000,10 +13018,10 @@
       <c r="L108" t="s">
         <v>559</v>
       </c>
-      <c r="M108" s="2" t="s">
+      <c r="M108" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="N108" s="2" t="s">
+      <c r="N108" s="3" t="s">
         <v>819</v>
       </c>
       <c r="O108">
@@ -13050,10 +13068,10 @@
       <c r="L109" t="s">
         <v>560</v>
       </c>
-      <c r="M109" s="2" t="s">
+      <c r="M109" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="N109" s="2" t="s">
+      <c r="N109" s="3" t="s">
         <v>820</v>
       </c>
       <c r="O109">
@@ -13100,10 +13118,10 @@
       <c r="L110" t="s">
         <v>561</v>
       </c>
-      <c r="M110" s="2" t="s">
+      <c r="M110" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="N110" s="2" t="s">
+      <c r="N110" s="3" t="s">
         <v>821</v>
       </c>
       <c r="O110">
@@ -13141,16 +13159,16 @@
       <c r="J111">
         <v>21.99</v>
       </c>
-      <c r="K111" s="2" t="s">
+      <c r="K111" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L111" t="s">
         <v>562</v>
       </c>
-      <c r="M111" s="2" t="s">
+      <c r="M111" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="N111" s="2" t="s">
+      <c r="N111" s="3" t="s">
         <v>822</v>
       </c>
       <c r="O111">
@@ -13197,10 +13215,10 @@
       <c r="L112" t="s">
         <v>563</v>
       </c>
-      <c r="M112" s="2" t="s">
+      <c r="M112" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="N112" s="2" t="s">
+      <c r="N112" s="3" t="s">
         <v>823</v>
       </c>
       <c r="O112">
@@ -13241,16 +13259,16 @@
       <c r="J113">
         <v>21.99</v>
       </c>
-      <c r="K113" s="2" t="s">
+      <c r="K113" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L113" t="s">
         <v>564</v>
       </c>
-      <c r="M113" s="2" t="s">
+      <c r="M113" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="N113" s="2" t="s">
+      <c r="N113" s="3" t="s">
         <v>824</v>
       </c>
       <c r="O113">
@@ -13291,10 +13309,10 @@
       <c r="L114" t="s">
         <v>565</v>
       </c>
-      <c r="M114" s="2" t="s">
+      <c r="M114" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="N114" s="2" t="s">
+      <c r="N114" s="3" t="s">
         <v>825</v>
       </c>
       <c r="O114">
@@ -13341,10 +13359,10 @@
       <c r="L115" t="s">
         <v>566</v>
       </c>
-      <c r="M115" s="2" t="s">
+      <c r="M115" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="N115" s="2" t="s">
+      <c r="N115" s="3" t="s">
         <v>826</v>
       </c>
       <c r="O115">
@@ -13382,16 +13400,16 @@
       <c r="J116">
         <v>21.99</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="K116" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L116" t="s">
         <v>567</v>
       </c>
-      <c r="M116" s="2" t="s">
+      <c r="M116" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="N116" s="2" t="s">
+      <c r="N116" s="3" t="s">
         <v>827</v>
       </c>
       <c r="O116">
@@ -13441,10 +13459,10 @@
       <c r="L117" t="s">
         <v>568</v>
       </c>
-      <c r="M117" s="2" t="s">
+      <c r="M117" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="N117" s="2" t="s">
+      <c r="N117" s="3" t="s">
         <v>828</v>
       </c>
       <c r="O117">
@@ -13494,10 +13512,10 @@
       <c r="L118" t="s">
         <v>569</v>
       </c>
-      <c r="M118" s="2" t="s">
+      <c r="M118" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="N118" s="2" t="s">
+      <c r="N118" s="3" t="s">
         <v>829</v>
       </c>
       <c r="O118">
@@ -13547,10 +13565,10 @@
       <c r="L119" t="s">
         <v>570</v>
       </c>
-      <c r="M119" s="2" t="s">
+      <c r="M119" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="N119" s="2" t="s">
+      <c r="N119" s="3" t="s">
         <v>830</v>
       </c>
       <c r="O119">
@@ -13600,10 +13618,10 @@
       <c r="L120" t="s">
         <v>571</v>
       </c>
-      <c r="M120" s="2" t="s">
+      <c r="M120" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="N120" s="2" t="s">
+      <c r="N120" s="3" t="s">
         <v>831</v>
       </c>
       <c r="O120">
@@ -13653,10 +13671,10 @@
       <c r="L121" t="s">
         <v>572</v>
       </c>
-      <c r="M121" s="2" t="s">
+      <c r="M121" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="N121" s="2" t="s">
+      <c r="N121" s="3" t="s">
         <v>832</v>
       </c>
       <c r="O121">
@@ -13706,10 +13724,10 @@
       <c r="L122" t="s">
         <v>573</v>
       </c>
-      <c r="M122" s="2" t="s">
+      <c r="M122" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="N122" s="2" t="s">
+      <c r="N122" s="3" t="s">
         <v>833</v>
       </c>
       <c r="O122">
@@ -13759,10 +13777,10 @@
       <c r="L123" t="s">
         <v>574</v>
       </c>
-      <c r="M123" s="2" t="s">
+      <c r="M123" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="N123" s="2" t="s">
+      <c r="N123" s="3" t="s">
         <v>834</v>
       </c>
       <c r="O123">
@@ -13806,16 +13824,16 @@
       <c r="J124">
         <v>19.67</v>
       </c>
-      <c r="K124" s="2" t="s">
+      <c r="K124" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L124" t="s">
         <v>575</v>
       </c>
-      <c r="M124" s="2" t="s">
+      <c r="M124" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="N124" s="2" t="s">
+      <c r="N124" s="3" t="s">
         <v>835</v>
       </c>
       <c r="O124">
@@ -13865,10 +13883,10 @@
       <c r="L125" t="s">
         <v>576</v>
       </c>
-      <c r="M125" s="2" t="s">
+      <c r="M125" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="N125" s="2" t="s">
+      <c r="N125" s="3" t="s">
         <v>836</v>
       </c>
       <c r="O125">
@@ -13912,16 +13930,16 @@
       <c r="J126">
         <v>19.67</v>
       </c>
-      <c r="K126" s="2" t="s">
+      <c r="K126" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L126" t="s">
         <v>577</v>
       </c>
-      <c r="M126" s="2" t="s">
+      <c r="M126" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="N126" s="2" t="s">
+      <c r="N126" s="3" t="s">
         <v>837</v>
       </c>
       <c r="O126">
@@ -13971,10 +13989,10 @@
       <c r="L127" t="s">
         <v>578</v>
       </c>
-      <c r="M127" s="2" t="s">
+      <c r="M127" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="N127" s="2" t="s">
+      <c r="N127" s="3" t="s">
         <v>838</v>
       </c>
       <c r="O127">
@@ -14024,10 +14042,10 @@
       <c r="L128" t="s">
         <v>579</v>
       </c>
-      <c r="M128" s="2" t="s">
+      <c r="M128" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="N128" s="2" t="s">
+      <c r="N128" s="3" t="s">
         <v>839</v>
       </c>
       <c r="O128">
@@ -14071,16 +14089,16 @@
       <c r="J129">
         <v>20.49</v>
       </c>
-      <c r="K129" s="2" t="s">
+      <c r="K129" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L129" t="s">
         <v>580</v>
       </c>
-      <c r="M129" s="2" t="s">
+      <c r="M129" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="N129" s="2" t="s">
+      <c r="N129" s="3" t="s">
         <v>840</v>
       </c>
       <c r="O129">
@@ -14124,16 +14142,16 @@
       <c r="J130">
         <v>20.49</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="K130" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L130" t="s">
         <v>581</v>
       </c>
-      <c r="M130" s="2" t="s">
+      <c r="M130" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="N130" s="2" t="s">
+      <c r="N130" s="3" t="s">
         <v>841</v>
       </c>
       <c r="O130">
@@ -14177,16 +14195,16 @@
       <c r="J131">
         <v>23.75</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="K131" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L131" t="s">
         <v>582</v>
       </c>
-      <c r="M131" s="2" t="s">
+      <c r="M131" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="N131" s="2" t="s">
+      <c r="N131" s="3" t="s">
         <v>842</v>
       </c>
       <c r="O131">
@@ -14230,16 +14248,16 @@
       <c r="J132">
         <v>20.49</v>
       </c>
-      <c r="K132" s="2" t="s">
+      <c r="K132" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L132" t="s">
         <v>583</v>
       </c>
-      <c r="M132" s="2" t="s">
+      <c r="M132" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="N132" s="2" t="s">
+      <c r="N132" s="3" t="s">
         <v>843</v>
       </c>
       <c r="O132">
@@ -14571,55 +14589,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -14657,10 +14675,10 @@
       <c r="L3" t="s">
         <v>2302</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>2305</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>2308</v>
       </c>
       <c r="O3">
@@ -14707,10 +14725,10 @@
       <c r="L4" t="s">
         <v>2303</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>2306</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>2309</v>
       </c>
       <c r="O4">
@@ -14754,10 +14772,10 @@
       <c r="L5" t="s">
         <v>2304</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>2307</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>2310</v>
       </c>
       <c r="O5">
@@ -14826,55 +14844,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -14912,10 +14930,10 @@
       <c r="L3" t="s">
         <v>1040</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>1060</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>1080</v>
       </c>
       <c r="O3">
@@ -14965,10 +14983,10 @@
       <c r="L4" t="s">
         <v>1041</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>1061</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>1081</v>
       </c>
       <c r="O4">
@@ -15015,10 +15033,10 @@
       <c r="L5" t="s">
         <v>1042</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>1082</v>
       </c>
       <c r="O5">
@@ -15065,10 +15083,10 @@
       <c r="L6" t="s">
         <v>1043</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>1063</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>1083</v>
       </c>
       <c r="O6">
@@ -15115,10 +15133,10 @@
       <c r="L7" t="s">
         <v>1044</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>1064</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>1084</v>
       </c>
       <c r="O7">
@@ -15165,10 +15183,10 @@
       <c r="L8" t="s">
         <v>1045</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>1085</v>
       </c>
       <c r="O8">
@@ -15215,10 +15233,10 @@
       <c r="L9" t="s">
         <v>1046</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>1086</v>
       </c>
       <c r="O9">
@@ -15265,10 +15283,10 @@
       <c r="L10" t="s">
         <v>1047</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>1067</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>1087</v>
       </c>
       <c r="O10">
@@ -15315,10 +15333,10 @@
       <c r="L11" t="s">
         <v>1048</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>1068</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>1088</v>
       </c>
       <c r="O11">
@@ -15365,10 +15383,10 @@
       <c r="L12" t="s">
         <v>1049</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>1089</v>
       </c>
       <c r="O12">
@@ -15415,10 +15433,10 @@
       <c r="L13" t="s">
         <v>1050</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>1070</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>1090</v>
       </c>
       <c r="O13">
@@ -15465,10 +15483,10 @@
       <c r="L14" t="s">
         <v>1051</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>1091</v>
       </c>
       <c r="O14">
@@ -15515,10 +15533,10 @@
       <c r="L15" t="s">
         <v>1052</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>1092</v>
       </c>
       <c r="O15">
@@ -15568,10 +15586,10 @@
       <c r="L16" t="s">
         <v>1053</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>1093</v>
       </c>
       <c r="O16">
@@ -15618,10 +15636,10 @@
       <c r="L17" t="s">
         <v>1054</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>1094</v>
       </c>
       <c r="O17">
@@ -15668,10 +15686,10 @@
       <c r="L18" t="s">
         <v>1055</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>1095</v>
       </c>
       <c r="O18">
@@ -15709,16 +15727,16 @@
       <c r="J19">
         <v>25.99</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L19" t="s">
         <v>1056</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="O19">
@@ -15756,16 +15774,16 @@
       <c r="J20">
         <v>26.49</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L20" t="s">
         <v>1057</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>1097</v>
       </c>
       <c r="O20">
@@ -15815,10 +15833,10 @@
       <c r="L21" t="s">
         <v>1058</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>1098</v>
       </c>
       <c r="O21">
@@ -15853,16 +15871,16 @@
       <c r="J22">
         <v>26.97</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L22" t="s">
         <v>1059</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>1099</v>
       </c>
       <c r="O22">
@@ -15968,55 +15986,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16057,10 +16075,10 @@
       <c r="L3" t="s">
         <v>1306</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>1369</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>1432</v>
       </c>
       <c r="O3">
@@ -16107,10 +16125,10 @@
       <c r="L4" t="s">
         <v>1307</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>1433</v>
       </c>
       <c r="O4">
@@ -16160,10 +16178,10 @@
       <c r="L5" t="s">
         <v>1308</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>1371</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>1434</v>
       </c>
       <c r="O5">
@@ -16210,10 +16228,10 @@
       <c r="L6" t="s">
         <v>1309</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>1435</v>
       </c>
       <c r="O6">
@@ -16260,10 +16278,10 @@
       <c r="L7" t="s">
         <v>1310</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>1373</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>1436</v>
       </c>
       <c r="O7">
@@ -16313,10 +16331,10 @@
       <c r="L8" t="s">
         <v>1311</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>1374</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>1437</v>
       </c>
       <c r="O8">
@@ -16360,10 +16378,10 @@
       <c r="L9" t="s">
         <v>1312</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>1375</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>1438</v>
       </c>
       <c r="O9">
@@ -16410,10 +16428,10 @@
       <c r="L10" t="s">
         <v>1313</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>1439</v>
       </c>
       <c r="O10">
@@ -16457,10 +16475,10 @@
       <c r="L11" t="s">
         <v>1314</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>1440</v>
       </c>
       <c r="O11">
@@ -16504,10 +16522,10 @@
       <c r="L12" t="s">
         <v>1315</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>1378</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>1441</v>
       </c>
       <c r="O12">
@@ -16554,10 +16572,10 @@
       <c r="L13" t="s">
         <v>1316</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>1379</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>1442</v>
       </c>
       <c r="O13">
@@ -16604,10 +16622,10 @@
       <c r="L14" t="s">
         <v>1317</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>1380</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>1443</v>
       </c>
       <c r="O14">
@@ -16654,10 +16672,10 @@
       <c r="L15" t="s">
         <v>1318</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>1444</v>
       </c>
       <c r="O15">
@@ -16707,10 +16725,10 @@
       <c r="L16" t="s">
         <v>1319</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>1382</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>1445</v>
       </c>
       <c r="O16">
@@ -16760,10 +16778,10 @@
       <c r="L17" t="s">
         <v>1320</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>1383</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>1446</v>
       </c>
       <c r="O17">
@@ -16813,10 +16831,10 @@
       <c r="L18" t="s">
         <v>1321</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>1384</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>1447</v>
       </c>
       <c r="O18">
@@ -16863,10 +16881,10 @@
       <c r="L19" t="s">
         <v>1322</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>1385</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>1448</v>
       </c>
       <c r="O19">
@@ -16916,10 +16934,10 @@
       <c r="L20" t="s">
         <v>1323</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>1386</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>1449</v>
       </c>
       <c r="O20">
@@ -16966,10 +16984,10 @@
       <c r="L21" t="s">
         <v>1324</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>1387</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>1450</v>
       </c>
       <c r="O21">
@@ -17019,10 +17037,10 @@
       <c r="L22" t="s">
         <v>1325</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>1451</v>
       </c>
       <c r="O22">
@@ -17069,10 +17087,10 @@
       <c r="L23" t="s">
         <v>1326</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>1452</v>
       </c>
       <c r="O23">
@@ -17122,10 +17140,10 @@
       <c r="L24" t="s">
         <v>1327</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>1390</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>1453</v>
       </c>
       <c r="O24">
@@ -17175,10 +17193,10 @@
       <c r="L25" t="s">
         <v>1328</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>1391</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>1454</v>
       </c>
       <c r="O25">
@@ -17228,10 +17246,10 @@
       <c r="L26" t="s">
         <v>1329</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>1392</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="O26">
@@ -17281,10 +17299,10 @@
       <c r="L27" t="s">
         <v>1330</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="3" t="s">
         <v>1393</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="O27">
@@ -17334,10 +17352,10 @@
       <c r="L28" t="s">
         <v>1331</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="M28" s="3" t="s">
         <v>1394</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="3" t="s">
         <v>1457</v>
       </c>
       <c r="O28">
@@ -17387,10 +17405,10 @@
       <c r="L29" t="s">
         <v>1332</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>1395</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>1458</v>
       </c>
       <c r="O29">
@@ -17437,10 +17455,10 @@
       <c r="L30" t="s">
         <v>1333</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="3" t="s">
         <v>1459</v>
       </c>
       <c r="O30">
@@ -17490,10 +17508,10 @@
       <c r="L31" t="s">
         <v>1334</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>1397</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="3" t="s">
         <v>1460</v>
       </c>
       <c r="O31">
@@ -17543,10 +17561,10 @@
       <c r="L32" t="s">
         <v>1335</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>1398</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="3" t="s">
         <v>1461</v>
       </c>
       <c r="O32">
@@ -17596,10 +17614,10 @@
       <c r="L33" t="s">
         <v>1336</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>1399</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="3" t="s">
         <v>1462</v>
       </c>
       <c r="O33">
@@ -17649,10 +17667,10 @@
       <c r="L34" t="s">
         <v>1337</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>1400</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="3" t="s">
         <v>1463</v>
       </c>
       <c r="O34">
@@ -17702,10 +17720,10 @@
       <c r="L35" t="s">
         <v>1338</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>1401</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" s="3" t="s">
         <v>1464</v>
       </c>
       <c r="O35">
@@ -17746,10 +17764,10 @@
       <c r="L36" t="s">
         <v>1339</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>1402</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="N36" s="3" t="s">
         <v>1465</v>
       </c>
       <c r="O36">
@@ -17799,10 +17817,10 @@
       <c r="L37" t="s">
         <v>1340</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="3" t="s">
         <v>1466</v>
       </c>
       <c r="O37">
@@ -17852,10 +17870,10 @@
       <c r="L38" t="s">
         <v>1341</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="3" t="s">
         <v>1404</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="3" t="s">
         <v>1467</v>
       </c>
       <c r="O38">
@@ -17905,10 +17923,10 @@
       <c r="L39" t="s">
         <v>1342</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M39" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="N39" s="3" t="s">
         <v>1468</v>
       </c>
       <c r="O39">
@@ -17958,10 +17976,10 @@
       <c r="L40" t="s">
         <v>1343</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M40" s="3" t="s">
         <v>1406</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="N40" s="3" t="s">
         <v>1469</v>
       </c>
       <c r="O40">
@@ -18008,10 +18026,10 @@
       <c r="L41" t="s">
         <v>1344</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="N41" s="3" t="s">
         <v>1470</v>
       </c>
       <c r="O41">
@@ -18061,10 +18079,10 @@
       <c r="L42" t="s">
         <v>1345</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="M42" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="N42" s="3" t="s">
         <v>1471</v>
       </c>
       <c r="O42">
@@ -18114,10 +18132,10 @@
       <c r="L43" t="s">
         <v>1346</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M43" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="N43" s="3" t="s">
         <v>1472</v>
       </c>
       <c r="O43">
@@ -18161,10 +18179,10 @@
       <c r="L44" t="s">
         <v>1347</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M44" s="3" t="s">
         <v>1410</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="N44" s="3" t="s">
         <v>1473</v>
       </c>
       <c r="O44">
@@ -18208,10 +18226,10 @@
       <c r="L45" t="s">
         <v>1348</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M45" s="3" t="s">
         <v>1411</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="N45" s="3" t="s">
         <v>1474</v>
       </c>
       <c r="O45">
@@ -18255,10 +18273,10 @@
       <c r="L46" t="s">
         <v>1349</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M46" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="N46" s="3" t="s">
         <v>1475</v>
       </c>
       <c r="O46">
@@ -18308,10 +18326,10 @@
       <c r="L47" t="s">
         <v>1350</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="M47" s="3" t="s">
         <v>1413</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="N47" s="3" t="s">
         <v>1476</v>
       </c>
       <c r="O47">
@@ -18358,10 +18376,10 @@
       <c r="L48" t="s">
         <v>1351</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="M48" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="N48" s="3" t="s">
         <v>1477</v>
       </c>
       <c r="O48">
@@ -18411,10 +18429,10 @@
       <c r="L49" t="s">
         <v>1352</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="M49" s="3" t="s">
         <v>1415</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="N49" s="3" t="s">
         <v>1478</v>
       </c>
       <c r="O49">
@@ -18461,10 +18479,10 @@
       <c r="L50" t="s">
         <v>1353</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="M50" s="3" t="s">
         <v>1416</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="N50" s="3" t="s">
         <v>1479</v>
       </c>
       <c r="O50">
@@ -18514,10 +18532,10 @@
       <c r="L51" t="s">
         <v>1354</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="3" t="s">
         <v>1417</v>
       </c>
-      <c r="N51" s="2" t="s">
+      <c r="N51" s="3" t="s">
         <v>1480</v>
       </c>
       <c r="O51">
@@ -18567,10 +18585,10 @@
       <c r="L52" t="s">
         <v>1355</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M52" s="3" t="s">
         <v>1418</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="N52" s="3" t="s">
         <v>1481</v>
       </c>
       <c r="O52">
@@ -18620,10 +18638,10 @@
       <c r="L53" t="s">
         <v>1356</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="3" t="s">
         <v>1419</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="N53" s="3" t="s">
         <v>1482</v>
       </c>
       <c r="O53">
@@ -18673,10 +18691,10 @@
       <c r="L54" t="s">
         <v>1357</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="M54" s="3" t="s">
         <v>1420</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="N54" s="3" t="s">
         <v>1483</v>
       </c>
       <c r="O54">
@@ -18726,10 +18744,10 @@
       <c r="L55" t="s">
         <v>1358</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="M55" s="3" t="s">
         <v>1421</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="N55" s="3" t="s">
         <v>1484</v>
       </c>
       <c r="O55">
@@ -18779,10 +18797,10 @@
       <c r="L56" t="s">
         <v>1359</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="M56" s="3" t="s">
         <v>1422</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="N56" s="3" t="s">
         <v>1485</v>
       </c>
       <c r="O56">
@@ -18832,10 +18850,10 @@
       <c r="L57" t="s">
         <v>1360</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="M57" s="3" t="s">
         <v>1423</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="N57" s="3" t="s">
         <v>1486</v>
       </c>
       <c r="O57">
@@ -18885,10 +18903,10 @@
       <c r="L58" t="s">
         <v>1361</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="M58" s="3" t="s">
         <v>1424</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="N58" s="3" t="s">
         <v>1487</v>
       </c>
       <c r="O58">
@@ -18932,10 +18950,10 @@
       <c r="L59" t="s">
         <v>1362</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="M59" s="3" t="s">
         <v>1425</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="N59" s="3" t="s">
         <v>1488</v>
       </c>
       <c r="O59">
@@ -18979,10 +18997,10 @@
       <c r="L60" t="s">
         <v>1363</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M60" s="3" t="s">
         <v>1426</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="N60" s="3" t="s">
         <v>1489</v>
       </c>
       <c r="O60">
@@ -19020,16 +19038,16 @@
       <c r="J61">
         <v>100</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K61" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L61" t="s">
         <v>1364</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M61" s="3" t="s">
         <v>1427</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="N61" s="3" t="s">
         <v>1490</v>
       </c>
       <c r="O61">
@@ -19067,16 +19085,16 @@
       <c r="J62">
         <v>100</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K62" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L62" t="s">
         <v>1365</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M62" s="3" t="s">
         <v>1428</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="N62" s="3" t="s">
         <v>1491</v>
       </c>
       <c r="O62">
@@ -19114,16 +19132,16 @@
       <c r="J63">
         <v>33</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K63" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L63" t="s">
         <v>1366</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="M63" s="3" t="s">
         <v>1429</v>
       </c>
-      <c r="N63" s="2" t="s">
+      <c r="N63" s="3" t="s">
         <v>1492</v>
       </c>
       <c r="O63">
@@ -19161,16 +19179,16 @@
       <c r="J64">
         <v>22</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="K64" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L64" t="s">
         <v>1367</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="M64" s="3" t="s">
         <v>1430</v>
       </c>
-      <c r="N64" s="2" t="s">
+      <c r="N64" s="3" t="s">
         <v>1493</v>
       </c>
       <c r="O64">
@@ -19220,10 +19238,10 @@
       <c r="L65" t="s">
         <v>1368</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="M65" s="3" t="s">
         <v>1431</v>
       </c>
-      <c r="N65" s="2" t="s">
+      <c r="N65" s="3" t="s">
         <v>1494</v>
       </c>
       <c r="O65">
@@ -19416,55 +19434,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19502,10 +19520,10 @@
       <c r="L3" t="s">
         <v>1627</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>1651</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>1675</v>
       </c>
       <c r="O3">
@@ -19552,10 +19570,10 @@
       <c r="L4" t="s">
         <v>1628</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>1652</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>1676</v>
       </c>
       <c r="O4">
@@ -19602,10 +19620,10 @@
       <c r="L5" t="s">
         <v>1629</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>1677</v>
       </c>
       <c r="O5">
@@ -19652,10 +19670,10 @@
       <c r="L6" t="s">
         <v>1630</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>1654</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>1678</v>
       </c>
       <c r="O6">
@@ -19702,10 +19720,10 @@
       <c r="L7" t="s">
         <v>1631</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>1655</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>1679</v>
       </c>
       <c r="O7">
@@ -19755,10 +19773,10 @@
       <c r="L8" t="s">
         <v>1632</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>1680</v>
       </c>
       <c r="O8">
@@ -19805,10 +19823,10 @@
       <c r="L9" t="s">
         <v>1633</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>1657</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>1681</v>
       </c>
       <c r="O9">
@@ -19855,10 +19873,10 @@
       <c r="L10" t="s">
         <v>1634</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>1658</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>1682</v>
       </c>
       <c r="O10">
@@ -19905,10 +19923,10 @@
       <c r="L11" t="s">
         <v>1635</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>1659</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>1683</v>
       </c>
       <c r="O11">
@@ -19955,10 +19973,10 @@
       <c r="L12" t="s">
         <v>1636</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>1684</v>
       </c>
       <c r="O12">
@@ -20005,10 +20023,10 @@
       <c r="L13" t="s">
         <v>1637</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>1661</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>1685</v>
       </c>
       <c r="O13">
@@ -20055,10 +20073,10 @@
       <c r="L14" t="s">
         <v>1638</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>1662</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>1686</v>
       </c>
       <c r="O14">
@@ -20105,10 +20123,10 @@
       <c r="L15" t="s">
         <v>1639</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>1663</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>1687</v>
       </c>
       <c r="O15">
@@ -20155,10 +20173,10 @@
       <c r="L16" t="s">
         <v>1640</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>1664</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>1688</v>
       </c>
       <c r="O16">
@@ -20205,10 +20223,10 @@
       <c r="L17" t="s">
         <v>1641</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>1665</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>1689</v>
       </c>
       <c r="O17">
@@ -20255,10 +20273,10 @@
       <c r="L18" t="s">
         <v>1642</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>1666</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>1690</v>
       </c>
       <c r="O18">
@@ -20299,10 +20317,10 @@
       <c r="L19" t="s">
         <v>1643</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>1667</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>1691</v>
       </c>
       <c r="O19">
@@ -20352,10 +20370,10 @@
       <c r="L20" t="s">
         <v>1644</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>1668</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>1692</v>
       </c>
       <c r="O20">
@@ -20402,10 +20420,10 @@
       <c r="L21" t="s">
         <v>1645</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>1669</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>1693</v>
       </c>
       <c r="O21">
@@ -20452,10 +20470,10 @@
       <c r="L22" t="s">
         <v>1646</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>1670</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>1694</v>
       </c>
       <c r="O22">
@@ -20502,10 +20520,10 @@
       <c r="L23" t="s">
         <v>1647</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>1671</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>1695</v>
       </c>
       <c r="O23">
@@ -20543,16 +20561,16 @@
       <c r="J24">
         <v>42.99</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L24" t="s">
         <v>1648</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>1696</v>
       </c>
       <c r="O24">
@@ -20596,10 +20614,10 @@
       <c r="L25" t="s">
         <v>1649</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>1673</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>1697</v>
       </c>
       <c r="O25">
@@ -20649,10 +20667,10 @@
       <c r="L26" t="s">
         <v>1650</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="3" t="s">
         <v>1698</v>
       </c>
       <c r="O26">
@@ -20764,55 +20782,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20850,10 +20868,10 @@
       <c r="L3" t="s">
         <v>1730</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>1733</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>1736</v>
       </c>
       <c r="O3">
@@ -20900,10 +20918,10 @@
       <c r="L4" t="s">
         <v>1731</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>1734</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>1737</v>
       </c>
       <c r="O4">
@@ -20950,10 +20968,10 @@
       <c r="L5" t="s">
         <v>1732</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>1738</v>
       </c>
       <c r="O5">
@@ -21022,55 +21040,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -21111,10 +21129,10 @@
       <c r="L3" t="s">
         <v>1841</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>1877</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>1913</v>
       </c>
       <c r="O3">
@@ -21164,10 +21182,10 @@
       <c r="L4" t="s">
         <v>1842</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>1878</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>1914</v>
       </c>
       <c r="O4">
@@ -21208,10 +21226,10 @@
       <c r="L5" t="s">
         <v>1843</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>1879</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>1915</v>
       </c>
       <c r="O5">
@@ -21261,10 +21279,10 @@
       <c r="L6" t="s">
         <v>1844</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>1880</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>1916</v>
       </c>
       <c r="O6">
@@ -21314,10 +21332,10 @@
       <c r="L7" t="s">
         <v>1845</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>1917</v>
       </c>
       <c r="O7">
@@ -21361,10 +21379,10 @@
       <c r="L8" t="s">
         <v>1846</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>1882</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>1918</v>
       </c>
       <c r="O8">
@@ -21414,10 +21432,10 @@
       <c r="L9" t="s">
         <v>1847</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>1883</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>1919</v>
       </c>
       <c r="O9">
@@ -21467,10 +21485,10 @@
       <c r="L10" t="s">
         <v>1848</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>1884</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>1920</v>
       </c>
       <c r="O10">
@@ -21520,10 +21538,10 @@
       <c r="L11" t="s">
         <v>1849</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>1885</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>1921</v>
       </c>
       <c r="O11">
@@ -21573,10 +21591,10 @@
       <c r="L12" t="s">
         <v>1850</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>1886</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>1922</v>
       </c>
       <c r="O12">
@@ -21626,10 +21644,10 @@
       <c r="L13" t="s">
         <v>1851</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>1887</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>1923</v>
       </c>
       <c r="O13">
@@ -21679,10 +21697,10 @@
       <c r="L14" t="s">
         <v>1852</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>1888</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>1924</v>
       </c>
       <c r="O14">
@@ -21732,10 +21750,10 @@
       <c r="L15" t="s">
         <v>1853</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>1889</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>1925</v>
       </c>
       <c r="O15">
@@ -21785,10 +21803,10 @@
       <c r="L16" t="s">
         <v>1854</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>1890</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>1926</v>
       </c>
       <c r="O16">
@@ -21838,10 +21856,10 @@
       <c r="L17" t="s">
         <v>1855</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>1891</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>1927</v>
       </c>
       <c r="O17">
@@ -21891,10 +21909,10 @@
       <c r="L18" t="s">
         <v>1856</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>1892</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>1928</v>
       </c>
       <c r="O18">
@@ -21944,10 +21962,10 @@
       <c r="L19" t="s">
         <v>1857</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>1893</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>1929</v>
       </c>
       <c r="O19">
@@ -21997,10 +22015,10 @@
       <c r="L20" t="s">
         <v>1858</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>1894</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>1930</v>
       </c>
       <c r="O20">
@@ -22050,10 +22068,10 @@
       <c r="L21" t="s">
         <v>1859</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>1895</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>1931</v>
       </c>
       <c r="O21">
@@ -22103,10 +22121,10 @@
       <c r="L22" t="s">
         <v>1860</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>1896</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>1932</v>
       </c>
       <c r="O22">
@@ -22156,10 +22174,10 @@
       <c r="L23" t="s">
         <v>1861</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>1897</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>1933</v>
       </c>
       <c r="O23">
@@ -22209,10 +22227,10 @@
       <c r="L24" t="s">
         <v>1862</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>1898</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>1934</v>
       </c>
       <c r="O24">
@@ -22262,10 +22280,10 @@
       <c r="L25" t="s">
         <v>1863</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>1899</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>1935</v>
       </c>
       <c r="O25">
@@ -22312,10 +22330,10 @@
       <c r="L26" t="s">
         <v>1864</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>1900</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="3" t="s">
         <v>1936</v>
       </c>
       <c r="O26">
@@ -22365,10 +22383,10 @@
       <c r="L27" t="s">
         <v>1865</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="3" t="s">
         <v>1901</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="3" t="s">
         <v>1937</v>
       </c>
       <c r="O27">
@@ -22418,10 +22436,10 @@
       <c r="L28" t="s">
         <v>1866</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="M28" s="3" t="s">
         <v>1902</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="3" t="s">
         <v>1938</v>
       </c>
       <c r="O28">
@@ -22471,10 +22489,10 @@
       <c r="L29" t="s">
         <v>1867</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>1903</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>1939</v>
       </c>
       <c r="O29">
@@ -22524,10 +22542,10 @@
       <c r="L30" t="s">
         <v>1868</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="3" t="s">
         <v>1940</v>
       </c>
       <c r="O30">
@@ -22577,10 +22595,10 @@
       <c r="L31" t="s">
         <v>1869</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="3" t="s">
         <v>1941</v>
       </c>
       <c r="O31">
@@ -22630,10 +22648,10 @@
       <c r="L32" t="s">
         <v>1870</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="3" t="s">
         <v>1942</v>
       </c>
       <c r="O32">
@@ -22683,10 +22701,10 @@
       <c r="L33" t="s">
         <v>1871</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="3" t="s">
         <v>1943</v>
       </c>
       <c r="O33">
@@ -22736,10 +22754,10 @@
       <c r="L34" t="s">
         <v>1872</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>1908</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="3" t="s">
         <v>1944</v>
       </c>
       <c r="O34">
@@ -22789,10 +22807,10 @@
       <c r="L35" t="s">
         <v>1873</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>1909</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" s="3" t="s">
         <v>1945</v>
       </c>
       <c r="O35">
@@ -22842,10 +22860,10 @@
       <c r="L36" t="s">
         <v>1874</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>1910</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="N36" s="3" t="s">
         <v>1946</v>
       </c>
       <c r="O36">
@@ -22895,10 +22913,10 @@
       <c r="L37" t="s">
         <v>1875</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>1911</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="3" t="s">
         <v>1947</v>
       </c>
       <c r="O37">
@@ -22948,10 +22966,10 @@
       <c r="L38" t="s">
         <v>1876</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="3" t="s">
         <v>1912</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="3" t="s">
         <v>1948</v>
       </c>
       <c r="O38">
@@ -23086,55 +23104,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -23175,10 +23193,10 @@
       <c r="L3" t="s">
         <v>2012</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>2023</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="O3">
@@ -23228,10 +23246,10 @@
       <c r="L4" t="s">
         <v>2013</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="O4">
@@ -23281,10 +23299,10 @@
       <c r="L5" t="s">
         <v>2014</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>2025</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="O5">
@@ -23334,10 +23352,10 @@
       <c r="L6" t="s">
         <v>2015</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>2026</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="O6">
@@ -23384,10 +23402,10 @@
       <c r="L7" t="s">
         <v>2016</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>2027</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>2038</v>
       </c>
       <c r="O7">
@@ -23434,10 +23452,10 @@
       <c r="L8" t="s">
         <v>2017</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>2028</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>2039</v>
       </c>
       <c r="O8">
@@ -23484,10 +23502,10 @@
       <c r="L9" t="s">
         <v>2018</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>2029</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>2040</v>
       </c>
       <c r="O9">
@@ -23528,16 +23546,16 @@
       <c r="J10">
         <v>24.99</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L10" t="s">
         <v>2019</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>2030</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="O10">
@@ -23587,10 +23605,10 @@
       <c r="L11" t="s">
         <v>2020</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>2031</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>2042</v>
       </c>
       <c r="O11">
@@ -23634,16 +23652,16 @@
       <c r="J12">
         <v>24.99</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="3" t="s">
         <v>453</v>
       </c>
       <c r="L12" t="s">
         <v>2021</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>2032</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>2043</v>
       </c>
       <c r="O12">
@@ -23690,10 +23708,10 @@
       <c r="L13" t="s">
         <v>2022</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>2033</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="O13">
@@ -23780,55 +23798,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -23869,10 +23887,10 @@
       <c r="L3" t="s">
         <v>2069</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>2073</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>2077</v>
       </c>
       <c r="O3">
@@ -23922,10 +23940,10 @@
       <c r="L4" t="s">
         <v>2070</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>2074</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>2078</v>
       </c>
       <c r="O4">
@@ -23975,10 +23993,10 @@
       <c r="L5" t="s">
         <v>2071</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>2075</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>2079</v>
       </c>
       <c r="O5">
@@ -24028,10 +24046,10 @@
       <c r="L6" t="s">
         <v>2072</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>2076</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>2080</v>
       </c>
       <c r="O6">
@@ -24102,55 +24120,55 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -24191,10 +24209,10 @@
       <c r="L3" t="s">
         <v>2167</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>2198</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>2229</v>
       </c>
       <c r="O3">
@@ -24241,10 +24259,10 @@
       <c r="L4" t="s">
         <v>2168</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>2199</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>2230</v>
       </c>
       <c r="O4">
@@ -24294,10 +24312,10 @@
       <c r="L5" t="s">
         <v>2169</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>2200</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>2231</v>
       </c>
       <c r="O5">
@@ -24347,10 +24365,10 @@
       <c r="L6" t="s">
         <v>2170</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>2201</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>2232</v>
       </c>
       <c r="O6">
@@ -24397,10 +24415,10 @@
       <c r="L7" t="s">
         <v>2171</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>2202</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>2233</v>
       </c>
       <c r="O7">
@@ -24450,10 +24468,10 @@
       <c r="L8" t="s">
         <v>2172</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>2203</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>2234</v>
       </c>
       <c r="O8">
@@ -24503,10 +24521,10 @@
       <c r="L9" t="s">
         <v>2173</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>2204</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>2235</v>
       </c>
       <c r="O9">
@@ -24556,10 +24574,10 @@
       <c r="L10" t="s">
         <v>2174</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>2205</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>2236</v>
       </c>
       <c r="O10">
@@ -24606,10 +24624,10 @@
       <c r="L11" t="s">
         <v>2175</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>2206</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>2237</v>
       </c>
       <c r="O11">
@@ -24656,10 +24674,10 @@
       <c r="L12" t="s">
         <v>2176</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>2207</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>2238</v>
       </c>
       <c r="O12">
@@ -24709,10 +24727,10 @@
       <c r="L13" t="s">
         <v>2177</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>2208</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="3" t="s">
         <v>2239</v>
       </c>
       <c r="O13">
@@ -24759,10 +24777,10 @@
       <c r="L14" t="s">
         <v>2178</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>2209</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="3" t="s">
         <v>2240</v>
       </c>
       <c r="O14">
@@ -24812,10 +24830,10 @@
       <c r="L15" t="s">
         <v>2179</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>2210</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="3" t="s">
         <v>2241</v>
       </c>
       <c r="O15">
@@ -24865,10 +24883,10 @@
       <c r="L16" t="s">
         <v>2180</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>2211</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>2242</v>
       </c>
       <c r="O16">
@@ -24915,10 +24933,10 @@
       <c r="L17" t="s">
         <v>2181</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>2212</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="3" t="s">
         <v>2243</v>
       </c>
       <c r="O17">
@@ -24965,10 +24983,10 @@
       <c r="L18" t="s">
         <v>2182</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>2213</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="3" t="s">
         <v>2244</v>
       </c>
       <c r="O18">
@@ -25018,10 +25036,10 @@
       <c r="L19" t="s">
         <v>2183</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>2214</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="3" t="s">
         <v>2245</v>
       </c>
       <c r="O19">
@@ -25068,10 +25086,10 @@
       <c r="L20" t="s">
         <v>2184</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>2215</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="3" t="s">
         <v>2246</v>
       </c>
       <c r="O20">
@@ -25121,10 +25139,10 @@
       <c r="L21" t="s">
         <v>2185</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>2216</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="3" t="s">
         <v>2247</v>
       </c>
       <c r="O21">
@@ -25171,10 +25189,10 @@
       <c r="L22" t="s">
         <v>2186</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>2217</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="3" t="s">
         <v>2248</v>
       </c>
       <c r="O22">
@@ -25224,10 +25242,10 @@
       <c r="L23" t="s">
         <v>2187</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>2218</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="3" t="s">
         <v>2249</v>
       </c>
       <c r="O23">
@@ -25277,10 +25295,10 @@
       <c r="L24" t="s">
         <v>2188</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>2219</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="3" t="s">
         <v>2250</v>
       </c>
       <c r="O24">
@@ -25330,10 +25348,10 @@
       <c r="L25" t="s">
         <v>2189</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>2220</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>2251</v>
       </c>
       <c r="O25">
@@ -25383,10 +25401,10 @@
       <c r="L26" t="s">
         <v>2190</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="3" t="s">
         <v>2252</v>
       </c>
       <c r="O26">
@@ -25436,10 +25454,10 @@
       <c r="L27" t="s">
         <v>2191</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="3" t="s">
         <v>2222</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="3" t="s">
         <v>2253</v>
       </c>
       <c r="O27">
@@ -25486,10 +25504,10 @@
       <c r="L28" t="s">
         <v>2192</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="M28" s="3" t="s">
         <v>2223</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="3" t="s">
         <v>2254</v>
       </c>
       <c r="O28">
@@ -25539,10 +25557,10 @@
       <c r="L29" t="s">
         <v>2193</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>2224</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="3" t="s">
         <v>2255</v>
       </c>
       <c r="O29">
@@ -25589,10 +25607,10 @@
       <c r="L30" t="s">
         <v>2194</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>2225</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="3" t="s">
         <v>2256</v>
       </c>
       <c r="O30">
@@ -25642,10 +25660,10 @@
       <c r="L31" t="s">
         <v>2195</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>2226</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="3" t="s">
         <v>2257</v>
       </c>
       <c r="O31">
@@ -25692,10 +25710,10 @@
       <c r="L32" t="s">
         <v>2196</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>2227</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="3" t="s">
         <v>2258</v>
       </c>
       <c r="O32">
@@ -25745,10 +25763,10 @@
       <c r="L33" t="s">
         <v>2197</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>2228</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="3" t="s">
         <v>2259</v>
       </c>
       <c r="O33">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4323" uniqueCount="2335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4326" uniqueCount="2335">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4336" uniqueCount="2340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="2340">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -15572,7 +15572,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -20567,7 +20567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21153,7 +21153,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -5240,7 +5240,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4347" uniqueCount="2345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="2345">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="2345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4359" uniqueCount="2350">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -3652,6 +3652,9 @@
     <t>Blast-Attak</t>
   </si>
   <si>
+    <t>Expand-Or</t>
+  </si>
+  <si>
     <t>Great Black Wizard</t>
   </si>
   <si>
@@ -4207,6 +4210,9 @@
     <t>/app/data/MOTU/images/blast-attak-12884.jpg</t>
   </si>
   <si>
+    <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/expand-or-13889.jpg</t>
+  </si>
+  <si>
     <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
@@ -4396,6 +4402,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/blast-attak-12884.jpg</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/images/expand-or-13889.jpg</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
   </si>
   <si>
@@ -4585,6 +4594,9 @@
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/blast-attak-12884.php</t>
   </si>
   <si>
+    <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/expand-or-13889.php</t>
+  </si>
+  <si>
     <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
   </si>
   <si>
@@ -4772,6 +4784,9 @@
   </si>
   <si>
     <t>12884</t>
+  </si>
+  <si>
+    <t>13889</t>
   </si>
   <si>
     <t>12852</t>
@@ -14915,7 +14930,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2322</v>
+        <v>2327</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14992,13 +15007,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2323</v>
+        <v>2328</v>
       </c>
       <c r="D3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E3" t="s">
-        <v>2326</v>
+        <v>2331</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15007,10 +15022,10 @@
         <v>0.51</v>
       </c>
       <c r="H3" t="s">
-        <v>2328</v>
+        <v>2333</v>
       </c>
       <c r="I3" t="s">
-        <v>2330</v>
+        <v>2335</v>
       </c>
       <c r="J3">
         <v>39.95</v>
@@ -15019,13 +15034,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>2333</v>
+        <v>2338</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>2336</v>
+        <v>2341</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>2339</v>
+        <v>2344</v>
       </c>
       <c r="O3">
         <v>20.51</v>
@@ -15034,7 +15049,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>2342</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15042,13 +15057,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2324</v>
+        <v>2329</v>
       </c>
       <c r="D4" t="s">
         <v>188</v>
       </c>
       <c r="E4" t="s">
-        <v>2327</v>
+        <v>2332</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15057,10 +15072,10 @@
         <v>0.6</v>
       </c>
       <c r="H4" t="s">
-        <v>2329</v>
+        <v>2334</v>
       </c>
       <c r="I4" t="s">
-        <v>2331</v>
+        <v>2336</v>
       </c>
       <c r="J4">
         <v>59.95</v>
@@ -15069,13 +15084,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>2334</v>
+        <v>2339</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>2337</v>
+        <v>2342</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>2340</v>
+        <v>2345</v>
       </c>
       <c r="O4">
         <v>36.25</v>
@@ -15084,7 +15099,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>2343</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -15092,13 +15107,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2325</v>
+        <v>2330</v>
       </c>
       <c r="D5" t="s">
         <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>2327</v>
+        <v>2332</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -15107,7 +15122,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="s">
-        <v>2332</v>
+        <v>2337</v>
       </c>
       <c r="J5">
         <v>59.95</v>
@@ -15116,13 +15131,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>2335</v>
+        <v>2340</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>2338</v>
+        <v>2343</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2341</v>
+        <v>2346</v>
       </c>
       <c r="O5">
         <v>138.16</v>
@@ -15131,7 +15146,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>2344</v>
+        <v>2349</v>
       </c>
     </row>
   </sheetData>
@@ -16307,7 +16322,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -16392,13 +16407,13 @@
         <v>1152</v>
       </c>
       <c r="C3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="D3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E3" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -16407,10 +16422,10 @@
         <v>9.84</v>
       </c>
       <c r="H3" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="I3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="J3">
         <v>39.99</v>
@@ -16419,13 +16434,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="O3">
         <v>393.33</v>
@@ -16434,7 +16449,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -16445,13 +16460,13 @@
         <v>1153</v>
       </c>
       <c r="C4" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D4" t="s">
         <v>188</v>
       </c>
       <c r="E4" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -16460,7 +16475,7 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="J4">
         <v>269.99</v>
@@ -16469,13 +16484,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="O4">
         <v>323.96</v>
@@ -16484,7 +16499,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -16495,13 +16510,13 @@
         <v>1154</v>
       </c>
       <c r="C5" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D5" t="s">
         <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -16510,10 +16525,10 @@
         <v>2.75</v>
       </c>
       <c r="H5" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="I5" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="J5">
         <v>39.99</v>
@@ -16522,13 +16537,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="O5">
         <v>110</v>
@@ -16537,7 +16552,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -16548,13 +16563,13 @@
         <v>1155</v>
       </c>
       <c r="C6" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D6" t="s">
         <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -16563,7 +16578,7 @@
         <v>5.83</v>
       </c>
       <c r="I6" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -16572,13 +16587,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="O6">
         <v>350</v>
@@ -16587,7 +16602,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -16598,13 +16613,13 @@
         <v>1156</v>
       </c>
       <c r="C7" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D7" t="s">
         <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -16613,7 +16628,7 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -16622,13 +16637,13 @@
         <v>465</v>
       </c>
       <c r="L7" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="O7">
         <v>216.32</v>
@@ -16637,7 +16652,7 @@
         <v>871</v>
       </c>
       <c r="Q7" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -16654,7 +16669,7 @@
         <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F8">
         <v>1537</v>
@@ -16663,10 +16678,10 @@
         <v>0.48</v>
       </c>
       <c r="H8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I8" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="J8">
         <v>29.99</v>
@@ -16675,13 +16690,13 @@
         <v>465</v>
       </c>
       <c r="L8" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="O8">
         <v>14.33</v>
@@ -16690,7 +16705,7 @@
         <v>871</v>
       </c>
       <c r="Q8" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -16701,13 +16716,13 @@
         <v>1158</v>
       </c>
       <c r="C9" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D9" t="s">
         <v>189</v>
       </c>
       <c r="E9" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -16722,13 +16737,13 @@
         <v>465</v>
       </c>
       <c r="L9" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="O9">
         <v>109.99</v>
@@ -16737,7 +16752,7 @@
         <v>871</v>
       </c>
       <c r="Q9" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -16748,13 +16763,13 @@
         <v>1159</v>
       </c>
       <c r="C10" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D10" t="s">
         <v>189</v>
       </c>
       <c r="E10" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16763,7 +16778,7 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -16772,13 +16787,13 @@
         <v>465</v>
       </c>
       <c r="L10" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="O10">
         <v>260</v>
@@ -16787,7 +16802,7 @@
         <v>871</v>
       </c>
       <c r="Q10" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -16798,13 +16813,13 @@
         <v>1160</v>
       </c>
       <c r="C11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D11" t="s">
         <v>189</v>
       </c>
       <c r="E11" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -16819,13 +16834,13 @@
         <v>465</v>
       </c>
       <c r="L11" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="O11">
         <v>299.95</v>
@@ -16834,7 +16849,7 @@
         <v>871</v>
       </c>
       <c r="Q11" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -16845,13 +16860,13 @@
         <v>1161</v>
       </c>
       <c r="C12" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D12" t="s">
         <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16866,13 +16881,13 @@
         <v>465</v>
       </c>
       <c r="L12" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="O12">
         <v>126.66</v>
@@ -16881,7 +16896,7 @@
         <v>871</v>
       </c>
       <c r="Q12" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -16892,13 +16907,13 @@
         <v>1162</v>
       </c>
       <c r="C13" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D13" t="s">
         <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16907,7 +16922,7 @@
         <v>4.33</v>
       </c>
       <c r="I13" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="J13">
         <v>50</v>
@@ -16916,13 +16931,13 @@
         <v>465</v>
       </c>
       <c r="L13" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="O13">
         <v>216.67</v>
@@ -16931,7 +16946,7 @@
         <v>871</v>
       </c>
       <c r="Q13" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -16942,13 +16957,13 @@
         <v>1163</v>
       </c>
       <c r="C14" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D14" t="s">
         <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -16957,7 +16972,7 @@
         <v>1.72</v>
       </c>
       <c r="I14" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -16966,13 +16981,13 @@
         <v>465</v>
       </c>
       <c r="L14" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="O14">
         <v>51.65</v>
@@ -16981,7 +16996,7 @@
         <v>871</v>
       </c>
       <c r="Q14" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -16992,13 +17007,13 @@
         <v>1164</v>
       </c>
       <c r="C15" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D15" t="s">
         <v>189</v>
       </c>
       <c r="E15" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F15">
         <v>503</v>
@@ -17007,7 +17022,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="J15">
         <v>17</v>
@@ -17016,13 +17031,13 @@
         <v>465</v>
       </c>
       <c r="L15" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="O15">
         <v>95.16</v>
@@ -17031,7 +17046,7 @@
         <v>871</v>
       </c>
       <c r="Q15" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -17048,7 +17063,7 @@
         <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F16">
         <v>606</v>
@@ -17057,10 +17072,10 @@
         <v>2.86</v>
       </c>
       <c r="H16" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="I16" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -17069,13 +17084,13 @@
         <v>465</v>
       </c>
       <c r="L16" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="O16">
         <v>85.70999999999999</v>
@@ -17084,7 +17099,7 @@
         <v>871</v>
       </c>
       <c r="Q16" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -17110,10 +17125,10 @@
         <v>2.33</v>
       </c>
       <c r="H17" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="I17" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="J17">
         <v>18</v>
@@ -17122,13 +17137,13 @@
         <v>465</v>
       </c>
       <c r="L17" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="O17">
         <v>42</v>
@@ -17137,7 +17152,7 @@
         <v>871</v>
       </c>
       <c r="Q17" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -17154,7 +17169,7 @@
         <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -17163,10 +17178,10 @@
         <v>0.53</v>
       </c>
       <c r="H18" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="I18" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="J18">
         <v>150</v>
@@ -17175,13 +17190,13 @@
         <v>465</v>
       </c>
       <c r="L18" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="O18">
         <v>79.75</v>
@@ -17190,7 +17205,7 @@
         <v>871</v>
       </c>
       <c r="Q18" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -17207,7 +17222,7 @@
         <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F19">
         <v>536</v>
@@ -17216,7 +17231,7 @@
         <v>4.54</v>
       </c>
       <c r="I19" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="J19">
         <v>17</v>
@@ -17225,13 +17240,13 @@
         <v>465</v>
       </c>
       <c r="L19" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="O19">
         <v>77.23999999999999</v>
@@ -17240,7 +17255,7 @@
         <v>871</v>
       </c>
       <c r="Q19" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -17266,10 +17281,10 @@
         <v>1.34</v>
       </c>
       <c r="H20" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="I20" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J20">
         <v>18</v>
@@ -17278,13 +17293,13 @@
         <v>465</v>
       </c>
       <c r="L20" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="O20">
         <v>24.09</v>
@@ -17293,7 +17308,7 @@
         <v>871</v>
       </c>
       <c r="Q20" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -17310,7 +17325,7 @@
         <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F21">
         <v>671</v>
@@ -17319,7 +17334,7 @@
         <v>0.4</v>
       </c>
       <c r="I21" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="J21">
         <v>49.99</v>
@@ -17328,13 +17343,13 @@
         <v>465</v>
       </c>
       <c r="L21" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="O21">
         <v>19.99</v>
@@ -17343,7 +17358,7 @@
         <v>871</v>
       </c>
       <c r="Q21" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -17360,7 +17375,7 @@
         <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F22">
         <v>911</v>
@@ -17369,10 +17384,10 @@
         <v>1.93</v>
       </c>
       <c r="H22" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="I22" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="J22">
         <v>17</v>
@@ -17381,13 +17396,13 @@
         <v>465</v>
       </c>
       <c r="L22" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="O22">
         <v>32.76</v>
@@ -17396,7 +17411,7 @@
         <v>871</v>
       </c>
       <c r="Q22" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -17410,7 +17425,7 @@
         <v>191</v>
       </c>
       <c r="E23" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F23">
         <v>524</v>
@@ -17419,10 +17434,10 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="I23" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="J23">
         <v>64.98999999999999</v>
@@ -17431,13 +17446,13 @@
         <v>465</v>
       </c>
       <c r="L23" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="O23">
         <v>129.79</v>
@@ -17446,7 +17461,7 @@
         <v>871</v>
       </c>
       <c r="Q23" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -17472,10 +17487,10 @@
         <v>1.91</v>
       </c>
       <c r="H24" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="I24" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -17484,13 +17499,13 @@
         <v>465</v>
       </c>
       <c r="L24" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="O24">
         <v>38.24</v>
@@ -17499,7 +17514,7 @@
         <v>871</v>
       </c>
       <c r="Q24" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -17525,10 +17540,10 @@
         <v>1.97</v>
       </c>
       <c r="H25" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="I25" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="J25">
         <v>17.99</v>
@@ -17537,13 +17552,13 @@
         <v>465</v>
       </c>
       <c r="L25" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="O25">
         <v>35.47</v>
@@ -17552,7 +17567,7 @@
         <v>871</v>
       </c>
       <c r="Q25" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -17578,10 +17593,10 @@
         <v>1.85</v>
       </c>
       <c r="H26" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="I26" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="J26">
         <v>17.99</v>
@@ -17590,13 +17605,13 @@
         <v>465</v>
       </c>
       <c r="L26" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="O26">
         <v>33.25</v>
@@ -17605,7 +17620,7 @@
         <v>871</v>
       </c>
       <c r="Q26" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -17622,7 +17637,7 @@
         <v>191</v>
       </c>
       <c r="E27" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="F27">
         <v>728</v>
@@ -17631,10 +17646,10 @@
         <v>1.2</v>
       </c>
       <c r="H27" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="I27" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="J27">
         <v>35</v>
@@ -17643,13 +17658,13 @@
         <v>465</v>
       </c>
       <c r="L27" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="O27">
         <v>41.94</v>
@@ -17658,7 +17673,7 @@
         <v>871</v>
       </c>
       <c r="Q27" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -17684,10 +17699,10 @@
         <v>2.29</v>
       </c>
       <c r="H28" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="I28" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="J28">
         <v>17.99</v>
@@ -17696,13 +17711,13 @@
         <v>465</v>
       </c>
       <c r="L28" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="O28">
         <v>41.11</v>
@@ -17711,7 +17726,7 @@
         <v>871</v>
       </c>
       <c r="Q28" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -17728,7 +17743,7 @@
         <v>191</v>
       </c>
       <c r="E29" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F29">
         <v>508</v>
@@ -17737,10 +17752,10 @@
         <v>0.52</v>
       </c>
       <c r="H29" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="I29" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J29">
         <v>49.99</v>
@@ -17749,13 +17764,13 @@
         <v>465</v>
       </c>
       <c r="L29" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="O29">
         <v>26.14</v>
@@ -17764,7 +17779,7 @@
         <v>871</v>
       </c>
       <c r="Q29" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -17778,7 +17793,7 @@
         <v>191</v>
       </c>
       <c r="E30" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F30">
         <v>759</v>
@@ -17787,10 +17802,10 @@
         <v>1.88</v>
       </c>
       <c r="H30" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="I30" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="J30">
         <v>31.99</v>
@@ -17799,13 +17814,13 @@
         <v>465</v>
       </c>
       <c r="L30" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="O30">
         <v>60</v>
@@ -17814,7 +17829,7 @@
         <v>871</v>
       </c>
       <c r="Q30" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -17831,7 +17846,7 @@
         <v>192</v>
       </c>
       <c r="E31" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F31">
         <v>568</v>
@@ -17840,10 +17855,10 @@
         <v>1.09</v>
       </c>
       <c r="H31" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="I31" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="J31">
         <v>22.97</v>
@@ -17852,13 +17867,13 @@
         <v>465</v>
       </c>
       <c r="L31" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="O31">
         <v>24.99</v>
@@ -17867,7 +17882,7 @@
         <v>871</v>
       </c>
       <c r="Q31" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -17884,7 +17899,7 @@
         <v>192</v>
       </c>
       <c r="E32" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F32">
         <v>560</v>
@@ -17893,10 +17908,10 @@
         <v>1.56</v>
       </c>
       <c r="H32" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="I32" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="J32">
         <v>20</v>
@@ -17905,13 +17920,13 @@
         <v>465</v>
       </c>
       <c r="L32" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="O32">
         <v>31.2</v>
@@ -17920,7 +17935,7 @@
         <v>871</v>
       </c>
       <c r="Q32" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -17937,7 +17952,7 @@
         <v>192</v>
       </c>
       <c r="E33" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -17946,10 +17961,10 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="I33" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="J33">
         <v>550</v>
@@ -17958,13 +17973,13 @@
         <v>465</v>
       </c>
       <c r="L33" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="O33">
         <v>700.51</v>
@@ -17973,7 +17988,7 @@
         <v>871</v>
       </c>
       <c r="Q33" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -17990,7 +18005,7 @@
         <v>192</v>
       </c>
       <c r="E34" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F34">
         <v>664</v>
@@ -17999,10 +18014,10 @@
         <v>1.5</v>
       </c>
       <c r="H34" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="I34" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="J34">
         <v>20</v>
@@ -18011,13 +18026,13 @@
         <v>465</v>
       </c>
       <c r="L34" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="O34">
         <v>29.98</v>
@@ -18026,7 +18041,7 @@
         <v>871</v>
       </c>
       <c r="Q34" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -18043,7 +18058,7 @@
         <v>192</v>
       </c>
       <c r="E35" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F35">
         <v>572</v>
@@ -18052,10 +18067,10 @@
         <v>0.88</v>
       </c>
       <c r="H35" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="I35" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="J35">
         <v>22.99</v>
@@ -18064,13 +18079,13 @@
         <v>465</v>
       </c>
       <c r="L35" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="O35">
         <v>20.23</v>
@@ -18079,7 +18094,7 @@
         <v>871</v>
       </c>
       <c r="Q35" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -18108,13 +18123,13 @@
         <v>465</v>
       </c>
       <c r="L36" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="O36">
         <v>198.33</v>
@@ -18123,7 +18138,7 @@
         <v>871</v>
       </c>
       <c r="Q36" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -18140,7 +18155,7 @@
         <v>192</v>
       </c>
       <c r="E37" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F37">
         <v>615</v>
@@ -18149,10 +18164,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="I37" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="J37">
         <v>22.97</v>
@@ -18161,13 +18176,13 @@
         <v>465</v>
       </c>
       <c r="L37" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="O37">
         <v>16.07</v>
@@ -18176,7 +18191,7 @@
         <v>871</v>
       </c>
       <c r="Q37" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -18193,7 +18208,7 @@
         <v>192</v>
       </c>
       <c r="E38" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F38">
         <v>708</v>
@@ -18202,10 +18217,10 @@
         <v>1.85</v>
       </c>
       <c r="H38" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="I38" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="J38">
         <v>20</v>
@@ -18214,13 +18229,13 @@
         <v>465</v>
       </c>
       <c r="L38" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="O38">
         <v>36.95</v>
@@ -18229,7 +18244,7 @@
         <v>871</v>
       </c>
       <c r="Q38" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -18246,7 +18261,7 @@
         <v>192</v>
       </c>
       <c r="E39" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -18255,10 +18270,10 @@
         <v>1.25</v>
       </c>
       <c r="H39" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="I39" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="J39">
         <v>45</v>
@@ -18267,13 +18282,13 @@
         <v>465</v>
       </c>
       <c r="L39" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="O39">
         <v>56.07</v>
@@ -18282,7 +18297,7 @@
         <v>871</v>
       </c>
       <c r="Q39" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -18299,7 +18314,7 @@
         <v>192</v>
       </c>
       <c r="E40" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F40">
         <v>700</v>
@@ -18308,10 +18323,10 @@
         <v>2.24</v>
       </c>
       <c r="H40" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="I40" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="J40">
         <v>24</v>
@@ -18320,13 +18335,13 @@
         <v>465</v>
       </c>
       <c r="L40" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="O40">
         <v>53.81</v>
@@ -18335,7 +18350,7 @@
         <v>871</v>
       </c>
       <c r="Q40" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -18346,13 +18361,13 @@
         <v>1190</v>
       </c>
       <c r="C41" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D41" t="s">
         <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -18361,7 +18376,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="J41">
         <v>90</v>
@@ -18370,13 +18385,13 @@
         <v>465</v>
       </c>
       <c r="L41" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -18385,7 +18400,7 @@
         <v>871</v>
       </c>
       <c r="Q41" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -18396,13 +18411,13 @@
         <v>1191</v>
       </c>
       <c r="C42" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="D42" t="s">
         <v>192</v>
       </c>
       <c r="E42" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -18411,10 +18426,10 @@
         <v>2.66</v>
       </c>
       <c r="H42" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="I42" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="J42">
         <v>50</v>
@@ -18423,13 +18438,13 @@
         <v>465</v>
       </c>
       <c r="L42" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="O42">
         <v>132.99</v>
@@ -18438,7 +18453,7 @@
         <v>871</v>
       </c>
       <c r="Q42" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -18455,7 +18470,7 @@
         <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -18464,10 +18479,10 @@
         <v>1.29</v>
       </c>
       <c r="H43" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="I43" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="J43">
         <v>64.98999999999999</v>
@@ -18476,13 +18491,13 @@
         <v>465</v>
       </c>
       <c r="L43" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="O43">
         <v>83.73</v>
@@ -18491,7 +18506,7 @@
         <v>871</v>
       </c>
       <c r="Q43" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -18508,7 +18523,7 @@
         <v>193</v>
       </c>
       <c r="E44" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -18523,13 +18538,13 @@
         <v>465</v>
       </c>
       <c r="L44" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="O44">
         <v>26.9</v>
@@ -18538,7 +18553,7 @@
         <v>871</v>
       </c>
       <c r="Q44" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -18555,7 +18570,7 @@
         <v>193</v>
       </c>
       <c r="E45" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -18570,13 +18585,13 @@
         <v>465</v>
       </c>
       <c r="L45" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="O45">
         <v>43.75</v>
@@ -18585,7 +18600,7 @@
         <v>871</v>
       </c>
       <c r="Q45" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -18608,7 +18623,7 @@
         <v>2.12</v>
       </c>
       <c r="I46" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J46">
         <v>19.99</v>
@@ -18617,13 +18632,13 @@
         <v>465</v>
       </c>
       <c r="L46" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="O46">
         <v>42.3</v>
@@ -18632,7 +18647,7 @@
         <v>871</v>
       </c>
       <c r="Q46" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -18643,13 +18658,13 @@
         <v>1196</v>
       </c>
       <c r="C47" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D47" t="s">
         <v>193</v>
       </c>
       <c r="E47" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -18658,10 +18673,10 @@
         <v>0.87</v>
       </c>
       <c r="H47" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="I47" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="J47">
         <v>20</v>
@@ -18670,13 +18685,13 @@
         <v>465</v>
       </c>
       <c r="L47" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="O47">
         <v>17.33</v>
@@ -18685,7 +18700,7 @@
         <v>871</v>
       </c>
       <c r="Q47" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -18696,13 +18711,13 @@
         <v>1197</v>
       </c>
       <c r="C48" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
       </c>
       <c r="E48" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -18711,7 +18726,7 @@
         <v>0.23</v>
       </c>
       <c r="I48" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="J48">
         <v>100</v>
@@ -18720,13 +18735,13 @@
         <v>465</v>
       </c>
       <c r="L48" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="O48">
         <v>22.95</v>
@@ -18735,7 +18750,7 @@
         <v>871</v>
       </c>
       <c r="Q48" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -18752,7 +18767,7 @@
         <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F49">
         <v>509</v>
@@ -18761,10 +18776,10 @@
         <v>0.49</v>
       </c>
       <c r="H49" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="I49" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="J49">
         <v>29.99</v>
@@ -18773,13 +18788,13 @@
         <v>465</v>
       </c>
       <c r="L49" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="O49">
         <v>14.81</v>
@@ -18788,7 +18803,7 @@
         <v>871</v>
       </c>
       <c r="Q49" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -18805,7 +18820,7 @@
         <v>193</v>
       </c>
       <c r="E50" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -18814,7 +18829,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J50">
         <v>34.99</v>
@@ -18823,13 +18838,13 @@
         <v>465</v>
       </c>
       <c r="L50" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="O50">
         <v>28.41</v>
@@ -18838,7 +18853,7 @@
         <v>871</v>
       </c>
       <c r="Q50" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -18855,7 +18870,7 @@
         <v>193</v>
       </c>
       <c r="E51" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F51">
         <v>552</v>
@@ -18864,10 +18879,10 @@
         <v>0.93</v>
       </c>
       <c r="H51" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="I51" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J51">
         <v>29.99</v>
@@ -18876,13 +18891,13 @@
         <v>465</v>
       </c>
       <c r="L51" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="O51">
         <v>27.99</v>
@@ -18891,7 +18906,7 @@
         <v>871</v>
       </c>
       <c r="Q51" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -18908,7 +18923,7 @@
         <v>193</v>
       </c>
       <c r="E52" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -18917,10 +18932,10 @@
         <v>1.06</v>
       </c>
       <c r="H52" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="I52" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="J52">
         <v>31.99</v>
@@ -18929,13 +18944,13 @@
         <v>465</v>
       </c>
       <c r="L52" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="O52">
         <v>34.04</v>
@@ -18944,7 +18959,7 @@
         <v>871</v>
       </c>
       <c r="Q52" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -18961,7 +18976,7 @@
         <v>193</v>
       </c>
       <c r="E53" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -18970,10 +18985,10 @@
         <v>0.92</v>
       </c>
       <c r="H53" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I53" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="J53">
         <v>44.99</v>
@@ -18982,13 +18997,13 @@
         <v>465</v>
       </c>
       <c r="L53" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="O53">
         <v>41.52</v>
@@ -18997,7 +19012,7 @@
         <v>871</v>
       </c>
       <c r="Q53" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -19014,7 +19029,7 @@
         <v>193</v>
       </c>
       <c r="E54" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F54">
         <v>609</v>
@@ -19023,10 +19038,10 @@
         <v>1.17</v>
       </c>
       <c r="H54" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="I54" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J54">
         <v>20</v>
@@ -19035,13 +19050,13 @@
         <v>465</v>
       </c>
       <c r="L54" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="O54">
         <v>23.48</v>
@@ -19050,7 +19065,7 @@
         <v>871</v>
       </c>
       <c r="Q54" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -19067,7 +19082,7 @@
         <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -19076,10 +19091,10 @@
         <v>0.87</v>
       </c>
       <c r="H55" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="I55" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="J55">
         <v>29.99</v>
@@ -19088,13 +19103,13 @@
         <v>465</v>
       </c>
       <c r="L55" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="O55">
         <v>26.18</v>
@@ -19103,7 +19118,7 @@
         <v>871</v>
       </c>
       <c r="Q55" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -19120,7 +19135,7 @@
         <v>193</v>
       </c>
       <c r="E56" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -19129,10 +19144,10 @@
         <v>0.97</v>
       </c>
       <c r="H56" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="I56" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="J56">
         <v>69.98999999999999</v>
@@ -19141,13 +19156,13 @@
         <v>465</v>
       </c>
       <c r="L56" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="O56">
         <v>67.75</v>
@@ -19156,7 +19171,7 @@
         <v>871</v>
       </c>
       <c r="Q56" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -19182,10 +19197,10 @@
         <v>0.87</v>
       </c>
       <c r="H57" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="I57" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="J57">
         <v>19.99</v>
@@ -19194,13 +19209,13 @@
         <v>465</v>
       </c>
       <c r="L57" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="O57">
         <v>17.42</v>
@@ -19209,7 +19224,7 @@
         <v>871</v>
       </c>
       <c r="Q57" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -19226,7 +19241,7 @@
         <v>193</v>
       </c>
       <c r="E58" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -19235,10 +19250,10 @@
         <v>1.1</v>
       </c>
       <c r="H58" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="I58" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J58">
         <v>20</v>
@@ -19247,13 +19262,13 @@
         <v>465</v>
       </c>
       <c r="L58" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="O58">
         <v>22</v>
@@ -19262,7 +19277,7 @@
         <v>871</v>
       </c>
       <c r="Q58" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -19294,13 +19309,13 @@
         <v>465</v>
       </c>
       <c r="L59" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="O59">
         <v>46.28</v>
@@ -19309,12 +19324,12 @@
         <v>871</v>
       </c>
       <c r="Q59" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
         <v>1209</v>
@@ -19326,37 +19341,37 @@
         <v>194</v>
       </c>
       <c r="E60" t="s">
-        <v>1233</v>
+        <v>202</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>31.99</v>
-      </c>
-      <c r="K60" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>465</v>
       </c>
       <c r="L60" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="O60">
-        <v>40.52</v>
+        <v>0</v>
       </c>
       <c r="P60" t="s">
         <v>871</v>
       </c>
       <c r="Q60" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -19373,37 +19388,37 @@
         <v>194</v>
       </c>
       <c r="E61" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="J61">
-        <v>100</v>
-      </c>
-      <c r="K61" s="3" t="s">
+        <v>31.99</v>
+      </c>
+      <c r="K61" t="s">
         <v>465</v>
       </c>
       <c r="L61" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>40.52</v>
       </c>
       <c r="P61" t="s">
         <v>871</v>
       </c>
       <c r="Q61" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -19420,7 +19435,7 @@
         <v>194</v>
       </c>
       <c r="E62" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -19435,13 +19450,13 @@
         <v>465</v>
       </c>
       <c r="L62" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -19450,7 +19465,7 @@
         <v>871</v>
       </c>
       <c r="Q62" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -19467,7 +19482,7 @@
         <v>194</v>
       </c>
       <c r="E63" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -19476,19 +19491,19 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>465</v>
       </c>
       <c r="L63" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -19497,7 +19512,7 @@
         <v>871</v>
       </c>
       <c r="Q63" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -19514,7 +19529,7 @@
         <v>194</v>
       </c>
       <c r="E64" t="s">
-        <v>202</v>
+        <v>1247</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -19523,19 +19538,19 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>465</v>
       </c>
       <c r="L64" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -19544,24 +19559,24 @@
         <v>871</v>
       </c>
       <c r="Q64" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="65" spans="1:17">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
         <v>1214</v>
       </c>
       <c r="C65" t="s">
-        <v>1029</v>
+        <v>178</v>
       </c>
       <c r="D65" t="s">
         <v>194</v>
       </c>
       <c r="E65" t="s">
-        <v>1247</v>
+        <v>202</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -19569,26 +19584,20 @@
       <c r="G65">
         <v>1</v>
       </c>
-      <c r="H65" t="s">
-        <v>1285</v>
-      </c>
-      <c r="I65" t="s">
-        <v>1336</v>
-      </c>
       <c r="J65">
-        <v>37.79</v>
-      </c>
-      <c r="K65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>465</v>
       </c>
       <c r="L65" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -19597,14 +19606,67 @@
         <v>871</v>
       </c>
       <c r="Q65" t="s">
-        <v>1588</v>
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D66" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I66" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J66">
+        <v>37.79</v>
+      </c>
+      <c r="K66" t="s">
+        <v>465</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1401</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66" t="s">
+        <v>871</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>1593</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A65">
+  <conditionalFormatting sqref="A3:A66">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Sí"</formula>
     </cfRule>
@@ -19613,7 +19675,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A66">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19732,9 +19794,9 @@
     <hyperlink ref="N58" r:id="rId112"/>
     <hyperlink ref="M59" r:id="rId113"/>
     <hyperlink ref="N59" r:id="rId114"/>
-    <hyperlink ref="M60" r:id="rId115"/>
-    <hyperlink ref="N60" r:id="rId116"/>
-    <hyperlink ref="K61" r:id="rId117"/>
+    <hyperlink ref="K60" r:id="rId115"/>
+    <hyperlink ref="M60" r:id="rId116"/>
+    <hyperlink ref="N60" r:id="rId117"/>
     <hyperlink ref="M61" r:id="rId118"/>
     <hyperlink ref="N61" r:id="rId119"/>
     <hyperlink ref="K62" r:id="rId120"/>
@@ -19746,8 +19808,11 @@
     <hyperlink ref="K64" r:id="rId126"/>
     <hyperlink ref="M64" r:id="rId127"/>
     <hyperlink ref="N64" r:id="rId128"/>
-    <hyperlink ref="M65" r:id="rId129"/>
-    <hyperlink ref="N65" r:id="rId130"/>
+    <hyperlink ref="K65" r:id="rId129"/>
+    <hyperlink ref="M65" r:id="rId130"/>
+    <hyperlink ref="N65" r:id="rId131"/>
+    <hyperlink ref="M66" r:id="rId132"/>
+    <hyperlink ref="N66" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19760,7 +19825,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19837,7 +19902,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
       <c r="C3" t="s">
         <v>183</v>
@@ -19846,7 +19911,7 @@
         <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F3">
         <v>1047</v>
@@ -19855,7 +19920,7 @@
         <v>0.67</v>
       </c>
       <c r="I3" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="J3">
         <v>49.99</v>
@@ -19864,13 +19929,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="O3">
         <v>33.33</v>
@@ -19879,7 +19944,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>1730</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -19887,7 +19952,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="D4" t="s">
         <v>189</v>
@@ -19902,10 +19967,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="I4" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="J4">
         <v>24.99</v>
@@ -19914,13 +19979,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="O4">
         <v>13.69</v>
@@ -19929,7 +19994,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -19937,13 +20002,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
       <c r="D5" t="s">
         <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="F5">
         <v>1752</v>
@@ -19952,10 +20017,10 @@
         <v>1.21</v>
       </c>
       <c r="H5" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="I5" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="J5">
         <v>74.98999999999999</v>
@@ -19964,13 +20029,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1708</v>
+        <v>1713</v>
       </c>
       <c r="O5">
         <v>90.84999999999999</v>
@@ -19979,7 +20044,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>1732</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19987,13 +20052,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="D6" t="s">
         <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F6">
         <v>1538</v>
@@ -20002,10 +20067,10 @@
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="I6" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -20014,13 +20079,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>1709</v>
+        <v>1714</v>
       </c>
       <c r="O6">
         <v>15.03</v>
@@ -20029,7 +20094,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>1733</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -20037,7 +20102,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="D7" t="s">
         <v>189</v>
@@ -20052,10 +20117,10 @@
         <v>0.59</v>
       </c>
       <c r="H7" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="I7" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="J7">
         <v>24.99</v>
@@ -20064,13 +20129,13 @@
         <v>465</v>
       </c>
       <c r="L7" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="O7">
         <v>14.62</v>
@@ -20079,7 +20144,7 @@
         <v>871</v>
       </c>
       <c r="Q7" t="s">
-        <v>1734</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -20087,7 +20152,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="C8" t="s">
         <v>177</v>
@@ -20096,7 +20161,7 @@
         <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F8">
         <v>1179</v>
@@ -20105,10 +20170,10 @@
         <v>0.54</v>
       </c>
       <c r="H8" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="I8" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="J8">
         <v>39.99</v>
@@ -20117,13 +20182,13 @@
         <v>465</v>
       </c>
       <c r="L8" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>1711</v>
+        <v>1716</v>
       </c>
       <c r="O8">
         <v>21.68</v>
@@ -20132,7 +20197,7 @@
         <v>871</v>
       </c>
       <c r="Q8" t="s">
-        <v>1735</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -20140,13 +20205,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
       <c r="D9" t="s">
         <v>189</v>
       </c>
       <c r="E9" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F9">
         <v>1805</v>
@@ -20155,10 +20220,10 @@
         <v>0.53</v>
       </c>
       <c r="H9" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="I9" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="J9">
         <v>29.99</v>
@@ -20167,13 +20232,13 @@
         <v>465</v>
       </c>
       <c r="L9" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1712</v>
+        <v>1717</v>
       </c>
       <c r="O9">
         <v>16</v>
@@ -20182,7 +20247,7 @@
         <v>871</v>
       </c>
       <c r="Q9" t="s">
-        <v>1736</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -20190,13 +20255,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="D10" t="s">
         <v>189</v>
       </c>
       <c r="E10" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F10">
         <v>1571</v>
@@ -20205,10 +20270,10 @@
         <v>0.74</v>
       </c>
       <c r="H10" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="I10" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -20217,13 +20282,13 @@
         <v>465</v>
       </c>
       <c r="L10" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>1713</v>
+        <v>1718</v>
       </c>
       <c r="O10">
         <v>22.11</v>
@@ -20232,7 +20297,7 @@
         <v>871</v>
       </c>
       <c r="Q10" t="s">
-        <v>1737</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -20240,13 +20305,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="D11" t="s">
         <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F11">
         <v>1159</v>
@@ -20255,10 +20320,10 @@
         <v>0.59</v>
       </c>
       <c r="H11" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="I11" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="J11">
         <v>29.99</v>
@@ -20267,13 +20332,13 @@
         <v>465</v>
       </c>
       <c r="L11" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="O11">
         <v>17.83</v>
@@ -20282,7 +20347,7 @@
         <v>871</v>
       </c>
       <c r="Q11" t="s">
-        <v>1738</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -20290,7 +20355,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="D12" t="s">
         <v>190</v>
@@ -20305,10 +20370,10 @@
         <v>0.71</v>
       </c>
       <c r="H12" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="I12" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -20317,13 +20382,13 @@
         <v>465</v>
       </c>
       <c r="L12" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="O12">
         <v>17.77</v>
@@ -20332,7 +20397,7 @@
         <v>871</v>
       </c>
       <c r="Q12" t="s">
-        <v>1739</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -20340,13 +20405,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="D13" t="s">
         <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F13">
         <v>857</v>
@@ -20355,10 +20420,10 @@
         <v>1.31</v>
       </c>
       <c r="H13" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I13" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="J13">
         <v>29.99</v>
@@ -20367,13 +20432,13 @@
         <v>465</v>
       </c>
       <c r="L13" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="O13">
         <v>39.37</v>
@@ -20382,7 +20447,7 @@
         <v>871</v>
       </c>
       <c r="Q13" t="s">
-        <v>1740</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -20390,13 +20455,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="D14" t="s">
         <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F14">
         <v>1215</v>
@@ -20405,10 +20470,10 @@
         <v>0.75</v>
       </c>
       <c r="H14" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
       <c r="I14" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="J14">
         <v>29.99</v>
@@ -20417,13 +20482,13 @@
         <v>465</v>
       </c>
       <c r="L14" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1693</v>
+        <v>1698</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="O14">
         <v>22.5</v>
@@ -20432,7 +20497,7 @@
         <v>871</v>
       </c>
       <c r="Q14" t="s">
-        <v>1741</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -20440,13 +20505,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="D15" t="s">
         <v>191</v>
       </c>
       <c r="E15" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F15">
         <v>755</v>
@@ -20467,13 +20532,13 @@
         <v>465</v>
       </c>
       <c r="L15" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>1694</v>
+        <v>1699</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="O15">
         <v>36.5</v>
@@ -20482,7 +20547,7 @@
         <v>871</v>
       </c>
       <c r="Q15" t="s">
-        <v>1742</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -20490,13 +20555,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="D16" t="s">
         <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="F16">
         <v>888</v>
@@ -20505,10 +20570,10 @@
         <v>3.33</v>
       </c>
       <c r="H16" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="I16" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="J16">
         <v>79.98999999999999</v>
@@ -20517,13 +20582,13 @@
         <v>465</v>
       </c>
       <c r="L16" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="O16">
         <v>266.38</v>
@@ -20532,7 +20597,7 @@
         <v>871</v>
       </c>
       <c r="Q16" t="s">
-        <v>1743</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -20540,13 +20605,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
       <c r="D17" t="s">
         <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F17">
         <v>1103</v>
@@ -20555,10 +20620,10 @@
         <v>0.42</v>
       </c>
       <c r="H17" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="I17" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="J17">
         <v>44.99</v>
@@ -20567,13 +20632,13 @@
         <v>465</v>
       </c>
       <c r="L17" t="s">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1696</v>
+        <v>1701</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="O17">
         <v>18.76</v>
@@ -20582,7 +20647,7 @@
         <v>871</v>
       </c>
       <c r="Q17" t="s">
-        <v>1744</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -20590,13 +20655,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="D18" t="s">
         <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F18">
         <v>520</v>
@@ -20605,10 +20670,10 @@
         <v>0.85</v>
       </c>
       <c r="H18" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I18" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="J18">
         <v>39.99</v>
@@ -20617,13 +20682,13 @@
         <v>465</v>
       </c>
       <c r="L18" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>1721</v>
+        <v>1726</v>
       </c>
       <c r="O18">
         <v>33.99</v>
@@ -20632,7 +20697,7 @@
         <v>871</v>
       </c>
       <c r="Q18" t="s">
-        <v>1745</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -20640,7 +20705,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
       <c r="C19" t="s">
         <v>178</v>
@@ -20661,13 +20726,13 @@
         <v>465</v>
       </c>
       <c r="L19" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="O19">
         <v>180</v>
@@ -20676,7 +20741,7 @@
         <v>871</v>
       </c>
       <c r="Q19" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -20684,7 +20749,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="C20" t="s">
         <v>178</v>
@@ -20693,7 +20758,7 @@
         <v>192</v>
       </c>
       <c r="E20" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F20">
         <v>609</v>
@@ -20702,10 +20767,10 @@
         <v>1.12</v>
       </c>
       <c r="H20" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="I20" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="J20">
         <v>33</v>
@@ -20714,13 +20779,13 @@
         <v>465</v>
       </c>
       <c r="L20" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>1699</v>
+        <v>1704</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="O20">
         <v>37.07</v>
@@ -20729,7 +20794,7 @@
         <v>871</v>
       </c>
       <c r="Q20" t="s">
-        <v>1747</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -20737,13 +20802,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="D21" t="s">
         <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F21">
         <v>799</v>
@@ -20752,10 +20817,10 @@
         <v>0.89</v>
       </c>
       <c r="H21" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="I21" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -20764,13 +20829,13 @@
         <v>465</v>
       </c>
       <c r="L21" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="O21">
         <v>26.75</v>
@@ -20779,7 +20844,7 @@
         <v>871</v>
       </c>
       <c r="Q21" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -20787,13 +20852,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="D22" t="s">
         <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -20802,10 +20867,10 @@
         <v>1.38</v>
       </c>
       <c r="H22" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="I22" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="J22">
         <v>91.98999999999999</v>
@@ -20814,13 +20879,13 @@
         <v>465</v>
       </c>
       <c r="L22" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="O22">
         <v>126.79</v>
@@ -20829,7 +20894,7 @@
         <v>871</v>
       </c>
       <c r="Q22" t="s">
-        <v>1749</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -20837,13 +20902,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="D23" t="s">
         <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -20852,10 +20917,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="I23" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="J23">
         <v>124.99</v>
@@ -20864,13 +20929,13 @@
         <v>465</v>
       </c>
       <c r="L23" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -20879,7 +20944,7 @@
         <v>871</v>
       </c>
       <c r="Q23" t="s">
-        <v>1750</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -20887,13 +20952,13 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="D24" t="s">
         <v>194</v>
       </c>
       <c r="E24" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -20902,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="J24">
         <v>42.99</v>
@@ -20911,13 +20976,13 @@
         <v>465</v>
       </c>
       <c r="L24" t="s">
-        <v>1679</v>
+        <v>1684</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -20926,7 +20991,7 @@
         <v>871</v>
       </c>
       <c r="Q24" t="s">
-        <v>1751</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -20934,7 +20999,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="C25" t="s">
         <v>178</v>
@@ -20943,7 +21008,7 @@
         <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -20958,13 +21023,13 @@
         <v>465</v>
       </c>
       <c r="L25" t="s">
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1704</v>
+        <v>1709</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1728</v>
+        <v>1733</v>
       </c>
       <c r="O25">
         <v>499.99</v>
@@ -20973,7 +21038,7 @@
         <v>871</v>
       </c>
       <c r="Q25" t="s">
-        <v>1752</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -20981,7 +21046,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="C26" t="s">
         <v>1029</v>
@@ -20990,7 +21055,7 @@
         <v>194</v>
       </c>
       <c r="E26" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -20999,10 +21064,10 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="I26" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="J26">
         <v>26.99</v>
@@ -21011,13 +21076,13 @@
         <v>465</v>
       </c>
       <c r="L26" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>1729</v>
+        <v>1734</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -21026,7 +21091,7 @@
         <v>871</v>
       </c>
       <c r="Q26" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
     </row>
   </sheetData>
@@ -21108,7 +21173,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21185,7 +21250,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="C3" t="s">
         <v>183</v>
@@ -21194,7 +21259,7 @@
         <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -21203,7 +21268,7 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="J3">
         <v>34.99</v>
@@ -21212,13 +21277,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>1761</v>
+        <v>1766</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="O3">
         <v>36.09</v>
@@ -21227,7 +21292,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21235,7 +21300,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="C4" t="s">
         <v>183</v>
@@ -21244,7 +21309,7 @@
         <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -21253,7 +21318,7 @@
         <v>0.64</v>
       </c>
       <c r="I4" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="J4">
         <v>34.99</v>
@@ -21262,13 +21327,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="O4">
         <v>22.55</v>
@@ -21277,7 +21342,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -21285,7 +21350,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="C5" t="s">
         <v>183</v>
@@ -21294,7 +21359,7 @@
         <v>193</v>
       </c>
       <c r="E5" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -21303,7 +21368,7 @@
         <v>1.36</v>
       </c>
       <c r="I5" t="s">
-        <v>1760</v>
+        <v>1765</v>
       </c>
       <c r="J5">
         <v>34.99</v>
@@ -21312,13 +21377,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="O5">
         <v>47.57</v>
@@ -21327,7 +21392,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>1772</v>
+        <v>1777</v>
       </c>
     </row>
   </sheetData>
@@ -21366,7 +21431,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21443,7 +21508,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="C3" t="s">
         <v>177</v>
@@ -21461,10 +21526,10 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="I3" t="s">
-        <v>1838</v>
+        <v>1843</v>
       </c>
       <c r="J3">
         <v>24.99</v>
@@ -21473,13 +21538,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1908</v>
+        <v>1913</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>1944</v>
+        <v>1949</v>
       </c>
       <c r="O3">
         <v>30.44</v>
@@ -21488,7 +21553,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21496,7 +21561,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>1775</v>
+        <v>1780</v>
       </c>
       <c r="C4" t="s">
         <v>177</v>
@@ -21505,7 +21570,7 @@
         <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -21514,10 +21579,10 @@
         <v>0.52</v>
       </c>
       <c r="H4" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="I4" t="s">
-        <v>1839</v>
+        <v>1844</v>
       </c>
       <c r="J4">
         <v>24.97</v>
@@ -21526,13 +21591,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>1873</v>
+        <v>1878</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1909</v>
+        <v>1914</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1945</v>
+        <v>1950</v>
       </c>
       <c r="O4">
         <v>12.96</v>
@@ -21541,7 +21606,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>1981</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -21549,7 +21614,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="C5" t="s">
         <v>183</v>
@@ -21570,13 +21635,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>1874</v>
+        <v>1879</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>1910</v>
+        <v>1915</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="O5">
         <v>48.73</v>
@@ -21585,7 +21650,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>1982</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -21593,7 +21658,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>1777</v>
+        <v>1782</v>
       </c>
       <c r="C6" t="s">
         <v>183</v>
@@ -21611,10 +21676,10 @@
         <v>0.92</v>
       </c>
       <c r="H6" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="I6" t="s">
-        <v>1840</v>
+        <v>1845</v>
       </c>
       <c r="J6">
         <v>24.99</v>
@@ -21623,13 +21688,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>1911</v>
+        <v>1916</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -21638,7 +21703,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>1983</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -21646,7 +21711,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="C7" t="s">
         <v>177</v>
@@ -21655,7 +21720,7 @@
         <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -21664,10 +21729,10 @@
         <v>0.82</v>
       </c>
       <c r="H7" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="I7" t="s">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="J7">
         <v>24.97</v>
@@ -21676,13 +21741,13 @@
         <v>465</v>
       </c>
       <c r="L7" t="s">
-        <v>1876</v>
+        <v>1881</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1912</v>
+        <v>1917</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="O7">
         <v>20.41</v>
@@ -21691,7 +21756,7 @@
         <v>871</v>
       </c>
       <c r="Q7" t="s">
-        <v>1984</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -21699,7 +21764,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>1779</v>
+        <v>1784</v>
       </c>
       <c r="C8" t="s">
         <v>177</v>
@@ -21723,13 +21788,13 @@
         <v>465</v>
       </c>
       <c r="L8" t="s">
-        <v>1877</v>
+        <v>1882</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1913</v>
+        <v>1918</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="O8">
         <v>37.99</v>
@@ -21738,7 +21803,7 @@
         <v>871</v>
       </c>
       <c r="Q8" t="s">
-        <v>1985</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -21746,7 +21811,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>1780</v>
+        <v>1785</v>
       </c>
       <c r="C9" t="s">
         <v>183</v>
@@ -21764,10 +21829,10 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="I9" t="s">
-        <v>1842</v>
+        <v>1847</v>
       </c>
       <c r="J9">
         <v>24.99</v>
@@ -21776,13 +21841,13 @@
         <v>465</v>
       </c>
       <c r="L9" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1914</v>
+        <v>1919</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="O9">
         <v>37.71</v>
@@ -21791,7 +21856,7 @@
         <v>871</v>
       </c>
       <c r="Q9" t="s">
-        <v>1986</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -21799,7 +21864,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="C10" t="s">
         <v>183</v>
@@ -21817,10 +21882,10 @@
         <v>0.78</v>
       </c>
       <c r="H10" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="I10" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -21829,13 +21894,13 @@
         <v>465</v>
       </c>
       <c r="L10" t="s">
-        <v>1879</v>
+        <v>1884</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1915</v>
+        <v>1920</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="O10">
         <v>19.54</v>
@@ -21844,7 +21909,7 @@
         <v>871</v>
       </c>
       <c r="Q10" t="s">
-        <v>1987</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -21852,7 +21917,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>1782</v>
+        <v>1787</v>
       </c>
       <c r="C11" t="s">
         <v>155</v>
@@ -21870,10 +21935,10 @@
         <v>0.82</v>
       </c>
       <c r="H11" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="I11" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -21882,13 +21947,13 @@
         <v>465</v>
       </c>
       <c r="L11" t="s">
-        <v>1880</v>
+        <v>1885</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1916</v>
+        <v>1921</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="O11">
         <v>16.43</v>
@@ -21897,7 +21962,7 @@
         <v>871</v>
       </c>
       <c r="Q11" t="s">
-        <v>1988</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -21905,7 +21970,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1783</v>
+        <v>1788</v>
       </c>
       <c r="C12" t="s">
         <v>155</v>
@@ -21923,10 +21988,10 @@
         <v>1.61</v>
       </c>
       <c r="H12" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="I12" t="s">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -21935,13 +22000,13 @@
         <v>465</v>
       </c>
       <c r="L12" t="s">
-        <v>1881</v>
+        <v>1886</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1917</v>
+        <v>1922</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="O12">
         <v>32.14</v>
@@ -21950,7 +22015,7 @@
         <v>871</v>
       </c>
       <c r="Q12" t="s">
-        <v>1989</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -21958,7 +22023,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>1784</v>
+        <v>1789</v>
       </c>
       <c r="C13" t="s">
         <v>155</v>
@@ -21976,10 +22041,10 @@
         <v>0.71</v>
       </c>
       <c r="H13" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="I13" t="s">
-        <v>1846</v>
+        <v>1851</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -21988,13 +22053,13 @@
         <v>465</v>
       </c>
       <c r="L13" t="s">
-        <v>1882</v>
+        <v>1887</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1918</v>
+        <v>1923</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="O13">
         <v>14.27</v>
@@ -22003,7 +22068,7 @@
         <v>871</v>
       </c>
       <c r="Q13" t="s">
-        <v>1990</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -22011,7 +22076,7 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="C14" t="s">
         <v>155</v>
@@ -22029,10 +22094,10 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="I14" t="s">
-        <v>1847</v>
+        <v>1852</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -22041,13 +22106,13 @@
         <v>465</v>
       </c>
       <c r="L14" t="s">
-        <v>1883</v>
+        <v>1888</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1919</v>
+        <v>1924</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="O14">
         <v>23.5</v>
@@ -22056,7 +22121,7 @@
         <v>871</v>
       </c>
       <c r="Q14" t="s">
-        <v>1991</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -22082,10 +22147,10 @@
         <v>0.65</v>
       </c>
       <c r="H15" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="I15" t="s">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -22094,13 +22159,13 @@
         <v>465</v>
       </c>
       <c r="L15" t="s">
-        <v>1884</v>
+        <v>1889</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>1920</v>
+        <v>1925</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="O15">
         <v>12.92</v>
@@ -22109,7 +22174,7 @@
         <v>871</v>
       </c>
       <c r="Q15" t="s">
-        <v>1992</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -22117,7 +22182,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
       <c r="C16" t="s">
         <v>156</v>
@@ -22135,10 +22200,10 @@
         <v>0.78</v>
       </c>
       <c r="H16" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="I16" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -22147,13 +22212,13 @@
         <v>465</v>
       </c>
       <c r="L16" t="s">
-        <v>1885</v>
+        <v>1890</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>1921</v>
+        <v>1926</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="O16">
         <v>15.59</v>
@@ -22162,7 +22227,7 @@
         <v>871</v>
       </c>
       <c r="Q16" t="s">
-        <v>1993</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -22170,7 +22235,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="C17" t="s">
         <v>156</v>
@@ -22188,10 +22253,10 @@
         <v>2.22</v>
       </c>
       <c r="H17" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="I17" t="s">
-        <v>1850</v>
+        <v>1855</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -22200,13 +22265,13 @@
         <v>465</v>
       </c>
       <c r="L17" t="s">
-        <v>1886</v>
+        <v>1891</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1922</v>
+        <v>1927</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="O17">
         <v>44.34</v>
@@ -22215,7 +22280,7 @@
         <v>871</v>
       </c>
       <c r="Q17" t="s">
-        <v>1994</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -22223,7 +22288,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="C18" t="s">
         <v>156</v>
@@ -22241,10 +22306,10 @@
         <v>2.09</v>
       </c>
       <c r="H18" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="I18" t="s">
-        <v>1851</v>
+        <v>1856</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -22253,13 +22318,13 @@
         <v>465</v>
       </c>
       <c r="L18" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>1923</v>
+        <v>1928</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>1959</v>
+        <v>1964</v>
       </c>
       <c r="O18">
         <v>41.71</v>
@@ -22268,7 +22333,7 @@
         <v>871</v>
       </c>
       <c r="Q18" t="s">
-        <v>1995</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -22276,7 +22341,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="C19" t="s">
         <v>157</v>
@@ -22294,10 +22359,10 @@
         <v>0.72</v>
       </c>
       <c r="H19" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="I19" t="s">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -22306,13 +22371,13 @@
         <v>465</v>
       </c>
       <c r="L19" t="s">
-        <v>1888</v>
+        <v>1893</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>1924</v>
+        <v>1929</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="O19">
         <v>14.3</v>
@@ -22321,7 +22386,7 @@
         <v>871</v>
       </c>
       <c r="Q19" t="s">
-        <v>1996</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -22329,7 +22394,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="C20" t="s">
         <v>157</v>
@@ -22347,10 +22412,10 @@
         <v>0.8</v>
       </c>
       <c r="H20" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="I20" t="s">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -22359,13 +22424,13 @@
         <v>465</v>
       </c>
       <c r="L20" t="s">
-        <v>1889</v>
+        <v>1894</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>1925</v>
+        <v>1930</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="O20">
         <v>15.98</v>
@@ -22374,7 +22439,7 @@
         <v>871</v>
       </c>
       <c r="Q20" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -22400,10 +22465,10 @@
         <v>0.9</v>
       </c>
       <c r="H21" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
       <c r="I21" t="s">
-        <v>1854</v>
+        <v>1859</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -22412,13 +22477,13 @@
         <v>465</v>
       </c>
       <c r="L21" t="s">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1926</v>
+        <v>1931</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="O21">
         <v>17.92</v>
@@ -22427,7 +22492,7 @@
         <v>871</v>
       </c>
       <c r="Q21" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -22453,10 +22518,10 @@
         <v>0.5</v>
       </c>
       <c r="H22" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="I22" t="s">
-        <v>1855</v>
+        <v>1860</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -22465,13 +22530,13 @@
         <v>465</v>
       </c>
       <c r="L22" t="s">
-        <v>1891</v>
+        <v>1896</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="O22">
         <v>10.03</v>
@@ -22480,7 +22545,7 @@
         <v>871</v>
       </c>
       <c r="Q22" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -22488,7 +22553,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="C23" t="s">
         <v>158</v>
@@ -22506,10 +22571,10 @@
         <v>0.89</v>
       </c>
       <c r="H23" t="s">
-        <v>1823</v>
+        <v>1828</v>
       </c>
       <c r="I23" t="s">
-        <v>1856</v>
+        <v>1861</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -22518,13 +22583,13 @@
         <v>465</v>
       </c>
       <c r="L23" t="s">
-        <v>1892</v>
+        <v>1897</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1928</v>
+        <v>1933</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="O23">
         <v>17.83</v>
@@ -22533,7 +22598,7 @@
         <v>871</v>
       </c>
       <c r="Q23" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -22541,7 +22606,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>1792</v>
+        <v>1797</v>
       </c>
       <c r="C24" t="s">
         <v>158</v>
@@ -22559,10 +22624,10 @@
         <v>0.72</v>
       </c>
       <c r="H24" t="s">
-        <v>1824</v>
+        <v>1829</v>
       </c>
       <c r="I24" t="s">
-        <v>1857</v>
+        <v>1862</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -22571,13 +22636,13 @@
         <v>465</v>
       </c>
       <c r="L24" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>1929</v>
+        <v>1934</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="O24">
         <v>14.35</v>
@@ -22586,7 +22651,7 @@
         <v>871</v>
       </c>
       <c r="Q24" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -22612,10 +22677,10 @@
         <v>0.73</v>
       </c>
       <c r="H25" t="s">
-        <v>1825</v>
+        <v>1830</v>
       </c>
       <c r="I25" t="s">
-        <v>1858</v>
+        <v>1863</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -22624,13 +22689,13 @@
         <v>465</v>
       </c>
       <c r="L25" t="s">
-        <v>1894</v>
+        <v>1899</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>1930</v>
+        <v>1935</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="O25">
         <v>14.69</v>
@@ -22639,7 +22704,7 @@
         <v>871</v>
       </c>
       <c r="Q25" t="s">
-        <v>2002</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -22665,7 +22730,7 @@
         <v>7.29</v>
       </c>
       <c r="I26" t="s">
-        <v>1859</v>
+        <v>1864</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -22674,13 +22739,13 @@
         <v>465</v>
       </c>
       <c r="L26" t="s">
-        <v>1895</v>
+        <v>1900</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>1931</v>
+        <v>1936</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="O26">
         <v>145.79</v>
@@ -22689,7 +22754,7 @@
         <v>871</v>
       </c>
       <c r="Q26" t="s">
-        <v>2003</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -22697,7 +22762,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="C27" t="s">
         <v>158</v>
@@ -22715,10 +22780,10 @@
         <v>0.88</v>
       </c>
       <c r="H27" t="s">
-        <v>1826</v>
+        <v>1831</v>
       </c>
       <c r="I27" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -22727,13 +22792,13 @@
         <v>465</v>
       </c>
       <c r="L27" t="s">
-        <v>1896</v>
+        <v>1901</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>1932</v>
+        <v>1937</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>1968</v>
+        <v>1973</v>
       </c>
       <c r="O27">
         <v>17.58</v>
@@ -22742,7 +22807,7 @@
         <v>871</v>
       </c>
       <c r="Q27" t="s">
-        <v>2004</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -22750,7 +22815,7 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="C28" t="s">
         <v>158</v>
@@ -22768,10 +22833,10 @@
         <v>0.82</v>
       </c>
       <c r="H28" t="s">
-        <v>1827</v>
+        <v>1832</v>
       </c>
       <c r="I28" t="s">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -22780,13 +22845,13 @@
         <v>465</v>
       </c>
       <c r="L28" t="s">
-        <v>1897</v>
+        <v>1902</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>1933</v>
+        <v>1938</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="O28">
         <v>16.46</v>
@@ -22795,7 +22860,7 @@
         <v>871</v>
       </c>
       <c r="Q28" t="s">
-        <v>2005</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -22803,7 +22868,7 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="C29" t="s">
         <v>159</v>
@@ -22812,7 +22877,7 @@
         <v>192</v>
       </c>
       <c r="E29" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -22821,10 +22886,10 @@
         <v>0.96</v>
       </c>
       <c r="H29" t="s">
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="I29" t="s">
-        <v>1862</v>
+        <v>1867</v>
       </c>
       <c r="J29">
         <v>20.99</v>
@@ -22833,13 +22898,13 @@
         <v>465</v>
       </c>
       <c r="L29" t="s">
-        <v>1898</v>
+        <v>1903</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>1934</v>
+        <v>1939</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="O29">
         <v>20.09</v>
@@ -22848,7 +22913,7 @@
         <v>871</v>
       </c>
       <c r="Q29" t="s">
-        <v>2006</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -22856,7 +22921,7 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="C30" t="s">
         <v>159</v>
@@ -22865,7 +22930,7 @@
         <v>192</v>
       </c>
       <c r="E30" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -22874,10 +22939,10 @@
         <v>0.83</v>
       </c>
       <c r="H30" t="s">
-        <v>1829</v>
+        <v>1834</v>
       </c>
       <c r="I30" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="J30">
         <v>20.99</v>
@@ -22886,13 +22951,13 @@
         <v>465</v>
       </c>
       <c r="L30" t="s">
-        <v>1899</v>
+        <v>1904</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="O30">
         <v>17.33</v>
@@ -22901,7 +22966,7 @@
         <v>871</v>
       </c>
       <c r="Q30" t="s">
-        <v>2007</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -22909,7 +22974,7 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="C31" t="s">
         <v>159</v>
@@ -22918,7 +22983,7 @@
         <v>192</v>
       </c>
       <c r="E31" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -22927,10 +22992,10 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="s">
-        <v>1830</v>
+        <v>1835</v>
       </c>
       <c r="I31" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
       <c r="J31">
         <v>20.99</v>
@@ -22939,13 +23004,13 @@
         <v>465</v>
       </c>
       <c r="L31" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>1936</v>
+        <v>1941</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="O31">
         <v>15.75</v>
@@ -22954,7 +23019,7 @@
         <v>871</v>
       </c>
       <c r="Q31" t="s">
-        <v>2008</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -22971,7 +23036,7 @@
         <v>192</v>
       </c>
       <c r="E32" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -22980,10 +23045,10 @@
         <v>0.84</v>
       </c>
       <c r="H32" t="s">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="I32" t="s">
-        <v>1865</v>
+        <v>1870</v>
       </c>
       <c r="J32">
         <v>20.99</v>
@@ -22992,13 +23057,13 @@
         <v>465</v>
       </c>
       <c r="L32" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>1937</v>
+        <v>1942</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="O32">
         <v>17.65</v>
@@ -23007,7 +23072,7 @@
         <v>871</v>
       </c>
       <c r="Q32" t="s">
-        <v>2009</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -23015,7 +23080,7 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="C33" t="s">
         <v>160</v>
@@ -23033,10 +23098,10 @@
         <v>0.76</v>
       </c>
       <c r="H33" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="I33" t="s">
-        <v>1866</v>
+        <v>1871</v>
       </c>
       <c r="J33">
         <v>23.99</v>
@@ -23045,13 +23110,13 @@
         <v>465</v>
       </c>
       <c r="L33" t="s">
-        <v>1902</v>
+        <v>1907</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="O33">
         <v>18.33</v>
@@ -23060,7 +23125,7 @@
         <v>871</v>
       </c>
       <c r="Q33" t="s">
-        <v>2010</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -23068,7 +23133,7 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="C34" t="s">
         <v>160</v>
@@ -23086,10 +23151,10 @@
         <v>0.86</v>
       </c>
       <c r="H34" t="s">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="I34" t="s">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="J34">
         <v>23.99</v>
@@ -23098,13 +23163,13 @@
         <v>465</v>
       </c>
       <c r="L34" t="s">
-        <v>1903</v>
+        <v>1908</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>1939</v>
+        <v>1944</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="O34">
         <v>20.58</v>
@@ -23113,7 +23178,7 @@
         <v>871</v>
       </c>
       <c r="Q34" t="s">
-        <v>2011</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -23121,7 +23186,7 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="C35" t="s">
         <v>160</v>
@@ -23139,10 +23204,10 @@
         <v>0.64</v>
       </c>
       <c r="H35" t="s">
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="I35" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="J35">
         <v>23.99</v>
@@ -23151,13 +23216,13 @@
         <v>465</v>
       </c>
       <c r="L35" t="s">
-        <v>1904</v>
+        <v>1909</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>1940</v>
+        <v>1945</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="O35">
         <v>15.31</v>
@@ -23166,7 +23231,7 @@
         <v>871</v>
       </c>
       <c r="Q35" t="s">
-        <v>2012</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -23192,10 +23257,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H36" t="s">
-        <v>1835</v>
+        <v>1840</v>
       </c>
       <c r="I36" t="s">
-        <v>1869</v>
+        <v>1874</v>
       </c>
       <c r="J36">
         <v>23.99</v>
@@ -23204,13 +23269,13 @@
         <v>465</v>
       </c>
       <c r="L36" t="s">
-        <v>1905</v>
+        <v>1910</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>1941</v>
+        <v>1946</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="O36">
         <v>19.5</v>
@@ -23219,7 +23284,7 @@
         <v>871</v>
       </c>
       <c r="Q36" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -23227,16 +23292,16 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="C37" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="D37" t="s">
         <v>193</v>
       </c>
       <c r="E37" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -23245,10 +23310,10 @@
         <v>0.99</v>
       </c>
       <c r="H37" t="s">
-        <v>1836</v>
+        <v>1841</v>
       </c>
       <c r="I37" t="s">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="J37">
         <v>45</v>
@@ -23257,13 +23322,13 @@
         <v>465</v>
       </c>
       <c r="L37" t="s">
-        <v>1906</v>
+        <v>1911</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>1942</v>
+        <v>1947</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="O37">
         <v>44.69</v>
@@ -23272,7 +23337,7 @@
         <v>871</v>
       </c>
       <c r="Q37" t="s">
-        <v>2014</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -23280,7 +23345,7 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="C38" t="s">
         <v>177</v>
@@ -23289,7 +23354,7 @@
         <v>193</v>
       </c>
       <c r="E38" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -23298,10 +23363,10 @@
         <v>0.78</v>
       </c>
       <c r="H38" t="s">
-        <v>1837</v>
+        <v>1842</v>
       </c>
       <c r="I38" t="s">
-        <v>1871</v>
+        <v>1876</v>
       </c>
       <c r="J38">
         <v>24.97</v>
@@ -23310,13 +23375,13 @@
         <v>465</v>
       </c>
       <c r="L38" t="s">
-        <v>1907</v>
+        <v>1912</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>1943</v>
+        <v>1948</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="O38">
         <v>19.45</v>
@@ -23325,7 +23390,7 @@
         <v>871</v>
       </c>
       <c r="Q38" t="s">
-        <v>2015</v>
+        <v>2020</v>
       </c>
     </row>
   </sheetData>
@@ -23430,7 +23495,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23507,7 +23572,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C3" t="s">
         <v>155</v>
@@ -23525,10 +23590,10 @@
         <v>1.16</v>
       </c>
       <c r="H3" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="I3" t="s">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -23537,13 +23602,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>2065</v>
+        <v>2070</v>
       </c>
       <c r="O3">
         <v>23.26</v>
@@ -23552,7 +23617,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23560,7 +23625,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="s">
         <v>155</v>
@@ -23578,10 +23643,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" t="s">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="I4" t="s">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -23590,13 +23655,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>2066</v>
+        <v>2071</v>
       </c>
       <c r="O4">
         <v>16.41</v>
@@ -23605,7 +23670,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>2077</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -23613,7 +23678,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="s">
         <v>155</v>
@@ -23631,10 +23696,10 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="I5" t="s">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -23643,13 +23708,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="O5">
         <v>23.79</v>
@@ -23658,7 +23723,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -23666,7 +23731,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C6" t="s">
         <v>155</v>
@@ -23675,7 +23740,7 @@
         <v>193</v>
       </c>
       <c r="E6" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -23684,10 +23749,10 @@
         <v>0.8</v>
       </c>
       <c r="H6" t="s">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="I6" t="s">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -23696,13 +23761,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>2057</v>
+        <v>2062</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>2068</v>
+        <v>2073</v>
       </c>
       <c r="O6">
         <v>23.94</v>
@@ -23711,7 +23776,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -23737,7 +23802,7 @@
         <v>1.15</v>
       </c>
       <c r="H7" t="s">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -23746,13 +23811,13 @@
         <v>465</v>
       </c>
       <c r="L7" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>2058</v>
+        <v>2063</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="O7">
         <v>22.99</v>
@@ -23761,7 +23826,7 @@
         <v>871</v>
       </c>
       <c r="Q7" t="s">
-        <v>2080</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -23769,7 +23834,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="s">
         <v>156</v>
@@ -23787,7 +23852,7 @@
         <v>1.52</v>
       </c>
       <c r="H8" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -23796,13 +23861,13 @@
         <v>465</v>
       </c>
       <c r="L8" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>2070</v>
+        <v>2075</v>
       </c>
       <c r="O8">
         <v>30.47</v>
@@ -23811,7 +23876,7 @@
         <v>871</v>
       </c>
       <c r="Q8" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -23819,7 +23884,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="C9" t="s">
         <v>156</v>
@@ -23837,7 +23902,7 @@
         <v>1.02</v>
       </c>
       <c r="H9" t="s">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -23846,13 +23911,13 @@
         <v>465</v>
       </c>
       <c r="L9" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>2060</v>
+        <v>2065</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
       <c r="O9">
         <v>20.39</v>
@@ -23861,7 +23926,7 @@
         <v>871</v>
       </c>
       <c r="Q9" t="s">
-        <v>2082</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -23869,7 +23934,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="C10" t="s">
         <v>157</v>
@@ -23887,7 +23952,7 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="s">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="J10">
         <v>24.99</v>
@@ -23896,13 +23961,13 @@
         <v>465</v>
       </c>
       <c r="L10" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>2061</v>
+        <v>2066</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>2072</v>
+        <v>2077</v>
       </c>
       <c r="O10">
         <v>29.95</v>
@@ -23911,7 +23976,7 @@
         <v>871</v>
       </c>
       <c r="Q10" t="s">
-        <v>2083</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -23919,7 +23984,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="C11" t="s">
         <v>157</v>
@@ -23937,10 +24002,10 @@
         <v>1.29</v>
       </c>
       <c r="H11" t="s">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="I11" t="s">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="J11">
         <v>24.99</v>
@@ -23949,13 +24014,13 @@
         <v>465</v>
       </c>
       <c r="L11" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>2062</v>
+        <v>2067</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="O11">
         <v>32.18</v>
@@ -23964,7 +24029,7 @@
         <v>871</v>
       </c>
       <c r="Q11" t="s">
-        <v>2084</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -23972,7 +24037,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="C12" t="s">
         <v>157</v>
@@ -23990,10 +24055,10 @@
         <v>1.2</v>
       </c>
       <c r="H12" t="s">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="I12" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="J12">
         <v>24.99</v>
@@ -24002,13 +24067,13 @@
         <v>465</v>
       </c>
       <c r="L12" t="s">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>2063</v>
+        <v>2068</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="O12">
         <v>29.95</v>
@@ -24017,7 +24082,7 @@
         <v>871</v>
       </c>
       <c r="Q12" t="s">
-        <v>2085</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -24025,7 +24090,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="C13" t="s">
         <v>157</v>
@@ -24043,7 +24108,7 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="J13">
         <v>24.99</v>
@@ -24052,13 +24117,13 @@
         <v>465</v>
       </c>
       <c r="L13" t="s">
-        <v>2053</v>
+        <v>2058</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>2064</v>
+        <v>2069</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="O13">
         <v>29.95</v>
@@ -24067,7 +24132,7 @@
         <v>871</v>
       </c>
       <c r="Q13" t="s">
-        <v>2085</v>
+        <v>2090</v>
       </c>
     </row>
   </sheetData>
@@ -24124,7 +24189,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -24201,7 +24266,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>2087</v>
+        <v>2092</v>
       </c>
       <c r="C3" t="s">
         <v>183</v>
@@ -24210,7 +24275,7 @@
         <v>193</v>
       </c>
       <c r="E3" t="s">
-        <v>2091</v>
+        <v>2096</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -24219,10 +24284,10 @@
         <v>0.65</v>
       </c>
       <c r="H3" t="s">
-        <v>2092</v>
+        <v>2097</v>
       </c>
       <c r="I3" t="s">
-        <v>2096</v>
+        <v>2101</v>
       </c>
       <c r="J3">
         <v>32.99</v>
@@ -24231,13 +24296,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>2100</v>
+        <v>2105</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>2108</v>
+        <v>2113</v>
       </c>
       <c r="O3">
         <v>21.34</v>
@@ -24246,7 +24311,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -24254,7 +24319,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>2088</v>
+        <v>2093</v>
       </c>
       <c r="C4" t="s">
         <v>183</v>
@@ -24263,7 +24328,7 @@
         <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>2091</v>
+        <v>2096</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -24272,10 +24337,10 @@
         <v>0.68</v>
       </c>
       <c r="H4" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="I4" t="s">
-        <v>2097</v>
+        <v>2102</v>
       </c>
       <c r="J4">
         <v>32.99</v>
@@ -24284,13 +24349,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>2109</v>
+        <v>2114</v>
       </c>
       <c r="O4">
         <v>22.3</v>
@@ -24299,7 +24364,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -24307,7 +24372,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="C5" t="s">
         <v>183</v>
@@ -24316,7 +24381,7 @@
         <v>193</v>
       </c>
       <c r="E5" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -24325,10 +24390,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="s">
-        <v>2094</v>
+        <v>2099</v>
       </c>
       <c r="I5" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="J5">
         <v>29.99</v>
@@ -24337,13 +24402,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>2106</v>
+        <v>2111</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2110</v>
+        <v>2115</v>
       </c>
       <c r="O5">
         <v>46.29</v>
@@ -24352,7 +24417,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -24360,7 +24425,7 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="C6" t="s">
         <v>183</v>
@@ -24369,7 +24434,7 @@
         <v>194</v>
       </c>
       <c r="E6" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -24378,10 +24443,10 @@
         <v>1.37</v>
       </c>
       <c r="H6" t="s">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="I6" t="s">
-        <v>2099</v>
+        <v>2104</v>
       </c>
       <c r="J6">
         <v>29.99</v>
@@ -24390,13 +24455,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>2107</v>
+        <v>2112</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>2111</v>
+        <v>2116</v>
       </c>
       <c r="O6">
         <v>41.15</v>
@@ -24405,7 +24470,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>2115</v>
+        <v>2120</v>
       </c>
     </row>
   </sheetData>
@@ -24446,7 +24511,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -24523,13 +24588,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="C3" t="s">
         <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E3" t="s">
         <v>197</v>
@@ -24541,10 +24606,10 @@
         <v>0.99</v>
       </c>
       <c r="H3" t="s">
-        <v>2148</v>
+        <v>2153</v>
       </c>
       <c r="I3" t="s">
-        <v>2167</v>
+        <v>2172</v>
       </c>
       <c r="J3">
         <v>19.99</v>
@@ -24553,13 +24618,13 @@
         <v>465</v>
       </c>
       <c r="L3" t="s">
-        <v>2198</v>
+        <v>2203</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>2260</v>
+        <v>2265</v>
       </c>
       <c r="O3">
         <v>19.84</v>
@@ -24568,7 +24633,7 @@
         <v>871</v>
       </c>
       <c r="Q3" t="s">
-        <v>2291</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -24576,13 +24641,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="C4" t="s">
         <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E4" t="s">
         <v>197</v>
@@ -24594,7 +24659,7 @@
         <v>1.42</v>
       </c>
       <c r="I4" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="J4">
         <v>19.99</v>
@@ -24603,13 +24668,13 @@
         <v>465</v>
       </c>
       <c r="L4" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>2230</v>
+        <v>2235</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>2261</v>
+        <v>2266</v>
       </c>
       <c r="O4">
         <v>28.43</v>
@@ -24618,7 +24683,7 @@
         <v>871</v>
       </c>
       <c r="Q4" t="s">
-        <v>2292</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -24626,13 +24691,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="C5" t="s">
         <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E5" t="s">
         <v>197</v>
@@ -24644,10 +24709,10 @@
         <v>1.22</v>
       </c>
       <c r="H5" t="s">
-        <v>2149</v>
+        <v>2154</v>
       </c>
       <c r="I5" t="s">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="J5">
         <v>19.99</v>
@@ -24656,13 +24721,13 @@
         <v>465</v>
       </c>
       <c r="L5" t="s">
-        <v>2200</v>
+        <v>2205</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2262</v>
+        <v>2267</v>
       </c>
       <c r="O5">
         <v>24.47</v>
@@ -24671,7 +24736,7 @@
         <v>871</v>
       </c>
       <c r="Q5" t="s">
-        <v>2293</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -24679,13 +24744,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="C6" t="s">
         <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E6" t="s">
         <v>197</v>
@@ -24697,10 +24762,10 @@
         <v>0.86</v>
       </c>
       <c r="H6" t="s">
-        <v>2150</v>
+        <v>2155</v>
       </c>
       <c r="I6" t="s">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="J6">
         <v>19.99</v>
@@ -24709,13 +24774,13 @@
         <v>465</v>
       </c>
       <c r="L6" t="s">
-        <v>2201</v>
+        <v>2206</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>2232</v>
+        <v>2237</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>2263</v>
+        <v>2268</v>
       </c>
       <c r="O6">
         <v>17.15</v>
@@ -24724,7 +24789,7 @@
         <v>871</v>
       </c>
       <c r="Q6" t="s">
-        <v>2294</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -24732,7 +24797,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>2121</v>
+        <v>2126</v>
       </c>
       <c r="C7" t="s">
         <v>156</v>
@@ -24750,7 +24815,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="s">
-        <v>2171</v>
+        <v>2176</v>
       </c>
       <c r="J7">
         <v>19.99</v>
@@ -24759,13 +24824,13 @@
         <v>465</v>
       </c>
       <c r="L7" t="s">
-        <v>2202</v>
+        <v>2207</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>2233</v>
+        <v>2238</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>2264</v>
+        <v>2269</v>
       </c>
       <c r="O7">
         <v>14.49</v>
@@ -24774,7 +24839,7 @@
         <v>871</v>
       </c>
       <c r="Q7" t="s">
-        <v>2295</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -24782,7 +24847,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>2122</v>
+        <v>2127</v>
       </c>
       <c r="C8" t="s">
         <v>156</v>
@@ -24800,10 +24865,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>2151</v>
+        <v>2156</v>
       </c>
       <c r="I8" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="J8">
         <v>19.99</v>
@@ -24812,13 +24877,13 @@
         <v>465</v>
       </c>
       <c r="L8" t="s">
-        <v>2203</v>
+        <v>2208</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="O8">
         <v>16.25</v>
@@ -24827,7 +24892,7 @@
         <v>871</v>
       </c>
       <c r="Q8" t="s">
-        <v>2296</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -24835,7 +24900,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="C9" t="s">
         <v>156</v>
@@ -24853,10 +24918,10 @@
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>2152</v>
+        <v>2157</v>
       </c>
       <c r="I9" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="J9">
         <v>19.99</v>
@@ -24865,13 +24930,13 @@
         <v>465</v>
       </c>
       <c r="L9" t="s">
-        <v>2204</v>
+        <v>2209</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>2266</v>
+        <v>2271</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -24880,7 +24945,7 @@
         <v>871</v>
       </c>
       <c r="Q9" t="s">
-        <v>2297</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -24888,7 +24953,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="C10" t="s">
         <v>156</v>
@@ -24906,10 +24971,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>2153</v>
+        <v>2158</v>
       </c>
       <c r="I10" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
       <c r="J10">
         <v>19.99</v>
@@ -24918,13 +24983,13 @@
         <v>465</v>
       </c>
       <c r="L10" t="s">
-        <v>2205</v>
+        <v>2210</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>2267</v>
+        <v>2272</v>
       </c>
       <c r="O10">
         <v>13.8</v>
@@ -24933,7 +24998,7 @@
         <v>871</v>
       </c>
       <c r="Q10" t="s">
-        <v>2298</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -24941,7 +25006,7 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="C11" t="s">
         <v>157</v>
@@ -24959,7 +25024,7 @@
         <v>0.82</v>
       </c>
       <c r="I11" t="s">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="J11">
         <v>19.99</v>
@@ -24968,13 +25033,13 @@
         <v>465</v>
       </c>
       <c r="L11" t="s">
-        <v>2206</v>
+        <v>2211</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>2268</v>
+        <v>2273</v>
       </c>
       <c r="O11">
         <v>16.49</v>
@@ -24983,7 +25048,7 @@
         <v>871</v>
       </c>
       <c r="Q11" t="s">
-        <v>2299</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -24991,7 +25056,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="C12" t="s">
         <v>157</v>
@@ -25009,7 +25074,7 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="s">
-        <v>2176</v>
+        <v>2181</v>
       </c>
       <c r="J12">
         <v>19.99</v>
@@ -25018,13 +25083,13 @@
         <v>465</v>
       </c>
       <c r="L12" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>2269</v>
+        <v>2274</v>
       </c>
       <c r="O12">
         <v>21.34</v>
@@ -25033,7 +25098,7 @@
         <v>871</v>
       </c>
       <c r="Q12" t="s">
-        <v>2300</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -25041,7 +25106,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>2127</v>
+        <v>2132</v>
       </c>
       <c r="C13" t="s">
         <v>157</v>
@@ -25059,10 +25124,10 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="s">
-        <v>2154</v>
+        <v>2159</v>
       </c>
       <c r="I13" t="s">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="J13">
         <v>19.99</v>
@@ -25071,13 +25136,13 @@
         <v>465</v>
       </c>
       <c r="L13" t="s">
-        <v>2208</v>
+        <v>2213</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>2239</v>
+        <v>2244</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>2270</v>
+        <v>2275</v>
       </c>
       <c r="O13">
         <v>35</v>
@@ -25086,7 +25151,7 @@
         <v>871</v>
       </c>
       <c r="Q13" t="s">
-        <v>2301</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -25094,7 +25159,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>2128</v>
+        <v>2133</v>
       </c>
       <c r="C14" t="s">
         <v>157</v>
@@ -25112,7 +25177,7 @@
         <v>2.38</v>
       </c>
       <c r="I14" t="s">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="J14">
         <v>19.99</v>
@@ -25121,13 +25186,13 @@
         <v>465</v>
       </c>
       <c r="L14" t="s">
-        <v>2209</v>
+        <v>2214</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>2240</v>
+        <v>2245</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>2271</v>
+        <v>2276</v>
       </c>
       <c r="O14">
         <v>47.66</v>
@@ -25136,7 +25201,7 @@
         <v>871</v>
       </c>
       <c r="Q14" t="s">
-        <v>2302</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -25144,7 +25209,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="C15" t="s">
         <v>158</v>
@@ -25162,10 +25227,10 @@
         <v>2.09</v>
       </c>
       <c r="H15" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="I15" t="s">
-        <v>2179</v>
+        <v>2184</v>
       </c>
       <c r="J15">
         <v>19.99</v>
@@ -25174,13 +25239,13 @@
         <v>465</v>
       </c>
       <c r="L15" t="s">
-        <v>2210</v>
+        <v>2215</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>2241</v>
+        <v>2246</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>2272</v>
+        <v>2277</v>
       </c>
       <c r="O15">
         <v>41.68</v>
@@ -25189,7 +25254,7 @@
         <v>871</v>
       </c>
       <c r="Q15" t="s">
-        <v>2303</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -25197,7 +25262,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="C16" t="s">
         <v>158</v>
@@ -25215,10 +25280,10 @@
         <v>1.82</v>
       </c>
       <c r="H16" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="I16" t="s">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="J16">
         <v>19.99</v>
@@ -25227,13 +25292,13 @@
         <v>465</v>
       </c>
       <c r="L16" t="s">
-        <v>2211</v>
+        <v>2216</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>2242</v>
+        <v>2247</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>2273</v>
+        <v>2278</v>
       </c>
       <c r="O16">
         <v>36.31</v>
@@ -25242,7 +25307,7 @@
         <v>871</v>
       </c>
       <c r="Q16" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -25250,7 +25315,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="C17" t="s">
         <v>158</v>
@@ -25268,7 +25333,7 @@
         <v>0.77</v>
       </c>
       <c r="I17" t="s">
-        <v>2181</v>
+        <v>2186</v>
       </c>
       <c r="J17">
         <v>19.99</v>
@@ -25277,13 +25342,13 @@
         <v>465</v>
       </c>
       <c r="L17" t="s">
-        <v>2212</v>
+        <v>2217</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>2243</v>
+        <v>2248</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>2274</v>
+        <v>2279</v>
       </c>
       <c r="O17">
         <v>15.49</v>
@@ -25292,7 +25357,7 @@
         <v>871</v>
       </c>
       <c r="Q17" t="s">
-        <v>2305</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -25300,7 +25365,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>2132</v>
+        <v>2137</v>
       </c>
       <c r="C18" t="s">
         <v>158</v>
@@ -25318,7 +25383,7 @@
         <v>1.84</v>
       </c>
       <c r="I18" t="s">
-        <v>2182</v>
+        <v>2187</v>
       </c>
       <c r="J18">
         <v>19.99</v>
@@ -25327,13 +25392,13 @@
         <v>465</v>
       </c>
       <c r="L18" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>2244</v>
+        <v>2249</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>2275</v>
+        <v>2280</v>
       </c>
       <c r="O18">
         <v>36.87</v>
@@ -25342,7 +25407,7 @@
         <v>871</v>
       </c>
       <c r="Q18" t="s">
-        <v>2306</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -25350,7 +25415,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="C19" t="s">
         <v>159</v>
@@ -25368,10 +25433,10 @@
         <v>0.59</v>
       </c>
       <c r="H19" t="s">
-        <v>2157</v>
+        <v>2162</v>
       </c>
       <c r="I19" t="s">
-        <v>2183</v>
+        <v>2188</v>
       </c>
       <c r="J19">
         <v>19.99</v>
@@ -25380,13 +25445,13 @@
         <v>465</v>
       </c>
       <c r="L19" t="s">
-        <v>2214</v>
+        <v>2219</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>2276</v>
+        <v>2281</v>
       </c>
       <c r="O19">
         <v>11.86</v>
@@ -25395,7 +25460,7 @@
         <v>871</v>
       </c>
       <c r="Q19" t="s">
-        <v>2307</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -25403,7 +25468,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2134</v>
+        <v>2139</v>
       </c>
       <c r="C20" t="s">
         <v>159</v>
@@ -25421,7 +25486,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="J20">
         <v>19.99</v>
@@ -25430,13 +25495,13 @@
         <v>465</v>
       </c>
       <c r="L20" t="s">
-        <v>2215</v>
+        <v>2220</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>2246</v>
+        <v>2251</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="O20">
         <v>12.35</v>
@@ -25445,7 +25510,7 @@
         <v>871</v>
       </c>
       <c r="Q20" t="s">
-        <v>2308</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -25453,7 +25518,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="C21" t="s">
         <v>159</v>
@@ -25471,10 +25536,10 @@
         <v>0.44</v>
       </c>
       <c r="H21" t="s">
-        <v>2158</v>
+        <v>2163</v>
       </c>
       <c r="I21" t="s">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="J21">
         <v>19.99</v>
@@ -25483,13 +25548,13 @@
         <v>465</v>
       </c>
       <c r="L21" t="s">
-        <v>2216</v>
+        <v>2221</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>2247</v>
+        <v>2252</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>2278</v>
+        <v>2283</v>
       </c>
       <c r="O21">
         <v>8.81</v>
@@ -25498,7 +25563,7 @@
         <v>871</v>
       </c>
       <c r="Q21" t="s">
-        <v>2309</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -25506,7 +25571,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
       <c r="C22" t="s">
         <v>159</v>
@@ -25524,7 +25589,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="J22">
         <v>19.99</v>
@@ -25533,13 +25598,13 @@
         <v>465</v>
       </c>
       <c r="L22" t="s">
-        <v>2217</v>
+        <v>2222</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>2248</v>
+        <v>2253</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>2279</v>
+        <v>2284</v>
       </c>
       <c r="O22">
         <v>11.2</v>
@@ -25548,7 +25613,7 @@
         <v>871</v>
       </c>
       <c r="Q22" t="s">
-        <v>2310</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -25556,7 +25621,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="C23" t="s">
         <v>160</v>
@@ -25574,10 +25639,10 @@
         <v>0.61</v>
       </c>
       <c r="H23" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="I23" t="s">
-        <v>2187</v>
+        <v>2192</v>
       </c>
       <c r="J23">
         <v>19.99</v>
@@ -25586,13 +25651,13 @@
         <v>465</v>
       </c>
       <c r="L23" t="s">
-        <v>2218</v>
+        <v>2223</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>2249</v>
+        <v>2254</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>2280</v>
+        <v>2285</v>
       </c>
       <c r="O23">
         <v>12.25</v>
@@ -25601,7 +25666,7 @@
         <v>871</v>
       </c>
       <c r="Q23" t="s">
-        <v>2311</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -25609,7 +25674,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
       <c r="C24" t="s">
         <v>160</v>
@@ -25627,10 +25692,10 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>2160</v>
+        <v>2165</v>
       </c>
       <c r="I24" t="s">
-        <v>2188</v>
+        <v>2193</v>
       </c>
       <c r="J24">
         <v>19.99</v>
@@ -25639,13 +25704,13 @@
         <v>465</v>
       </c>
       <c r="L24" t="s">
-        <v>2219</v>
+        <v>2224</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>2250</v>
+        <v>2255</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>2281</v>
+        <v>2286</v>
       </c>
       <c r="O24">
         <v>10.89</v>
@@ -25654,7 +25719,7 @@
         <v>871</v>
       </c>
       <c r="Q24" t="s">
-        <v>2312</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -25662,7 +25727,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="C25" t="s">
         <v>160</v>
@@ -25680,10 +25745,10 @@
         <v>0.38</v>
       </c>
       <c r="H25" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
       <c r="I25" t="s">
-        <v>2189</v>
+        <v>2194</v>
       </c>
       <c r="J25">
         <v>19.99</v>
@@ -25692,13 +25757,13 @@
         <v>465</v>
       </c>
       <c r="L25" t="s">
-        <v>2220</v>
+        <v>2225</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>2251</v>
+        <v>2256</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>2282</v>
+        <v>2287</v>
       </c>
       <c r="O25">
         <v>7.5</v>
@@ -25707,7 +25772,7 @@
         <v>871</v>
       </c>
       <c r="Q25" t="s">
-        <v>2313</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -25715,7 +25780,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="C26" t="s">
         <v>160</v>
@@ -25733,10 +25798,10 @@
         <v>0.62</v>
       </c>
       <c r="H26" t="s">
-        <v>2162</v>
+        <v>2167</v>
       </c>
       <c r="I26" t="s">
-        <v>2190</v>
+        <v>2195</v>
       </c>
       <c r="J26">
         <v>19.99</v>
@@ -25745,13 +25810,13 @@
         <v>465</v>
       </c>
       <c r="L26" t="s">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>2252</v>
+        <v>2257</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>2283</v>
+        <v>2288</v>
       </c>
       <c r="O26">
         <v>12.32</v>
@@ -25760,7 +25825,7 @@
         <v>871</v>
       </c>
       <c r="Q26" t="s">
-        <v>2314</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -25768,7 +25833,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>2141</v>
+        <v>2146</v>
       </c>
       <c r="C27" t="s">
         <v>161</v>
@@ -25786,10 +25851,10 @@
         <v>2.43</v>
       </c>
       <c r="H27" t="s">
-        <v>2163</v>
+        <v>2168</v>
       </c>
       <c r="I27" t="s">
-        <v>2191</v>
+        <v>2196</v>
       </c>
       <c r="J27">
         <v>19.99</v>
@@ -25798,13 +25863,13 @@
         <v>465</v>
       </c>
       <c r="L27" t="s">
-        <v>2222</v>
+        <v>2227</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>2253</v>
+        <v>2258</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>2284</v>
+        <v>2289</v>
       </c>
       <c r="O27">
         <v>48.66</v>
@@ -25813,7 +25878,7 @@
         <v>871</v>
       </c>
       <c r="Q27" t="s">
-        <v>2315</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -25821,7 +25886,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>2142</v>
+        <v>2147</v>
       </c>
       <c r="C28" t="s">
         <v>161</v>
@@ -25839,7 +25904,7 @@
         <v>1.83</v>
       </c>
       <c r="I28" t="s">
-        <v>2192</v>
+        <v>2197</v>
       </c>
       <c r="J28">
         <v>19.99</v>
@@ -25848,13 +25913,13 @@
         <v>465</v>
       </c>
       <c r="L28" t="s">
-        <v>2223</v>
+        <v>2228</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>2254</v>
+        <v>2259</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>2285</v>
+        <v>2290</v>
       </c>
       <c r="O28">
         <v>36.49</v>
@@ -25863,7 +25928,7 @@
         <v>871</v>
       </c>
       <c r="Q28" t="s">
-        <v>2316</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -25871,7 +25936,7 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>2143</v>
+        <v>2148</v>
       </c>
       <c r="C29" t="s">
         <v>161</v>
@@ -25889,10 +25954,10 @@
         <v>1.33</v>
       </c>
       <c r="H29" t="s">
-        <v>2164</v>
+        <v>2169</v>
       </c>
       <c r="I29" t="s">
-        <v>2193</v>
+        <v>2198</v>
       </c>
       <c r="J29">
         <v>19.99</v>
@@ -25901,13 +25966,13 @@
         <v>465</v>
       </c>
       <c r="L29" t="s">
-        <v>2224</v>
+        <v>2229</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>2255</v>
+        <v>2260</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>2286</v>
+        <v>2291</v>
       </c>
       <c r="O29">
         <v>26.63</v>
@@ -25916,7 +25981,7 @@
         <v>871</v>
       </c>
       <c r="Q29" t="s">
-        <v>2317</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -25924,7 +25989,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
       <c r="C30" t="s">
         <v>161</v>
@@ -25942,7 +26007,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="s">
-        <v>2194</v>
+        <v>2199</v>
       </c>
       <c r="J30">
         <v>19.99</v>
@@ -25951,13 +26016,13 @@
         <v>465</v>
       </c>
       <c r="L30" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>2256</v>
+        <v>2261</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>2287</v>
+        <v>2292</v>
       </c>
       <c r="O30">
         <v>50.71</v>
@@ -25966,7 +26031,7 @@
         <v>871</v>
       </c>
       <c r="Q30" t="s">
-        <v>2318</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -25974,7 +26039,7 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
       <c r="C31" t="s">
         <v>162</v>
@@ -25992,10 +26057,10 @@
         <v>0.85</v>
       </c>
       <c r="H31" t="s">
-        <v>2165</v>
+        <v>2170</v>
       </c>
       <c r="I31" t="s">
-        <v>2195</v>
+        <v>2200</v>
       </c>
       <c r="J31">
         <v>19.99</v>
@@ -26004,13 +26069,13 @@
         <v>465</v>
       </c>
       <c r="L31" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>2288</v>
+        <v>2293</v>
       </c>
       <c r="O31">
         <v>16.93</v>
@@ -26019,7 +26084,7 @@
         <v>871</v>
       </c>
       <c r="Q31" t="s">
-        <v>2319</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -26027,7 +26092,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
       <c r="C32" t="s">
         <v>162</v>
@@ -26045,7 +26110,7 @@
         <v>0.9</v>
       </c>
       <c r="I32" t="s">
-        <v>2196</v>
+        <v>2201</v>
       </c>
       <c r="J32">
         <v>19.99</v>
@@ -26054,13 +26119,13 @@
         <v>465</v>
       </c>
       <c r="L32" t="s">
-        <v>2227</v>
+        <v>2232</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>2258</v>
+        <v>2263</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>2289</v>
+        <v>2294</v>
       </c>
       <c r="O32">
         <v>17.97</v>
@@ -26069,7 +26134,7 @@
         <v>871</v>
       </c>
       <c r="Q32" t="s">
-        <v>2320</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -26077,7 +26142,7 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="C33" t="s">
         <v>162</v>
@@ -26095,10 +26160,10 @@
         <v>0.89</v>
       </c>
       <c r="H33" t="s">
-        <v>2166</v>
+        <v>2171</v>
       </c>
       <c r="I33" t="s">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="J33">
         <v>19.99</v>
@@ -26107,13 +26172,13 @@
         <v>465</v>
       </c>
       <c r="L33" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>2259</v>
+        <v>2264</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>2290</v>
+        <v>2295</v>
       </c>
       <c r="O33">
         <v>17.84</v>
@@ -26122,7 +26187,7 @@
         <v>871</v>
       </c>
       <c r="Q33" t="s">
-        <v>2321</v>
+        <v>2326</v>
       </c>
     </row>
   </sheetData>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -11227,7 +11227,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -27966,7 +27966,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4456" uniqueCount="2398">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4456" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4423" uniqueCount="2398">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -13414,7 +13414,7 @@
       <c r="J111">
         <v>19.99</v>
       </c>
-      <c r="K111" s="3" t="s">
+      <c r="K111" t="s">
         <v>482</v>
       </c>
       <c r="L111" t="s">
@@ -13458,7 +13458,7 @@
       <c r="J112">
         <v>22</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="K112" t="s">
         <v>482</v>
       </c>
       <c r="L112" t="s">
@@ -13505,7 +13505,7 @@
       <c r="J113">
         <v>21.99</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="K113" t="s">
         <v>482</v>
       </c>
       <c r="L113" t="s">
@@ -13555,7 +13555,7 @@
       <c r="J114">
         <v>19.99</v>
       </c>
-      <c r="K114" s="3" t="s">
+      <c r="K114" t="s">
         <v>482</v>
       </c>
       <c r="L114" t="s">
@@ -13652,7 +13652,7 @@
       <c r="J116">
         <v>21.99</v>
       </c>
-      <c r="K116" s="3" t="s">
+      <c r="K116" t="s">
         <v>482</v>
       </c>
       <c r="L116" t="s">
@@ -13699,7 +13699,7 @@
       <c r="J117">
         <v>23.99</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="K117" t="s">
         <v>482</v>
       </c>
       <c r="L117" t="s">
@@ -13749,7 +13749,7 @@
       <c r="J118">
         <v>21.99</v>
       </c>
-      <c r="K118" s="3" t="s">
+      <c r="K118" t="s">
         <v>482</v>
       </c>
       <c r="L118" t="s">
@@ -13890,7 +13890,7 @@
       <c r="J121">
         <v>42.99</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="K121" t="s">
         <v>482</v>
       </c>
       <c r="L121" t="s">
@@ -13937,7 +13937,7 @@
       <c r="J122">
         <v>21.99</v>
       </c>
-      <c r="K122" s="3" t="s">
+      <c r="K122" t="s">
         <v>482</v>
       </c>
       <c r="L122" t="s">
@@ -13984,7 +13984,7 @@
       <c r="J123">
         <v>17.99</v>
       </c>
-      <c r="K123" s="3" t="s">
+      <c r="K123" t="s">
         <v>482</v>
       </c>
       <c r="L123" t="s">
@@ -14031,7 +14031,7 @@
       <c r="J124">
         <v>21.99</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="K124" t="s">
         <v>482</v>
       </c>
       <c r="L124" t="s">
@@ -14078,7 +14078,7 @@
       <c r="J125">
         <v>17.99</v>
       </c>
-      <c r="K125" s="3" t="s">
+      <c r="K125" t="s">
         <v>482</v>
       </c>
       <c r="L125" t="s">
@@ -14125,7 +14125,7 @@
       <c r="J126">
         <v>17.99</v>
       </c>
-      <c r="K126" s="3" t="s">
+      <c r="K126" t="s">
         <v>482</v>
       </c>
       <c r="L126" t="s">
@@ -14172,7 +14172,7 @@
       <c r="J127">
         <v>21.99</v>
       </c>
-      <c r="K127" s="3" t="s">
+      <c r="K127" t="s">
         <v>482</v>
       </c>
       <c r="L127" t="s">
@@ -14222,7 +14222,7 @@
       <c r="J128">
         <v>19.99</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="K128" t="s">
         <v>482</v>
       </c>
       <c r="L128" t="s">
@@ -14266,7 +14266,7 @@
       <c r="J129">
         <v>24.99</v>
       </c>
-      <c r="K129" s="3" t="s">
+      <c r="K129" t="s">
         <v>482</v>
       </c>
       <c r="L129" t="s">
@@ -14690,7 +14690,7 @@
       <c r="J137">
         <v>19.67</v>
       </c>
-      <c r="K137" s="3" t="s">
+      <c r="K137" t="s">
         <v>482</v>
       </c>
       <c r="L137" t="s">
@@ -14796,7 +14796,7 @@
       <c r="J139">
         <v>19.67</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="K139" t="s">
         <v>482</v>
       </c>
       <c r="L139" t="s">
@@ -14955,7 +14955,7 @@
       <c r="J142">
         <v>20.49</v>
       </c>
-      <c r="K142" s="3" t="s">
+      <c r="K142" t="s">
         <v>482</v>
       </c>
       <c r="L142" t="s">
@@ -15008,7 +15008,7 @@
       <c r="J143">
         <v>20.49</v>
       </c>
-      <c r="K143" s="3" t="s">
+      <c r="K143" t="s">
         <v>482</v>
       </c>
       <c r="L143" t="s">
@@ -15061,7 +15061,7 @@
       <c r="J144">
         <v>23.75</v>
       </c>
-      <c r="K144" s="3" t="s">
+      <c r="K144" t="s">
         <v>482</v>
       </c>
       <c r="L144" t="s">
@@ -15114,7 +15114,7 @@
       <c r="J145">
         <v>20.49</v>
       </c>
-      <c r="K145" s="3" t="s">
+      <c r="K145" t="s">
         <v>482</v>
       </c>
       <c r="L145" t="s">
@@ -15370,98 +15370,76 @@
     <hyperlink ref="N109" r:id="rId214"/>
     <hyperlink ref="M110" r:id="rId215"/>
     <hyperlink ref="N110" r:id="rId216"/>
-    <hyperlink ref="K111" r:id="rId217"/>
-    <hyperlink ref="M111" r:id="rId218"/>
-    <hyperlink ref="N111" r:id="rId219"/>
-    <hyperlink ref="K112" r:id="rId220"/>
-    <hyperlink ref="M112" r:id="rId221"/>
-    <hyperlink ref="N112" r:id="rId222"/>
-    <hyperlink ref="K113" r:id="rId223"/>
-    <hyperlink ref="M113" r:id="rId224"/>
-    <hyperlink ref="N113" r:id="rId225"/>
-    <hyperlink ref="K114" r:id="rId226"/>
-    <hyperlink ref="M114" r:id="rId227"/>
-    <hyperlink ref="N114" r:id="rId228"/>
-    <hyperlink ref="M115" r:id="rId229"/>
-    <hyperlink ref="N115" r:id="rId230"/>
-    <hyperlink ref="K116" r:id="rId231"/>
-    <hyperlink ref="M116" r:id="rId232"/>
-    <hyperlink ref="N116" r:id="rId233"/>
-    <hyperlink ref="K117" r:id="rId234"/>
-    <hyperlink ref="M117" r:id="rId235"/>
-    <hyperlink ref="N117" r:id="rId236"/>
-    <hyperlink ref="K118" r:id="rId237"/>
-    <hyperlink ref="M118" r:id="rId238"/>
-    <hyperlink ref="N118" r:id="rId239"/>
-    <hyperlink ref="M119" r:id="rId240"/>
-    <hyperlink ref="N119" r:id="rId241"/>
-    <hyperlink ref="M120" r:id="rId242"/>
-    <hyperlink ref="N120" r:id="rId243"/>
-    <hyperlink ref="K121" r:id="rId244"/>
-    <hyperlink ref="M121" r:id="rId245"/>
-    <hyperlink ref="N121" r:id="rId246"/>
-    <hyperlink ref="K122" r:id="rId247"/>
-    <hyperlink ref="M122" r:id="rId248"/>
-    <hyperlink ref="N122" r:id="rId249"/>
-    <hyperlink ref="K123" r:id="rId250"/>
-    <hyperlink ref="M123" r:id="rId251"/>
-    <hyperlink ref="N123" r:id="rId252"/>
-    <hyperlink ref="K124" r:id="rId253"/>
-    <hyperlink ref="M124" r:id="rId254"/>
-    <hyperlink ref="N124" r:id="rId255"/>
-    <hyperlink ref="K125" r:id="rId256"/>
-    <hyperlink ref="M125" r:id="rId257"/>
-    <hyperlink ref="N125" r:id="rId258"/>
-    <hyperlink ref="K126" r:id="rId259"/>
-    <hyperlink ref="M126" r:id="rId260"/>
-    <hyperlink ref="N126" r:id="rId261"/>
-    <hyperlink ref="K127" r:id="rId262"/>
-    <hyperlink ref="M127" r:id="rId263"/>
-    <hyperlink ref="N127" r:id="rId264"/>
-    <hyperlink ref="K128" r:id="rId265"/>
-    <hyperlink ref="M128" r:id="rId266"/>
-    <hyperlink ref="N128" r:id="rId267"/>
-    <hyperlink ref="K129" r:id="rId268"/>
-    <hyperlink ref="M129" r:id="rId269"/>
-    <hyperlink ref="N129" r:id="rId270"/>
-    <hyperlink ref="M130" r:id="rId271"/>
-    <hyperlink ref="N130" r:id="rId272"/>
-    <hyperlink ref="M131" r:id="rId273"/>
-    <hyperlink ref="N131" r:id="rId274"/>
-    <hyperlink ref="M132" r:id="rId275"/>
-    <hyperlink ref="N132" r:id="rId276"/>
-    <hyperlink ref="M133" r:id="rId277"/>
-    <hyperlink ref="N133" r:id="rId278"/>
-    <hyperlink ref="M134" r:id="rId279"/>
-    <hyperlink ref="N134" r:id="rId280"/>
-    <hyperlink ref="M135" r:id="rId281"/>
-    <hyperlink ref="N135" r:id="rId282"/>
-    <hyperlink ref="M136" r:id="rId283"/>
-    <hyperlink ref="N136" r:id="rId284"/>
-    <hyperlink ref="K137" r:id="rId285"/>
-    <hyperlink ref="M137" r:id="rId286"/>
-    <hyperlink ref="N137" r:id="rId287"/>
-    <hyperlink ref="M138" r:id="rId288"/>
-    <hyperlink ref="N138" r:id="rId289"/>
-    <hyperlink ref="K139" r:id="rId290"/>
-    <hyperlink ref="M139" r:id="rId291"/>
-    <hyperlink ref="N139" r:id="rId292"/>
-    <hyperlink ref="M140" r:id="rId293"/>
-    <hyperlink ref="N140" r:id="rId294"/>
-    <hyperlink ref="M141" r:id="rId295"/>
-    <hyperlink ref="N141" r:id="rId296"/>
-    <hyperlink ref="K142" r:id="rId297"/>
-    <hyperlink ref="M142" r:id="rId298"/>
-    <hyperlink ref="N142" r:id="rId299"/>
-    <hyperlink ref="K143" r:id="rId300"/>
-    <hyperlink ref="M143" r:id="rId301"/>
-    <hyperlink ref="N143" r:id="rId302"/>
-    <hyperlink ref="K144" r:id="rId303"/>
-    <hyperlink ref="M144" r:id="rId304"/>
-    <hyperlink ref="N144" r:id="rId305"/>
-    <hyperlink ref="K145" r:id="rId306"/>
-    <hyperlink ref="M145" r:id="rId307"/>
-    <hyperlink ref="N145" r:id="rId308"/>
+    <hyperlink ref="M111" r:id="rId217"/>
+    <hyperlink ref="N111" r:id="rId218"/>
+    <hyperlink ref="M112" r:id="rId219"/>
+    <hyperlink ref="N112" r:id="rId220"/>
+    <hyperlink ref="M113" r:id="rId221"/>
+    <hyperlink ref="N113" r:id="rId222"/>
+    <hyperlink ref="M114" r:id="rId223"/>
+    <hyperlink ref="N114" r:id="rId224"/>
+    <hyperlink ref="M115" r:id="rId225"/>
+    <hyperlink ref="N115" r:id="rId226"/>
+    <hyperlink ref="M116" r:id="rId227"/>
+    <hyperlink ref="N116" r:id="rId228"/>
+    <hyperlink ref="M117" r:id="rId229"/>
+    <hyperlink ref="N117" r:id="rId230"/>
+    <hyperlink ref="M118" r:id="rId231"/>
+    <hyperlink ref="N118" r:id="rId232"/>
+    <hyperlink ref="M119" r:id="rId233"/>
+    <hyperlink ref="N119" r:id="rId234"/>
+    <hyperlink ref="M120" r:id="rId235"/>
+    <hyperlink ref="N120" r:id="rId236"/>
+    <hyperlink ref="M121" r:id="rId237"/>
+    <hyperlink ref="N121" r:id="rId238"/>
+    <hyperlink ref="M122" r:id="rId239"/>
+    <hyperlink ref="N122" r:id="rId240"/>
+    <hyperlink ref="M123" r:id="rId241"/>
+    <hyperlink ref="N123" r:id="rId242"/>
+    <hyperlink ref="M124" r:id="rId243"/>
+    <hyperlink ref="N124" r:id="rId244"/>
+    <hyperlink ref="M125" r:id="rId245"/>
+    <hyperlink ref="N125" r:id="rId246"/>
+    <hyperlink ref="M126" r:id="rId247"/>
+    <hyperlink ref="N126" r:id="rId248"/>
+    <hyperlink ref="M127" r:id="rId249"/>
+    <hyperlink ref="N127" r:id="rId250"/>
+    <hyperlink ref="M128" r:id="rId251"/>
+    <hyperlink ref="N128" r:id="rId252"/>
+    <hyperlink ref="M129" r:id="rId253"/>
+    <hyperlink ref="N129" r:id="rId254"/>
+    <hyperlink ref="M130" r:id="rId255"/>
+    <hyperlink ref="N130" r:id="rId256"/>
+    <hyperlink ref="M131" r:id="rId257"/>
+    <hyperlink ref="N131" r:id="rId258"/>
+    <hyperlink ref="M132" r:id="rId259"/>
+    <hyperlink ref="N132" r:id="rId260"/>
+    <hyperlink ref="M133" r:id="rId261"/>
+    <hyperlink ref="N133" r:id="rId262"/>
+    <hyperlink ref="M134" r:id="rId263"/>
+    <hyperlink ref="N134" r:id="rId264"/>
+    <hyperlink ref="M135" r:id="rId265"/>
+    <hyperlink ref="N135" r:id="rId266"/>
+    <hyperlink ref="M136" r:id="rId267"/>
+    <hyperlink ref="N136" r:id="rId268"/>
+    <hyperlink ref="M137" r:id="rId269"/>
+    <hyperlink ref="N137" r:id="rId270"/>
+    <hyperlink ref="M138" r:id="rId271"/>
+    <hyperlink ref="N138" r:id="rId272"/>
+    <hyperlink ref="M139" r:id="rId273"/>
+    <hyperlink ref="N139" r:id="rId274"/>
+    <hyperlink ref="M140" r:id="rId275"/>
+    <hyperlink ref="N140" r:id="rId276"/>
+    <hyperlink ref="M141" r:id="rId277"/>
+    <hyperlink ref="N141" r:id="rId278"/>
+    <hyperlink ref="M142" r:id="rId279"/>
+    <hyperlink ref="N142" r:id="rId280"/>
+    <hyperlink ref="M143" r:id="rId281"/>
+    <hyperlink ref="N143" r:id="rId282"/>
+    <hyperlink ref="M144" r:id="rId283"/>
+    <hyperlink ref="N144" r:id="rId284"/>
+    <hyperlink ref="M145" r:id="rId285"/>
+    <hyperlink ref="N145" r:id="rId286"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16632,7 +16610,7 @@
       <c r="J19">
         <v>25.99</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" t="s">
         <v>482</v>
       </c>
       <c r="L19" t="s">
@@ -16679,7 +16657,7 @@
       <c r="J20">
         <v>26.49</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" t="s">
         <v>482</v>
       </c>
       <c r="L20" t="s">
@@ -16776,7 +16754,7 @@
       <c r="J22">
         <v>26.97</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" t="s">
         <v>482</v>
       </c>
       <c r="L22" t="s">
@@ -16848,17 +16826,14 @@
     <hyperlink ref="N17" r:id="rId30"/>
     <hyperlink ref="M18" r:id="rId31"/>
     <hyperlink ref="N18" r:id="rId32"/>
-    <hyperlink ref="K19" r:id="rId33"/>
-    <hyperlink ref="M19" r:id="rId34"/>
-    <hyperlink ref="N19" r:id="rId35"/>
-    <hyperlink ref="K20" r:id="rId36"/>
-    <hyperlink ref="M20" r:id="rId37"/>
-    <hyperlink ref="N20" r:id="rId38"/>
-    <hyperlink ref="M21" r:id="rId39"/>
-    <hyperlink ref="N21" r:id="rId40"/>
-    <hyperlink ref="K22" r:id="rId41"/>
-    <hyperlink ref="M22" r:id="rId42"/>
-    <hyperlink ref="N22" r:id="rId43"/>
+    <hyperlink ref="M19" r:id="rId33"/>
+    <hyperlink ref="N19" r:id="rId34"/>
+    <hyperlink ref="M20" r:id="rId35"/>
+    <hyperlink ref="N20" r:id="rId36"/>
+    <hyperlink ref="M21" r:id="rId37"/>
+    <hyperlink ref="N21" r:id="rId38"/>
+    <hyperlink ref="M22" r:id="rId39"/>
+    <hyperlink ref="N22" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19896,7 +19871,7 @@
       <c r="J60">
         <v>22</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="K60" t="s">
         <v>482</v>
       </c>
       <c r="L60" t="s">
@@ -19990,7 +19965,7 @@
       <c r="J62">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K62" t="s">
         <v>482</v>
       </c>
       <c r="L62" t="s">
@@ -20037,7 +20012,7 @@
       <c r="J63">
         <v>100</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="K63" t="s">
         <v>482</v>
       </c>
       <c r="L63" t="s">
@@ -20084,7 +20059,7 @@
       <c r="J64">
         <v>33</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="K64" t="s">
         <v>482</v>
       </c>
       <c r="L64" t="s">
@@ -20131,7 +20106,7 @@
       <c r="J65">
         <v>22</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="K65" t="s">
         <v>482</v>
       </c>
       <c r="L65" t="s">
@@ -20338,25 +20313,20 @@
     <hyperlink ref="N58" r:id="rId112"/>
     <hyperlink ref="M59" r:id="rId113"/>
     <hyperlink ref="N59" r:id="rId114"/>
-    <hyperlink ref="K60" r:id="rId115"/>
-    <hyperlink ref="M60" r:id="rId116"/>
-    <hyperlink ref="N60" r:id="rId117"/>
-    <hyperlink ref="M61" r:id="rId118"/>
-    <hyperlink ref="N61" r:id="rId119"/>
-    <hyperlink ref="K62" r:id="rId120"/>
-    <hyperlink ref="M62" r:id="rId121"/>
-    <hyperlink ref="N62" r:id="rId122"/>
-    <hyperlink ref="K63" r:id="rId123"/>
-    <hyperlink ref="M63" r:id="rId124"/>
-    <hyperlink ref="N63" r:id="rId125"/>
-    <hyperlink ref="K64" r:id="rId126"/>
-    <hyperlink ref="M64" r:id="rId127"/>
-    <hyperlink ref="N64" r:id="rId128"/>
-    <hyperlink ref="K65" r:id="rId129"/>
-    <hyperlink ref="M65" r:id="rId130"/>
-    <hyperlink ref="N65" r:id="rId131"/>
-    <hyperlink ref="M66" r:id="rId132"/>
-    <hyperlink ref="N66" r:id="rId133"/>
+    <hyperlink ref="M60" r:id="rId115"/>
+    <hyperlink ref="N60" r:id="rId116"/>
+    <hyperlink ref="M61" r:id="rId117"/>
+    <hyperlink ref="N61" r:id="rId118"/>
+    <hyperlink ref="M62" r:id="rId119"/>
+    <hyperlink ref="N62" r:id="rId120"/>
+    <hyperlink ref="M63" r:id="rId121"/>
+    <hyperlink ref="N63" r:id="rId122"/>
+    <hyperlink ref="M64" r:id="rId123"/>
+    <hyperlink ref="N64" r:id="rId124"/>
+    <hyperlink ref="M65" r:id="rId125"/>
+    <hyperlink ref="N65" r:id="rId126"/>
+    <hyperlink ref="M66" r:id="rId127"/>
+    <hyperlink ref="N66" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21516,7 +21486,7 @@
       <c r="J24">
         <v>42.99</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" t="s">
         <v>482</v>
       </c>
       <c r="L24" t="s">
@@ -21698,13 +21668,12 @@
     <hyperlink ref="N22" r:id="rId40"/>
     <hyperlink ref="M23" r:id="rId41"/>
     <hyperlink ref="N23" r:id="rId42"/>
-    <hyperlink ref="K24" r:id="rId43"/>
-    <hyperlink ref="M24" r:id="rId44"/>
-    <hyperlink ref="N24" r:id="rId45"/>
-    <hyperlink ref="M25" r:id="rId46"/>
-    <hyperlink ref="N25" r:id="rId47"/>
-    <hyperlink ref="M26" r:id="rId48"/>
-    <hyperlink ref="N26" r:id="rId49"/>
+    <hyperlink ref="M24" r:id="rId43"/>
+    <hyperlink ref="N24" r:id="rId44"/>
+    <hyperlink ref="M25" r:id="rId45"/>
+    <hyperlink ref="N25" r:id="rId46"/>
+    <hyperlink ref="M26" r:id="rId47"/>
+    <hyperlink ref="N26" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24501,7 +24470,7 @@
       <c r="J10">
         <v>24.99</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" t="s">
         <v>482</v>
       </c>
       <c r="L10" t="s">
@@ -24607,7 +24576,7 @@
       <c r="J12">
         <v>24.99</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" t="s">
         <v>482</v>
       </c>
       <c r="L12" t="s">
@@ -24711,16 +24680,14 @@
     <hyperlink ref="N8" r:id="rId12"/>
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14"/>
-    <hyperlink ref="K10" r:id="rId15"/>
-    <hyperlink ref="M10" r:id="rId16"/>
-    <hyperlink ref="N10" r:id="rId17"/>
-    <hyperlink ref="M11" r:id="rId18"/>
-    <hyperlink ref="N11" r:id="rId19"/>
-    <hyperlink ref="K12" r:id="rId20"/>
-    <hyperlink ref="M12" r:id="rId21"/>
-    <hyperlink ref="N12" r:id="rId22"/>
-    <hyperlink ref="M13" r:id="rId23"/>
-    <hyperlink ref="N13" r:id="rId24"/>
+    <hyperlink ref="M10" r:id="rId15"/>
+    <hyperlink ref="N10" r:id="rId16"/>
+    <hyperlink ref="M11" r:id="rId17"/>
+    <hyperlink ref="N11" r:id="rId18"/>
+    <hyperlink ref="M12" r:id="rId19"/>
+    <hyperlink ref="N12" r:id="rId20"/>
+    <hyperlink ref="M13" r:id="rId21"/>
+    <hyperlink ref="N13" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="2408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="2408">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -14721,7 +14721,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -27803,7 +27803,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -27882,7 +27882,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -27961,7 +27961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q147"/>
+  <dimension ref="A1:Q148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Teela (Camila Mendez - Movie)</t>
+          <t>Tauraton</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>$21.99</t>
+          <t>$33.00</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -10214,13 +10214,8 @@
       <c r="G127" t="n">
         <v>1</v>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>194735397419</t>
-        </is>
-      </c>
       <c r="J127" t="n">
-        <v>21.99</v>
+        <v>33</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
@@ -10229,17 +10224,17 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/teela-camila-mendez-movie-14039.webp</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/tauraton-14049.webp</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/teela-camila-mendez-movie-14039.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/tauraton-14049.jpg</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/teela-camila-mendez-movie-14039.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/tauraton-14049.php</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -10252,7 +10247,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14049</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10259,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Trap Jaw (200x - Cartoon Collection)</t>
+          <t>Teela (Camila Mendez - Movie)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10274,7 +10269,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>$17.99</t>
+          <t>$21.99</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -10285,30 +10280,30 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>194735333264</t>
+          <t>194735397419</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="K128" t="inlineStr">
+        <v>21.99</v>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
         <is>
           <t>Ver Imagen</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/trap-jaw-200x-cartoon-collection-13915.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/teela-camila-mendez-movie-14039.webp</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/trap-jaw-200x-cartoon-collection-13915.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/teela-camila-mendez-movie-14039.jpg</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/trap-jaw-200x-cartoon-collection-13915.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/teela-camila-mendez-movie-14039.php</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -10321,7 +10316,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>14039</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10328,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tri-Klops (Movie)</t>
+          <t>Trap Jaw (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10343,7 +10338,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>$21.99</t>
+          <t>$17.99</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -10354,11 +10349,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>194735350858</t>
+          <t>194735333264</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>21.99</v>
+        <v>17.99</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -10367,17 +10362,17 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/tri-klops-movie-13978.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/trap-jaw-200x-cartoon-collection-13915.jpg</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/tri-klops-movie-13978.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/trap-jaw-200x-cartoon-collection-13915.jpg</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/tri-klops-movie-13978.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/trap-jaw-200x-cartoon-collection-13915.php</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -10390,7 +10385,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>13915</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10397,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Webstor (200x - Cartoon Collection)</t>
+          <t>Tri-Klops (Movie)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10412,7 +10407,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$21.99</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -10421,18 +10416,13 @@
       <c r="G130" t="n">
         <v>1</v>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>B0G43BQCDK</t>
-        </is>
-      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>194735333370</t>
+          <t>194735350858</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>19.99</v>
+        <v>21.99</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -10441,17 +10431,17 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/webstor-200x-cartoon-collection-13601.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/tri-klops-movie-13978.jpg</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/webstor-200x-cartoon-collection-13601.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/tri-klops-movie-13978.jpg</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/webstor-200x-cartoon-collection-13601.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/tri-klops-movie-13978.php</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -10464,7 +10454,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13978</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10466,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Whiplash (200x - Cartoon Collection)</t>
+          <t>Webstor (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10486,7 +10476,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>$24.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -10495,8 +10485,18 @@
       <c r="G131" t="n">
         <v>1</v>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>B0G43BQCDK</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>194735333370</t>
+        </is>
+      </c>
       <c r="J131" t="n">
-        <v>24.99</v>
+        <v>19.99</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -10505,17 +10505,17 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/whiplash-200x-cartoon-collection-13885.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/webstor-200x-cartoon-collection-13601.jpg</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/whiplash-200x-cartoon-collection-13885.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/webstor-200x-cartoon-collection-13601.jpg</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/whiplash-200x-cartoon-collection-13885.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/webstor-200x-cartoon-collection-13601.php</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -10528,24 +10528,19 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13601</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Beast Man (200x - Cartoon Collection)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>27</t>
+          <t>Whiplash (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10555,27 +10550,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>$23.75</t>
+          <t>$24.99</t>
         </is>
       </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>B0FHKK8GJW</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>194735333493</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>23.75</v>
+        <v>24.99</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -10584,21 +10569,21 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/beast-man-200x-cartoon-collection-12169.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/whiplash-200x-cartoon-collection-13885.jpg</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/beast-man-200x-cartoon-collection-12169.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/whiplash-200x-cartoon-collection-13885.jpg</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/beast-man-200x-cartoon-collection-12169.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/whiplash-200x-cartoon-collection-13885.php</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>29.63</v>
+        <v>0</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -10607,7 +10592,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>13885</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10604,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>He-Man (200x - Cartoon Collection)</t>
+          <t>Beast Man (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10634,27 +10619,27 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>$19.43</t>
+          <t>$23.75</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>B0FHKLTV9J</t>
+          <t>B0FHKK8GJW</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>194735333219</t>
+          <t>194735333493</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>19.43</v>
+        <v>23.75</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10663,21 +10648,21 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/he-man-200x-cartoon-collection-12170.jpg</t>
+          <t>/app/data/MOTU/images/beast-man-200x-cartoon-collection-12169.jpg</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-200x-cartoon-collection-12170.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/beast-man-200x-cartoon-collection-12169.jpg</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/he-man-200x-cartoon-collection-12170.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/beast-man-200x-cartoon-collection-12169.php</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>31.31</v>
+        <v>29.63</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10686,7 +10671,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>12169</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10683,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Stratos (200x - Cartoon Collection)</t>
+          <t>He-Man (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10720,16 +10705,16 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>B0FHKK77TL</t>
+          <t>B0FHKLTV9J</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>194735333509</t>
+          <t>194735333219</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -10742,21 +10727,21 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/stratos-200x-cartoon-collection-12171.jpg</t>
+          <t>/app/data/MOTU/images/he-man-200x-cartoon-collection-12170.jpg</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/stratos-200x-cartoon-collection-12171.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-200x-cartoon-collection-12170.jpg</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/stratos-200x-cartoon-collection-12171.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/he-man-200x-cartoon-collection-12170.php</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>27.95</v>
+        <v>31.31</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -10765,7 +10750,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12170</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10762,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tri-Klops (200x - Cartoon Collection)</t>
+          <t>Stratos (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10799,16 +10784,16 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>B0FHKN7JNF</t>
+          <t>B0FHKK77TL</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>194735333448</t>
+          <t>194735333509</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -10821,21 +10806,21 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/tri-klops-200x-cartoon-collection-12172.jpg</t>
+          <t>/app/data/MOTU/images/stratos-200x-cartoon-collection-12171.jpg</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/tri-klops-200x-cartoon-collection-12172.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/stratos-200x-cartoon-collection-12171.jpg</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/tri-klops-200x-cartoon-collection-12172.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/stratos-200x-cartoon-collection-12171.php</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>27.95</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10844,7 +10829,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12171</t>
         </is>
       </c>
     </row>
@@ -10856,12 +10841,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Evil-Lyn (200x - Cartoon Collection)</t>
+          <t>Tri-Klops (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10871,7 +10856,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$19.43</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -10882,16 +10867,16 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>B0FHJ3KJ1Y</t>
+          <t>B0FHKN7JNF</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>194735333240</t>
+          <t>194735333448</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>19.99</v>
+        <v>19.43</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10900,17 +10885,17 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/evil-lyn-200x-cartoon-collection-12503.jpg</t>
+          <t>/app/data/MOTU/images/tri-klops-200x-cartoon-collection-12172.jpg</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/evil-lyn-200x-cartoon-collection-12503.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/tri-klops-200x-cartoon-collection-12172.jpg</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/evil-lyn-200x-cartoon-collection-12503.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/tri-klops-200x-cartoon-collection-12172.php</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -10923,7 +10908,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12172</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10920,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Man-At-Arms (200x - Cartoon Collection)</t>
+          <t>Evil-Lyn (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10961,12 +10946,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>B0FHKL8G9G</t>
+          <t>B0FHJ3KJ1Y</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>194735333332</t>
+          <t>194735333240</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -10979,17 +10964,17 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/man-at-arms-200x-cartoon-collection-12504.jpg</t>
+          <t>/app/data/MOTU/images/evil-lyn-200x-cartoon-collection-12503.jpg</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/man-at-arms-200x-cartoon-collection-12504.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/evil-lyn-200x-cartoon-collection-12503.jpg</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/man-at-arms-200x-cartoon-collection-12504.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/evil-lyn-200x-cartoon-collection-12503.php</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -11002,7 +10987,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12503</t>
         </is>
       </c>
     </row>
@@ -11014,7 +10999,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Moss Man (200x - Cartoon Collection)</t>
+          <t>Man-At-Arms (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11036,16 +11021,16 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>B0FHJQQN37</t>
+          <t>B0FHKL8G9G</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>194735333462</t>
+          <t>194735333332</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -11058,21 +11043,21 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/moss-man-200x-cartoon-collection-12502.jpg</t>
+          <t>/app/data/MOTU/images/man-at-arms-200x-cartoon-collection-12504.jpg</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/moss-man-200x-cartoon-collection-12502.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/man-at-arms-200x-cartoon-collection-12504.jpg</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/moss-man-200x-cartoon-collection-12502.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/man-at-arms-200x-cartoon-collection-12504.php</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>29.48</v>
+        <v>0</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -11081,24 +11066,24 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12504</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>He-Man (Reissue)</t>
+          <t>Moss Man (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11108,27 +11093,27 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>$19.67</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>1.47</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>B0FRJ675FT</t>
+          <t>B0FHJQQN37</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>194735401949</t>
+          <t>194735333462</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>19.67</v>
+        <v>19.99</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -11137,21 +11122,21 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/he-man-reissue-13228.jpg</t>
+          <t>/app/data/MOTU/images/moss-man-200x-cartoon-collection-12502.jpg</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-reissue-13228.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/moss-man-200x-cartoon-collection-12502.jpg</t>
         </is>
       </c>
       <c r="N139" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/he-man-reissue-13228.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/moss-man-200x-cartoon-collection-12502.php</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>29.48</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -11160,19 +11145,19 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12502</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Prince Adam (200x - Cartoon Collection)</t>
+          <t>He-Man (Reissue)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -11187,7 +11172,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>$21.99</t>
+          <t>$19.67</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -11198,16 +11183,16 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>B0FHKNQ68K</t>
+          <t>B0FRJ675FT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>194735333165</t>
+          <t>194735401949</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>21.99</v>
+        <v>19.67</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -11216,17 +11201,17 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/prince-adam-200x-cartoon-collection-12849.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/he-man-reissue-13228.jpg</t>
         </is>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-200x-cartoon-collection-12849.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-reissue-13228.jpg</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/prince-adam-200x-cartoon-collection-12849.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/he-man-reissue-13228.php</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -11239,19 +11224,19 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13228</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Skeletor (Reissue)</t>
+          <t>Prince Adam (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11266,7 +11251,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>$19.67</t>
+          <t>$21.99</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -11277,16 +11262,16 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>B0FRJMJRYW</t>
+          <t>B0FHKNQ68K</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>194735401956</t>
+          <t>194735333165</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>19.67</v>
+        <v>21.99</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -11295,17 +11280,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/skeletor-reissue-13227.jpg</t>
+          <t>/app/data/MOTU/images/prince-adam-200x-cartoon-collection-12849.jpg</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/skeletor-reissue-13227.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/prince-adam-200x-cartoon-collection-12849.jpg</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/skeletor-reissue-13227.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/prince-adam-200x-cartoon-collection-12849.php</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -11318,19 +11303,19 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>12849</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Skeletor (200x - Cartoon Collection)</t>
+          <t>Skeletor (Reissue)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11345,27 +11330,27 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>$21.99</t>
+          <t>$19.67</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>3.41</v>
+        <v>1</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>B0FHKL6J22</t>
+          <t>B0FRJMJRYW</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>194735333356</t>
+          <t>194735401956</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>21.99</v>
+        <v>19.67</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -11374,21 +11359,21 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/skeletor-200x-cartoon-collection-12847.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/skeletor-reissue-13227.jpg</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/skeletor-200x-cartoon-collection-12847.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/skeletor-reissue-13227.jpg</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/skeletor-200x-cartoon-collection-12847.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/skeletor-reissue-13227.php</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>74.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -11397,7 +11382,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13227</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11394,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zodac (200x - Cartoon Collection)</t>
+          <t>Skeletor (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11431,16 +11416,16 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>3.41</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>B0FHJQRFQF</t>
+          <t>B0FHKL6J22</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>194735333295</t>
+          <t>194735333356</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -11453,21 +11438,21 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/zodac-200x-cartoon-collection-12848.jpg</t>
+          <t>/app/data/MOTU/images/skeletor-200x-cartoon-collection-12847.jpg</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/zodac-200x-cartoon-collection-12848.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/skeletor-200x-cartoon-collection-12847.jpg</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/zodac-200x-cartoon-collection-12848.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/skeletor-200x-cartoon-collection-12847.php</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -11476,7 +11461,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12847</t>
         </is>
       </c>
     </row>
@@ -11488,12 +11473,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mer-Man (200x - Cartoon Collection)</t>
+          <t>Zodac (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11503,7 +11488,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>$20.49</t>
+          <t>$21.99</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -11514,16 +11499,16 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>B0FHKJMTZZ</t>
+          <t>B0FHJQRFQF</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>194735333226</t>
+          <t>194735333295</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>20.49</v>
+        <v>21.99</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -11532,17 +11517,17 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/mer-man-200x-cartoon-collection-13223.jpg</t>
+          <t>/app/data/MOTU/images/zodac-200x-cartoon-collection-12848.jpg</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/mer-man-200x-cartoon-collection-13223.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/zodac-200x-cartoon-collection-12848.jpg</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/mer-man-200x-cartoon-collection-13223.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/zodac-200x-cartoon-collection-12848.php</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -11555,7 +11540,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>12848</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11552,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Orko (200x - Cartoon Collection)</t>
+          <t>Mer-Man (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11593,12 +11578,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>B0FHJQRX3C</t>
+          <t>B0FHKJMTZZ</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>194735333301</t>
+          <t>194735333226</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -11611,17 +11596,17 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/orko-200x-cartoon-collection-13224.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/mer-man-200x-cartoon-collection-13223.jpg</t>
         </is>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/orko-200x-cartoon-collection-13224.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/mer-man-200x-cartoon-collection-13223.jpg</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/orko-200x-cartoon-collection-13224.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/mer-man-200x-cartoon-collection-13223.php</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -11634,7 +11619,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>13223</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11631,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Roboto (200x - Cartoon Collection - Deluxe)</t>
+          <t>Orko (200x - Cartoon Collection)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -11661,7 +11646,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>$23.75</t>
+          <t>$20.49</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -11672,16 +11657,16 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>B0FJ25MN3Z</t>
+          <t>B0FHJQRX3C</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>194735333349</t>
+          <t>194735333301</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>23.75</v>
+        <v>20.49</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11690,17 +11675,17 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/roboto-200x-cartoon-collection-deluxe-13225.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/orko-200x-cartoon-collection-13224.jpg</t>
         </is>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/roboto-200x-cartoon-collection-deluxe-13225.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/orko-200x-cartoon-collection-13224.jpg</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/roboto-200x-cartoon-collection-deluxe-13225.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/orko-200x-cartoon-collection-13224.php</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -11713,7 +11698,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13224</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11710,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Teela (200x - Cartoon Collection)</t>
+          <t>Roboto (200x - Cartoon Collection - Deluxe)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11740,7 +11725,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>$20.49</t>
+          <t>$23.75</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -11751,16 +11736,16 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>B0FHKLMW62</t>
+          <t>B0FJ25MN3Z</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>194735333257</t>
+          <t>194735333349</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>20.49</v>
+        <v>23.75</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11769,17 +11754,17 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/teela-200x-cartoon-collection-13222.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/roboto-200x-cartoon-collection-deluxe-13225.jpg</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/teela-200x-cartoon-collection-13222.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/roboto-200x-cartoon-collection-deluxe-13225.jpg</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/teela-200x-cartoon-collection-13222.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/roboto-200x-cartoon-collection-deluxe-13225.php</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -11791,6 +11776,85 @@
         </is>
       </c>
       <c r="Q147" t="inlineStr">
+        <is>
+          <t>13225</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Teela (200x - Cartoon Collection)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>$20.49</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>B0FHKLMW62</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>194735333257</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/teela-200x-cartoon-collection-13222.jpg</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/teela-200x-cartoon-collection-13222.jpg</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-action-figures/teela-200x-cartoon-collection-13222.php</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
         <is>
           <t>13222</t>
         </is>
@@ -11800,7 +11864,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A147">
+  <conditionalFormatting sqref="A3:A148">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Sí"</formula>
     </cfRule>
@@ -11809,7 +11873,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A147" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A3:A148" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12066,46 +12130,49 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N131" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N132" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N133" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N134" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N135" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N136" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N137" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N138" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N139" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N140" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N141" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N143" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N145" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N147" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N148" r:id="rId295"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14241,7 +14308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17401,7 +17468,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Battle of Eternia Multipack</t>
+          <t>Battle for Eternia Multipack</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -17423,7 +17490,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -17438,28 +17505,28 @@
       <c r="J43" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>Ver Imagen</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/battle-of-eternia-multipack-10371.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/battle-for-eternia-multipack-10371.webp</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/battle-of-eternia-multipack-10371.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/battle-for-eternia-multipack-10371.jpg</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/battle-of-eternia-multipack-10371.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/battle-for-eternia-multipack-10371.php</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>83.73</v>
+        <v>99.98</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -18620,17 +18687,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blast-Attak</t>
+          <t>Battle for Subternia 4 Pack</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Creations</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -18640,40 +18707,45 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>$22.00</t>
+          <t>$74.99</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.1</v>
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>194735377718</t>
+        </is>
       </c>
       <c r="J59" t="n">
-        <v>22</v>
-      </c>
-      <c r="K59" t="inlineStr">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>Ver Imagen</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/blast-attak-12884.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/battle-for-subternia-4-pack-14047.webp</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/blast-attak-12884.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/battle-for-subternia-4-pack-14047.jpg</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/blast-attak-12884.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/battle-for-subternia-4-pack-14047.php</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>46.28</v>
+        <v>0</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -18682,7 +18754,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>14047</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18766,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expand-Or</t>
+          <t>Blast-Attak</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18716,7 +18788,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>22</v>
@@ -18728,21 +18800,21 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/expand-or-13889.jpg</t>
+          <t>/app/data/MOTU/images/blast-attak-12884.jpg</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/expand-or-13889.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/blast-attak-12884.jpg</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/expand-or-13889.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/blast-attak-12884.php</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>46.28</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -18751,7 +18823,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>13889</t>
+          <t>12884</t>
         </is>
       </c>
     </row>
@@ -18763,7 +18835,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Great Black Wizard</t>
+          <t>Expand-Or</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18778,17 +18850,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>$31.99</t>
+          <t>$22.00</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>31.99</v>
+        <v>22</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -18797,21 +18869,21 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/expand-or-13889.jpg</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/expand-or-13889.jpg</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/expand-or-13889.php</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>40.52</v>
+        <v>0</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -18820,7 +18892,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13889</t>
         </is>
       </c>
     </row>
@@ -18832,7 +18904,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>James Jean Coral Skeletor and Panthor</t>
+          <t>Great Black Wizard</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18847,17 +18919,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>$100.00</t>
+          <t>$31.99</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>31.99</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -18866,21 +18938,21 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+          <t>/app/data/MOTU/images/great-black-wizard-12852.jpg</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/great-black-wizard-12852.jpg</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-coral-skeletor-and-panthor-13312.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/great-black-wizard-12852.php</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>40.52</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -18889,7 +18961,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12852</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18973,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>James Jean Floral He-Man and Battle Cat</t>
+          <t>James Jean Coral Skeletor and Panthor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18935,17 +19007,17 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-coral-skeletor-and-panthor-13312.jpg</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-floral-he-man-and-battle-cat-13313.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-coral-skeletor-and-panthor-13312.php</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -18958,7 +19030,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13312</t>
         </is>
       </c>
     </row>
@@ -18970,7 +19042,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Laser Power He-Man</t>
+          <t>James Jean Floral He-Man and Battle Cat</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18985,7 +19057,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>$33.00</t>
+          <t>$100.00</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -18995,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -19004,17 +19076,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/james-jean-floral-he-man-and-battle-cat-13313.jpg</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/james-jean-floral-he-man-and-battle-cat-13313.php</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -19027,7 +19099,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13313</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19111,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stonedar</t>
+          <t>Laser Power He-Man</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19054,7 +19126,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>$22.00</t>
+          <t>$33.00</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -19064,7 +19136,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -19073,17 +19145,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/laser-power-he-man-13263.jpg</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/laser-power-he-man-13263.jpg</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/laser-power-he-man-13263.php</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -19096,7 +19168,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13263</t>
         </is>
       </c>
     </row>
@@ -19108,22 +19180,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026 Movie 4 Pack</t>
+          <t>Skeletal Lady Slither</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Creations</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>$37.79</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -19132,37 +19199,27 @@
       <c r="G66" t="n">
         <v>1</v>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>B0FK1LWB99</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>194735350803</t>
-        </is>
-      </c>
       <c r="J66" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="K66" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>Ver Imagen</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/2026-movie-4-pack-13440.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/skeletal-lady-slither-14050.webp</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/2026-movie-4-pack-13440.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/skeletal-lady-slither-14050.jpg</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/2026-movie-4-pack-13440.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/skeletal-lady-slither-14050.php</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -19174,6 +19231,233 @@
         </is>
       </c>
       <c r="Q66" t="inlineStr">
+        <is>
+          <t>14050</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Stonedar</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Creations</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>$22.00</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>22</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/stonedar-13031.jpg</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/stonedar-13031.jpg</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/stonedar-13031.php</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>13031</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Battle of Eternia Multipack</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>$64.99</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>B0DT281JJH</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>194735307562</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>/app/data/MOTU/images/battle-of-eternia-multipack-10371.jpg</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/battle-of-eternia-multipack-10371.jpg</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/battle-of-eternia-multipack-10371.php</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>10371</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026 Movie 4 Pack</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>$37.79</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>B0FK1LWB99</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>194735350803</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/2026-movie-4-pack-13440.jpg</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/2026-movie-4-pack-13440.jpg</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-exclusives/2026-movie-4-pack-13440.php</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
         <is>
           <t>13440</t>
         </is>
@@ -19183,7 +19467,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A66">
+  <conditionalFormatting sqref="A3:A69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Sí"</formula>
     </cfRule>
@@ -19192,7 +19476,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A3:A69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19277,54 +19561,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19336,7 +19629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21064,7 +21357,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snake Lair Playset</t>
+          <t>Fright Pit Playset</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -21079,40 +21372,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>$300.00</t>
+          <t>$49.00</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>300</v>
-      </c>
-      <c r="K25" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Ver Imagen</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>/app/data/MOTU/images/snake-lair-playset-11542.jpg</t>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/fright-pit-playset-14048.webp</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/images/snake-lair-playset-11542.jpg</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/fright-pit-playset-14048.jpg</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/snake-lair-playset-11542.php</t>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/fright-pit-playset-14048.php</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>499.99</v>
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -21121,7 +21414,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>14048</t>
         </is>
       </c>
     </row>
@@ -21133,12 +21426,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>He-Man and Sky Sled (2026 Movie)</t>
+          <t>Snake Lair Playset</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Creations</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21148,57 +21441,126 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>$26.99</t>
+          <t>$300.00</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J26" t="n">
+        <v>300</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>/app/data/MOTU/images/snake-lair-playset-11542.jpg</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/snake-lair-playset-11542.jpg</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/snake-lair-playset-11542.php</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>He-Man and Sky Sled (2026 Movie)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>$26.99</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>B0FS9N9PXH</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>194735377770</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>26.99</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Ver Imagen</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/he-man-and-sky-sled-2026-movie-13444.jpg</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://www.actionfigure411.com/masters-of-the-universe/images/he-man-and-sky-sled-2026-movie-13444.jpg</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>https://www.actionfigure411.com/masters-of-the-universe/origins/origins-beasts-vehicles-and-playsets/he-man-and-sky-sled-2026-movie-13444.php</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>13444</t>
         </is>
@@ -21208,7 +21570,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A26">
+  <conditionalFormatting sqref="A3:A27">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Sí"</formula>
     </cfRule>
@@ -21217,7 +21579,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A3:A27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21266,10 +21628,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -9426,7 +9426,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10392,7 +10392,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10461,7 +10461,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -3976,7 +3976,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -3976,7 +3976,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10190,7 +10190,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -14044,7 +14044,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -14108,7 +14108,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -14172,7 +14172,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15987,7 +15987,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21352,7 +21352,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -1300,7 +1300,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9352,7 +9352,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10190,7 +10190,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -14044,7 +14044,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -14108,7 +14108,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -14172,7 +14172,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15987,7 +15987,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21352,7 +21352,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -7758,7 +7758,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9914,7 +9914,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -4529,7 +4529,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12498,11 +12498,85 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fright Zone Ring</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>$55.00</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>197300346338</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>55</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/fright-zone-ring-14278.webp</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/fright-zone-ring-14278.jpg</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-rings/fright-zone-ring-14278.php</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14278</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A5">
+  <conditionalFormatting sqref="A3:A6">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Sí"</formula>
     </cfRule>
@@ -12511,7 +12585,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A3:A6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12522,6 +12596,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26454,7 +26531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28940,11 +29017,608 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bray Wyatt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>194735411917</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/bray-wyatt-14270.webp</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/bray-wyatt-14270.jpg</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/bray-wyatt-14270.php</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>14270</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>"The American Nightmare" Cody Rhodes</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>B0H6T4T6C6</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>194735411863</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/the-american-nightmare-cody-rhodes-14271.webp</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/the-american-nightmare-cody-rhodes-14271.jpg</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/the-american-nightmare-cody-rhodes-14271.php</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>14271</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>"Hollywood" Hulk Hogan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>194735411948</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/hollywood-hulk-hogan-14272.webp</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/hollywood-hulk-hogan-14272.jpg</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/hollywood-hulk-hogan-14272.php</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>14272</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shawn Michaels</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>194735411788</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/shawn-michaels-14273.webp</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/shawn-michaels-14273.jpg</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/shawn-michaels-14273.php</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>14273</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Demolition Ax</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>194735411870</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/demolition-ax-14275.webp</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/demolition-ax-14275.jpg</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/demolition-ax-14275.php</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>14275</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Demolition Crush</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>194735448586</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/demolition-crush-14276.webp</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/demolition-crush-14276.jpg</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/demolition-crush-14276.php</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14276</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Demolition Smash</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>194735411801</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/demolition-smash-14277.webp</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/demolition-smash-14277.jpg</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/demolition-smash-14277.php</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>14277</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The Rock Final Boss</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>194735411887</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Ver Imagen</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/oraculo-nueva-eternia/oraculo-nueva-eternia/data/MOTU/images/the-rock-final-boss-14274.webp</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/images/the-rock-final-boss-14274.jpg</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.actionfigure411.com/masters-of-the-universe/origins/masters-of-the-wwe-universe-action-figures/the-rock-final-boss-14274.php</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>14274</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A33">
+  <conditionalFormatting sqref="A3:A41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Sí"</formula>
     </cfRule>
@@ -28953,7 +29627,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A3:A41" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29020,6 +29694,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
